--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC10C9C-6F5A-AB49-BF8E-53C950956132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3B4170-FDE9-BC49-83AF-DA3215772A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8000" yWindow="3500" windowWidth="28800" windowHeight="16120" activeTab="11" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="6" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="145">
   <si>
     <t>Type</t>
   </si>
@@ -601,16 +601,7 @@
     <t>Group</t>
   </si>
   <si>
-    <t>GINII</t>
-  </si>
-  <si>
     <t>Industrial Solutions</t>
-  </si>
-  <si>
-    <t>RGUARD</t>
-  </si>
-  <si>
-    <t>SARA</t>
   </si>
   <si>
     <t>WeShape</t>
@@ -621,6 +612,60 @@
   <si>
     <t>Total FTE</t>
   </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Mgmt</t>
+  </si>
+  <si>
+    <t>Logged</t>
+  </si>
+  <si>
+    <t>Q1 Plan</t>
+  </si>
+  <si>
+    <t>Plan-PS</t>
+  </si>
+  <si>
+    <t>Plan-PD</t>
+  </si>
+  <si>
+    <t>Actual-PS</t>
+  </si>
+  <si>
+    <t>Actual-PD</t>
+  </si>
+  <si>
+    <t>CAP</t>
+  </si>
+  <si>
+    <t>SCG Home</t>
+  </si>
+  <si>
+    <t>1.1 PS</t>
+  </si>
+  <si>
+    <t>1.2 Product</t>
+  </si>
+  <si>
+    <t>2 R&amp;D</t>
+  </si>
+  <si>
+    <t>3 Policy</t>
+  </si>
+  <si>
+    <t>7 DO Tools</t>
+  </si>
+  <si>
+    <t>KM</t>
+  </si>
+  <si>
+    <t>R-Guard</t>
+  </si>
+  <si>
+    <t>SA-RA</t>
+  </si>
 </sst>
 </file>
 
@@ -629,7 +674,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -759,8 +804,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="6"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -893,6 +976,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -924,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1019,12 +1126,36 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF007D39"/>
+      <color rgb="FF009744"/>
+      <color rgb="FF006930"/>
+      <color rgb="FF008C40"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1430,37 +1561,37 @@
         <v>151</v>
       </c>
       <c r="G2" s="8">
+        <v>152</v>
+      </c>
+      <c r="H2" s="8">
+        <v>151</v>
+      </c>
+      <c r="I2" s="8">
         <v>150</v>
       </c>
-      <c r="H2" s="8">
+      <c r="J2" s="8">
         <v>150</v>
       </c>
-      <c r="I2" s="8">
-        <v>149</v>
-      </c>
-      <c r="J2" s="8">
-        <v>149</v>
-      </c>
       <c r="K2" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L2" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M2" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N2" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O2" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P2" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q2" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -1471,49 +1602,49 @@
         <v>17</v>
       </c>
       <c r="C3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q3" s="8">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -1606,37 +1737,37 @@
         <v>0.94789999999999996</v>
       </c>
       <c r="G6" s="19">
-        <v>0.97919999999999996</v>
+        <v>0.96630000000000005</v>
       </c>
       <c r="H6" s="19">
-        <v>0.95830000000000004</v>
+        <v>0.95189999999999997</v>
       </c>
       <c r="I6" s="19">
-        <v>0.95909999999999995</v>
+        <v>0.95269999999999999</v>
       </c>
       <c r="J6" s="19">
-        <v>0.93759999999999999</v>
+        <v>0.93130000000000002</v>
       </c>
       <c r="K6" s="19">
-        <v>0.93179999999999996</v>
+        <v>0.92559999999999998</v>
       </c>
       <c r="L6" s="19">
-        <v>0.88370000000000004</v>
+        <v>0.87780000000000002</v>
       </c>
       <c r="M6" s="19">
-        <v>0.87409999999999999</v>
+        <v>0.86829999999999996</v>
       </c>
       <c r="N6" s="19">
-        <v>0.86939999999999995</v>
+        <v>0.86360000000000003</v>
       </c>
       <c r="O6" s="19">
-        <v>0.70230000000000004</v>
+        <v>0.6976</v>
       </c>
       <c r="P6" s="19">
-        <v>0.70020000000000004</v>
+        <v>0.6956</v>
       </c>
       <c r="Q6" s="19">
-        <v>0.70020000000000004</v>
+        <v>0.6956</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -1657,37 +1788,37 @@
         <v>8</v>
       </c>
       <c r="G7" s="20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" s="20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L7" s="20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" s="20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N7" s="20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O7" s="20">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P7" s="20">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q7" s="20">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -1729,37 +1860,37 @@
         <v>118</v>
       </c>
       <c r="G9" s="8">
+        <v>119</v>
+      </c>
+      <c r="H9" s="8">
+        <v>118</v>
+      </c>
+      <c r="I9" s="8">
         <v>117</v>
       </c>
-      <c r="H9" s="8">
+      <c r="J9" s="8">
         <v>117</v>
       </c>
-      <c r="I9" s="8">
-        <v>116</v>
-      </c>
-      <c r="J9" s="8">
-        <v>116</v>
-      </c>
       <c r="K9" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L9" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M9" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N9" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O9" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P9" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q9" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
@@ -1770,49 +1901,49 @@
         <v>19</v>
       </c>
       <c r="C10" s="8">
+        <v>118</v>
+      </c>
+      <c r="D10" s="8">
+        <v>118</v>
+      </c>
+      <c r="E10" s="8">
+        <v>118</v>
+      </c>
+      <c r="F10" s="8">
         <v>117</v>
       </c>
-      <c r="D10" s="8">
+      <c r="G10" s="8">
         <v>117</v>
       </c>
-      <c r="E10" s="8">
+      <c r="H10" s="8">
         <v>117</v>
       </c>
-      <c r="F10" s="8">
-        <v>116</v>
-      </c>
-      <c r="G10" s="8">
-        <v>116</v>
-      </c>
-      <c r="H10" s="8">
-        <v>116</v>
-      </c>
       <c r="I10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q10" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
@@ -2224,6 +2355,57 @@
         <v>7</v>
       </c>
     </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="70">
+        <v>11</v>
+      </c>
+      <c r="D22" s="70">
+        <v>11</v>
+      </c>
+      <c r="E22" s="70">
+        <v>11</v>
+      </c>
+      <c r="F22" s="70">
+        <v>11</v>
+      </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="69" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="71">
+        <v>117.04</v>
+      </c>
+      <c r="D23" s="71">
+        <v>125.05</v>
+      </c>
+      <c r="E23" s="70">
+        <v>126.04</v>
+      </c>
+      <c r="F23" s="70">
+        <v>126.8</v>
+      </c>
+    </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
       <c r="B31" s="1" t="s">
@@ -2257,16 +2439,16 @@
         <v>149</v>
       </c>
       <c r="D32" s="21">
+        <v>151</v>
+      </c>
+      <c r="E32" s="21">
         <v>150</v>
       </c>
-      <c r="E32" s="21">
-        <v>149</v>
-      </c>
       <c r="F32" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G32" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H32" s="21"/>
     </row>
@@ -2278,19 +2460,19 @@
         <v>17</v>
       </c>
       <c r="C33" s="26">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D33" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E33" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F33" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G33" s="21">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H33" s="21"/>
     </row>
@@ -2325,16 +2507,16 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D35" s="28">
-        <v>3.8199999999999998E-2</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="E35" s="28">
-        <v>5.7200000000000001E-2</v>
+        <v>6.3500000000000001E-2</v>
       </c>
       <c r="F35" s="28">
-        <v>0.12429999999999999</v>
+        <v>0.13009999999999999</v>
       </c>
       <c r="G35" s="28">
-        <v>0.29909999999999998</v>
+        <v>0.30380000000000001</v>
       </c>
       <c r="H35" s="8"/>
     </row>
@@ -2347,16 +2529,16 @@
         <v>0.92500000000000004</v>
       </c>
       <c r="D36" s="19">
-        <v>0.96179999999999999</v>
+        <v>0.95540000000000003</v>
       </c>
       <c r="E36" s="19">
-        <v>0.94279999999999997</v>
+        <v>0.9365</v>
       </c>
       <c r="F36" s="19">
-        <v>0.87570000000000003</v>
+        <v>0.86990000000000001</v>
       </c>
       <c r="G36" s="19">
-        <v>0.70089999999999997</v>
+        <v>0.69620000000000004</v>
       </c>
       <c r="H36" s="20"/>
     </row>
@@ -2369,16 +2551,16 @@
         <v>11</v>
       </c>
       <c r="D37" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" s="20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G37" s="20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H37" s="20"/>
     </row>
@@ -2403,16 +2585,16 @@
         <v>120</v>
       </c>
       <c r="D39" s="21">
+        <v>118</v>
+      </c>
+      <c r="E39" s="21">
         <v>117</v>
       </c>
-      <c r="E39" s="21">
-        <v>116</v>
-      </c>
       <c r="F39" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G39" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" s="21"/>
     </row>
@@ -2424,19 +2606,19 @@
         <v>19</v>
       </c>
       <c r="C40" s="26">
+        <v>118</v>
+      </c>
+      <c r="D40" s="21">
         <v>117</v>
       </c>
-      <c r="D40" s="21">
-        <v>116</v>
-      </c>
       <c r="E40" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F40" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G40" s="21">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H40" s="21"/>
     </row>
@@ -2729,47 +2911,47 @@
       </c>
       <c r="F2">
         <f>IF(AIC!G2&gt;0,AIC!G2,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
         <f>IF(AIC!H2&gt;0,AIC!H2,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <f>IF(AIC!I2&gt;0,AIC!I2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <f>IF(AIC!J2&gt;0,AIC!J2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <f>IF(AIC!K2&gt;0,AIC!K2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2">
         <f>IF(AIC!L2&gt;0,AIC!L2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2">
         <f>IF(AIC!M2&gt;0,AIC!M2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <f>IF(AIC!N2&gt;0,AIC!N2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2">
         <f>IF(AIC!O2&gt;0,AIC!O2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O2">
         <f>IF(AIC!P2&gt;0,AIC!P2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2">
         <f>IF(AIC!Q2&gt;0,AIC!Q2,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -2779,63 +2961,63 @@
       </c>
       <c r="B3">
         <f>IF(AIC!C3&gt;0,AIC!C3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <f>IF(AIC!D3&gt;0,AIC!D3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <f>IF(AIC!E3&gt;0,AIC!E3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <f>IF(AIC!F3&gt;0,AIC!F3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <f>IF(AIC!G3&gt;0,AIC!G3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <f>IF(AIC!H3&gt;0,AIC!H3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <f>IF(AIC!I3&gt;0,AIC!I3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3">
         <f>IF(AIC!J3&gt;0,AIC!J3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <f>IF(AIC!K3&gt;0,AIC!K3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3">
         <f>IF(AIC!L3&gt;0,AIC!L3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3">
         <f>IF(AIC!M3&gt;0,AIC!M3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3">
         <f>IF(AIC!N3&gt;0,AIC!N3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3">
         <f>IF(AIC!O3&gt;0,AIC!O3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3">
         <f>IF(AIC!P3&gt;0,AIC!P3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3">
         <f>IF(AIC!Q3&gt;0,AIC!Q3,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -3187,47 +3369,47 @@
       </c>
       <c r="F12">
         <f>IF(AIC!G9&gt;0,AIC!G9,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12">
         <f>IF(AIC!H9&gt;0,AIC!H9,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12">
         <f>IF(AIC!I9&gt;0,AIC!I9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I12">
         <f>IF(AIC!J9&gt;0,AIC!J9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12">
         <f>IF(AIC!K9&gt;0,AIC!K9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12">
         <f>IF(AIC!L9&gt;0,AIC!L9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12">
         <f>IF(AIC!M9&gt;0,AIC!M9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M12">
         <f>IF(AIC!N9&gt;0,AIC!N9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N12">
         <f>IF(AIC!O9&gt;0,AIC!O9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O12">
         <f>IF(AIC!P9&gt;0,AIC!P9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P12">
         <f>IF(AIC!Q9&gt;0,AIC!Q9,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -3237,63 +3419,63 @@
       </c>
       <c r="B13">
         <f>IF(AIC!C10&gt;0,AIC!C10,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <f>IF(AIC!D10&gt;0,AIC!D10,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13">
         <f>IF(AIC!E10&gt;0,AIC!E10,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <f>IF(AIC!F10&gt;0,AIC!F10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <f>IF(AIC!G10&gt;0,AIC!G10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13">
         <f>IF(AIC!H10&gt;0,AIC!H10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13">
         <f>IF(AIC!I10&gt;0,AIC!I10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I13">
         <f>IF(AIC!J10&gt;0,AIC!J10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J13">
         <f>IF(AIC!K10&gt;0,AIC!K10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K13">
         <f>IF(AIC!L10&gt;0,AIC!L10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L13">
         <f>IF(AIC!M10&gt;0,AIC!M10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M13">
         <f>IF(AIC!N10&gt;0,AIC!N10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N13">
         <f>IF(AIC!O10&gt;0,AIC!O10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O13">
         <f>IF(AIC!P10&gt;0,AIC!P10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P13">
         <f>IF(AIC!Q10&gt;0,AIC!Q10,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -3915,19 +4097,19 @@
       </c>
       <c r="C42">
         <f>IF(AIC!D32&gt;0,AIC!D32,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <f>IF(AIC!E32&gt;0,AIC!E32,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E42">
         <f>IF(AIC!F32&gt;0,AIC!F32,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F42">
         <f>IF(AIC!G32&gt;0,AIC!G32,"")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
@@ -3937,23 +4119,23 @@
       </c>
       <c r="B43">
         <f>IF(AIC!C33&gt;0,AIC!C33,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C43">
         <f>IF(AIC!D33&gt;0,AIC!D33,"")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D43">
         <f>IF(AIC!E33&gt;0,AIC!E33,"")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E43">
         <f>IF(AIC!F33&gt;0,AIC!F33,"")</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F43">
         <f>IF(AIC!G33&gt;0,AIC!G33,"")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -5082,47 +5264,47 @@
       </c>
       <c r="F82">
         <f>AIC!G70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82">
         <f>AIC!H70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H82">
         <f>AIC!I70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I82">
         <f>AIC!J70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J82">
         <f>AIC!K70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K82">
         <f>AIC!L70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L82">
         <f>AIC!M70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82">
         <f>AIC!N70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N82">
         <f>AIC!O70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O82">
         <f>AIC!P70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P82">
         <f>AIC!Q70</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
@@ -5213,47 +5395,47 @@
       </c>
       <c r="F84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.10499999999999998</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="G84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.125</v>
+        <v>0.875</v>
       </c>
       <c r="H84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.125</v>
+        <v>0.875</v>
       </c>
       <c r="I84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.125</v>
+        <v>0.875</v>
       </c>
       <c r="J84" s="67">
         <f t="shared" si="6"/>
-        <v>0.42499999999999982</v>
+        <v>1.4249999999999998</v>
       </c>
       <c r="K84" s="67">
         <f t="shared" si="6"/>
-        <v>0.125</v>
+        <v>1.125</v>
       </c>
       <c r="L84" s="67">
         <f t="shared" si="6"/>
-        <v>7.5000000000000178E-2</v>
+        <v>1.0750000000000002</v>
       </c>
       <c r="M84" s="67">
         <f t="shared" si="6"/>
-        <v>0.375</v>
+        <v>1.375</v>
       </c>
       <c r="N84" s="67">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O84" s="67">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="P84" s="67">
         <f t="shared" si="6"/>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
@@ -5289,19 +5471,19 @@
       </c>
       <c r="C86" s="59">
         <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
-        <v>98.3</v>
+        <v>81.916666666666671</v>
       </c>
       <c r="D86" s="59">
         <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
-        <v>98.055555555555557</v>
+        <v>73.541666666666657</v>
       </c>
       <c r="E86" s="59">
         <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
-        <v>93.611111111111128</v>
+        <v>70.208333333333343</v>
       </c>
       <c r="F86" s="59">
         <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
-        <v>13.333333333333336</v>
+        <v>10.000000000000002</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
@@ -5696,47 +5878,47 @@
       </c>
       <c r="F152">
         <f>AIC!G6*100</f>
-        <v>91.97</v>
+        <v>87.59</v>
       </c>
       <c r="G152">
         <f>AIC!H6*100</f>
-        <v>89.82</v>
+        <v>85.54</v>
       </c>
       <c r="H152">
         <f>AIC!I6*100</f>
-        <v>83.28</v>
+        <v>79.11</v>
       </c>
       <c r="I152">
         <f>AIC!J6*100</f>
-        <v>78.8</v>
+        <v>74.86</v>
       </c>
       <c r="J152">
         <f>AIC!K6*100</f>
-        <v>75.64</v>
+        <v>71.86</v>
       </c>
       <c r="K152">
         <f>AIC!L6*100</f>
-        <v>71.5</v>
+        <v>67.930000000000007</v>
       </c>
       <c r="L152">
         <f>AIC!M6*100</f>
-        <v>71.760000000000005</v>
+        <v>68.179999999999993</v>
       </c>
       <c r="M152">
         <f>AIC!N6*100</f>
-        <v>70.179999999999993</v>
+        <v>66.679999999999993</v>
       </c>
       <c r="N152">
         <f>AIC!O6*100</f>
-        <v>44.13</v>
+        <v>41.93</v>
       </c>
       <c r="O152">
         <f>AIC!P6*100</f>
-        <v>44.13</v>
+        <v>41.93</v>
       </c>
       <c r="P152">
         <f>AIC!Q6*100</f>
-        <v>44.13</v>
+        <v>41.93</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -5762,47 +5944,47 @@
       </c>
       <c r="F153">
         <f>AIC!G7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G153">
         <f>AIC!H7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H153">
         <f>AIC!I7</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I153">
         <f>AIC!J7</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J153">
         <f>AIC!K7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K153">
         <f>AIC!L7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L153">
         <f>AIC!M7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M153">
         <f>AIC!N7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N153">
         <f>AIC!O7</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O153">
         <f>AIC!P7</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P153">
         <f>AIC!Q7</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -5838,19 +6020,19 @@
       </c>
       <c r="C156">
         <f>AIC!D36*100</f>
-        <v>90.03</v>
+        <v>87.17</v>
       </c>
       <c r="D156">
         <f>AIC!E36*100</f>
-        <v>79.239999999999995</v>
+        <v>75.28</v>
       </c>
       <c r="E156">
         <f>AIC!F36*100</f>
-        <v>71.150000000000006</v>
+        <v>67.589999999999989</v>
       </c>
       <c r="F156">
         <f>AIC!G36*100</f>
-        <v>44.13</v>
+        <v>41.93</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -5864,19 +6046,19 @@
       </c>
       <c r="C157">
         <f>AIC!D37</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D157">
         <f>AIC!E37</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E157">
         <f>AIC!F37</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F157">
         <f>AIC!G37</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11203,7 +11385,7 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -11267,52 +11449,52 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B2" s="8">
-        <v>2.46</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C2" s="8">
-        <v>2.4649999999999999</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="D2" s="8">
-        <v>2.4649999999999999</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="E2" s="8">
-        <v>1.95</v>
+        <v>0.8</v>
       </c>
       <c r="F2" s="8">
-        <v>2.2999999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="G2" s="8">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="8">
-        <v>2.9</v>
+        <v>0.75</v>
       </c>
       <c r="I2" s="8">
-        <v>2.7749999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="J2" s="8">
-        <v>2.7749999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K2" s="8">
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="L2" s="8">
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="M2" s="8">
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="N2" s="8">
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="O2" s="8">
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="P2" s="8">
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -11323,52 +11505,52 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="8">
-        <v>3.37</v>
+        <v>3.27</v>
       </c>
       <c r="C3" s="8">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="D3" s="8">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="E3" s="8">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="F3" s="8">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="G3" s="8">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="H3" s="8">
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="I3" s="8">
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="J3" s="8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="K3" s="8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="L3" s="8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="M3" s="8">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="N3" s="8">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="O3" s="8">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="P3" s="8">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -11379,52 +11561,52 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B4" s="8">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.375</v>
+      </c>
+      <c r="D4" s="8">
         <v>1.75</v>
       </c>
-      <c r="C4" s="8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D4" s="8">
-        <v>1.2749999999999999</v>
-      </c>
       <c r="E4" s="8">
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="F4" s="8">
-        <v>0.8</v>
+        <v>1.675</v>
       </c>
       <c r="G4" s="8">
-        <v>0.6</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="H4" s="8">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="I4" s="8">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="J4" s="8">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="K4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="L4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="M4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="N4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="O4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="P4" s="8">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
@@ -11435,7 +11617,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="B5" s="8">
         <v>3.2650000000000001</v>
@@ -11447,40 +11629,40 @@
         <v>3.0649999999999999</v>
       </c>
       <c r="E5" s="8">
-        <v>2.7250000000000001</v>
+        <v>3.125</v>
       </c>
       <c r="F5" s="8">
-        <v>2.875</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="G5" s="8">
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="H5" s="8">
-        <v>2.6850000000000001</v>
+        <v>3.085</v>
       </c>
       <c r="I5" s="8">
-        <v>2.9849999999999999</v>
+        <v>3.3849999999999998</v>
       </c>
       <c r="J5" s="8">
-        <v>2.9849999999999999</v>
+        <v>3.3849999999999998</v>
       </c>
       <c r="K5" s="8">
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="L5" s="8">
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="M5" s="8">
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="N5" s="8">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="O5" s="8">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="P5" s="8">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
@@ -11491,52 +11673,52 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B6" s="8">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="C6" s="8">
-        <v>3.625</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="D6" s="8">
-        <v>3.67</v>
+        <v>7.22</v>
       </c>
       <c r="E6" s="8">
-        <v>3.4824999999999999</v>
+        <v>6.5949999999999998</v>
       </c>
       <c r="F6" s="8">
-        <v>2.9824999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="G6" s="8">
-        <v>2.9874999999999998</v>
+        <v>5.375</v>
       </c>
       <c r="H6" s="8">
-        <v>2.3125</v>
+        <v>5.1312499999999996</v>
       </c>
       <c r="I6" s="8">
-        <v>2.2124999999999999</v>
+        <v>5.1062500000000002</v>
       </c>
       <c r="J6" s="8">
-        <v>3.1124999999999998</v>
+        <v>5.4562499999999998</v>
       </c>
       <c r="K6" s="8">
-        <v>3.1124999999999998</v>
+        <v>5.2562499999999996</v>
       </c>
       <c r="L6" s="8">
-        <v>3.1124999999999998</v>
+        <v>5.7062499999999998</v>
       </c>
       <c r="M6" s="8">
-        <v>3.1124999999999998</v>
+        <v>5.5062499999999996</v>
       </c>
       <c r="N6" s="8">
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="O6" s="8">
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="P6" s="8">
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -11546,22 +11728,54 @@
       <c r="V6" s="56"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="A7" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="8">
+        <v>6.4124999999999996</v>
+      </c>
+      <c r="C7" s="8">
+        <v>5.9124999999999996</v>
+      </c>
+      <c r="D7" s="8">
+        <v>6.6624999999999996</v>
+      </c>
+      <c r="E7" s="8">
+        <v>7.7</v>
+      </c>
+      <c r="F7" s="8">
+        <v>7.875</v>
+      </c>
+      <c r="G7" s="8">
+        <v>7.875</v>
+      </c>
+      <c r="H7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="I7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="J7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="K7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="L7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="M7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="N7" s="8">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="O7" s="8">
+        <v>8.0124999999999993</v>
+      </c>
+      <c r="P7" s="8">
+        <v>8.0124999999999993</v>
+      </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="56"/>
@@ -11974,7 +12188,7 @@
         <v>102</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I21" s="54"/>
       <c r="K21" s="54"/>
@@ -12104,6 +12318,1165 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="Q26" s="8"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B30" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="H30" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="L30" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="M30" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+    </row>
+    <row r="31" spans="1:17" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="74">
+        <f t="shared" ref="B31:M31" si="0">SUM(B32,B33)</f>
+        <v>2717433</v>
+      </c>
+      <c r="C31" s="74">
+        <f t="shared" si="0"/>
+        <v>6209433</v>
+      </c>
+      <c r="D31" s="74">
+        <f t="shared" si="0"/>
+        <v>13563433</v>
+      </c>
+      <c r="E31" s="74">
+        <f t="shared" si="0"/>
+        <v>7233433</v>
+      </c>
+      <c r="F31" s="74">
+        <f t="shared" si="0"/>
+        <v>7406433</v>
+      </c>
+      <c r="G31" s="74">
+        <f t="shared" si="0"/>
+        <v>19319433</v>
+      </c>
+      <c r="H31" s="74">
+        <f t="shared" si="0"/>
+        <v>13479433</v>
+      </c>
+      <c r="I31" s="74">
+        <f t="shared" si="0"/>
+        <v>10679433</v>
+      </c>
+      <c r="J31" s="74">
+        <f t="shared" si="0"/>
+        <v>18089433</v>
+      </c>
+      <c r="K31" s="74">
+        <f t="shared" si="0"/>
+        <v>16179433</v>
+      </c>
+      <c r="L31" s="74">
+        <f t="shared" si="0"/>
+        <v>14539433</v>
+      </c>
+      <c r="M31" s="74">
+        <f t="shared" si="0"/>
+        <v>19853233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="75">
+        <v>1787433</v>
+      </c>
+      <c r="C32" s="75">
+        <v>4779433</v>
+      </c>
+      <c r="D32" s="75">
+        <v>7833433</v>
+      </c>
+      <c r="E32" s="75">
+        <v>5233433</v>
+      </c>
+      <c r="F32" s="75">
+        <v>4206433</v>
+      </c>
+      <c r="G32" s="75">
+        <v>14379433</v>
+      </c>
+      <c r="H32" s="75">
+        <v>9279433</v>
+      </c>
+      <c r="I32" s="75">
+        <v>6279433</v>
+      </c>
+      <c r="J32" s="75">
+        <v>10379433</v>
+      </c>
+      <c r="K32" s="75">
+        <v>11279433</v>
+      </c>
+      <c r="L32" s="75">
+        <v>4379433</v>
+      </c>
+      <c r="M32" s="75">
+        <v>10453233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="76" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="75">
+        <v>930000</v>
+      </c>
+      <c r="C33" s="75">
+        <v>1430000</v>
+      </c>
+      <c r="D33" s="75">
+        <v>5730000</v>
+      </c>
+      <c r="E33" s="75">
+        <v>2000000</v>
+      </c>
+      <c r="F33" s="75">
+        <v>3200000</v>
+      </c>
+      <c r="G33" s="75">
+        <v>4940000</v>
+      </c>
+      <c r="H33" s="75">
+        <v>4200000</v>
+      </c>
+      <c r="I33" s="75">
+        <v>4400000</v>
+      </c>
+      <c r="J33" s="75">
+        <v>7710000</v>
+      </c>
+      <c r="K33" s="75">
+        <v>4900000</v>
+      </c>
+      <c r="L33" s="75">
+        <v>10160000</v>
+      </c>
+      <c r="M33" s="75">
+        <v>9400000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="73" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="78" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="74">
+        <f>SUM(B35,B36)</f>
+        <v>1049908</v>
+      </c>
+      <c r="C34" s="74">
+        <f t="shared" ref="C34:E34" si="1">SUM(C35,C36)</f>
+        <v>6155989</v>
+      </c>
+      <c r="D34" s="74">
+        <f t="shared" si="1"/>
+        <v>9094371</v>
+      </c>
+      <c r="E34" s="74">
+        <f t="shared" si="1"/>
+        <v>6308025</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="75">
+        <v>1002658</v>
+      </c>
+      <c r="C35" s="75">
+        <v>5710093</v>
+      </c>
+      <c r="D35" s="75">
+        <v>8544505</v>
+      </c>
+      <c r="E35" s="75">
+        <v>4855248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="72" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="75">
+        <v>47250</v>
+      </c>
+      <c r="C36" s="75">
+        <v>445896</v>
+      </c>
+      <c r="D36" s="75">
+        <v>549866</v>
+      </c>
+      <c r="E36" s="75">
+        <v>1452777</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="80" t="str">
+        <f>B30</f>
+        <v>JAN</v>
+      </c>
+      <c r="C40" s="80" t="str">
+        <f t="shared" ref="C40:M40" si="2">C30</f>
+        <v>FEB</v>
+      </c>
+      <c r="D40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>MAR</v>
+      </c>
+      <c r="E40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>APR</v>
+      </c>
+      <c r="F40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>MAY</v>
+      </c>
+      <c r="G40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>JUN</v>
+      </c>
+      <c r="H40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>JUL</v>
+      </c>
+      <c r="I40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>AUG</v>
+      </c>
+      <c r="J40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>SEP</v>
+      </c>
+      <c r="K40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>OCT</v>
+      </c>
+      <c r="L40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>NOV</v>
+      </c>
+      <c r="M40" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="80" t="str">
+        <f>A31</f>
+        <v>Plan</v>
+      </c>
+      <c r="B41" s="81">
+        <f>B31/1000000</f>
+        <v>2.7174330000000002</v>
+      </c>
+      <c r="C41" s="81">
+        <f t="shared" ref="C41:M41" si="3">C31/1000000</f>
+        <v>6.2094329999999998</v>
+      </c>
+      <c r="D41" s="81">
+        <f t="shared" si="3"/>
+        <v>13.563433</v>
+      </c>
+      <c r="E41" s="81">
+        <f t="shared" si="3"/>
+        <v>7.2334329999999998</v>
+      </c>
+      <c r="F41" s="81">
+        <f t="shared" si="3"/>
+        <v>7.4064329999999998</v>
+      </c>
+      <c r="G41" s="81">
+        <f t="shared" si="3"/>
+        <v>19.319433</v>
+      </c>
+      <c r="H41" s="81">
+        <f t="shared" si="3"/>
+        <v>13.479433</v>
+      </c>
+      <c r="I41" s="81">
+        <f t="shared" si="3"/>
+        <v>10.679433</v>
+      </c>
+      <c r="J41" s="81">
+        <f t="shared" si="3"/>
+        <v>18.089433</v>
+      </c>
+      <c r="K41" s="81">
+        <f t="shared" si="3"/>
+        <v>16.179433</v>
+      </c>
+      <c r="L41" s="81">
+        <f t="shared" si="3"/>
+        <v>14.539433000000001</v>
+      </c>
+      <c r="M41" s="81">
+        <f t="shared" si="3"/>
+        <v>19.853232999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="80" t="str">
+        <f>A34</f>
+        <v>Actual</v>
+      </c>
+      <c r="B42" s="81">
+        <f>B34/1000000</f>
+        <v>1.0499080000000001</v>
+      </c>
+      <c r="C42" s="81">
+        <f t="shared" ref="C42:E42" si="4">C34/1000000</f>
+        <v>6.1559889999999999</v>
+      </c>
+      <c r="D42" s="81">
+        <f t="shared" si="4"/>
+        <v>9.0943710000000006</v>
+      </c>
+      <c r="E42" s="81">
+        <f t="shared" si="4"/>
+        <v>6.3080249999999998</v>
+      </c>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
+      <c r="M42" s="81"/>
+    </row>
+    <row r="43" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="80" t="str">
+        <f>A32</f>
+        <v>Plan-PS</v>
+      </c>
+      <c r="B43" s="81">
+        <f>B32/1000000</f>
+        <v>1.787433</v>
+      </c>
+      <c r="C43" s="81">
+        <f t="shared" ref="C43:M43" si="5">C32/1000000</f>
+        <v>4.779433</v>
+      </c>
+      <c r="D43" s="81">
+        <f t="shared" si="5"/>
+        <v>7.8334330000000003</v>
+      </c>
+      <c r="E43" s="81">
+        <f t="shared" si="5"/>
+        <v>5.2334329999999998</v>
+      </c>
+      <c r="F43" s="81">
+        <f t="shared" si="5"/>
+        <v>4.2064329999999996</v>
+      </c>
+      <c r="G43" s="81">
+        <f t="shared" si="5"/>
+        <v>14.379433000000001</v>
+      </c>
+      <c r="H43" s="81">
+        <f t="shared" si="5"/>
+        <v>9.2794329999999992</v>
+      </c>
+      <c r="I43" s="81">
+        <f t="shared" si="5"/>
+        <v>6.279433</v>
+      </c>
+      <c r="J43" s="81">
+        <f t="shared" si="5"/>
+        <v>10.379433000000001</v>
+      </c>
+      <c r="K43" s="81">
+        <f t="shared" si="5"/>
+        <v>11.279432999999999</v>
+      </c>
+      <c r="L43" s="81">
+        <f t="shared" si="5"/>
+        <v>4.3794329999999997</v>
+      </c>
+      <c r="M43" s="81">
+        <f t="shared" si="5"/>
+        <v>10.453233000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="80" t="str">
+        <f>A35</f>
+        <v>Actual-PS</v>
+      </c>
+      <c r="B44" s="81">
+        <f>B35/1000000</f>
+        <v>1.002658</v>
+      </c>
+      <c r="C44" s="81">
+        <f t="shared" ref="C44:E44" si="6">C35/1000000</f>
+        <v>5.7100929999999996</v>
+      </c>
+      <c r="D44" s="81">
+        <f t="shared" si="6"/>
+        <v>8.5445049999999991</v>
+      </c>
+      <c r="E44" s="81">
+        <f t="shared" si="6"/>
+        <v>4.8552479999999996</v>
+      </c>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
+      <c r="M44" s="81"/>
+    </row>
+    <row r="45" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="80" t="str">
+        <f>A33</f>
+        <v>Plan-PD</v>
+      </c>
+      <c r="B45" s="81">
+        <f>B33/1000000</f>
+        <v>0.93</v>
+      </c>
+      <c r="C45" s="81">
+        <f t="shared" ref="C45:M45" si="7">C33/1000000</f>
+        <v>1.43</v>
+      </c>
+      <c r="D45" s="81">
+        <f t="shared" si="7"/>
+        <v>5.73</v>
+      </c>
+      <c r="E45" s="81">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="F45" s="81">
+        <f t="shared" si="7"/>
+        <v>3.2</v>
+      </c>
+      <c r="G45" s="81">
+        <f t="shared" si="7"/>
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="H45" s="81">
+        <f t="shared" si="7"/>
+        <v>4.2</v>
+      </c>
+      <c r="I45" s="81">
+        <f t="shared" si="7"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J45" s="81">
+        <f t="shared" si="7"/>
+        <v>7.71</v>
+      </c>
+      <c r="K45" s="81">
+        <f t="shared" si="7"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L45" s="81">
+        <f t="shared" si="7"/>
+        <v>10.16</v>
+      </c>
+      <c r="M45" s="81">
+        <f t="shared" si="7"/>
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="80" t="str">
+        <f>A36</f>
+        <v>Actual-PD</v>
+      </c>
+      <c r="B46" s="81">
+        <f>B36/1000000</f>
+        <v>4.725E-2</v>
+      </c>
+      <c r="C46" s="81">
+        <f t="shared" ref="C46:E46" si="8">C36/1000000</f>
+        <v>0.44589600000000001</v>
+      </c>
+      <c r="D46" s="81">
+        <f t="shared" si="8"/>
+        <v>0.54986599999999997</v>
+      </c>
+      <c r="E46" s="81">
+        <f t="shared" si="8"/>
+        <v>1.452777</v>
+      </c>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="81"/>
+      <c r="M46" s="81"/>
+    </row>
+    <row r="47" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:13" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="80" t="str">
+        <f t="shared" ref="B51:M51" si="9">B40</f>
+        <v>JAN</v>
+      </c>
+      <c r="C51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>FEB</v>
+      </c>
+      <c r="D51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>MAR</v>
+      </c>
+      <c r="E51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>APR</v>
+      </c>
+      <c r="F51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>MAY</v>
+      </c>
+      <c r="G51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>JUN</v>
+      </c>
+      <c r="H51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>JUL</v>
+      </c>
+      <c r="I51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>AUG</v>
+      </c>
+      <c r="J51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>SEP</v>
+      </c>
+      <c r="K51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>OCT</v>
+      </c>
+      <c r="L51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>NOV</v>
+      </c>
+      <c r="M51" s="80" t="str">
+        <f t="shared" si="9"/>
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="80" t="str">
+        <f>A41</f>
+        <v>Plan</v>
+      </c>
+      <c r="B52" s="80">
+        <v>2.72</v>
+      </c>
+      <c r="C52" s="80">
+        <v>6.21</v>
+      </c>
+      <c r="D52" s="80">
+        <v>13.56</v>
+      </c>
+      <c r="E52" s="80">
+        <v>7.23</v>
+      </c>
+      <c r="F52" s="80">
+        <v>7.41</v>
+      </c>
+      <c r="G52" s="80">
+        <v>19.32</v>
+      </c>
+      <c r="H52" s="80">
+        <v>13.48</v>
+      </c>
+      <c r="I52" s="80">
+        <v>10.68</v>
+      </c>
+      <c r="J52" s="80">
+        <v>18.09</v>
+      </c>
+      <c r="K52" s="80">
+        <v>16.18</v>
+      </c>
+      <c r="L52" s="80">
+        <v>14.54</v>
+      </c>
+      <c r="M52" s="80">
+        <v>19.850000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="80" t="str">
+        <f t="shared" ref="A53:A57" si="10">A42</f>
+        <v>Actual</v>
+      </c>
+      <c r="B53" s="80">
+        <v>1.05</v>
+      </c>
+      <c r="C53" s="80">
+        <v>6.16</v>
+      </c>
+      <c r="D53" s="80">
+        <v>9.09</v>
+      </c>
+      <c r="E53" s="80">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="80" t="str">
+        <f t="shared" si="10"/>
+        <v>Plan-PS</v>
+      </c>
+      <c r="B54" s="80">
+        <v>1.79</v>
+      </c>
+      <c r="C54" s="80">
+        <v>4.78</v>
+      </c>
+      <c r="D54" s="80">
+        <v>7.83</v>
+      </c>
+      <c r="E54" s="80">
+        <v>5.23</v>
+      </c>
+      <c r="F54" s="80">
+        <v>4.21</v>
+      </c>
+      <c r="G54" s="80">
+        <v>14.38</v>
+      </c>
+      <c r="H54" s="80">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="I54" s="80">
+        <v>6.28</v>
+      </c>
+      <c r="J54" s="80">
+        <v>10.38</v>
+      </c>
+      <c r="K54" s="80">
+        <v>11.28</v>
+      </c>
+      <c r="L54" s="80">
+        <v>4.38</v>
+      </c>
+      <c r="M54" s="80">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="80" t="str">
+        <f t="shared" si="10"/>
+        <v>Actual-PS</v>
+      </c>
+      <c r="B55" s="80">
+        <v>1</v>
+      </c>
+      <c r="C55" s="80">
+        <v>5.71</v>
+      </c>
+      <c r="D55" s="80">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="E55" s="80">
+        <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="80" t="str">
+        <f t="shared" si="10"/>
+        <v>Plan-PD</v>
+      </c>
+      <c r="B56" s="80">
+        <v>0.93</v>
+      </c>
+      <c r="C56" s="80">
+        <v>1.43</v>
+      </c>
+      <c r="D56" s="80">
+        <v>5.73</v>
+      </c>
+      <c r="E56" s="80">
+        <v>2</v>
+      </c>
+      <c r="F56" s="80">
+        <v>3.2</v>
+      </c>
+      <c r="G56" s="80">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="H56" s="80">
+        <v>4.2</v>
+      </c>
+      <c r="I56" s="80">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J56" s="80">
+        <v>7.71</v>
+      </c>
+      <c r="K56" s="80">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L56" s="80">
+        <v>10.16</v>
+      </c>
+      <c r="M56" s="80">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="80" t="str">
+        <f t="shared" si="10"/>
+        <v>Actual-PD</v>
+      </c>
+      <c r="B57" s="80">
+        <v>0.05</v>
+      </c>
+      <c r="C57" s="80">
+        <v>0.45</v>
+      </c>
+      <c r="D57" s="80">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E57" s="80">
+        <v>1.45</v>
+      </c>
+      <c r="F57" s="81"/>
+      <c r="L57" s="81"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" s="55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E61" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="H61" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="J61" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="K61" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="L61" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="M61" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="N61" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="O61" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="P61" s="55" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="8">
+        <v>64.239999999999995</v>
+      </c>
+      <c r="C62" s="8">
+        <v>70.52</v>
+      </c>
+      <c r="D62" s="8">
+        <v>74.53</v>
+      </c>
+      <c r="E62" s="8">
+        <v>73.02</v>
+      </c>
+      <c r="F62" s="8">
+        <v>78.36</v>
+      </c>
+      <c r="G62" s="8">
+        <v>74.459999999999994</v>
+      </c>
+      <c r="H62" s="8">
+        <v>77.349999999999994</v>
+      </c>
+      <c r="I62" s="8">
+        <v>74.92</v>
+      </c>
+      <c r="J62" s="8">
+        <v>73.989999999999995</v>
+      </c>
+      <c r="K62" s="8">
+        <v>68.13</v>
+      </c>
+      <c r="L62" s="8">
+        <v>66.87</v>
+      </c>
+      <c r="M62" s="8">
+        <v>66.739999999999995</v>
+      </c>
+      <c r="N62" s="8">
+        <v>48.29</v>
+      </c>
+      <c r="O62" s="8">
+        <v>48.11</v>
+      </c>
+      <c r="P62" s="8">
+        <v>48.11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="8">
+        <v>27.83</v>
+      </c>
+      <c r="C63" s="8">
+        <v>26.6</v>
+      </c>
+      <c r="D63" s="8">
+        <v>26.34</v>
+      </c>
+      <c r="E63" s="8">
+        <v>25.01</v>
+      </c>
+      <c r="F63" s="8">
+        <v>23.52</v>
+      </c>
+      <c r="G63" s="8">
+        <v>24.04</v>
+      </c>
+      <c r="H63" s="8">
+        <v>21.89</v>
+      </c>
+      <c r="I63" s="8">
+        <v>22.11</v>
+      </c>
+      <c r="J63" s="8">
+        <v>22.34</v>
+      </c>
+      <c r="K63" s="8">
+        <v>21.37</v>
+      </c>
+      <c r="L63" s="8">
+        <v>21.77</v>
+      </c>
+      <c r="M63" s="8">
+        <v>21.37</v>
+      </c>
+      <c r="N63" s="8">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="O63" s="8">
+        <v>18.43</v>
+      </c>
+      <c r="P63" s="8">
+        <v>18.43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" s="8">
+        <v>7.89</v>
+      </c>
+      <c r="C64" s="8">
+        <v>10.74</v>
+      </c>
+      <c r="D64" s="8">
+        <v>9.69</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11.7</v>
+      </c>
+      <c r="F64" s="8">
+        <v>11.65</v>
+      </c>
+      <c r="G64" s="8">
+        <v>11.9</v>
+      </c>
+      <c r="H64" s="8">
+        <v>10.27</v>
+      </c>
+      <c r="I64" s="8">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="J64" s="8">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="K64" s="8">
+        <v>8.67</v>
+      </c>
+      <c r="L64" s="8">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="M64" s="8">
+        <v>7.92</v>
+      </c>
+      <c r="N64" s="8">
+        <v>4.66</v>
+      </c>
+      <c r="O64" s="8">
+        <v>4.66</v>
+      </c>
+      <c r="P64" s="8">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A65" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="C65" s="8">
+        <v>0.71</v>
+      </c>
+      <c r="D65" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.26</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="H65" s="8">
+        <v>0.31</v>
+      </c>
+      <c r="I65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="J65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="K65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="L65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="M65" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="N65" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="O65" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="P65" s="8">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A66" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="8">
+        <v>0</v>
+      </c>
+      <c r="C66" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="D66" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="E66" s="8">
+        <v>0.38</v>
+      </c>
+      <c r="F66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G66" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="H66" s="8">
+        <v>0.73</v>
+      </c>
+      <c r="I66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="K66" s="8">
+        <v>0.63</v>
+      </c>
+      <c r="L66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M66" s="8">
+        <v>0.63</v>
+      </c>
+      <c r="N66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O66" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P66" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="82"/>
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
+      <c r="H67" s="82"/>
+      <c r="I67" s="82"/>
+      <c r="J67" s="82"/>
+      <c r="K67" s="82"/>
+      <c r="L67" s="82"/>
+      <c r="M67" s="82"/>
+      <c r="N67" s="82"/>
+      <c r="O67" s="82"/>
+      <c r="P67" s="8"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
+      <c r="H68" s="82"/>
+      <c r="I68" s="82"/>
+      <c r="J68" s="82"/>
+      <c r="K68" s="82"/>
+      <c r="L68" s="82"/>
+      <c r="M68" s="82"/>
+      <c r="N68" s="82"/>
+      <c r="O68" s="82"/>
+      <c r="P68" s="8"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="N69" s="8"/>
+      <c r="O69" s="8"/>
+      <c r="P69" s="8"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="8"/>
+      <c r="O70" s="8"/>
+      <c r="P70" s="8"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="82"/>
+      <c r="E71" s="82"/>
+      <c r="F71" s="82"/>
+      <c r="G71" s="82"/>
+      <c r="H71" s="82"/>
+      <c r="I71" s="82"/>
+      <c r="J71" s="82"/>
+      <c r="K71" s="82"/>
+      <c r="L71" s="82"/>
+      <c r="M71" s="82"/>
+      <c r="N71" s="82"/>
+      <c r="O71" s="82"/>
+      <c r="P71" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12115,10 +13488,10 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="58" customFormat="1" x14ac:dyDescent="0.2">
@@ -12206,67 +13579,67 @@
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>IF(Project!A2&gt;0,Project!A2,"")</f>
-        <v>GINII</v>
+        <v>KM</v>
       </c>
       <c r="B2">
         <f>IF(Project!B2&gt;0,Project!B2,"")</f>
-        <v>2.46</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C2">
         <f>IF(Project!C2&gt;0,Project!C2,"")</f>
-        <v>2.4649999999999999</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="D2">
         <f>IF(Project!D2&gt;0,Project!D2,"")</f>
-        <v>2.4649999999999999</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="E2">
         <f>IF(Project!E2&gt;0,Project!E2,"")</f>
-        <v>1.95</v>
+        <v>0.8</v>
       </c>
       <c r="F2">
         <f>IF(Project!F2&gt;0,Project!F2,"")</f>
-        <v>2.2999999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="G2">
         <f>IF(Project!G2&gt;0,Project!G2,"")</f>
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="H2">
         <f>IF(Project!H2&gt;0,Project!H2,"")</f>
-        <v>2.9</v>
+        <v>0.75</v>
       </c>
       <c r="I2">
         <f>IF(Project!I2&gt;0,Project!I2,"")</f>
-        <v>2.7749999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="J2">
         <f>IF(Project!J2&gt;0,Project!J2,"")</f>
-        <v>2.7749999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K2">
         <f>IF(Project!K2&gt;0,Project!K2,"")</f>
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="L2">
         <f>IF(Project!L2&gt;0,Project!L2,"")</f>
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="M2">
         <f>IF(Project!M2&gt;0,Project!M2,"")</f>
-        <v>2.6124999999999998</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="N2">
         <f>IF(Project!N2&gt;0,Project!N2,"")</f>
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="O2">
         <f>IF(Project!O2&gt;0,Project!O2,"")</f>
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="P2">
         <f>IF(Project!P2&gt;0,Project!P2,"")</f>
-        <v>0.80249999999999999</v>
+        <v>0.1125</v>
       </c>
       <c r="Q2" t="str">
         <f>IF(Project!Q2&gt;0,Project!Q2,"")</f>
@@ -12292,63 +13665,63 @@
       </c>
       <c r="B3">
         <f>IF(Project!B3&gt;0,Project!B3,"")</f>
-        <v>3.37</v>
+        <v>3.27</v>
       </c>
       <c r="C3">
         <f>IF(Project!C3&gt;0,Project!C3,"")</f>
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="D3">
         <f>IF(Project!D3&gt;0,Project!D3,"")</f>
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="E3">
         <f>IF(Project!E3&gt;0,Project!E3,"")</f>
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="F3">
         <f>IF(Project!F3&gt;0,Project!F3,"")</f>
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="G3">
         <f>IF(Project!G3&gt;0,Project!G3,"")</f>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
         <f>IF(Project!H3&gt;0,Project!H3,"")</f>
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="I3">
         <f>IF(Project!I3&gt;0,Project!I3,"")</f>
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="J3">
         <f>IF(Project!J3&gt;0,Project!J3,"")</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="K3">
         <f>IF(Project!K3&gt;0,Project!K3,"")</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="L3">
         <f>IF(Project!L3&gt;0,Project!L3,"")</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="M3">
         <f>IF(Project!M3&gt;0,Project!M3,"")</f>
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="N3">
         <f>IF(Project!N3&gt;0,Project!N3,"")</f>
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="O3">
         <f>IF(Project!O3&gt;0,Project!O3,"")</f>
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="P3">
         <f>IF(Project!P3&gt;0,Project!P3,"")</f>
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="Q3" t="str">
         <f>IF(Project!Q3&gt;0,Project!Q3,"")</f>
@@ -12370,67 +13743,67 @@
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>IF(Project!A4&gt;0,Project!A4,"")</f>
-        <v>RGUARD</v>
+        <v>R-Guard</v>
       </c>
       <c r="B4">
         <f>IF(Project!B4&gt;0,Project!B4,"")</f>
-        <v>1.75</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="C4">
         <f>IF(Project!C4&gt;0,Project!C4,"")</f>
-        <v>1.1000000000000001</v>
+        <v>1.375</v>
       </c>
       <c r="D4">
         <f>IF(Project!D4&gt;0,Project!D4,"")</f>
-        <v>1.2749999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="E4">
         <f>IF(Project!E4&gt;0,Project!E4,"")</f>
-        <v>0.95</v>
+        <v>1.7</v>
       </c>
       <c r="F4">
         <f>IF(Project!F4&gt;0,Project!F4,"")</f>
-        <v>0.8</v>
+        <v>1.675</v>
       </c>
       <c r="G4">
         <f>IF(Project!G4&gt;0,Project!G4,"")</f>
-        <v>0.6</v>
+        <v>1.4750000000000001</v>
       </c>
       <c r="H4">
         <f>IF(Project!H4&gt;0,Project!H4,"")</f>
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="I4">
         <f>IF(Project!I4&gt;0,Project!I4,"")</f>
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="J4">
         <f>IF(Project!J4&gt;0,Project!J4,"")</f>
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="K4">
         <f>IF(Project!K4&gt;0,Project!K4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="L4">
         <f>IF(Project!L4&gt;0,Project!L4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="M4">
         <f>IF(Project!M4&gt;0,Project!M4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="N4">
         <f>IF(Project!N4&gt;0,Project!N4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="O4">
         <f>IF(Project!O4&gt;0,Project!O4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="P4">
         <f>IF(Project!P4&gt;0,Project!P4,"")</f>
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="Q4" t="str">
         <f>IF(Project!Q4&gt;0,Project!Q4,"")</f>
@@ -12452,7 +13825,7 @@
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>IF(Project!A5&gt;0,Project!A5,"")</f>
-        <v>SARA</v>
+        <v>SA-RA</v>
       </c>
       <c r="B5">
         <f>IF(Project!B5&gt;0,Project!B5,"")</f>
@@ -12468,51 +13841,51 @@
       </c>
       <c r="E5">
         <f>IF(Project!E5&gt;0,Project!E5,"")</f>
-        <v>2.7250000000000001</v>
+        <v>3.125</v>
       </c>
       <c r="F5">
         <f>IF(Project!F5&gt;0,Project!F5,"")</f>
-        <v>2.875</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="G5">
         <f>IF(Project!G5&gt;0,Project!G5,"")</f>
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="H5">
         <f>IF(Project!H5&gt;0,Project!H5,"")</f>
-        <v>2.6850000000000001</v>
+        <v>3.085</v>
       </c>
       <c r="I5">
         <f>IF(Project!I5&gt;0,Project!I5,"")</f>
-        <v>2.9849999999999999</v>
+        <v>3.3849999999999998</v>
       </c>
       <c r="J5">
         <f>IF(Project!J5&gt;0,Project!J5,"")</f>
-        <v>2.9849999999999999</v>
+        <v>3.3849999999999998</v>
       </c>
       <c r="K5">
         <f>IF(Project!K5&gt;0,Project!K5,"")</f>
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="L5">
         <f>IF(Project!L5&gt;0,Project!L5,"")</f>
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="M5">
         <f>IF(Project!M5&gt;0,Project!M5,"")</f>
-        <v>2.9224999999999999</v>
+        <v>3.3224999999999998</v>
       </c>
       <c r="N5">
         <f>IF(Project!N5&gt;0,Project!N5,"")</f>
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="O5">
         <f>IF(Project!O5&gt;0,Project!O5,"")</f>
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="P5">
         <f>IF(Project!P5&gt;0,Project!P5,"")</f>
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="Q5" t="str">
         <f>IF(Project!Q5&gt;0,Project!Q5,"")</f>
@@ -12538,63 +13911,63 @@
       </c>
       <c r="B6">
         <f>IF(Project!B6&gt;0,Project!B6,"")</f>
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="C6">
         <f>IF(Project!C6&gt;0,Project!C6,"")</f>
-        <v>3.625</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="D6">
         <f>IF(Project!D6&gt;0,Project!D6,"")</f>
-        <v>3.67</v>
+        <v>7.22</v>
       </c>
       <c r="E6">
         <f>IF(Project!E6&gt;0,Project!E6,"")</f>
-        <v>3.4824999999999999</v>
+        <v>6.5949999999999998</v>
       </c>
       <c r="F6">
         <f>IF(Project!F6&gt;0,Project!F6,"")</f>
-        <v>2.9824999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="G6">
         <f>IF(Project!G6&gt;0,Project!G6,"")</f>
-        <v>2.9874999999999998</v>
+        <v>5.375</v>
       </c>
       <c r="H6">
         <f>IF(Project!H6&gt;0,Project!H6,"")</f>
-        <v>2.3125</v>
+        <v>5.1312499999999996</v>
       </c>
       <c r="I6">
         <f>IF(Project!I6&gt;0,Project!I6,"")</f>
-        <v>2.2124999999999999</v>
+        <v>5.1062500000000002</v>
       </c>
       <c r="J6">
         <f>IF(Project!J6&gt;0,Project!J6,"")</f>
-        <v>3.1124999999999998</v>
+        <v>5.4562499999999998</v>
       </c>
       <c r="K6">
         <f>IF(Project!K6&gt;0,Project!K6,"")</f>
-        <v>3.1124999999999998</v>
+        <v>5.2562499999999996</v>
       </c>
       <c r="L6">
         <f>IF(Project!L6&gt;0,Project!L6,"")</f>
-        <v>3.1124999999999998</v>
+        <v>5.7062499999999998</v>
       </c>
       <c r="M6">
         <f>IF(Project!M6&gt;0,Project!M6,"")</f>
-        <v>3.1124999999999998</v>
+        <v>5.5062499999999996</v>
       </c>
       <c r="N6">
         <f>IF(Project!N6&gt;0,Project!N6,"")</f>
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="O6">
         <f>IF(Project!O6&gt;0,Project!O6,"")</f>
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="P6">
         <f>IF(Project!P6&gt;0,Project!P6,"")</f>
-        <v>3.05</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="Q6" t="str">
         <f>IF(Project!Q6&gt;0,Project!Q6,"")</f>
@@ -12616,67 +13989,67 @@
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>IF(Project!A7&gt;0,Project!A7,"")</f>
-        <v/>
-      </c>
-      <c r="B7" t="str">
+        <v>CAP</v>
+      </c>
+      <c r="B7">
         <f>IF(Project!B7&gt;0,Project!B7,"")</f>
-        <v/>
-      </c>
-      <c r="C7" t="str">
+        <v>6.4124999999999996</v>
+      </c>
+      <c r="C7">
         <f>IF(Project!C7&gt;0,Project!C7,"")</f>
-        <v/>
-      </c>
-      <c r="D7" t="str">
+        <v>5.9124999999999996</v>
+      </c>
+      <c r="D7">
         <f>IF(Project!D7&gt;0,Project!D7,"")</f>
-        <v/>
-      </c>
-      <c r="E7" t="str">
+        <v>6.6624999999999996</v>
+      </c>
+      <c r="E7">
         <f>IF(Project!E7&gt;0,Project!E7,"")</f>
-        <v/>
-      </c>
-      <c r="F7" t="str">
+        <v>7.7</v>
+      </c>
+      <c r="F7">
         <f>IF(Project!F7&gt;0,Project!F7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" t="str">
+        <v>7.875</v>
+      </c>
+      <c r="G7">
         <f>IF(Project!G7&gt;0,Project!G7,"")</f>
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v>7.875</v>
+      </c>
+      <c r="H7">
         <f>IF(Project!H7&gt;0,Project!H7,"")</f>
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="I7">
         <f>IF(Project!I7&gt;0,Project!I7,"")</f>
-        <v/>
-      </c>
-      <c r="J7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="J7">
         <f>IF(Project!J7&gt;0,Project!J7,"")</f>
-        <v/>
-      </c>
-      <c r="K7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="K7">
         <f>IF(Project!K7&gt;0,Project!K7,"")</f>
-        <v/>
-      </c>
-      <c r="L7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="L7">
         <f>IF(Project!L7&gt;0,Project!L7,"")</f>
-        <v/>
-      </c>
-      <c r="M7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="M7">
         <f>IF(Project!M7&gt;0,Project!M7,"")</f>
-        <v/>
-      </c>
-      <c r="N7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="N7">
         <f>IF(Project!N7&gt;0,Project!N7,"")</f>
-        <v/>
-      </c>
-      <c r="O7" t="str">
+        <v>8.1374999999999993</v>
+      </c>
+      <c r="O7">
         <f>IF(Project!O7&gt;0,Project!O7,"")</f>
-        <v/>
-      </c>
-      <c r="P7" t="str">
+        <v>8.0124999999999993</v>
+      </c>
+      <c r="P7">
         <f>IF(Project!P7&gt;0,Project!P7,"")</f>
-        <v/>
+        <v>8.0124999999999993</v>
       </c>
       <c r="Q7" t="str">
         <f>IF(Project!Q7&gt;0,Project!Q7,"")</f>
@@ -13782,9 +15155,8 @@
         <f>IF(Project!A25&gt;0,Project!A25,"")</f>
         <v>PromptPlus</v>
       </c>
-      <c r="F21" s="64" t="str">
-        <f>IF(Project!A26&gt;0,Project!A26,"")</f>
-        <v>WeShape platform</v>
+      <c r="F21" s="64" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
@@ -13808,10 +15180,7 @@
         <f>IF(Project!B25&gt;0,Project!B25,"")</f>
         <v/>
       </c>
-      <c r="F22" s="64">
-        <f>IF(Project!B26&gt;0,Project!B26,"")</f>
-        <v>0.8</v>
-      </c>
+      <c r="F22" s="64"/>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="58" t="str">
@@ -13912,10 +15281,7 @@
         <f>IF(Project!F25&gt;0,Project!F25,"")</f>
         <v/>
       </c>
-      <c r="F26" s="64">
-        <f>IF(Project!F26&gt;0,Project!F26,"")</f>
-        <v>34.655000000000001</v>
-      </c>
+      <c r="F26" s="64"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="58" t="str">
@@ -13938,14 +15304,13 @@
         <f>IF(Project!G25&gt;0,Project!G25,"")</f>
         <v>23.7</v>
       </c>
-      <c r="F27" s="64" t="str">
-        <f>IF(Project!G26&gt;0,Project!G26,"")</f>
-        <v/>
+      <c r="F27" s="64">
+        <v>28.8</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="58" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B28" s="61">
         <f>IF(Project!H22&gt;0,Project!H22,"")</f>
@@ -13970,6 +15335,696 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="58"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A31" s="58"/>
+      <c r="B31" s="58" t="str">
+        <f>Project!B51</f>
+        <v>JAN</v>
+      </c>
+      <c r="C31" s="58" t="str">
+        <f>Project!C51</f>
+        <v>FEB</v>
+      </c>
+      <c r="D31" s="58" t="str">
+        <f>Project!D51</f>
+        <v>MAR</v>
+      </c>
+      <c r="E31" s="58" t="str">
+        <f>Project!E51</f>
+        <v>APR</v>
+      </c>
+      <c r="F31" s="58" t="str">
+        <f>Project!F51</f>
+        <v>MAY</v>
+      </c>
+      <c r="G31" s="58" t="str">
+        <f>Project!G51</f>
+        <v>JUN</v>
+      </c>
+      <c r="H31" s="58" t="str">
+        <f>Project!H51</f>
+        <v>JUL</v>
+      </c>
+      <c r="I31" s="58" t="str">
+        <f>Project!I51</f>
+        <v>AUG</v>
+      </c>
+      <c r="J31" s="58" t="str">
+        <f>Project!J51</f>
+        <v>SEP</v>
+      </c>
+      <c r="K31" s="58" t="str">
+        <f>Project!K51</f>
+        <v>OCT</v>
+      </c>
+      <c r="L31" s="58" t="str">
+        <f>Project!L51</f>
+        <v>NOV</v>
+      </c>
+      <c r="M31" s="58" t="str">
+        <f>Project!M51</f>
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>Project!A52</f>
+        <v>Plan</v>
+      </c>
+      <c r="B32">
+        <f>Project!B52</f>
+        <v>2.72</v>
+      </c>
+      <c r="C32">
+        <f>Project!C52</f>
+        <v>6.21</v>
+      </c>
+      <c r="D32">
+        <f>Project!D52</f>
+        <v>13.56</v>
+      </c>
+      <c r="E32">
+        <f>Project!E52</f>
+        <v>7.23</v>
+      </c>
+      <c r="F32">
+        <f>Project!F52</f>
+        <v>7.41</v>
+      </c>
+      <c r="G32">
+        <f>Project!G52</f>
+        <v>19.32</v>
+      </c>
+      <c r="H32">
+        <f>Project!H52</f>
+        <v>13.48</v>
+      </c>
+      <c r="I32">
+        <f>Project!I52</f>
+        <v>10.68</v>
+      </c>
+      <c r="J32">
+        <f>Project!J52</f>
+        <v>18.09</v>
+      </c>
+      <c r="K32">
+        <f>Project!K52</f>
+        <v>16.18</v>
+      </c>
+      <c r="L32">
+        <f>Project!L52</f>
+        <v>14.54</v>
+      </c>
+      <c r="M32">
+        <f>Project!M52</f>
+        <v>19.850000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>Project!A53</f>
+        <v>Actual</v>
+      </c>
+      <c r="B33">
+        <f>Project!B53</f>
+        <v>1.05</v>
+      </c>
+      <c r="C33">
+        <f>Project!C53</f>
+        <v>6.16</v>
+      </c>
+      <c r="D33">
+        <f>Project!D53</f>
+        <v>9.09</v>
+      </c>
+      <c r="E33">
+        <f>Project!E53</f>
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>Project!A54</f>
+        <v>Plan-PS</v>
+      </c>
+      <c r="B34">
+        <f>Project!B54</f>
+        <v>1.79</v>
+      </c>
+      <c r="C34">
+        <f>Project!C54</f>
+        <v>4.78</v>
+      </c>
+      <c r="D34">
+        <f>Project!D54</f>
+        <v>7.83</v>
+      </c>
+      <c r="E34">
+        <f>Project!E54</f>
+        <v>5.23</v>
+      </c>
+      <c r="F34">
+        <f>Project!F54</f>
+        <v>4.21</v>
+      </c>
+      <c r="G34">
+        <f>Project!G54</f>
+        <v>14.38</v>
+      </c>
+      <c r="H34">
+        <f>Project!H54</f>
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="I34">
+        <f>Project!I54</f>
+        <v>6.28</v>
+      </c>
+      <c r="J34">
+        <f>Project!J54</f>
+        <v>10.38</v>
+      </c>
+      <c r="K34">
+        <f>Project!K54</f>
+        <v>11.28</v>
+      </c>
+      <c r="L34">
+        <f>Project!L54</f>
+        <v>4.38</v>
+      </c>
+      <c r="M34">
+        <f>Project!M54</f>
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>Project!A55</f>
+        <v>Actual-PS</v>
+      </c>
+      <c r="B35">
+        <f>Project!B55</f>
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <f>Project!C55</f>
+        <v>5.71</v>
+      </c>
+      <c r="D35">
+        <f>Project!D55</f>
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="E35">
+        <f>Project!E55</f>
+        <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
+        <f>Project!A56</f>
+        <v>Plan-PD</v>
+      </c>
+      <c r="B36">
+        <f>Project!B56</f>
+        <v>0.93</v>
+      </c>
+      <c r="C36">
+        <f>Project!C56</f>
+        <v>1.43</v>
+      </c>
+      <c r="D36">
+        <f>Project!D56</f>
+        <v>5.73</v>
+      </c>
+      <c r="E36">
+        <f>Project!E56</f>
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <f>Project!F56</f>
+        <v>3.2</v>
+      </c>
+      <c r="G36">
+        <f>Project!G56</f>
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="H36">
+        <f>Project!H56</f>
+        <v>4.2</v>
+      </c>
+      <c r="I36">
+        <f>Project!I56</f>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J36">
+        <f>Project!J56</f>
+        <v>7.71</v>
+      </c>
+      <c r="K36">
+        <f>Project!K56</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L36">
+        <f>Project!L56</f>
+        <v>10.16</v>
+      </c>
+      <c r="M36">
+        <f>Project!M56</f>
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
+        <f>Project!A57</f>
+        <v>Actual-PD</v>
+      </c>
+      <c r="B37">
+        <f>Project!B57</f>
+        <v>0.05</v>
+      </c>
+      <c r="C37">
+        <f>Project!C57</f>
+        <v>0.45</v>
+      </c>
+      <c r="D37">
+        <f>Project!D57</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E37">
+        <f>Project!E57</f>
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="54"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" s="8"/>
+      <c r="B41" s="17" t="str">
+        <f>Project!B61</f>
+        <v>JAN</v>
+      </c>
+      <c r="C41" s="17" t="str">
+        <f>Project!C61</f>
+        <v>FEB</v>
+      </c>
+      <c r="D41" s="17" t="str">
+        <f>Project!D61</f>
+        <v>MAR</v>
+      </c>
+      <c r="E41" s="17" t="str">
+        <f>Project!E61</f>
+        <v>APR</v>
+      </c>
+      <c r="F41" s="17" t="str">
+        <f>Project!F61</f>
+        <v>MAY</v>
+      </c>
+      <c r="G41" s="17" t="str">
+        <f>Project!G61</f>
+        <v>JUN</v>
+      </c>
+      <c r="H41" s="17" t="str">
+        <f>Project!H61</f>
+        <v>JUL</v>
+      </c>
+      <c r="I41" s="17" t="str">
+        <f>Project!I61</f>
+        <v>AUG</v>
+      </c>
+      <c r="J41" s="17" t="str">
+        <f>Project!J61</f>
+        <v>SEP</v>
+      </c>
+      <c r="K41" s="17" t="str">
+        <f>Project!K61</f>
+        <v>OCT</v>
+      </c>
+      <c r="L41" s="17" t="str">
+        <f>Project!L61</f>
+        <v>NOV</v>
+      </c>
+      <c r="M41" s="17" t="str">
+        <f>Project!M61</f>
+        <v>DEC</v>
+      </c>
+      <c r="N41" s="17" t="str">
+        <f>Project!N61</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O41" s="17" t="str">
+        <f>Project!O61</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P41" s="17" t="str">
+        <f>Project!P61</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="str">
+        <f>Project!A62</f>
+        <v>1.1 PS</v>
+      </c>
+      <c r="B42" s="8">
+        <f>Project!B62</f>
+        <v>64.239999999999995</v>
+      </c>
+      <c r="C42" s="8">
+        <f>Project!C62</f>
+        <v>70.52</v>
+      </c>
+      <c r="D42" s="8">
+        <f>Project!D62</f>
+        <v>74.53</v>
+      </c>
+      <c r="E42" s="8">
+        <f>Project!E62</f>
+        <v>73.02</v>
+      </c>
+      <c r="F42" s="8">
+        <f>Project!F62</f>
+        <v>78.36</v>
+      </c>
+      <c r="G42" s="8">
+        <f>Project!G62</f>
+        <v>74.459999999999994</v>
+      </c>
+      <c r="H42" s="8">
+        <f>Project!H62</f>
+        <v>77.349999999999994</v>
+      </c>
+      <c r="I42" s="8">
+        <f>Project!I62</f>
+        <v>74.92</v>
+      </c>
+      <c r="J42" s="8">
+        <f>Project!J62</f>
+        <v>73.989999999999995</v>
+      </c>
+      <c r="K42" s="8">
+        <f>Project!K62</f>
+        <v>68.13</v>
+      </c>
+      <c r="L42" s="8">
+        <f>Project!L62</f>
+        <v>66.87</v>
+      </c>
+      <c r="M42" s="8">
+        <f>Project!M62</f>
+        <v>66.739999999999995</v>
+      </c>
+      <c r="N42" s="8">
+        <f>Project!N62</f>
+        <v>48.29</v>
+      </c>
+      <c r="O42" s="8">
+        <f>Project!O62</f>
+        <v>48.11</v>
+      </c>
+      <c r="P42" s="8">
+        <f>Project!P62</f>
+        <v>48.11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="str">
+        <f>Project!A63</f>
+        <v>1.2 Product</v>
+      </c>
+      <c r="B43" s="8">
+        <f>Project!B63</f>
+        <v>27.83</v>
+      </c>
+      <c r="C43" s="8">
+        <f>Project!C63</f>
+        <v>26.6</v>
+      </c>
+      <c r="D43" s="8">
+        <f>Project!D63</f>
+        <v>26.34</v>
+      </c>
+      <c r="E43" s="8">
+        <f>Project!E63</f>
+        <v>25.01</v>
+      </c>
+      <c r="F43" s="8">
+        <f>Project!F63</f>
+        <v>23.52</v>
+      </c>
+      <c r="G43" s="8">
+        <f>Project!G63</f>
+        <v>24.04</v>
+      </c>
+      <c r="H43" s="8">
+        <f>Project!H63</f>
+        <v>21.89</v>
+      </c>
+      <c r="I43" s="8">
+        <f>Project!I63</f>
+        <v>22.11</v>
+      </c>
+      <c r="J43" s="8">
+        <f>Project!J63</f>
+        <v>22.34</v>
+      </c>
+      <c r="K43" s="8">
+        <f>Project!K63</f>
+        <v>21.37</v>
+      </c>
+      <c r="L43" s="8">
+        <f>Project!L63</f>
+        <v>21.77</v>
+      </c>
+      <c r="M43" s="8">
+        <f>Project!M63</f>
+        <v>21.37</v>
+      </c>
+      <c r="N43" s="8">
+        <f>Project!N63</f>
+        <v>18.559999999999999</v>
+      </c>
+      <c r="O43" s="8">
+        <f>Project!O63</f>
+        <v>18.43</v>
+      </c>
+      <c r="P43" s="8">
+        <f>Project!P63</f>
+        <v>18.43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="str">
+        <f>Project!A64</f>
+        <v>2 R&amp;D</v>
+      </c>
+      <c r="B44" s="8">
+        <f>Project!B64</f>
+        <v>7.89</v>
+      </c>
+      <c r="C44" s="8">
+        <f>Project!C64</f>
+        <v>10.74</v>
+      </c>
+      <c r="D44" s="8">
+        <f>Project!D64</f>
+        <v>9.69</v>
+      </c>
+      <c r="E44" s="8">
+        <f>Project!E64</f>
+        <v>11.7</v>
+      </c>
+      <c r="F44" s="8">
+        <f>Project!F64</f>
+        <v>11.65</v>
+      </c>
+      <c r="G44" s="8">
+        <f>Project!G64</f>
+        <v>11.9</v>
+      </c>
+      <c r="H44" s="8">
+        <f>Project!H64</f>
+        <v>10.27</v>
+      </c>
+      <c r="I44" s="8">
+        <f>Project!I64</f>
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="J44" s="8">
+        <f>Project!J64</f>
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="K44" s="8">
+        <f>Project!K64</f>
+        <v>8.67</v>
+      </c>
+      <c r="L44" s="8">
+        <f>Project!L64</f>
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="M44" s="8">
+        <f>Project!M64</f>
+        <v>7.92</v>
+      </c>
+      <c r="N44" s="8">
+        <f>Project!N64</f>
+        <v>4.66</v>
+      </c>
+      <c r="O44" s="8">
+        <f>Project!O64</f>
+        <v>4.66</v>
+      </c>
+      <c r="P44" s="8">
+        <f>Project!P64</f>
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" t="str">
+        <f>Project!A65</f>
+        <v>3 Policy</v>
+      </c>
+      <c r="B45">
+        <f>Project!B65</f>
+        <v>0.1</v>
+      </c>
+      <c r="C45">
+        <f>Project!C65</f>
+        <v>0.71</v>
+      </c>
+      <c r="D45">
+        <f>Project!D65</f>
+        <v>0.75</v>
+      </c>
+      <c r="E45">
+        <f>Project!E65</f>
+        <v>0.26</v>
+      </c>
+      <c r="F45">
+        <f>Project!F65</f>
+        <v>0.21</v>
+      </c>
+      <c r="G45">
+        <f>Project!G65</f>
+        <v>0.21</v>
+      </c>
+      <c r="H45">
+        <f>Project!H65</f>
+        <v>0.31</v>
+      </c>
+      <c r="I45">
+        <f>Project!I65</f>
+        <v>0.32</v>
+      </c>
+      <c r="J45">
+        <f>Project!J65</f>
+        <v>0.32</v>
+      </c>
+      <c r="K45">
+        <f>Project!K65</f>
+        <v>0.32</v>
+      </c>
+      <c r="L45">
+        <f>Project!L65</f>
+        <v>0.32</v>
+      </c>
+      <c r="M45">
+        <f>Project!M65</f>
+        <v>0.32</v>
+      </c>
+      <c r="N45">
+        <f>Project!N65</f>
+        <v>0.11</v>
+      </c>
+      <c r="O45">
+        <f>Project!O65</f>
+        <v>0.11</v>
+      </c>
+      <c r="P45">
+        <f>Project!P65</f>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" t="str">
+        <f>Project!A66</f>
+        <v>7 DO Tools</v>
+      </c>
+      <c r="B46">
+        <f>Project!B66</f>
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <f>Project!C66</f>
+        <v>0.15</v>
+      </c>
+      <c r="D46">
+        <f>Project!D66</f>
+        <v>0.15</v>
+      </c>
+      <c r="E46">
+        <f>Project!E66</f>
+        <v>0.38</v>
+      </c>
+      <c r="F46">
+        <f>Project!F66</f>
+        <v>0.5</v>
+      </c>
+      <c r="G46">
+        <f>Project!G66</f>
+        <v>0.6</v>
+      </c>
+      <c r="H46">
+        <f>Project!H66</f>
+        <v>0.73</v>
+      </c>
+      <c r="I46">
+        <f>Project!I66</f>
+        <v>0.5</v>
+      </c>
+      <c r="J46">
+        <f>Project!J66</f>
+        <v>0.5</v>
+      </c>
+      <c r="K46">
+        <f>Project!K66</f>
+        <v>0.63</v>
+      </c>
+      <c r="L46">
+        <f>Project!L66</f>
+        <v>0.5</v>
+      </c>
+      <c r="M46">
+        <f>Project!M66</f>
+        <v>0.63</v>
+      </c>
+      <c r="N46">
+        <f>Project!N66</f>
+        <v>0.5</v>
+      </c>
+      <c r="O46">
+        <f>Project!O66</f>
+        <v>0.5</v>
+      </c>
+      <c r="P46">
+        <f>Project!P66</f>
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13981,7 +16036,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P157"/>
+  <dimension ref="A1:P165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -14072,47 +16127,47 @@
       </c>
       <c r="F2">
         <f>IF(ALL!G2&gt;0,ALL!G2,"")</f>
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G2">
         <f>IF(ALL!H2&gt;0,ALL!H2,"")</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H2">
         <f>IF(ALL!I2&gt;0,ALL!I2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I2">
         <f>IF(ALL!J2&gt;0,ALL!J2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J2">
         <f>IF(ALL!K2&gt;0,ALL!K2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <f>IF(ALL!L2&gt;0,ALL!L2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L2">
         <f>IF(ALL!M2&gt;0,ALL!M2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M2">
         <f>IF(ALL!N2&gt;0,ALL!N2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N2">
         <f>IF(ALL!O2&gt;0,ALL!O2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O2">
         <f>IF(ALL!P2&gt;0,ALL!P2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P2">
         <f>IF(ALL!Q2&gt;0,ALL!Q2,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -14122,63 +16177,63 @@
       </c>
       <c r="B3">
         <f>IF(ALL!C3&gt;0,ALL!C3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C3">
         <f>IF(ALL!D3&gt;0,ALL!D3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3">
         <f>IF(ALL!E3&gt;0,ALL!E3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3">
         <f>IF(ALL!F3&gt;0,ALL!F3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <f>IF(ALL!G3&gt;0,ALL!G3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G3">
         <f>IF(ALL!H3&gt;0,ALL!H3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H3">
         <f>IF(ALL!I3&gt;0,ALL!I3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I3">
         <f>IF(ALL!J3&gt;0,ALL!J3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J3">
         <f>IF(ALL!K3&gt;0,ALL!K3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K3">
         <f>IF(ALL!L3&gt;0,ALL!L3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L3">
         <f>IF(ALL!M3&gt;0,ALL!M3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M3">
         <f>IF(ALL!N3&gt;0,ALL!N3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N3">
         <f>IF(ALL!O3&gt;0,ALL!O3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O3">
         <f>IF(ALL!P3&gt;0,ALL!P3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P3">
         <f>IF(ALL!Q3&gt;0,ALL!Q3,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -14530,47 +16585,47 @@
       </c>
       <c r="F12">
         <f>IF(ALL!G9&gt;0,ALL!G9,"")</f>
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G12">
         <f>IF(ALL!H9&gt;0,ALL!H9,"")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12">
         <f>IF(ALL!I9&gt;0,ALL!I9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I12">
         <f>IF(ALL!J9&gt;0,ALL!J9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J12">
         <f>IF(ALL!K9&gt;0,ALL!K9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K12">
         <f>IF(ALL!L9&gt;0,ALL!L9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L12">
         <f>IF(ALL!M9&gt;0,ALL!M9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M12">
         <f>IF(ALL!N9&gt;0,ALL!N9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N12">
         <f>IF(ALL!O9&gt;0,ALL!O9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O12">
         <f>IF(ALL!P9&gt;0,ALL!P9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P12">
         <f>IF(ALL!Q9&gt;0,ALL!Q9,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -14580,63 +16635,63 @@
       </c>
       <c r="B13">
         <f>IF(ALL!C10&gt;0,ALL!C10,"")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13">
         <f>IF(ALL!D10&gt;0,ALL!D10,"")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <f>IF(ALL!E10&gt;0,ALL!E10,"")</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E13">
         <f>IF(ALL!F10&gt;0,ALL!F10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F13">
         <f>IF(ALL!G10&gt;0,ALL!G10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G13">
         <f>IF(ALL!H10&gt;0,ALL!H10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H13">
         <f>IF(ALL!I10&gt;0,ALL!I10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I13">
         <f>IF(ALL!J10&gt;0,ALL!J10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J13">
         <f>IF(ALL!K10&gt;0,ALL!K10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K13">
         <f>IF(ALL!L10&gt;0,ALL!L10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L13">
         <f>IF(ALL!M10&gt;0,ALL!M10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M13">
         <f>IF(ALL!N10&gt;0,ALL!N10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N13">
         <f>IF(ALL!O10&gt;0,ALL!O10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O13">
         <f>IF(ALL!P10&gt;0,ALL!P10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P13">
         <f>IF(ALL!Q10&gt;0,ALL!Q10,"")</f>
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -15258,19 +17313,19 @@
       </c>
       <c r="C42">
         <f>IF(ALL!D32&gt;0,ALL!D32,"")</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D42">
         <f>IF(ALL!E32&gt;0,ALL!E32,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E42">
         <f>IF(ALL!F32&gt;0,ALL!F32,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42">
         <f>IF(ALL!G32&gt;0,ALL!G32,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
@@ -15280,23 +17335,23 @@
       </c>
       <c r="B43">
         <f>IF(ALL!C33&gt;0,ALL!C33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43">
         <f>IF(ALL!D33&gt;0,ALL!D33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D43">
         <f>IF(ALL!E33&gt;0,ALL!E33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E43">
         <f>IF(ALL!F33&gt;0,ALL!F33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F43">
         <f>IF(ALL!G33&gt;0,ALL!G33,"")</f>
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -15488,47 +17543,47 @@
       </c>
       <c r="F152">
         <f>ALL!G6*100</f>
-        <v>97.92</v>
+        <v>96.63000000000001</v>
       </c>
       <c r="G152">
         <f>ALL!H6*100</f>
-        <v>95.83</v>
+        <v>95.19</v>
       </c>
       <c r="H152">
         <f>ALL!I6*100</f>
-        <v>95.91</v>
+        <v>95.27</v>
       </c>
       <c r="I152">
         <f>ALL!J6*100</f>
-        <v>93.76</v>
+        <v>93.13</v>
       </c>
       <c r="J152">
         <f>ALL!K6*100</f>
-        <v>93.179999999999993</v>
+        <v>92.56</v>
       </c>
       <c r="K152">
         <f>ALL!L6*100</f>
-        <v>88.37</v>
+        <v>87.78</v>
       </c>
       <c r="L152">
         <f>ALL!M6*100</f>
-        <v>87.41</v>
+        <v>86.83</v>
       </c>
       <c r="M152">
         <f>ALL!N6*100</f>
-        <v>86.94</v>
+        <v>86.36</v>
       </c>
       <c r="N152">
         <f>ALL!O6*100</f>
-        <v>70.23</v>
+        <v>69.760000000000005</v>
       </c>
       <c r="O152">
         <f>ALL!P6*100</f>
-        <v>70.02000000000001</v>
+        <v>69.56</v>
       </c>
       <c r="P152">
         <f>ALL!Q6*100</f>
-        <v>70.02000000000001</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -15554,47 +17609,47 @@
       </c>
       <c r="F153">
         <f>ALL!G7</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G153">
         <f>ALL!H7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H153">
         <f>ALL!I7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I153">
         <f>ALL!J7</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J153">
         <f>ALL!K7</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K153">
         <f>ALL!L7</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L153">
         <f>ALL!M7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M153">
         <f>ALL!N7</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N153">
         <f>ALL!O7</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O153">
         <f>ALL!P7</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P153">
         <f>ALL!Q7</f>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -15630,19 +17685,19 @@
       </c>
       <c r="C156">
         <f>ALL!D36*100</f>
-        <v>96.179999999999993</v>
+        <v>95.54</v>
       </c>
       <c r="D156">
         <f>ALL!E36*100</f>
-        <v>94.28</v>
+        <v>93.65</v>
       </c>
       <c r="E156">
         <f>ALL!F36*100</f>
-        <v>87.570000000000007</v>
+        <v>86.99</v>
       </c>
       <c r="F156">
         <f>ALL!G36*100</f>
-        <v>70.09</v>
+        <v>69.62</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -15656,19 +17711,263 @@
       </c>
       <c r="C157">
         <f>ALL!D37</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D157">
         <f>ALL!E37</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E157">
         <f>ALL!F37</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F157">
         <f>ALL!G37</f>
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B161" t="str">
+        <f>ALL!C1</f>
+        <v>JAN</v>
+      </c>
+      <c r="C161" t="str">
+        <f>ALL!D1</f>
+        <v>FEB</v>
+      </c>
+      <c r="D161" t="str">
+        <f>ALL!E1</f>
+        <v>MAR</v>
+      </c>
+      <c r="E161" t="str">
+        <f>ALL!F1</f>
+        <v>APR</v>
+      </c>
+      <c r="F161" t="str">
+        <f>ALL!G1</f>
+        <v>MAY</v>
+      </c>
+      <c r="G161" t="str">
+        <f>ALL!H1</f>
+        <v>JUN</v>
+      </c>
+      <c r="H161" t="str">
+        <f>ALL!I1</f>
+        <v>JUL</v>
+      </c>
+      <c r="I161" t="str">
+        <f>ALL!J1</f>
+        <v>AUG</v>
+      </c>
+      <c r="J161" t="str">
+        <f>ALL!K1</f>
+        <v>SEP</v>
+      </c>
+      <c r="K161" t="str">
+        <f>ALL!L1</f>
+        <v>OCT</v>
+      </c>
+      <c r="L161" t="str">
+        <f>ALL!M1</f>
+        <v>NOV</v>
+      </c>
+      <c r="M161" t="str">
+        <f>ALL!N1</f>
+        <v>DEC</v>
+      </c>
+      <c r="N161" t="str">
+        <f>ALL!O1</f>
+        <v>JAN'27</v>
+      </c>
+      <c r="O161" t="str">
+        <f>ALL!P1</f>
+        <v>FEB'27</v>
+      </c>
+      <c r="P161" t="str">
+        <f>ALL!Q1</f>
+        <v>MAR'27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A162" t="str">
+        <f>A2</f>
+        <v>Staff</v>
+      </c>
+      <c r="B162">
+        <f t="shared" ref="B162:P162" si="0">B2</f>
+        <v>148</v>
+      </c>
+      <c r="C162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="D162">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="E162">
+        <f t="shared" si="0"/>
+        <v>151</v>
+      </c>
+      <c r="F162">
+        <f t="shared" si="0"/>
+        <v>152</v>
+      </c>
+      <c r="G162">
+        <f t="shared" si="0"/>
+        <v>151</v>
+      </c>
+      <c r="H162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="I162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="J162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="K162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="L162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="M162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="N162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="O162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="P162">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A163" t="str">
+        <f>A4</f>
+        <v>Plan</v>
+      </c>
+      <c r="E163">
+        <f t="shared" ref="E163:P163" si="1">E4</f>
+        <v>143</v>
+      </c>
+      <c r="F163">
+        <f t="shared" si="1"/>
+        <v>147</v>
+      </c>
+      <c r="G163">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+      <c r="H163">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="I163">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="J163">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+      <c r="K163">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+      <c r="L163">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="M163">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="N163">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="O163">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="P163">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>127</v>
+      </c>
+      <c r="B164">
+        <f>SUM(ALL!C22:C23)</f>
+        <v>128.04000000000002</v>
+      </c>
+      <c r="C164">
+        <f>SUM(ALL!D22:D23)</f>
+        <v>136.05000000000001</v>
+      </c>
+      <c r="D164">
+        <f>SUM(ALL!E22:E23)</f>
+        <v>137.04000000000002</v>
+      </c>
+      <c r="E164">
+        <f>SUM(ALL!F22:F23)</f>
+        <v>137.80000000000001</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>130</v>
+      </c>
+      <c r="B165">
+        <v>127</v>
+      </c>
+      <c r="C165">
+        <v>136</v>
+      </c>
+      <c r="D165">
+        <v>136</v>
+      </c>
+      <c r="E165">
+        <v>132</v>
+      </c>
+      <c r="F165">
+        <v>132</v>
+      </c>
+      <c r="G165">
+        <v>130</v>
+      </c>
+      <c r="H165">
+        <v>118</v>
+      </c>
+      <c r="I165">
+        <v>114</v>
+      </c>
+      <c r="J165">
+        <v>111</v>
+      </c>
+      <c r="K165">
+        <v>109</v>
+      </c>
+      <c r="L165">
+        <v>105</v>
+      </c>
+      <c r="M165">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -15796,49 +18095,49 @@
         <v>17</v>
       </c>
       <c r="C3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="D3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="E3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="F3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="G3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="H3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="I3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="J3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="K3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="L3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="M3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="N3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="O3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="P3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="Q3" s="8">
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -15849,25 +18148,25 @@
         <v>18</v>
       </c>
       <c r="C4" s="8">
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="D4" s="8">
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="E4" s="8">
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="F4" s="14">
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G4" s="14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H4" s="14">
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I4" s="8">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="J4" s="8">
         <v>16</v>
@@ -15876,22 +18175,22 @@
         <v>16</v>
       </c>
       <c r="L4" s="8">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="M4" s="8">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N4" s="8">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="O4" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P4" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="Q4" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -16095,13 +18394,13 @@
         <v>19</v>
       </c>
       <c r="C10" s="8">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="D10" s="8">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="E10" s="8">
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="F10" s="8">
         <v>17</v>
@@ -16148,25 +18447,25 @@
         <v>19</v>
       </c>
       <c r="C11" s="8">
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="D11" s="8">
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="E11" s="8">
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="F11" s="14">
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G11" s="14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H11" s="14">
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I11" s="8">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="J11" s="8">
         <v>16</v>
@@ -16175,22 +18474,22 @@
         <v>16</v>
       </c>
       <c r="L11" s="8">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="M11" s="8">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N11" s="8">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="O11" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P11" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="Q11" s="8">
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -16577,19 +18876,19 @@
       <c r="B32" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32">
         <v>18</v>
       </c>
-      <c r="D32" s="21">
+      <c r="D32">
         <v>17</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32">
         <v>17</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F32">
         <v>17</v>
       </c>
-      <c r="G32" s="21">
+      <c r="G32">
         <v>17</v>
       </c>
     </row>
@@ -16600,20 +18899,20 @@
       <c r="B33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="26">
-        <v>17</v>
-      </c>
-      <c r="D33" s="21">
-        <v>17</v>
-      </c>
-      <c r="E33" s="21">
-        <v>17</v>
-      </c>
-      <c r="F33" s="21">
-        <v>17</v>
-      </c>
-      <c r="G33" s="21">
-        <v>17</v>
+      <c r="C33">
+        <v>17.2</v>
+      </c>
+      <c r="D33">
+        <v>17.2</v>
+      </c>
+      <c r="E33">
+        <v>17.2</v>
+      </c>
+      <c r="F33">
+        <v>17.2</v>
+      </c>
+      <c r="G33">
+        <v>17.2</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -16623,38 +18922,38 @@
       <c r="B34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="26">
-        <v>17</v>
-      </c>
-      <c r="D34" s="14">
-        <v>17</v>
-      </c>
-      <c r="E34" s="21">
-        <v>16</v>
-      </c>
-      <c r="F34" s="21">
-        <v>16</v>
-      </c>
-      <c r="G34" s="21">
-        <v>14</v>
+      <c r="C34">
+        <v>16.816669999999998</v>
+      </c>
+      <c r="D34">
+        <v>17.433330000000002</v>
+      </c>
+      <c r="E34">
+        <v>16.066669999999998</v>
+      </c>
+      <c r="F34">
+        <v>15.76667</v>
+      </c>
+      <c r="G34">
+        <v>14.2</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
       <c r="B35" s="8"/>
-      <c r="C35" s="27">
+      <c r="C35" s="83">
         <v>6.5699999999999995E-2</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="83">
         <v>-2.5499999999999998E-2</v>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="83">
         <v>5.4899999999999997E-2</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="83">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="83">
         <v>0.16470000000000001</v>
       </c>
     </row>
@@ -16663,19 +18962,19 @@
       <c r="B36" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="83">
         <v>0.93430000000000002</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="83">
         <v>1.0255000000000001</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="83">
         <v>0.94510000000000005</v>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="83">
         <v>0.92749999999999999</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="83">
         <v>0.83530000000000004</v>
       </c>
     </row>
@@ -16684,30 +18983,25 @@
       <c r="B37" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37">
         <v>1</v>
       </c>
-      <c r="D37" s="20">
-        <v>0</v>
-      </c>
-      <c r="E37" s="20">
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
         <v>1</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37">
         <v>1</v>
       </c>
-      <c r="G37" s="20">
+      <c r="G37">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="8"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
@@ -16716,19 +19010,19 @@
       <c r="B39" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39">
         <v>18</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39">
         <v>17</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39">
         <v>17</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39">
         <v>17</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39">
         <v>17</v>
       </c>
     </row>
@@ -16739,19 +19033,19 @@
       <c r="B40" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40">
         <v>17</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40">
         <v>17</v>
       </c>
-      <c r="E40" s="21">
+      <c r="E40">
         <v>17</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40">
         <v>17</v>
       </c>
-      <c r="G40" s="21">
+      <c r="G40">
         <v>17</v>
       </c>
     </row>
@@ -16762,30 +19056,25 @@
       <c r="B41" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="26">
+      <c r="C41">
         <v>17</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41">
         <v>17</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E41">
         <v>16</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41">
         <v>16</v>
       </c>
-      <c r="G41" s="21">
+      <c r="G41">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="17"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
@@ -16794,19 +19083,19 @@
       <c r="B43" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="26">
-        <v>0</v>
-      </c>
-      <c r="D43" s="21">
-        <v>0</v>
-      </c>
-      <c r="E43" s="21">
-        <v>0</v>
-      </c>
-      <c r="F43" s="21">
-        <v>0</v>
-      </c>
-      <c r="G43" s="21">
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
         <v>0</v>
       </c>
     </row>
@@ -16817,19 +19106,19 @@
       <c r="B44" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="26">
-        <v>0</v>
-      </c>
-      <c r="D44" s="21">
-        <v>0</v>
-      </c>
-      <c r="E44" s="21">
-        <v>0</v>
-      </c>
-      <c r="F44" s="21">
-        <v>0</v>
-      </c>
-      <c r="G44" s="21">
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
         <v>0</v>
       </c>
     </row>
@@ -16840,30 +19129,25 @@
       <c r="B45" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="26">
-        <v>0</v>
-      </c>
-      <c r="D45" s="21">
-        <v>0</v>
-      </c>
-      <c r="E45" s="21">
-        <v>0</v>
-      </c>
-      <c r="F45" s="21">
-        <v>0</v>
-      </c>
-      <c r="G45" s="21">
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="17"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
@@ -16872,19 +19156,19 @@
       <c r="B47" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="26">
-        <v>0</v>
-      </c>
-      <c r="D47" s="21">
-        <v>0</v>
-      </c>
-      <c r="E47" s="21">
-        <v>0</v>
-      </c>
-      <c r="F47" s="21">
-        <v>0</v>
-      </c>
-      <c r="G47" s="21">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0</v>
       </c>
     </row>
@@ -16895,19 +19179,19 @@
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="26">
-        <v>0</v>
-      </c>
-      <c r="D48" s="21">
-        <v>0</v>
-      </c>
-      <c r="E48" s="21">
-        <v>0</v>
-      </c>
-      <c r="F48" s="21">
-        <v>0</v>
-      </c>
-      <c r="G48" s="21">
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
         <v>0</v>
       </c>
     </row>
@@ -16918,19 +19202,19 @@
       <c r="B49" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="26">
-        <v>0</v>
-      </c>
-      <c r="D49" s="21">
-        <v>0</v>
-      </c>
-      <c r="E49" s="21">
-        <v>0</v>
-      </c>
-      <c r="F49" s="21">
-        <v>0</v>
-      </c>
-      <c r="G49" s="21">
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
         <v>0</v>
       </c>
     </row>
@@ -17556,63 +19840,63 @@
       </c>
       <c r="B3">
         <f>IF(CPS!C3&gt;0,CPS!C3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="C3">
         <f>IF(CPS!D3&gt;0,CPS!D3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="D3">
         <f>IF(CPS!E3&gt;0,CPS!E3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="E3">
         <f>IF(CPS!F3&gt;0,CPS!F3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="F3">
         <f>IF(CPS!G3&gt;0,CPS!G3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="G3">
         <f>IF(CPS!H3&gt;0,CPS!H3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="H3">
         <f>IF(CPS!I3&gt;0,CPS!I3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="I3">
         <f>IF(CPS!J3&gt;0,CPS!J3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="J3">
         <f>IF(CPS!K3&gt;0,CPS!K3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="K3">
         <f>IF(CPS!L3&gt;0,CPS!L3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="L3">
         <f>IF(CPS!M3&gt;0,CPS!M3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="M3">
         <f>IF(CPS!N3&gt;0,CPS!N3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="N3">
         <f>IF(CPS!O3&gt;0,CPS!O3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="O3">
         <f>IF(CPS!P3&gt;0,CPS!P3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="P3">
         <f>IF(CPS!Q3&gt;0,CPS!Q3,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -17622,31 +19906,31 @@
       </c>
       <c r="B4">
         <f>IF(CPS!C4&gt;0,CPS!C4,"")</f>
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="C4">
         <f>IF(CPS!D4&gt;0,CPS!D4,"")</f>
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="D4">
         <f>IF(CPS!E4&gt;0,CPS!E4,"")</f>
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="E4">
         <f>IF(CPS!F4&gt;0,CPS!F4,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F4">
         <f>IF(CPS!G4&gt;0,CPS!G4,"")</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G4">
         <f>IF(CPS!H4&gt;0,CPS!H4,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H4">
         <f>IF(CPS!I4&gt;0,CPS!I4,"")</f>
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="I4">
         <f>IF(CPS!J4&gt;0,CPS!J4,"")</f>
@@ -17658,27 +19942,27 @@
       </c>
       <c r="K4">
         <f>IF(CPS!L4&gt;0,CPS!L4,"")</f>
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="L4">
         <f>IF(CPS!M4&gt;0,CPS!M4,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="M4">
         <f>IF(CPS!N4&gt;0,CPS!N4,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N4">
         <f>IF(CPS!O4&gt;0,CPS!O4,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="O4">
         <f>IF(CPS!P4&gt;0,CPS!P4,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P4">
         <f>IF(CPS!Q4&gt;0,CPS!Q4,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -17688,31 +19972,31 @@
       </c>
       <c r="B5">
         <f>IF(CPS!C11&gt;0,CPS!C11,"")</f>
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="C5">
         <f>IF(CPS!D11&gt;0,CPS!D11,"")</f>
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="D5">
         <f>IF(CPS!E11&gt;0,CPS!E11,"")</f>
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="E5">
         <f>IF(CPS!F11&gt;0,CPS!F11,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F5">
         <f>IF(CPS!G11&gt;0,CPS!G11,"")</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G5">
         <f>IF(CPS!H11&gt;0,CPS!H11,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H5">
         <f>IF(CPS!I11&gt;0,CPS!I11,"")</f>
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="I5">
         <f>IF(CPS!J11&gt;0,CPS!J11,"")</f>
@@ -17724,27 +20008,27 @@
       </c>
       <c r="K5">
         <f>IF(CPS!L11&gt;0,CPS!L11,"")</f>
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="L5">
         <f>IF(CPS!M11&gt;0,CPS!M11,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="M5">
         <f>IF(CPS!N11&gt;0,CPS!N11,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N5">
         <f>IF(CPS!O11&gt;0,CPS!O11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="O5">
         <f>IF(CPS!P11&gt;0,CPS!P11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P5">
         <f>IF(CPS!Q11&gt;0,CPS!Q11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -18014,15 +20298,15 @@
       </c>
       <c r="B13">
         <f>IF(CPS!C10&gt;0,CPS!C10,"")</f>
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="C13">
         <f>IF(CPS!D10&gt;0,CPS!D10,"")</f>
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="D13">
         <f>IF(CPS!E10&gt;0,CPS!E10,"")</f>
-        <v>17</v>
+        <v>17.25</v>
       </c>
       <c r="E13">
         <f>IF(CPS!F10&gt;0,CPS!F10,"")</f>
@@ -18080,31 +20364,31 @@
       </c>
       <c r="B14">
         <f>IF(CPS!C11&gt;0,CPS!C11,"")</f>
-        <v>17</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="C14">
         <f>IF(CPS!D11&gt;0,CPS!D11,"")</f>
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="D14">
         <f>IF(CPS!E11&gt;0,CPS!E11,"")</f>
-        <v>17</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="E14">
         <f>IF(CPS!F11&gt;0,CPS!F11,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F14">
         <f>IF(CPS!G11&gt;0,CPS!G11,"")</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G14">
         <f>IF(CPS!H11&gt;0,CPS!H11,"")</f>
-        <v>17</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="H14">
         <f>IF(CPS!I11&gt;0,CPS!I11,"")</f>
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="I14">
         <f>IF(CPS!J11&gt;0,CPS!J11,"")</f>
@@ -18116,27 +20400,27 @@
       </c>
       <c r="K14">
         <f>IF(CPS!L11&gt;0,CPS!L11,"")</f>
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="L14">
         <f>IF(CPS!M11&gt;0,CPS!M11,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="M14">
         <f>IF(CPS!N11&gt;0,CPS!N11,"")</f>
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N14">
         <f>IF(CPS!O11&gt;0,CPS!O11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="O14">
         <f>IF(CPS!P11&gt;0,CPS!P11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="P14">
         <f>IF(CPS!Q11&gt;0,CPS!Q11,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -18714,23 +20998,23 @@
       </c>
       <c r="B43">
         <f>IF(CPS!C33&gt;0,CPS!C33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="C43">
         <f>IF(CPS!D33&gt;0,CPS!D33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="D43">
         <f>IF(CPS!E33&gt;0,CPS!E33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="E43">
         <f>IF(CPS!F33&gt;0,CPS!F33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="F43">
         <f>IF(CPS!G33&gt;0,CPS!G33,"")</f>
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
@@ -18740,23 +21024,23 @@
       </c>
       <c r="B44">
         <f>IF(CPS!C34&gt;0,CPS!C34,"")</f>
-        <v>17</v>
+        <v>16.816669999999998</v>
       </c>
       <c r="C44">
         <f>IF(CPS!D34&gt;0,CPS!D34,"")</f>
-        <v>17</v>
+        <v>17.433330000000002</v>
       </c>
       <c r="D44">
         <f>IF(CPS!E34&gt;0,CPS!E34,"")</f>
-        <v>16</v>
+        <v>16.066669999999998</v>
       </c>
       <c r="E44">
         <f>IF(CPS!F34&gt;0,CPS!F34,"")</f>
-        <v>16</v>
+        <v>15.76667</v>
       </c>
       <c r="F44">
         <f>IF(CPS!G34&gt;0,CPS!G34,"")</f>
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -20660,13 +22944,13 @@
         <v>47</v>
       </c>
       <c r="D33" s="21">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E33" s="21">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F33" s="21">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G33" s="21">
         <v>47</v>
@@ -23304,15 +25588,15 @@
       </c>
       <c r="C43">
         <f>IF(PSE!D33&gt;0,PSE!D33,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D43">
         <f>IF(PSE!E33&gt;0,PSE!E33,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E43">
         <f>IF(PSE!F33&gt;0,PSE!F33,"")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F43">
         <f>IF(PSE!G33&gt;0,PSE!G33,"")</f>
@@ -24397,7 +26681,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="8">
         <v>46</v>
@@ -24502,7 +26786,7 @@
       <c r="F4" s="8">
         <v>44</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="8">
         <v>46</v>
       </c>
       <c r="H4" s="14">
@@ -24573,7 +26857,7 @@
         <v>0.95079999999999998</v>
       </c>
       <c r="G6" s="19">
-        <v>1.0044999999999999</v>
+        <v>0.98309999999999997</v>
       </c>
       <c r="H6" s="19">
         <v>1.0102</v>
@@ -24624,7 +26908,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="20">
         <v>0</v>
@@ -24696,7 +26980,7 @@
         <v>35</v>
       </c>
       <c r="G9" s="8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" s="8">
         <v>35</v>
@@ -25288,7 +27572,7 @@
         <v>-1E-3</v>
       </c>
       <c r="D35" s="28">
-        <v>1.15E-2</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="E35" s="28">
         <v>-9.7999999999999997E-3</v>
@@ -25309,7 +27593,7 @@
         <v>1.0009999999999999</v>
       </c>
       <c r="D36" s="19">
-        <v>0.98850000000000005</v>
+        <v>0.98140000000000005</v>
       </c>
       <c r="E36" s="19">
         <v>1.0098</v>
@@ -25645,7 +27929,7 @@
         <v>46</v>
       </c>
       <c r="G62" s="12">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" s="12">
         <v>46</v>
@@ -25684,49 +27968,49 @@
         <v>18</v>
       </c>
       <c r="C63" s="48">
-        <v>34.077500000000001</v>
+        <v>40.457500000000003</v>
       </c>
       <c r="D63" s="48">
-        <v>38.524999999999999</v>
+        <v>45.84</v>
       </c>
       <c r="E63" s="48">
-        <v>40.520000000000003</v>
+        <v>47.835000000000001</v>
       </c>
       <c r="F63" s="48">
-        <v>36.765000000000001</v>
+        <v>43.734999999999999</v>
       </c>
       <c r="G63" s="48">
-        <v>39.619999999999997</v>
+        <v>46.204999999999998</v>
       </c>
       <c r="H63" s="48">
-        <v>39.774999999999999</v>
+        <v>46.47</v>
       </c>
       <c r="I63" s="48">
-        <v>40.583750000000002</v>
+        <v>47.778750000000002</v>
       </c>
       <c r="J63" s="48">
-        <v>38.893250000000002</v>
+        <v>46.163249999999998</v>
       </c>
       <c r="K63" s="48">
-        <v>38.455750000000002</v>
+        <v>45.405749999999998</v>
       </c>
       <c r="L63" s="48">
-        <v>35.549500000000002</v>
+        <v>42.499499999999998</v>
       </c>
       <c r="M63" s="48">
-        <v>34.582500000000003</v>
+        <v>41.902500000000003</v>
       </c>
       <c r="N63" s="48">
-        <v>33.2575</v>
+        <v>41.502499999999998</v>
       </c>
       <c r="O63" s="48">
-        <v>24.421250000000001</v>
+        <v>32.401249999999997</v>
       </c>
       <c r="P63" s="48">
-        <v>24.12125</v>
+        <v>32.10125</v>
       </c>
       <c r="Q63" s="48">
-        <v>24.12125</v>
+        <v>32.10125</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -26703,7 +28987,7 @@
         <v>5</v>
       </c>
       <c r="G82" s="49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H82" s="49">
         <v>5</v>
@@ -27420,7 +29704,7 @@
       </c>
       <c r="F2">
         <f>IF(SD!G2&gt;0,SD!G2,"")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <f>IF(SD!H2&gt;0,SD!H2,"")</f>
@@ -27878,7 +30162,7 @@
       </c>
       <c r="F12">
         <f>IF(SD!G9&gt;0,SD!G9,"")</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12">
         <f>IF(SD!H9&gt;0,SD!H9,"")</f>
@@ -30706,7 +32990,7 @@
       </c>
       <c r="F112">
         <f>SD!G82</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G112">
         <f>SD!H82</f>
@@ -30837,7 +33121,7 @@
       </c>
       <c r="F114" s="67">
         <f t="shared" si="12"/>
-        <v>-0.99000000000000021</v>
+        <v>9.9999999999997868E-3</v>
       </c>
       <c r="G114" s="67">
         <f t="shared" si="12"/>
@@ -30913,7 +33197,7 @@
       </c>
       <c r="C116" s="59">
         <f>(AVERAGE(E113:G113)/AVERAGE(E112:G112))*100</f>
-        <v>111.73333333333333</v>
+        <v>104.74999999999999</v>
       </c>
       <c r="D116" s="59">
         <f>(AVERAGE(H113:J113)/AVERAGE(H112:J112))*100</f>
@@ -31635,7 +33919,7 @@
       </c>
       <c r="F152">
         <f>SD!G6*100</f>
-        <v>100.44999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="G152">
         <f>SD!H6*100</f>
@@ -31701,7 +33985,7 @@
       </c>
       <c r="F153">
         <f>SD!G7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153">
         <f>SD!H7</f>
@@ -31777,7 +34061,7 @@
       </c>
       <c r="C156">
         <f>SD!D36*100</f>
-        <v>98.850000000000009</v>
+        <v>98.14</v>
       </c>
       <c r="D156">
         <f>SD!E36*100</f>
@@ -31902,37 +34186,37 @@
         <v>21</v>
       </c>
       <c r="G2" s="8">
+        <v>21</v>
+      </c>
+      <c r="H2" s="8">
+        <v>21</v>
+      </c>
+      <c r="I2" s="8">
         <v>20</v>
       </c>
-      <c r="H2" s="8">
+      <c r="J2" s="8">
         <v>20</v>
       </c>
-      <c r="I2" s="8">
-        <v>19</v>
-      </c>
-      <c r="J2" s="8">
-        <v>19</v>
-      </c>
       <c r="K2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
@@ -31943,49 +34227,49 @@
         <v>17</v>
       </c>
       <c r="C3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -32078,37 +34362,37 @@
         <v>0.88400000000000001</v>
       </c>
       <c r="G6" s="19">
-        <v>0.91969999999999996</v>
+        <v>0.87590000000000001</v>
       </c>
       <c r="H6" s="19">
-        <v>0.8982</v>
+        <v>0.85540000000000005</v>
       </c>
       <c r="I6" s="19">
-        <v>0.83279999999999998</v>
+        <v>0.79110000000000003</v>
       </c>
       <c r="J6" s="19">
-        <v>0.78800000000000003</v>
+        <v>0.74860000000000004</v>
       </c>
       <c r="K6" s="19">
-        <v>0.75639999999999996</v>
+        <v>0.71860000000000002</v>
       </c>
       <c r="L6" s="19">
-        <v>0.71499999999999997</v>
+        <v>0.67930000000000001</v>
       </c>
       <c r="M6" s="19">
-        <v>0.71760000000000002</v>
+        <v>0.68179999999999996</v>
       </c>
       <c r="N6" s="19">
-        <v>0.70179999999999998</v>
+        <v>0.66679999999999995</v>
       </c>
       <c r="O6" s="19">
-        <v>0.44130000000000003</v>
+        <v>0.41930000000000001</v>
       </c>
       <c r="P6" s="19">
-        <v>0.44130000000000003</v>
+        <v>0.41930000000000001</v>
       </c>
       <c r="Q6" s="19">
-        <v>0.44130000000000003</v>
+        <v>0.41930000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -32129,37 +34413,37 @@
         <v>2</v>
       </c>
       <c r="G7" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L7" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7" s="20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O7" s="20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P7" s="20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q7" s="20">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -32201,37 +34485,37 @@
         <v>21</v>
       </c>
       <c r="G9" s="8">
+        <v>21</v>
+      </c>
+      <c r="H9" s="8">
+        <v>21</v>
+      </c>
+      <c r="I9" s="8">
         <v>20</v>
       </c>
-      <c r="H9" s="8">
+      <c r="J9" s="8">
         <v>20</v>
       </c>
-      <c r="I9" s="8">
-        <v>19</v>
-      </c>
-      <c r="J9" s="8">
-        <v>19</v>
-      </c>
       <c r="K9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q9" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
@@ -32242,49 +34526,49 @@
         <v>19</v>
       </c>
       <c r="C10" s="8">
+        <v>21</v>
+      </c>
+      <c r="D10" s="8">
+        <v>21</v>
+      </c>
+      <c r="E10" s="8">
+        <v>21</v>
+      </c>
+      <c r="F10" s="8">
         <v>20</v>
       </c>
-      <c r="D10" s="8">
+      <c r="G10" s="8">
         <v>20</v>
       </c>
-      <c r="E10" s="8">
+      <c r="H10" s="8">
         <v>20</v>
       </c>
-      <c r="F10" s="8">
-        <v>19</v>
-      </c>
-      <c r="G10" s="8">
-        <v>19</v>
-      </c>
-      <c r="H10" s="8">
-        <v>19</v>
-      </c>
       <c r="I10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q10" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
@@ -32728,16 +35012,16 @@
         <v>23</v>
       </c>
       <c r="D32" s="21">
+        <v>21</v>
+      </c>
+      <c r="E32" s="21">
         <v>20</v>
       </c>
-      <c r="E32" s="21">
-        <v>19</v>
-      </c>
       <c r="F32" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -32748,19 +35032,19 @@
         <v>17</v>
       </c>
       <c r="C33" s="26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33" s="21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E33" s="21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F33" s="21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G33" s="21">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -32793,16 +35077,16 @@
         <v>0.27929999999999999</v>
       </c>
       <c r="D35" s="28">
-        <v>9.9699999999999997E-2</v>
+        <v>0.1283</v>
       </c>
       <c r="E35" s="28">
-        <v>0.20760000000000001</v>
+        <v>0.2472</v>
       </c>
       <c r="F35" s="28">
-        <v>0.28849999999999998</v>
+        <v>0.3241</v>
       </c>
       <c r="G35" s="28">
-        <v>0.55869999999999997</v>
+        <v>0.58079999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -32814,16 +35098,16 @@
         <v>0.72070000000000001</v>
       </c>
       <c r="D36" s="19">
-        <v>0.90029999999999999</v>
+        <v>0.87170000000000003</v>
       </c>
       <c r="E36" s="19">
-        <v>0.79239999999999999</v>
+        <v>0.75280000000000002</v>
       </c>
       <c r="F36" s="19">
-        <v>0.71150000000000002</v>
+        <v>0.67589999999999995</v>
       </c>
       <c r="G36" s="19">
-        <v>0.44130000000000003</v>
+        <v>0.41930000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -32835,16 +35119,16 @@
         <v>6</v>
       </c>
       <c r="D37" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37" s="20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -32867,16 +35151,16 @@
         <v>23</v>
       </c>
       <c r="D39" s="21">
+        <v>21</v>
+      </c>
+      <c r="E39" s="21">
         <v>20</v>
       </c>
-      <c r="E39" s="21">
-        <v>19</v>
-      </c>
       <c r="F39" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G39" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -32887,19 +35171,19 @@
         <v>19</v>
       </c>
       <c r="C40" s="26">
+        <v>21</v>
+      </c>
+      <c r="D40" s="21">
         <v>20</v>
       </c>
-      <c r="D40" s="21">
-        <v>19</v>
-      </c>
       <c r="E40" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" s="21">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -33150,37 +35434,37 @@
         <v>21</v>
       </c>
       <c r="G62" s="12">
+        <v>21</v>
+      </c>
+      <c r="H62" s="12">
+        <v>21</v>
+      </c>
+      <c r="I62" s="12">
         <v>20</v>
       </c>
-      <c r="H62" s="12">
+      <c r="J62" s="12">
         <v>20</v>
       </c>
-      <c r="I62" s="12">
-        <v>19</v>
-      </c>
-      <c r="J62" s="12">
-        <v>19</v>
-      </c>
       <c r="K62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q62" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
@@ -33572,37 +35856,37 @@
         <v>4</v>
       </c>
       <c r="G70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q70" s="35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3B4170-FDE9-BC49-83AF-DA3215772A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0310FB-BF74-4F49-89E2-1ED1086A96B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="6" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="13" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -1031,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1141,7 +1141,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1655,7 +1654,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="8">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D4" s="8">
         <v>139</v>
@@ -1685,7 +1684,7 @@
         <v>132</v>
       </c>
       <c r="M4" s="8">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N4" s="8">
         <v>130</v>
@@ -1725,40 +1724,40 @@
         <v>23</v>
       </c>
       <c r="C6" s="19">
-        <v>0.88260000000000005</v>
+        <v>0.88139999999999996</v>
       </c>
       <c r="D6" s="19">
-        <v>0.93620000000000003</v>
+        <v>0.93569999999999998</v>
       </c>
       <c r="E6" s="19">
-        <v>0.95589999999999997</v>
+        <v>0.95509999999999995</v>
       </c>
       <c r="F6" s="19">
-        <v>0.94789999999999996</v>
+        <v>0.94579999999999997</v>
       </c>
       <c r="G6" s="19">
-        <v>0.96630000000000005</v>
+        <v>0.96530000000000005</v>
       </c>
       <c r="H6" s="19">
-        <v>0.95189999999999997</v>
+        <v>0.95079999999999998</v>
       </c>
       <c r="I6" s="19">
-        <v>0.95269999999999999</v>
+        <v>0.95050000000000001</v>
       </c>
       <c r="J6" s="19">
-        <v>0.93130000000000002</v>
+        <v>0.93310000000000004</v>
       </c>
       <c r="K6" s="19">
-        <v>0.92559999999999998</v>
+        <v>0.92679999999999996</v>
       </c>
       <c r="L6" s="19">
-        <v>0.87780000000000002</v>
+        <v>0.88319999999999999</v>
       </c>
       <c r="M6" s="19">
-        <v>0.86829999999999996</v>
+        <v>0.87150000000000005</v>
       </c>
       <c r="N6" s="19">
-        <v>0.86360000000000003</v>
+        <v>0.86650000000000005</v>
       </c>
       <c r="O6" s="19">
         <v>0.6976</v>
@@ -1776,7 +1775,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="20">
         <v>10</v>
@@ -1806,7 +1805,7 @@
         <v>18</v>
       </c>
       <c r="M7" s="20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N7" s="20">
         <v>20</v>
@@ -1975,19 +1974,19 @@
         <v>108</v>
       </c>
       <c r="J11" s="8">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K11" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L11" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M11" s="8">
         <v>99</v>
       </c>
       <c r="N11" s="8">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O11" s="8">
         <v>81</v>
@@ -2150,10 +2149,10 @@
         <v>20</v>
       </c>
       <c r="I15" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J15" s="8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K15" s="8">
         <v>20</v>
@@ -2374,7 +2373,9 @@
       <c r="F22" s="70">
         <v>11</v>
       </c>
-      <c r="G22" s="8"/>
+      <c r="G22" s="70">
+        <v>11</v>
+      </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
@@ -2405,6 +2406,9 @@
       <c r="F23" s="70">
         <v>126.8</v>
       </c>
+      <c r="G23" s="70">
+        <v>132.74</v>
+      </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
@@ -2484,16 +2488,16 @@
         <v>18</v>
       </c>
       <c r="C34" s="26">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D34" s="21">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E34" s="21">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F34" s="21">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G34" s="21">
         <v>104</v>
@@ -2504,19 +2508,19 @@
       <c r="A35" s="17"/>
       <c r="B35" s="8"/>
       <c r="C35" s="27">
-        <v>7.4999999999999997E-2</v>
+        <v>7.5899999999999995E-2</v>
       </c>
       <c r="D35" s="28">
-        <v>4.4600000000000001E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="E35" s="28">
-        <v>6.3500000000000001E-2</v>
+        <v>6.3200000000000006E-2</v>
       </c>
       <c r="F35" s="28">
-        <v>0.13009999999999999</v>
+        <v>0.1263</v>
       </c>
       <c r="G35" s="28">
-        <v>0.30380000000000001</v>
+        <v>0.30370000000000003</v>
       </c>
       <c r="H35" s="8"/>
     </row>
@@ -2526,19 +2530,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="29">
-        <v>0.92500000000000004</v>
+        <v>0.92410000000000003</v>
       </c>
       <c r="D36" s="19">
-        <v>0.95540000000000003</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="E36" s="19">
-        <v>0.9365</v>
+        <v>0.93679999999999997</v>
       </c>
       <c r="F36" s="19">
-        <v>0.86990000000000001</v>
+        <v>0.87380000000000002</v>
       </c>
       <c r="G36" s="19">
-        <v>0.69620000000000004</v>
+        <v>0.69630000000000003</v>
       </c>
       <c r="H36" s="20"/>
     </row>
@@ -2554,13 +2558,13 @@
         <v>7</v>
       </c>
       <c r="E37" s="20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F37" s="20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" s="20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H37" s="20"/>
     </row>
@@ -2636,10 +2640,10 @@
         <v>112</v>
       </c>
       <c r="E41" s="21">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F41" s="21">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G41" s="21">
         <v>81</v>
@@ -2718,7 +2722,7 @@
         <v>21</v>
       </c>
       <c r="E45" s="21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F45" s="21">
         <v>19</v>
@@ -13143,49 +13147,49 @@
         <v>137</v>
       </c>
       <c r="B62" s="8">
-        <v>64.239999999999995</v>
+        <v>64.02</v>
       </c>
       <c r="C62" s="8">
-        <v>70.52</v>
+        <v>70.39</v>
       </c>
       <c r="D62" s="8">
-        <v>74.53</v>
+        <v>74.349999999999994</v>
       </c>
       <c r="E62" s="8">
-        <v>73.02</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="F62" s="8">
-        <v>78.36</v>
+        <v>78.16</v>
       </c>
       <c r="G62" s="8">
-        <v>74.459999999999994</v>
+        <v>74.239999999999995</v>
       </c>
       <c r="H62" s="8">
-        <v>77.349999999999994</v>
+        <v>77.010000000000005</v>
       </c>
       <c r="I62" s="8">
-        <v>74.92</v>
+        <v>75.19</v>
       </c>
       <c r="J62" s="8">
-        <v>73.989999999999995</v>
+        <v>74.180000000000007</v>
       </c>
       <c r="K62" s="8">
-        <v>68.13</v>
+        <v>68.94</v>
       </c>
       <c r="L62" s="8">
-        <v>66.87</v>
+        <v>67.36</v>
       </c>
       <c r="M62" s="8">
-        <v>66.739999999999995</v>
+        <v>67.180000000000007</v>
       </c>
       <c r="N62" s="8">
-        <v>48.29</v>
+        <v>48.3</v>
       </c>
       <c r="O62" s="8">
-        <v>48.11</v>
+        <v>48.12</v>
       </c>
       <c r="P62" s="8">
-        <v>48.11</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
@@ -15703,63 +15707,63 @@
       </c>
       <c r="B42" s="8">
         <f>Project!B62</f>
-        <v>64.239999999999995</v>
+        <v>64.02</v>
       </c>
       <c r="C42" s="8">
         <f>Project!C62</f>
-        <v>70.52</v>
+        <v>70.39</v>
       </c>
       <c r="D42" s="8">
         <f>Project!D62</f>
-        <v>74.53</v>
+        <v>74.349999999999994</v>
       </c>
       <c r="E42" s="8">
         <f>Project!E62</f>
-        <v>73.02</v>
+        <v>72.650000000000006</v>
       </c>
       <c r="F42" s="8">
         <f>Project!F62</f>
-        <v>78.36</v>
+        <v>78.16</v>
       </c>
       <c r="G42" s="8">
         <f>Project!G62</f>
-        <v>74.459999999999994</v>
+        <v>74.239999999999995</v>
       </c>
       <c r="H42" s="8">
         <f>Project!H62</f>
-        <v>77.349999999999994</v>
+        <v>77.010000000000005</v>
       </c>
       <c r="I42" s="8">
         <f>Project!I62</f>
-        <v>74.92</v>
+        <v>75.19</v>
       </c>
       <c r="J42" s="8">
         <f>Project!J62</f>
-        <v>73.989999999999995</v>
+        <v>74.180000000000007</v>
       </c>
       <c r="K42" s="8">
         <f>Project!K62</f>
-        <v>68.13</v>
+        <v>68.94</v>
       </c>
       <c r="L42" s="8">
         <f>Project!L62</f>
-        <v>66.87</v>
+        <v>67.36</v>
       </c>
       <c r="M42" s="8">
         <f>Project!M62</f>
-        <v>66.739999999999995</v>
+        <v>67.180000000000007</v>
       </c>
       <c r="N42" s="8">
         <f>Project!N62</f>
-        <v>48.29</v>
+        <v>48.3</v>
       </c>
       <c r="O42" s="8">
         <f>Project!O62</f>
-        <v>48.11</v>
+        <v>48.12</v>
       </c>
       <c r="P42" s="8">
         <f>Project!P62</f>
-        <v>48.11</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
@@ -16243,7 +16247,7 @@
       </c>
       <c r="B4">
         <f>IF(ALL!C4&gt;0,ALL!C4,"")</f>
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4">
         <f>IF(ALL!D4&gt;0,ALL!D4,"")</f>
@@ -16283,7 +16287,7 @@
       </c>
       <c r="L4">
         <f>IF(ALL!M4&gt;0,ALL!M4,"")</f>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M4">
         <f>IF(ALL!N4&gt;0,ALL!N4,"")</f>
@@ -16337,15 +16341,15 @@
       </c>
       <c r="I5">
         <f>IF(ALL!J11&gt;0,ALL!J11,"")</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J5">
         <f>IF(ALL!K11&gt;0,ALL!K11,"")</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K5">
         <f>IF(ALL!L11&gt;0,ALL!L11,"")</f>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5">
         <f>IF(ALL!M11&gt;0,ALL!M11,"")</f>
@@ -16353,7 +16357,7 @@
       </c>
       <c r="M5">
         <f>IF(ALL!N11&gt;0,ALL!N11,"")</f>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N5">
         <f>IF(ALL!O11&gt;0,ALL!O11,"")</f>
@@ -16399,11 +16403,11 @@
       </c>
       <c r="H6">
         <f>IF(ALL!I15&gt;0,ALL!I15,"")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6">
         <f>IF(ALL!J15&gt;0,ALL!J15,"")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <f>IF(ALL!K15&gt;0,ALL!K15,"")</f>
@@ -16729,15 +16733,15 @@
       </c>
       <c r="I14">
         <f>IF(ALL!J11&gt;0,ALL!J11,"")</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J14">
         <f>IF(ALL!K11&gt;0,ALL!K11,"")</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K14">
         <f>IF(ALL!L11&gt;0,ALL!L11,"")</f>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L14">
         <f>IF(ALL!M11&gt;0,ALL!M11,"")</f>
@@ -16745,7 +16749,7 @@
       </c>
       <c r="M14">
         <f>IF(ALL!N11&gt;0,ALL!N11,"")</f>
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N14">
         <f>IF(ALL!O11&gt;0,ALL!O11,"")</f>
@@ -16985,11 +16989,11 @@
       </c>
       <c r="H24">
         <f>IF(ALL!I15&gt;0,ALL!I15,"")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I24">
         <f>IF(ALL!J15&gt;0,ALL!J15,"")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J24">
         <f>IF(ALL!K15&gt;0,ALL!K15,"")</f>
@@ -17361,19 +17365,19 @@
       </c>
       <c r="B44">
         <f>IF(ALL!C34&gt;0,ALL!C34,"")</f>
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C44">
         <f>IF(ALL!D34&gt;0,ALL!D34,"")</f>
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D44">
         <f>IF(ALL!E34&gt;0,ALL!E34,"")</f>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E44">
         <f>IF(ALL!F34&gt;0,ALL!F34,"")</f>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F44">
         <f>IF(ALL!G34&gt;0,ALL!G34,"")</f>
@@ -17395,11 +17399,11 @@
       </c>
       <c r="D45">
         <f>IF(ALL!E41&gt;0,ALL!E41,"")</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E45">
         <f>IF(ALL!F41&gt;0,ALL!F41,"")</f>
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F45">
         <f>IF(ALL!G41&gt;0,ALL!G41,"")</f>
@@ -17421,7 +17425,7 @@
       </c>
       <c r="D46">
         <f>IF(ALL!E45&gt;0,ALL!E45,"")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46">
         <f>IF(ALL!F45&gt;0,ALL!F45,"")</f>
@@ -17527,51 +17531,51 @@
       </c>
       <c r="B152">
         <f>ALL!C6*100</f>
-        <v>88.26</v>
+        <v>88.14</v>
       </c>
       <c r="C152">
         <f>ALL!D6*100</f>
-        <v>93.62</v>
+        <v>93.57</v>
       </c>
       <c r="D152">
         <f>ALL!E6*100</f>
-        <v>95.59</v>
+        <v>95.509999999999991</v>
       </c>
       <c r="E152">
         <f>ALL!F6*100</f>
-        <v>94.789999999999992</v>
+        <v>94.58</v>
       </c>
       <c r="F152">
         <f>ALL!G6*100</f>
-        <v>96.63000000000001</v>
+        <v>96.53</v>
       </c>
       <c r="G152">
         <f>ALL!H6*100</f>
-        <v>95.19</v>
+        <v>95.08</v>
       </c>
       <c r="H152">
         <f>ALL!I6*100</f>
-        <v>95.27</v>
+        <v>95.05</v>
       </c>
       <c r="I152">
         <f>ALL!J6*100</f>
-        <v>93.13</v>
+        <v>93.31</v>
       </c>
       <c r="J152">
         <f>ALL!K6*100</f>
-        <v>92.56</v>
+        <v>92.679999999999993</v>
       </c>
       <c r="K152">
         <f>ALL!L6*100</f>
-        <v>87.78</v>
+        <v>88.32</v>
       </c>
       <c r="L152">
         <f>ALL!M6*100</f>
-        <v>86.83</v>
+        <v>87.15</v>
       </c>
       <c r="M152">
         <f>ALL!N6*100</f>
-        <v>86.36</v>
+        <v>86.65</v>
       </c>
       <c r="N152">
         <f>ALL!O6*100</f>
@@ -17593,7 +17597,7 @@
       </c>
       <c r="B153">
         <f>ALL!C7</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C153">
         <f>ALL!D7</f>
@@ -17633,7 +17637,7 @@
       </c>
       <c r="L153">
         <f>ALL!M7</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M153">
         <f>ALL!N7</f>
@@ -17681,23 +17685,23 @@
       </c>
       <c r="B156">
         <f>ALL!C36*100</f>
-        <v>92.5</v>
+        <v>92.41</v>
       </c>
       <c r="C156">
         <f>ALL!D36*100</f>
-        <v>95.54</v>
+        <v>95.399999999999991</v>
       </c>
       <c r="D156">
         <f>ALL!E36*100</f>
-        <v>93.65</v>
+        <v>93.679999999999993</v>
       </c>
       <c r="E156">
         <f>ALL!F36*100</f>
-        <v>86.99</v>
+        <v>87.38</v>
       </c>
       <c r="F156">
         <f>ALL!G36*100</f>
-        <v>69.62</v>
+        <v>69.63000000000001</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -17715,15 +17719,15 @@
       </c>
       <c r="D157">
         <f>ALL!E37</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E157">
         <f>ALL!F37</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F157">
         <f>ALL!G37</f>
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.2">
@@ -17889,7 +17893,7 @@
       </c>
       <c r="L163">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M163">
         <f t="shared" si="1"/>
@@ -18876,19 +18880,19 @@
       <c r="B32" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="26">
         <v>18</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="21">
         <v>17</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="21">
         <v>17</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="21">
         <v>17</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="21">
         <v>17</v>
       </c>
     </row>
@@ -18899,19 +18903,19 @@
       <c r="B33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="26">
         <v>17.2</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="21">
         <v>17.2</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="21">
         <v>17.2</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="21">
         <v>17.2</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="21">
         <v>17.2</v>
       </c>
     </row>
@@ -18922,38 +18926,38 @@
       <c r="B34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C34">
-        <v>16.816669999999998</v>
-      </c>
-      <c r="D34">
-        <v>17.433330000000002</v>
-      </c>
-      <c r="E34">
-        <v>16.066669999999998</v>
-      </c>
-      <c r="F34">
-        <v>15.76667</v>
-      </c>
-      <c r="G34">
+      <c r="C34" s="26">
+        <v>16.81666667</v>
+      </c>
+      <c r="D34" s="14">
+        <v>17.43333333</v>
+      </c>
+      <c r="E34" s="21">
+        <v>16.06666667</v>
+      </c>
+      <c r="F34" s="21">
+        <v>15.766666669999999</v>
+      </c>
+      <c r="G34" s="21">
         <v>14.2</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
       <c r="B35" s="8"/>
-      <c r="C35" s="83">
+      <c r="C35" s="27">
         <v>6.5699999999999995E-2</v>
       </c>
-      <c r="D35" s="83">
+      <c r="D35" s="28">
         <v>-2.5499999999999998E-2</v>
       </c>
-      <c r="E35" s="83">
+      <c r="E35" s="28">
         <v>5.4899999999999997E-2</v>
       </c>
-      <c r="F35" s="83">
+      <c r="F35" s="28">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="G35" s="83">
+      <c r="G35" s="28">
         <v>0.16470000000000001</v>
       </c>
     </row>
@@ -18962,19 +18966,19 @@
       <c r="B36" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="83">
+      <c r="C36" s="29">
         <v>0.93430000000000002</v>
       </c>
-      <c r="D36" s="83">
+      <c r="D36" s="19">
         <v>1.0255000000000001</v>
       </c>
-      <c r="E36" s="83">
+      <c r="E36" s="19">
         <v>0.94510000000000005</v>
       </c>
-      <c r="F36" s="83">
+      <c r="F36" s="19">
         <v>0.92749999999999999</v>
       </c>
-      <c r="G36" s="83">
+      <c r="G36" s="19">
         <v>0.83530000000000004</v>
       </c>
     </row>
@@ -18983,25 +18987,30 @@
       <c r="B37" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="30">
         <v>1</v>
       </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
         <v>1</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="20">
         <v>1</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="8"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
@@ -19010,19 +19019,19 @@
       <c r="B39" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="26">
         <v>18</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="21">
         <v>17</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="21">
         <v>17</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="21">
         <v>17</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="21">
         <v>17</v>
       </c>
     </row>
@@ -19033,19 +19042,19 @@
       <c r="B40" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="26">
         <v>17</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="21">
         <v>17</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="21">
         <v>17</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="21">
         <v>17</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="21">
         <v>17</v>
       </c>
     </row>
@@ -19056,25 +19065,30 @@
       <c r="B41" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="26">
         <v>17</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="14">
         <v>17</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="21">
         <v>16</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="21">
         <v>16</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="21">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="17"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
@@ -19083,19 +19097,19 @@
       <c r="B43" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
+      <c r="C43" s="26">
+        <v>0</v>
+      </c>
+      <c r="D43" s="21">
+        <v>0</v>
+      </c>
+      <c r="E43" s="21">
+        <v>0</v>
+      </c>
+      <c r="F43" s="21">
+        <v>0</v>
+      </c>
+      <c r="G43" s="21">
         <v>0</v>
       </c>
     </row>
@@ -19106,19 +19120,19 @@
       <c r="B44" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
+      <c r="C44" s="26">
+        <v>0</v>
+      </c>
+      <c r="D44" s="21">
+        <v>0</v>
+      </c>
+      <c r="E44" s="21">
+        <v>0</v>
+      </c>
+      <c r="F44" s="21">
+        <v>0</v>
+      </c>
+      <c r="G44" s="21">
         <v>0</v>
       </c>
     </row>
@@ -19129,25 +19143,30 @@
       <c r="B45" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
+      <c r="C45" s="26">
+        <v>0</v>
+      </c>
+      <c r="D45" s="21">
+        <v>0</v>
+      </c>
+      <c r="E45" s="21">
+        <v>0</v>
+      </c>
+      <c r="F45" s="21">
+        <v>0</v>
+      </c>
+      <c r="G45" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="17"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
@@ -19156,19 +19175,19 @@
       <c r="B47" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
+      <c r="C47" s="26">
+        <v>0</v>
+      </c>
+      <c r="D47" s="21">
+        <v>0</v>
+      </c>
+      <c r="E47" s="21">
+        <v>0</v>
+      </c>
+      <c r="F47" s="21">
+        <v>0</v>
+      </c>
+      <c r="G47" s="21">
         <v>0</v>
       </c>
     </row>
@@ -19179,19 +19198,19 @@
       <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
+      <c r="C48" s="26">
+        <v>0</v>
+      </c>
+      <c r="D48" s="21">
+        <v>0</v>
+      </c>
+      <c r="E48" s="21">
+        <v>0</v>
+      </c>
+      <c r="F48" s="21">
+        <v>0</v>
+      </c>
+      <c r="G48" s="21">
         <v>0</v>
       </c>
     </row>
@@ -19202,19 +19221,19 @@
       <c r="B49" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
+      <c r="C49" s="26">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21">
+        <v>0</v>
+      </c>
+      <c r="E49" s="21">
+        <v>0</v>
+      </c>
+      <c r="F49" s="21">
+        <v>0</v>
+      </c>
+      <c r="G49" s="21">
         <v>0</v>
       </c>
     </row>
@@ -21024,19 +21043,19 @@
       </c>
       <c r="B44">
         <f>IF(CPS!C34&gt;0,CPS!C34,"")</f>
-        <v>16.816669999999998</v>
+        <v>16.81666667</v>
       </c>
       <c r="C44">
         <f>IF(CPS!D34&gt;0,CPS!D34,"")</f>
-        <v>17.433330000000002</v>
+        <v>17.43333333</v>
       </c>
       <c r="D44">
         <f>IF(CPS!E34&gt;0,CPS!E34,"")</f>
-        <v>16.066669999999998</v>
+        <v>16.06666667</v>
       </c>
       <c r="E44">
         <f>IF(CPS!F34&gt;0,CPS!F34,"")</f>
-        <v>15.76667</v>
+        <v>15.766666669999999</v>
       </c>
       <c r="F44">
         <f>IF(CPS!G34&gt;0,CPS!G34,"")</f>
@@ -22274,25 +22293,25 @@
         <v>0.97460000000000002</v>
       </c>
       <c r="H6" s="19">
-        <v>0.91479999999999995</v>
+        <v>0.91439999999999999</v>
       </c>
       <c r="I6" s="19">
-        <v>0.93979999999999997</v>
+        <v>0.93520000000000003</v>
       </c>
       <c r="J6" s="19">
-        <v>0.92830000000000001</v>
+        <v>0.93130000000000002</v>
       </c>
       <c r="K6" s="19">
-        <v>0.93879999999999997</v>
+        <v>0.94169999999999998</v>
       </c>
       <c r="L6" s="19">
-        <v>0.86850000000000005</v>
+        <v>0.88439999999999996</v>
       </c>
       <c r="M6" s="19">
-        <v>0.85419999999999996</v>
+        <v>0.86250000000000004</v>
       </c>
       <c r="N6" s="19">
-        <v>0.85419999999999996</v>
+        <v>0.86250000000000004</v>
       </c>
       <c r="O6" s="19">
         <v>0.65939999999999999</v>
@@ -22509,19 +22528,19 @@
         <v>27</v>
       </c>
       <c r="J11" s="8">
+        <v>27</v>
+      </c>
+      <c r="K11" s="8">
+        <v>27</v>
+      </c>
+      <c r="L11" s="8">
         <v>26</v>
       </c>
-      <c r="K11" s="8">
-        <v>26</v>
-      </c>
-      <c r="L11" s="8">
+      <c r="M11" s="8">
         <v>25</v>
       </c>
-      <c r="M11" s="8">
-        <v>24</v>
-      </c>
       <c r="N11" s="8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O11" s="8">
         <v>19</v>
@@ -22684,10 +22703,10 @@
         <v>16</v>
       </c>
       <c r="I15" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K15" s="8">
         <v>16</v>
@@ -22973,7 +22992,7 @@
         <v>45</v>
       </c>
       <c r="F34" s="21">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G34" s="21">
         <v>32</v>
@@ -22986,13 +23005,13 @@
         <v>5.7599999999999998E-2</v>
       </c>
       <c r="D35" s="28">
-        <v>5.4699999999999999E-2</v>
+        <v>5.4899999999999997E-2</v>
       </c>
       <c r="E35" s="28">
-        <v>6.4399999999999999E-2</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="F35" s="28">
-        <v>0.14099999999999999</v>
+        <v>0.13020000000000001</v>
       </c>
       <c r="G35" s="28">
         <v>0.34060000000000001</v>
@@ -23007,13 +23026,13 @@
         <v>0.94240000000000002</v>
       </c>
       <c r="D36" s="19">
-        <v>0.94530000000000003</v>
+        <v>0.94510000000000005</v>
       </c>
       <c r="E36" s="19">
-        <v>0.93559999999999999</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="F36" s="19">
-        <v>0.85899999999999999</v>
+        <v>0.86980000000000002</v>
       </c>
       <c r="G36" s="19">
         <v>0.65939999999999999</v>
@@ -23034,7 +23053,7 @@
         <v>3</v>
       </c>
       <c r="F37" s="20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G37" s="20">
         <v>10</v>
@@ -23109,10 +23128,10 @@
         <v>27</v>
       </c>
       <c r="E41" s="21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F41" s="21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G41" s="21">
         <v>19</v>
@@ -23187,7 +23206,7 @@
         <v>17</v>
       </c>
       <c r="E45" s="21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F45" s="21">
         <v>15</v>
@@ -23397,25 +23416,25 @@
         <v>46.78</v>
       </c>
       <c r="H63" s="38">
-        <v>43.91</v>
+        <v>43.89</v>
       </c>
       <c r="I63" s="38">
-        <v>45.11</v>
+        <v>44.89</v>
       </c>
       <c r="J63" s="38">
-        <v>44.56</v>
+        <v>44.7</v>
       </c>
       <c r="K63" s="38">
-        <v>45.06</v>
+        <v>45.2</v>
       </c>
       <c r="L63" s="38">
-        <v>41.69</v>
+        <v>42.45</v>
       </c>
       <c r="M63" s="38">
-        <v>41</v>
+        <v>41.4</v>
       </c>
       <c r="N63" s="38">
-        <v>41</v>
+        <v>41.4</v>
       </c>
       <c r="O63" s="38">
         <v>31.65</v>
@@ -23927,25 +23946,25 @@
         <v>39.78</v>
       </c>
       <c r="H73" s="8">
-        <v>36.909999999999997</v>
+        <v>36.89</v>
       </c>
       <c r="I73" s="8">
-        <v>38.11</v>
+        <v>37.89</v>
       </c>
       <c r="J73" s="8">
-        <v>37.56</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="K73" s="8">
-        <v>38.06</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="L73" s="8">
-        <v>34.69</v>
+        <v>35.450000000000003</v>
       </c>
       <c r="M73" s="8">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="N73" s="8">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="O73" s="8">
         <v>24.65</v>
@@ -24033,25 +24052,25 @@
         <v>21.28</v>
       </c>
       <c r="H75" s="41">
-        <v>19.36</v>
+        <v>19.34</v>
       </c>
       <c r="I75" s="41">
-        <v>20.51</v>
+        <v>20.89</v>
       </c>
       <c r="J75" s="41">
-        <v>19.96</v>
+        <v>20.7</v>
       </c>
       <c r="K75" s="41">
-        <v>19.96</v>
+        <v>20.7</v>
       </c>
       <c r="L75" s="41">
-        <v>18.79</v>
+        <v>19.55</v>
       </c>
       <c r="M75" s="41">
-        <v>18.100000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="N75" s="41">
-        <v>18.100000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="O75" s="41">
         <v>13.15</v>
@@ -24142,13 +24161,13 @@
         <v>14.55</v>
       </c>
       <c r="I77" s="41">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="J77" s="41">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="K77" s="41">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="L77" s="41">
         <v>13.9</v>
@@ -24586,23 +24605,23 @@
       </c>
       <c r="I5">
         <f>IF(PSE!J11&gt;0,PSE!J11,"")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J5">
         <f>IF(PSE!K11&gt;0,PSE!K11,"")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K5">
         <f>IF(PSE!L11&gt;0,PSE!L11,"")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5">
         <f>IF(PSE!M11&gt;0,PSE!M11,"")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5">
         <f>IF(PSE!N11&gt;0,PSE!N11,"")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N5">
         <f>IF(PSE!O11&gt;0,PSE!O11,"")</f>
@@ -24648,11 +24667,11 @@
       </c>
       <c r="H6">
         <f>IF(PSE!I15&gt;0,PSE!I15,"")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <f>IF(PSE!J15&gt;0,PSE!J15,"")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <f>IF(PSE!K15&gt;0,PSE!K15,"")</f>
@@ -24978,23 +24997,23 @@
       </c>
       <c r="I14">
         <f>IF(PSE!J11&gt;0,PSE!J11,"")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J14">
         <f>IF(PSE!K11&gt;0,PSE!K11,"")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K14">
         <f>IF(PSE!L11&gt;0,PSE!L11,"")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L14">
         <f>IF(PSE!M11&gt;0,PSE!M11,"")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M14">
         <f>IF(PSE!N11&gt;0,PSE!N11,"")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N14">
         <f>IF(PSE!O11&gt;0,PSE!O11,"")</f>
@@ -25234,11 +25253,11 @@
       </c>
       <c r="H24">
         <f>PSE!I15</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I24">
         <f>PSE!J15</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J24">
         <f>PSE!K15</f>
@@ -25622,7 +25641,7 @@
       </c>
       <c r="E44">
         <f>IF(PSE!F34&gt;0,PSE!F34,"")</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F44">
         <f>IF(PSE!G34&gt;0,PSE!G34,"")</f>
@@ -25644,11 +25663,11 @@
       </c>
       <c r="D45">
         <f>IF(PSE!E41&gt;0,PSE!E41,"")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E45">
         <f>IF(PSE!F41&gt;0,PSE!F41,"")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F45">
         <f>IF(PSE!G41&gt;0,PSE!G41,"")</f>
@@ -25670,7 +25689,7 @@
       </c>
       <c r="D46">
         <f>IF(PSE!E45&gt;0,PSE!E45,"")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46">
         <f>IF(PSE!F45&gt;0,PSE!F45,"")</f>
@@ -26177,31 +26196,31 @@
       </c>
       <c r="G63">
         <f>PSE!H73</f>
-        <v>36.909999999999997</v>
+        <v>36.89</v>
       </c>
       <c r="H63">
         <f>PSE!I73</f>
-        <v>38.11</v>
+        <v>37.89</v>
       </c>
       <c r="I63">
         <f>PSE!J73</f>
-        <v>37.56</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="J63">
         <f>PSE!K73</f>
-        <v>38.06</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="K63">
         <f>PSE!L73</f>
-        <v>34.69</v>
+        <v>35.450000000000003</v>
       </c>
       <c r="L63">
         <f>PSE!M73</f>
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="M63">
         <f>PSE!N73</f>
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="N63">
         <f>PSE!O73</f>
@@ -26242,31 +26261,31 @@
       </c>
       <c r="G64" s="67">
         <f t="shared" si="2"/>
-        <v>4.0900000000000034</v>
+        <v>4.1099999999999994</v>
       </c>
       <c r="H64" s="67">
         <f t="shared" si="2"/>
-        <v>2.8900000000000006</v>
+        <v>3.1099999999999994</v>
       </c>
       <c r="I64" s="67">
         <f t="shared" si="2"/>
-        <v>3.4399999999999977</v>
+        <v>3.2999999999999972</v>
       </c>
       <c r="J64" s="67">
         <f t="shared" si="2"/>
-        <v>2.9399999999999977</v>
+        <v>2.7999999999999972</v>
       </c>
       <c r="K64" s="67">
         <f t="shared" si="2"/>
-        <v>6.3100000000000023</v>
+        <v>5.5499999999999972</v>
       </c>
       <c r="L64" s="67">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6.6000000000000014</v>
       </c>
       <c r="M64" s="67">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6.6000000000000014</v>
       </c>
       <c r="N64" s="67">
         <f t="shared" si="2"/>
@@ -26314,15 +26333,15 @@
       </c>
       <c r="C66" s="59">
         <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
-        <v>93.593495934959364</v>
+        <v>93.577235772357724</v>
       </c>
       <c r="D66" s="59">
         <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
-        <v>92.463414634146346</v>
+        <v>92.512195121951223</v>
       </c>
       <c r="E66" s="59">
         <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
-        <v>83.487804878048777</v>
+        <v>84.756097560975604</v>
       </c>
       <c r="F66" s="59">
         <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
@@ -26418,31 +26437,31 @@
       </c>
       <c r="G152">
         <f>PSE!H6*100</f>
-        <v>91.47999999999999</v>
+        <v>91.44</v>
       </c>
       <c r="H152">
         <f>PSE!I6*100</f>
-        <v>93.97999999999999</v>
+        <v>93.52000000000001</v>
       </c>
       <c r="I152">
         <f>PSE!J6*100</f>
-        <v>92.83</v>
+        <v>93.13</v>
       </c>
       <c r="J152">
         <f>PSE!K6*100</f>
-        <v>93.88</v>
+        <v>94.17</v>
       </c>
       <c r="K152">
         <f>PSE!L6*100</f>
-        <v>86.850000000000009</v>
+        <v>88.44</v>
       </c>
       <c r="L152">
         <f>PSE!M6*100</f>
-        <v>85.42</v>
+        <v>86.25</v>
       </c>
       <c r="M152">
         <f>PSE!N6*100</f>
-        <v>85.42</v>
+        <v>86.25</v>
       </c>
       <c r="N152">
         <f>PSE!O6*100</f>
@@ -26556,15 +26575,15 @@
       </c>
       <c r="C156">
         <f>PSE!D36*100</f>
-        <v>94.53</v>
+        <v>94.51</v>
       </c>
       <c r="D156">
         <f>PSE!E36*100</f>
-        <v>93.56</v>
+        <v>93.600000000000009</v>
       </c>
       <c r="E156">
         <f>PSE!F36*100</f>
-        <v>85.9</v>
+        <v>86.98</v>
       </c>
       <c r="F156">
         <f>PSE!G36*100</f>
@@ -26590,7 +26609,7 @@
       </c>
       <c r="E157">
         <f>PSE!F37</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F157">
         <f>PSE!G37</f>
@@ -26784,7 +26803,7 @@
         <v>48</v>
       </c>
       <c r="F4" s="8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" s="8">
         <v>46</v>
@@ -26802,7 +26821,7 @@
         <v>45</v>
       </c>
       <c r="L4" s="8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="8">
         <v>42</v>
@@ -26845,49 +26864,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="19">
-        <v>0.94089999999999996</v>
+        <v>0.93679999999999997</v>
       </c>
       <c r="D6" s="19">
-        <v>1.0186999999999999</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="E6" s="19">
-        <v>1.0399</v>
+        <v>1.0371999999999999</v>
       </c>
       <c r="F6" s="19">
-        <v>0.95079999999999998</v>
+        <v>0.94389999999999996</v>
       </c>
       <c r="G6" s="19">
-        <v>0.98309999999999997</v>
+        <v>0.9798</v>
       </c>
       <c r="H6" s="19">
-        <v>1.0102</v>
+        <v>1.0068999999999999</v>
       </c>
       <c r="I6" s="19">
-        <v>1.0387</v>
+        <v>1.0361</v>
       </c>
       <c r="J6" s="19">
-        <v>1.0035000000000001</v>
+        <v>1.0063</v>
       </c>
       <c r="K6" s="19">
-        <v>0.98709999999999998</v>
+        <v>0.98809999999999998</v>
       </c>
       <c r="L6" s="19">
-        <v>0.92390000000000005</v>
+        <v>0.92490000000000006</v>
       </c>
       <c r="M6" s="19">
-        <v>0.91090000000000004</v>
+        <v>0.91290000000000004</v>
       </c>
       <c r="N6" s="19">
-        <v>0.9022</v>
+        <v>0.90310000000000001</v>
       </c>
       <c r="O6" s="19">
-        <v>0.70440000000000003</v>
+        <v>0.7046</v>
       </c>
       <c r="P6" s="19">
-        <v>0.69789999999999996</v>
+        <v>0.69810000000000005</v>
       </c>
       <c r="Q6" s="19">
-        <v>0.69789999999999996</v>
+        <v>0.69810000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -26905,7 +26924,7 @@
         <v>-2</v>
       </c>
       <c r="F7" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="20">
         <v>1</v>
@@ -26923,7 +26942,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7" s="20">
         <v>4</v>
@@ -27074,7 +27093,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="8">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="14">
         <v>35</v>
@@ -27549,7 +27568,7 @@
       <c r="B34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="26">
         <v>45</v>
       </c>
       <c r="D34" s="21">
@@ -27569,19 +27588,19 @@
       <c r="A35" s="17"/>
       <c r="B35" s="8"/>
       <c r="C35" s="27">
-        <v>-1E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="D35" s="28">
-        <v>1.8599999999999998E-2</v>
+        <v>2.3099999999999999E-2</v>
       </c>
       <c r="E35" s="28">
-        <v>-9.7999999999999997E-3</v>
+        <v>-1.0200000000000001E-2</v>
       </c>
       <c r="F35" s="28">
-        <v>8.7599999999999997E-2</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="G35" s="28">
-        <v>0.3</v>
+        <v>0.29980000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -27590,19 +27609,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="29">
-        <v>1.0009999999999999</v>
+        <v>0.99819999999999998</v>
       </c>
       <c r="D36" s="19">
-        <v>0.98140000000000005</v>
+        <v>0.97689999999999999</v>
       </c>
       <c r="E36" s="19">
-        <v>1.0098</v>
+        <v>1.0102</v>
       </c>
       <c r="F36" s="19">
-        <v>0.91239999999999999</v>
+        <v>0.91359999999999997</v>
       </c>
       <c r="G36" s="19">
-        <v>0.7</v>
+        <v>0.70020000000000004</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -27968,49 +27987,49 @@
         <v>18</v>
       </c>
       <c r="C63" s="48">
-        <v>40.457500000000003</v>
+        <v>40.282499999999999</v>
       </c>
       <c r="D63" s="48">
-        <v>45.84</v>
+        <v>45.765000000000001</v>
       </c>
       <c r="E63" s="48">
-        <v>47.835000000000001</v>
+        <v>47.71</v>
       </c>
       <c r="F63" s="48">
-        <v>43.734999999999999</v>
+        <v>43.42</v>
       </c>
       <c r="G63" s="48">
-        <v>46.204999999999998</v>
+        <v>46.052500000000002</v>
       </c>
       <c r="H63" s="48">
-        <v>46.47</v>
+        <v>46.317500000000003</v>
       </c>
       <c r="I63" s="48">
-        <v>47.778750000000002</v>
+        <v>47.658749999999998</v>
       </c>
       <c r="J63" s="48">
-        <v>46.163249999999998</v>
+        <v>46.291249999999998</v>
       </c>
       <c r="K63" s="48">
-        <v>45.405749999999998</v>
+        <v>45.453749999999999</v>
       </c>
       <c r="L63" s="48">
-        <v>42.499499999999998</v>
+        <v>42.547499999999999</v>
       </c>
       <c r="M63" s="48">
-        <v>41.902500000000003</v>
+        <v>41.9925</v>
       </c>
       <c r="N63" s="48">
-        <v>41.502499999999998</v>
+        <v>41.542499999999997</v>
       </c>
       <c r="O63" s="48">
-        <v>32.401249999999997</v>
+        <v>32.411250000000003</v>
       </c>
       <c r="P63" s="48">
-        <v>32.10125</v>
+        <v>32.111249999999998</v>
       </c>
       <c r="Q63" s="48">
-        <v>32.10125</v>
+        <v>32.111249999999998</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -28192,28 +28211,28 @@
         <v>3.3</v>
       </c>
       <c r="G67" s="8">
-        <v>4.0250000000000004</v>
+        <v>4.125</v>
       </c>
       <c r="H67" s="8">
-        <v>4.0250000000000004</v>
+        <v>4.125</v>
       </c>
       <c r="I67" s="8">
-        <v>3.9812500000000002</v>
+        <v>4.03125</v>
       </c>
       <c r="J67" s="8">
-        <v>3.2937500000000002</v>
+        <v>3.34375</v>
       </c>
       <c r="K67" s="8">
-        <v>2.9312499999999999</v>
+        <v>3.03125</v>
       </c>
       <c r="L67" s="8">
-        <v>2.7124999999999999</v>
+        <v>2.8125</v>
       </c>
       <c r="M67" s="8">
-        <v>2.5874999999999999</v>
+        <v>2.6875</v>
       </c>
       <c r="N67" s="8">
-        <v>2.3875000000000002</v>
+        <v>2.4375</v>
       </c>
       <c r="O67" s="8">
         <v>1.28125</v>
@@ -28613,40 +28632,40 @@
         <v>4.3250000000000002</v>
       </c>
       <c r="F75" s="8">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="G75" s="8">
-        <v>3.5150000000000001</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="H75" s="8">
-        <v>3.4649999999999999</v>
+        <v>3.4249999999999998</v>
       </c>
       <c r="I75" s="8">
-        <v>3.3650000000000002</v>
+        <v>3.3250000000000002</v>
       </c>
       <c r="J75" s="8">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="K75" s="8">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="L75" s="8">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="M75" s="8">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="N75" s="8">
-        <v>3.0449999999999999</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="O75" s="8">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="P75" s="8">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="Q75" s="8">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
@@ -28710,22 +28729,22 @@
         <v>18</v>
       </c>
       <c r="C77" s="8">
-        <v>3.3849999999999998</v>
+        <v>3.2349999999999999</v>
       </c>
       <c r="D77" s="8">
-        <v>3.0750000000000002</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E77" s="8">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="F77" s="8">
-        <v>2.6549999999999998</v>
+        <v>2.5550000000000002</v>
       </c>
       <c r="G77" s="8">
-        <v>2.6850000000000001</v>
+        <v>2.585</v>
       </c>
       <c r="H77" s="8">
-        <v>2.4649999999999999</v>
+        <v>2.3650000000000002</v>
       </c>
       <c r="I77" s="8">
         <v>2.3149999999999999</v>
@@ -28816,22 +28835,22 @@
         <v>18</v>
       </c>
       <c r="C79" s="8">
-        <v>3.2749999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="D79" s="8">
-        <v>3.2749999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="E79" s="8">
-        <v>3.2250000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="F79" s="8">
-        <v>2.875</v>
+        <v>2.85</v>
       </c>
       <c r="G79" s="8">
-        <v>3.1124999999999998</v>
+        <v>3.1</v>
       </c>
       <c r="H79" s="8">
-        <v>2.8624999999999998</v>
+        <v>2.85</v>
       </c>
       <c r="I79" s="8">
         <v>2.6</v>
@@ -28934,28 +28953,28 @@
         <v>3.85</v>
       </c>
       <c r="G81" s="8">
-        <v>4.16</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H81" s="8">
-        <v>4.0599999999999996</v>
+        <v>4</v>
       </c>
       <c r="I81" s="8">
-        <v>4.2750000000000004</v>
+        <v>4.125</v>
       </c>
       <c r="J81" s="8">
-        <v>4.1520000000000001</v>
+        <v>4.07</v>
       </c>
       <c r="K81" s="8">
-        <v>3.927</v>
+        <v>3.8450000000000002</v>
       </c>
       <c r="L81" s="8">
-        <v>3.7269999999999999</v>
+        <v>3.645</v>
       </c>
       <c r="M81" s="8">
-        <v>3.4849999999999999</v>
+        <v>3.4449999999999998</v>
       </c>
       <c r="N81" s="8">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="O81" s="8">
         <v>1</v>
@@ -29037,31 +29056,31 @@
         <v>5.05</v>
       </c>
       <c r="F83" s="8">
-        <v>5.28</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="G83" s="8">
-        <v>5.99</v>
+        <v>5.95</v>
       </c>
       <c r="H83" s="8">
-        <v>5.49</v>
+        <v>5.45</v>
       </c>
       <c r="I83" s="8">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
       <c r="J83" s="8">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="K83" s="8">
-        <v>4.5</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="L83" s="8">
-        <v>4.5</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="M83" s="8">
-        <v>4.5</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="N83" s="8">
-        <v>4.5</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="O83" s="8">
         <v>3.22</v>
@@ -29832,7 +29851,7 @@
       </c>
       <c r="E4">
         <f>IF(SD!F4&gt;0,SD!F4,"")</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4">
         <f>IF(SD!G4&gt;0,SD!G4,"")</f>
@@ -29856,7 +29875,7 @@
       </c>
       <c r="K4">
         <f>IF(SD!L4&gt;0,SD!L4,"")</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4">
         <f>IF(SD!M4&gt;0,SD!M4,"")</f>
@@ -29886,7 +29905,7 @@
       </c>
       <c r="B5">
         <f>IF(SD!C11&gt;0,SD!C11,"")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <f>IF(SD!D11&gt;0,SD!D11,"")</f>
@@ -30278,7 +30297,7 @@
       </c>
       <c r="B14">
         <f>IF(SD!C11&gt;0,SD!C11,"")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <f>IF(SD!D11&gt;0,SD!D11,"")</f>
@@ -31190,35 +31209,35 @@
       </c>
       <c r="F53">
         <f>SD!G67</f>
-        <v>4.0250000000000004</v>
+        <v>4.125</v>
       </c>
       <c r="G53">
         <f>SD!H67</f>
-        <v>4.0250000000000004</v>
+        <v>4.125</v>
       </c>
       <c r="H53">
         <f>SD!I67</f>
-        <v>3.9812500000000002</v>
+        <v>4.03125</v>
       </c>
       <c r="I53">
         <f>SD!J67</f>
-        <v>3.2937500000000002</v>
+        <v>3.34375</v>
       </c>
       <c r="J53">
         <f>SD!K67</f>
-        <v>2.9312499999999999</v>
+        <v>3.03125</v>
       </c>
       <c r="K53">
         <f>SD!L67</f>
-        <v>2.7124999999999999</v>
+        <v>2.8125</v>
       </c>
       <c r="L53">
         <f>SD!M67</f>
-        <v>2.5874999999999999</v>
+        <v>2.6875</v>
       </c>
       <c r="M53">
         <f>SD!N67</f>
-        <v>2.3875000000000002</v>
+        <v>2.4375</v>
       </c>
       <c r="N53">
         <f>SD!O67</f>
@@ -31255,35 +31274,35 @@
       </c>
       <c r="F54" s="67">
         <f t="shared" si="0"/>
-        <v>-2.5000000000000355E-2</v>
+        <v>-0.125</v>
       </c>
       <c r="G54" s="67">
         <f t="shared" si="0"/>
-        <v>-2.5000000000000355E-2</v>
+        <v>-0.125</v>
       </c>
       <c r="H54" s="67">
         <f t="shared" si="0"/>
-        <v>1.8749999999999822E-2</v>
+        <v>-3.125E-2</v>
       </c>
       <c r="I54" s="67">
         <f t="shared" si="0"/>
-        <v>0.70624999999999982</v>
+        <v>0.65625</v>
       </c>
       <c r="J54" s="67">
         <f t="shared" si="0"/>
-        <v>1.0687500000000001</v>
+        <v>0.96875</v>
       </c>
       <c r="K54" s="67">
         <f t="shared" si="0"/>
-        <v>1.2875000000000001</v>
+        <v>1.1875</v>
       </c>
       <c r="L54" s="67">
         <f t="shared" si="0"/>
-        <v>1.4125000000000001</v>
+        <v>1.3125</v>
       </c>
       <c r="M54" s="67">
         <f t="shared" si="0"/>
-        <v>1.6124999999999998</v>
+        <v>1.5625</v>
       </c>
       <c r="N54" s="67">
         <f t="shared" si="0"/>
@@ -31331,15 +31350,15 @@
       </c>
       <c r="C56" s="59">
         <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
-        <v>94.583333333333343</v>
+        <v>96.25</v>
       </c>
       <c r="D56" s="59">
         <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
-        <v>85.052083333333343</v>
+        <v>86.71875</v>
       </c>
       <c r="E56" s="59">
         <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
-        <v>64.0625</v>
+        <v>66.145833333333343</v>
       </c>
       <c r="F56" s="59">
         <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
@@ -31808,51 +31827,51 @@
       </c>
       <c r="E73">
         <f>SD!F75</f>
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="F73">
         <f>SD!G75</f>
-        <v>3.5150000000000001</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="G73">
         <f>SD!H75</f>
-        <v>3.4649999999999999</v>
+        <v>3.4249999999999998</v>
       </c>
       <c r="H73">
         <f>SD!I75</f>
-        <v>3.3650000000000002</v>
+        <v>3.3250000000000002</v>
       </c>
       <c r="I73">
         <f>SD!J75</f>
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="J73">
         <f>SD!K75</f>
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="K73">
         <f>SD!L75</f>
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="L73">
         <f>SD!M75</f>
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="M73">
         <f>SD!N75</f>
-        <v>3.0449999999999999</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="N73">
         <f>SD!O75</f>
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="O73">
         <f>SD!P75</f>
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="P73">
         <f>SD!Q75</f>
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="74" spans="1:16" s="66" customFormat="1" x14ac:dyDescent="0.2">
@@ -31873,51 +31892,51 @@
       </c>
       <c r="E74" s="67">
         <f t="shared" si="4"/>
-        <v>0.10000000000000009</v>
+        <v>0.10999999999999988</v>
       </c>
       <c r="F74" s="67">
         <f t="shared" si="4"/>
-        <v>0.48499999999999988</v>
+        <v>0.52499999999999991</v>
       </c>
       <c r="G74" s="67">
         <f t="shared" si="4"/>
-        <v>0.53500000000000014</v>
+        <v>0.57500000000000018</v>
       </c>
       <c r="H74" s="67">
         <f t="shared" si="4"/>
-        <v>0.63499999999999979</v>
+        <v>0.67499999999999982</v>
       </c>
       <c r="I74" s="67">
         <f t="shared" si="4"/>
-        <v>0.56000000000000005</v>
+        <v>0.41999999999999993</v>
       </c>
       <c r="J74" s="67">
         <f t="shared" si="4"/>
-        <v>0.87999999999999989</v>
+        <v>0.87000000000000011</v>
       </c>
       <c r="K74" s="67">
         <f t="shared" si="4"/>
-        <v>0.87999999999999989</v>
+        <v>0.87000000000000011</v>
       </c>
       <c r="L74" s="67">
         <f t="shared" si="4"/>
-        <v>0.87999999999999989</v>
+        <v>0.87000000000000011</v>
       </c>
       <c r="M74" s="67">
         <f t="shared" si="4"/>
-        <v>0.95500000000000007</v>
+        <v>0.94499999999999984</v>
       </c>
       <c r="N74" s="67">
         <f t="shared" si="4"/>
-        <v>1.2200000000000002</v>
+        <v>1.21</v>
       </c>
       <c r="O74" s="67">
         <f t="shared" si="4"/>
-        <v>1.2200000000000002</v>
+        <v>1.21</v>
       </c>
       <c r="P74" s="67">
         <f t="shared" si="4"/>
-        <v>1.2200000000000002</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="75" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.2">
@@ -31953,19 +31972,19 @@
       </c>
       <c r="C76" s="59">
         <f>(AVERAGE(E73:G73)/AVERAGE(E72:G72))*100</f>
-        <v>90.666666666666657</v>
+        <v>89.916666666666657</v>
       </c>
       <c r="D76" s="59">
         <f>(AVERAGE(H73:J73)/AVERAGE(H72:J72))*100</f>
-        <v>82.708333333333343</v>
+        <v>83.625</v>
       </c>
       <c r="E76" s="59">
         <f>(AVERAGE(K73:M73)/AVERAGE(K72:M72))*100</f>
-        <v>77.375</v>
+        <v>77.625</v>
       </c>
       <c r="F76" s="59">
         <f>(AVERAGE(N73:P73)/AVERAGE(N72:P72))*100</f>
-        <v>69.5</v>
+        <v>69.750000000000014</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
@@ -32107,27 +32126,27 @@
       </c>
       <c r="B83">
         <f>SD!C77</f>
-        <v>3.3849999999999998</v>
+        <v>3.2349999999999999</v>
       </c>
       <c r="C83">
         <f>SD!D77</f>
-        <v>3.0750000000000002</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="D83">
         <f>SD!E77</f>
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="E83">
         <f>SD!F77</f>
-        <v>2.6549999999999998</v>
+        <v>2.5550000000000002</v>
       </c>
       <c r="F83">
         <f>SD!G77</f>
-        <v>2.6850000000000001</v>
+        <v>2.585</v>
       </c>
       <c r="G83">
         <f>SD!H77</f>
-        <v>2.4649999999999999</v>
+        <v>2.3650000000000002</v>
       </c>
       <c r="H83">
         <f>SD!I77</f>
@@ -32172,27 +32191,27 @@
       </c>
       <c r="B84" s="67">
         <f>B82-B83</f>
-        <v>-1.3849999999999998</v>
+        <v>-1.2349999999999999</v>
       </c>
       <c r="C84" s="67">
         <f t="shared" ref="C84:P84" si="6">C82-C83</f>
-        <v>-1.0750000000000002</v>
+        <v>-1.0249999999999999</v>
       </c>
       <c r="D84" s="67">
         <f t="shared" si="6"/>
-        <v>-2.2199999999999998</v>
+        <v>-2.12</v>
       </c>
       <c r="E84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.6549999999999998</v>
+        <v>-0.55500000000000016</v>
       </c>
       <c r="F84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.68500000000000005</v>
+        <v>-0.58499999999999996</v>
       </c>
       <c r="G84" s="67">
         <f t="shared" si="6"/>
-        <v>-0.46499999999999986</v>
+        <v>-0.36500000000000021</v>
       </c>
       <c r="H84" s="67">
         <f t="shared" si="6"/>
@@ -32260,11 +32279,11 @@
       </c>
       <c r="B86" s="59">
         <f>(AVERAGE(B83:D83)/AVERAGE(B82:D82))*100</f>
-        <v>178</v>
+        <v>172.99999999999997</v>
       </c>
       <c r="C86" s="59">
         <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
-        <v>130.08333333333331</v>
+        <v>125.08333333333334</v>
       </c>
       <c r="D86" s="59">
         <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
@@ -32418,27 +32437,27 @@
       </c>
       <c r="B93">
         <f>SD!C79</f>
-        <v>3.2749999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="C93">
         <f>SD!D79</f>
-        <v>3.2749999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="D93">
         <f>SD!E79</f>
-        <v>3.2250000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="E93">
         <f>SD!F79</f>
-        <v>2.875</v>
+        <v>2.85</v>
       </c>
       <c r="F93">
         <f>SD!G79</f>
-        <v>3.1124999999999998</v>
+        <v>3.1</v>
       </c>
       <c r="G93">
         <f>SD!H79</f>
-        <v>2.8624999999999998</v>
+        <v>2.85</v>
       </c>
       <c r="H93">
         <f>SD!I79</f>
@@ -32483,27 +32502,27 @@
       </c>
       <c r="B94" s="67">
         <f>B92-B93</f>
-        <v>-0.27499999999999991</v>
+        <v>-0.25</v>
       </c>
       <c r="C94" s="67">
         <f t="shared" ref="C94:P94" si="8">C92-C93</f>
-        <v>-0.27499999999999991</v>
+        <v>-0.25</v>
       </c>
       <c r="D94" s="67">
         <f t="shared" si="8"/>
-        <v>-0.22500000000000009</v>
+        <v>-0.20000000000000018</v>
       </c>
       <c r="E94" s="67">
         <f t="shared" si="8"/>
-        <v>0.125</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="F94" s="67">
         <f t="shared" si="8"/>
-        <v>-0.11249999999999982</v>
+        <v>-0.10000000000000009</v>
       </c>
       <c r="G94" s="67">
         <f t="shared" si="8"/>
-        <v>0.13750000000000018</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="H94" s="67">
         <f t="shared" si="8"/>
@@ -32571,11 +32590,11 @@
       </c>
       <c r="B96" s="59">
         <f>(AVERAGE(B93:D93)/AVERAGE(B92:D92))*100</f>
-        <v>108.6111111111111</v>
+        <v>107.77777777777777</v>
       </c>
       <c r="C96" s="59">
         <f>(AVERAGE(E93:G93)/AVERAGE(E92:G92))*100</f>
-        <v>98.333333333333329</v>
+        <v>97.777777777777786</v>
       </c>
       <c r="D96" s="59">
         <f>(AVERAGE(H93:J93)/AVERAGE(H92:J92))*100</f>
@@ -32745,35 +32764,35 @@
       </c>
       <c r="F103">
         <f>SD!G81</f>
-        <v>4.16</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G103">
         <f>SD!H81</f>
-        <v>4.0599999999999996</v>
+        <v>4</v>
       </c>
       <c r="H103">
         <f>SD!I81</f>
-        <v>4.2750000000000004</v>
+        <v>4.125</v>
       </c>
       <c r="I103">
         <f>SD!J81</f>
-        <v>4.1520000000000001</v>
+        <v>4.07</v>
       </c>
       <c r="J103">
         <f>SD!K81</f>
-        <v>3.927</v>
+        <v>3.8450000000000002</v>
       </c>
       <c r="K103">
         <f>SD!L81</f>
-        <v>3.7269999999999999</v>
+        <v>3.645</v>
       </c>
       <c r="L103">
         <f>SD!M81</f>
-        <v>3.4849999999999999</v>
+        <v>3.4449999999999998</v>
       </c>
       <c r="M103">
         <f>SD!N81</f>
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="N103">
         <f>SD!O81</f>
@@ -32810,35 +32829,35 @@
       </c>
       <c r="F104" s="67">
         <f t="shared" si="10"/>
-        <v>-0.16000000000000014</v>
+        <v>-9.9999999999999645E-2</v>
       </c>
       <c r="G104" s="67">
         <f t="shared" si="10"/>
-        <v>-5.9999999999999609E-2</v>
+        <v>0</v>
       </c>
       <c r="H104" s="67">
         <f t="shared" si="10"/>
-        <v>-0.27500000000000036</v>
+        <v>-0.125</v>
       </c>
       <c r="I104" s="67">
         <f t="shared" si="10"/>
-        <v>-0.15200000000000014</v>
+        <v>-7.0000000000000284E-2</v>
       </c>
       <c r="J104" s="67">
         <f t="shared" si="10"/>
-        <v>7.2999999999999954E-2</v>
+        <v>0.1549999999999998</v>
       </c>
       <c r="K104" s="67">
         <f t="shared" si="10"/>
-        <v>0.27300000000000013</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="L104" s="67">
         <f t="shared" si="10"/>
-        <v>0.51500000000000012</v>
+        <v>0.55500000000000016</v>
       </c>
       <c r="M104" s="67">
         <f t="shared" si="10"/>
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="N104" s="67">
         <f t="shared" si="10"/>
@@ -32886,15 +32905,15 @@
       </c>
       <c r="C106" s="59">
         <f>(AVERAGE(E103:G103)/AVERAGE(E102:G102))*100</f>
-        <v>100.58333333333334</v>
+        <v>99.583333333333329</v>
       </c>
       <c r="D106" s="59">
         <f>(AVERAGE(H103:J103)/AVERAGE(H102:J102))*100</f>
-        <v>102.94999999999999</v>
+        <v>100.33333333333334</v>
       </c>
       <c r="E106" s="59">
         <f>(AVERAGE(K103:M103)/AVERAGE(K102:M102))*100</f>
-        <v>82.683333333333337</v>
+        <v>81.333333333333329</v>
       </c>
       <c r="F106" s="59">
         <f>(AVERAGE(N103:P103)/AVERAGE(N102:P102))*100</f>
@@ -33052,39 +33071,39 @@
       </c>
       <c r="E113">
         <f>SD!F83</f>
-        <v>5.28</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F113">
         <f>SD!G83</f>
-        <v>5.99</v>
+        <v>5.95</v>
       </c>
       <c r="G113">
         <f>SD!H83</f>
-        <v>5.49</v>
+        <v>5.45</v>
       </c>
       <c r="H113">
         <f>SD!I83</f>
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
       <c r="I113">
         <f>SD!J83</f>
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="J113">
         <f>SD!K83</f>
-        <v>4.5</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="K113">
         <f>SD!L83</f>
-        <v>4.5</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="L113">
         <f>SD!M83</f>
-        <v>4.5</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="M113">
         <f>SD!N83</f>
-        <v>4.5</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="N113">
         <f>SD!O83</f>
@@ -33117,39 +33136,39 @@
       </c>
       <c r="E114" s="67">
         <f t="shared" si="12"/>
-        <v>-0.28000000000000025</v>
+        <v>-9.9999999999999645E-2</v>
       </c>
       <c r="F114" s="67">
         <f t="shared" si="12"/>
-        <v>9.9999999999997868E-3</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="G114" s="67">
         <f t="shared" si="12"/>
-        <v>-0.49000000000000021</v>
+        <v>-0.45000000000000018</v>
       </c>
       <c r="H114" s="67">
         <f t="shared" si="12"/>
-        <v>-0.15000000000000036</v>
+        <v>-0.16999999999999993</v>
       </c>
       <c r="I114" s="67">
         <f t="shared" si="12"/>
-        <v>0.29999999999999982</v>
+        <v>0.28000000000000025</v>
       </c>
       <c r="J114" s="67">
         <f t="shared" si="12"/>
-        <v>0.5</v>
+        <v>0.48000000000000043</v>
       </c>
       <c r="K114" s="67">
         <f t="shared" si="12"/>
-        <v>0.5</v>
+        <v>0.48000000000000043</v>
       </c>
       <c r="L114" s="67">
         <f t="shared" si="12"/>
-        <v>0.5</v>
+        <v>0.48000000000000043</v>
       </c>
       <c r="M114" s="67">
         <f t="shared" si="12"/>
-        <v>0.5</v>
+        <v>0.48000000000000043</v>
       </c>
       <c r="N114" s="67">
         <f t="shared" si="12"/>
@@ -33197,15 +33216,15 @@
       </c>
       <c r="C116" s="59">
         <f>(AVERAGE(E113:G113)/AVERAGE(E112:G112))*100</f>
-        <v>104.74999999999999</v>
+        <v>103.125</v>
       </c>
       <c r="D116" s="59">
         <f>(AVERAGE(H113:J113)/AVERAGE(H112:J112))*100</f>
-        <v>95.666666666666671</v>
+        <v>96.066666666666677</v>
       </c>
       <c r="E116" s="59">
         <f>(AVERAGE(K113:M113)/AVERAGE(K112:M112))*100</f>
-        <v>90</v>
+        <v>90.399999999999991</v>
       </c>
       <c r="F116" s="59">
         <f>(AVERAGE(N113:P113)/AVERAGE(N112:P112))*100</f>
@@ -33903,63 +33922,63 @@
       </c>
       <c r="B152">
         <f>SD!C6*100</f>
-        <v>94.089999999999989</v>
+        <v>93.679999999999993</v>
       </c>
       <c r="C152">
         <f>SD!D6*100</f>
-        <v>101.86999999999999</v>
+        <v>101.69999999999999</v>
       </c>
       <c r="D152">
         <f>SD!E6*100</f>
-        <v>103.99000000000001</v>
+        <v>103.71999999999998</v>
       </c>
       <c r="E152">
         <f>SD!F6*100</f>
-        <v>95.08</v>
+        <v>94.39</v>
       </c>
       <c r="F152">
         <f>SD!G6*100</f>
-        <v>98.31</v>
+        <v>97.98</v>
       </c>
       <c r="G152">
         <f>SD!H6*100</f>
-        <v>101.02</v>
+        <v>100.69</v>
       </c>
       <c r="H152">
         <f>SD!I6*100</f>
-        <v>103.86999999999999</v>
+        <v>103.61</v>
       </c>
       <c r="I152">
         <f>SD!J6*100</f>
-        <v>100.35000000000001</v>
+        <v>100.63</v>
       </c>
       <c r="J152">
         <f>SD!K6*100</f>
-        <v>98.71</v>
+        <v>98.81</v>
       </c>
       <c r="K152">
         <f>SD!L6*100</f>
-        <v>92.39</v>
+        <v>92.490000000000009</v>
       </c>
       <c r="L152">
         <f>SD!M6*100</f>
-        <v>91.09</v>
+        <v>91.29</v>
       </c>
       <c r="M152">
         <f>SD!N6*100</f>
-        <v>90.22</v>
+        <v>90.31</v>
       </c>
       <c r="N152">
         <f>SD!O6*100</f>
-        <v>70.44</v>
+        <v>70.459999999999994</v>
       </c>
       <c r="O152">
         <f>SD!P6*100</f>
-        <v>69.789999999999992</v>
+        <v>69.81</v>
       </c>
       <c r="P152">
         <f>SD!Q6*100</f>
-        <v>69.789999999999992</v>
+        <v>69.81</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -33981,7 +34000,7 @@
       </c>
       <c r="E153">
         <f>SD!F7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153">
         <f>SD!G7</f>
@@ -34005,7 +34024,7 @@
       </c>
       <c r="K153">
         <f>SD!L7</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L153">
         <f>SD!M7</f>
@@ -34057,23 +34076,23 @@
       </c>
       <c r="B156">
         <f>SD!C36*100</f>
-        <v>100.1</v>
+        <v>99.82</v>
       </c>
       <c r="C156">
         <f>SD!D36*100</f>
-        <v>98.14</v>
+        <v>97.69</v>
       </c>
       <c r="D156">
         <f>SD!E36*100</f>
-        <v>100.98</v>
+        <v>101.02</v>
       </c>
       <c r="E156">
         <f>SD!F36*100</f>
-        <v>91.24</v>
+        <v>91.36</v>
       </c>
       <c r="F156">
         <f>SD!G36*100</f>
-        <v>70</v>
+        <v>70.02000000000001</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981F7F55-52A3-0C44-AC9A-6EB8E52730C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E87B0-B56C-2044-8DD5-6A106F9878F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="4220" windowWidth="40720" windowHeight="15880" activeTab="3" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="7920" yWindow="3800" windowWidth="40720" windowHeight="15880" activeTab="2" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -845,7 +845,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1002,6 +1002,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1033,7 +1039,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1143,6 +1149,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -25307,19 +25314,19 @@
         <v>128</v>
       </c>
       <c r="C22" s="70">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D22" s="70">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E22" s="70">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F22" s="70">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G22" s="70">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -25340,19 +25347,19 @@
         <v>129</v>
       </c>
       <c r="C23" s="71">
-        <v>117.04</v>
+        <v>86.27</v>
       </c>
       <c r="D23" s="71">
-        <v>125.05</v>
+        <v>91.07</v>
       </c>
       <c r="E23" s="70">
-        <v>126.04</v>
+        <v>93.43</v>
       </c>
       <c r="F23" s="70">
-        <v>126.8</v>
+        <v>94.74</v>
       </c>
       <c r="G23" s="70">
-        <v>132.74</v>
+        <v>99.94</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
@@ -27647,23 +27654,23 @@
       </c>
       <c r="B164">
         <f>SUM(DV!C22:C23)</f>
-        <v>128.04000000000002</v>
+        <v>92.27</v>
       </c>
       <c r="C164">
         <f>SUM(DV!D22:D23)</f>
-        <v>136.05000000000001</v>
+        <v>97.07</v>
       </c>
       <c r="D164">
         <f>SUM(DV!E22:E23)</f>
-        <v>137.04000000000002</v>
+        <v>99.43</v>
       </c>
       <c r="E164">
         <f>SUM(DV!F22:F23)</f>
-        <v>137.80000000000001</v>
+        <v>100.74</v>
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
+      <c r="A165" s="83" t="s">
         <v>130</v>
       </c>
       <c r="B165">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E87B0-B56C-2044-8DD5-6A106F9878F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E0848B-44FA-4842-9271-859C30365557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7920" yWindow="3800" windowWidth="40720" windowHeight="15880" activeTab="2" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="4080" yWindow="3800" windowWidth="40720" windowHeight="15880" activeTab="3" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -27673,42 +27673,45 @@
       <c r="A165" s="83" t="s">
         <v>130</v>
       </c>
-      <c r="B165">
-        <v>127</v>
-      </c>
-      <c r="C165">
-        <v>136</v>
-      </c>
-      <c r="D165">
-        <v>136</v>
-      </c>
-      <c r="E165">
-        <v>132</v>
-      </c>
-      <c r="F165">
-        <v>132</v>
-      </c>
-      <c r="G165">
-        <v>130</v>
-      </c>
-      <c r="H165">
-        <v>118</v>
-      </c>
-      <c r="I165">
-        <v>114</v>
-      </c>
-      <c r="J165">
-        <v>111</v>
-      </c>
-      <c r="K165">
-        <v>109</v>
-      </c>
-      <c r="L165">
-        <v>105</v>
-      </c>
-      <c r="M165">
-        <v>104</v>
-      </c>
+      <c r="B165" s="83">
+        <v>97</v>
+      </c>
+      <c r="C165" s="83">
+        <v>103</v>
+      </c>
+      <c r="D165" s="83">
+        <v>103</v>
+      </c>
+      <c r="E165" s="83">
+        <v>100</v>
+      </c>
+      <c r="F165" s="83">
+        <v>101</v>
+      </c>
+      <c r="G165" s="83">
+        <v>99</v>
+      </c>
+      <c r="H165" s="83">
+        <v>92</v>
+      </c>
+      <c r="I165" s="83">
+        <v>87</v>
+      </c>
+      <c r="J165" s="83">
+        <v>85</v>
+      </c>
+      <c r="K165" s="83">
+        <v>83</v>
+      </c>
+      <c r="L165" s="83">
+        <v>79</v>
+      </c>
+      <c r="M165" s="83">
+        <v>79</v>
+      </c>
+      <c r="N165" s="83"/>
+      <c r="O165" s="83"/>
+      <c r="P165" s="83"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737A349B-E77D-A34E-AF21-C18D4B2DEE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A2EA2D-7A6B-214D-8B9C-696BA90B0913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="44800" windowHeight="22640" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3811" uniqueCount="492">
   <si>
     <t>Type</t>
   </si>
@@ -2953,8 +2953,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52B5FC57-107C-A641-9F28-02FC652ECBAA}" name="SummaryTable" displayName="SummaryTable" ref="A1:N200" totalsRowShown="0">
-  <autoFilter ref="A1:N200" xr:uid="{52B5FC57-107C-A641-9F28-02FC652ECBAA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52B5FC57-107C-A641-9F28-02FC652ECBAA}" name="SummaryTable" displayName="SummaryTable" ref="A1:N194" totalsRowShown="0">
+  <autoFilter ref="A1:N194" xr:uid="{52B5FC57-107C-A641-9F28-02FC652ECBAA}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{FF7AF450-6999-9D44-8AA4-D45E1EDE4E90}" name="page"/>
     <tableColumn id="2" xr3:uid="{68BAF763-A4DF-8B46-B430-D6E3E194A665}" name="summary_title"/>
@@ -3318,7 +3318,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:N200"/>
+  <dimension ref="A1:N194"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5034,7 +5034,7 @@
         <v>155</v>
       </c>
       <c r="G47" s="107" t="s">
-        <v>367</v>
+        <v>195</v>
       </c>
       <c r="H47" s="107"/>
       <c r="I47" s="107"/>
@@ -5068,17 +5068,17 @@
         <v>152</v>
       </c>
       <c r="G48" s="107" t="s">
-        <v>189</v>
-      </c>
-      <c r="H48" s="107" t="s">
-        <v>233</v>
-      </c>
-      <c r="I48" s="107"/>
+        <v>103</v>
+      </c>
+      <c r="H48" s="107"/>
+      <c r="I48" s="107" t="s">
+        <v>239</v>
+      </c>
       <c r="J48" s="109" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K48" s="107" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="L48" s="109" t="s">
         <v>144</v>
@@ -5106,17 +5106,17 @@
         <v>152</v>
       </c>
       <c r="G49" s="107" t="s">
-        <v>102</v>
-      </c>
-      <c r="H49" s="107" t="s">
-        <v>233</v>
-      </c>
-      <c r="I49" s="107"/>
+        <v>111</v>
+      </c>
+      <c r="H49" s="107"/>
+      <c r="I49" s="107" t="s">
+        <v>240</v>
+      </c>
       <c r="J49" s="109" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K49" s="107" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="L49" s="109" t="s">
         <v>144</v>
@@ -5144,17 +5144,17 @@
         <v>152</v>
       </c>
       <c r="G50" s="107" t="s">
-        <v>234</v>
-      </c>
-      <c r="H50" s="107" t="s">
-        <v>233</v>
-      </c>
-      <c r="I50" s="107"/>
+        <v>167</v>
+      </c>
+      <c r="H50" s="107"/>
+      <c r="I50" s="107" t="s">
+        <v>241</v>
+      </c>
       <c r="J50" s="109" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K50" s="107" t="s">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="L50" s="109" t="s">
         <v>144</v>
@@ -5170,24 +5170,28 @@
       </c>
       <c r="B51" s="107"/>
       <c r="C51" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D51" s="108">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E51" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G51" s="107" t="s">
-        <v>195</v>
-      </c>
-      <c r="H51" s="107"/>
-      <c r="I51" s="107"/>
+        <v>419</v>
+      </c>
+      <c r="H51" s="107" t="s">
+        <v>420</v>
+      </c>
+      <c r="I51" s="107" t="s">
+        <v>205</v>
+      </c>
       <c r="J51" s="109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K51" s="107"/>
       <c r="L51" s="109" t="s">
@@ -5204,32 +5208,28 @@
       </c>
       <c r="B52" s="107"/>
       <c r="C52" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D52" s="108">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E52" s="108">
         <v>2</v>
       </c>
       <c r="F52" s="107" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G52" s="107" t="s">
-        <v>103</v>
+        <v>427</v>
       </c>
       <c r="H52" s="107"/>
-      <c r="I52" s="107" t="s">
-        <v>239</v>
-      </c>
+      <c r="I52" s="107"/>
       <c r="J52" s="109" t="s">
-        <v>158</v>
-      </c>
-      <c r="K52" s="107" t="s">
-        <v>166</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K52" s="107"/>
       <c r="L52" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M52" s="110" t="b">
         <v>1</v>
@@ -5242,29 +5242,29 @@
       </c>
       <c r="B53" s="107"/>
       <c r="C53" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D53" s="108">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E53" s="108">
         <v>2</v>
       </c>
       <c r="F53" s="107" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="G53" s="107" t="s">
-        <v>111</v>
-      </c>
-      <c r="H53" s="107"/>
-      <c r="I53" s="107" t="s">
-        <v>240</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H53" s="107" t="s">
+        <v>370</v>
+      </c>
+      <c r="I53" s="107"/>
       <c r="J53" s="109" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K53" s="107" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="L53" s="109" t="s">
         <v>144</v>
@@ -5280,32 +5280,30 @@
       </c>
       <c r="B54" s="107"/>
       <c r="C54" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D54" s="108">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E54" s="108">
         <v>2</v>
       </c>
       <c r="F54" s="107" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="G54" s="107" t="s">
-        <v>167</v>
-      </c>
-      <c r="H54" s="107"/>
-      <c r="I54" s="107" t="s">
-        <v>241</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="H54" s="107" t="s">
+        <v>478</v>
+      </c>
+      <c r="I54" s="107"/>
       <c r="J54" s="109" t="s">
-        <v>158</v>
-      </c>
-      <c r="K54" s="107" t="s">
-        <v>156</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K54" s="107"/>
       <c r="L54" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M54" s="110" t="b">
         <v>1</v>
@@ -5321,25 +5319,21 @@
         <v>6</v>
       </c>
       <c r="D55" s="108">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E55" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G55" s="107" t="s">
-        <v>419</v>
-      </c>
-      <c r="H55" s="107" t="s">
-        <v>420</v>
-      </c>
-      <c r="I55" s="107" t="s">
-        <v>205</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="H55" s="107"/>
+      <c r="I55" s="107"/>
       <c r="J55" s="109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K55" s="107"/>
       <c r="L55" s="109" t="s">
@@ -5359,25 +5353,29 @@
         <v>6</v>
       </c>
       <c r="D56" s="108">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E56" s="108">
         <v>2</v>
       </c>
       <c r="F56" s="107" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G56" s="107" t="s">
-        <v>427</v>
-      </c>
-      <c r="H56" s="107"/>
+        <v>112</v>
+      </c>
+      <c r="H56" s="107" t="s">
+        <v>242</v>
+      </c>
       <c r="I56" s="107"/>
       <c r="J56" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="K56" s="107"/>
+      <c r="K56" s="107" t="s">
+        <v>162</v>
+      </c>
       <c r="L56" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M56" s="110" t="b">
         <v>1</v>
@@ -5393,29 +5391,25 @@
         <v>6</v>
       </c>
       <c r="D57" s="108">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E57" s="108">
         <v>2</v>
       </c>
       <c r="F57" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G57" s="107" t="s">
-        <v>112</v>
-      </c>
-      <c r="H57" s="107" t="s">
-        <v>370</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="H57" s="107"/>
       <c r="I57" s="107"/>
       <c r="J57" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="K57" s="107" t="s">
-        <v>162</v>
-      </c>
+      <c r="K57" s="107"/>
       <c r="L57" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M57" s="110" t="b">
         <v>1</v>
@@ -5431,27 +5425,29 @@
         <v>6</v>
       </c>
       <c r="D58" s="108">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E58" s="108">
         <v>2</v>
       </c>
       <c r="F58" s="107" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="G58" s="107" t="s">
-        <v>479</v>
-      </c>
-      <c r="H58" s="107" t="s">
-        <v>478</v>
-      </c>
-      <c r="I58" s="107"/>
+        <v>103</v>
+      </c>
+      <c r="H58" s="107"/>
+      <c r="I58" s="107" t="s">
+        <v>246</v>
+      </c>
       <c r="J58" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K58" s="107"/>
+        <v>158</v>
+      </c>
+      <c r="K58" s="107" t="s">
+        <v>166</v>
+      </c>
       <c r="L58" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M58" s="110" t="b">
         <v>1</v>
@@ -5467,25 +5463,29 @@
         <v>6</v>
       </c>
       <c r="D59" s="108">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E59" s="108">
         <v>2</v>
       </c>
       <c r="F59" s="107" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G59" s="107" t="s">
-        <v>367</v>
+        <v>111</v>
       </c>
       <c r="H59" s="107"/>
-      <c r="I59" s="107"/>
+      <c r="I59" s="107" t="s">
+        <v>247</v>
+      </c>
       <c r="J59" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K59" s="107"/>
+        <v>158</v>
+      </c>
+      <c r="K59" s="107" t="s">
+        <v>201</v>
+      </c>
       <c r="L59" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M59" s="110" t="b">
         <v>1</v>
@@ -5501,7 +5501,7 @@
         <v>6</v>
       </c>
       <c r="D60" s="108">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E60" s="108">
         <v>2</v>
@@ -5510,17 +5510,17 @@
         <v>152</v>
       </c>
       <c r="G60" s="107" t="s">
-        <v>112</v>
-      </c>
-      <c r="H60" s="107" t="s">
-        <v>242</v>
-      </c>
-      <c r="I60" s="107"/>
+        <v>167</v>
+      </c>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107" t="s">
+        <v>248</v>
+      </c>
       <c r="J60" s="109" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K60" s="107" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="L60" s="109" t="s">
         <v>144</v>
@@ -5539,29 +5539,25 @@
         <v>6</v>
       </c>
       <c r="D61" s="108">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E61" s="108">
         <v>2</v>
       </c>
       <c r="F61" s="107" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G61" s="107" t="s">
-        <v>189</v>
-      </c>
-      <c r="H61" s="107" t="s">
-        <v>233</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="H61" s="107"/>
       <c r="I61" s="107"/>
       <c r="J61" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="K61" s="107" t="s">
-        <v>157</v>
-      </c>
+      <c r="K61" s="107"/>
       <c r="L61" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M61" s="110" t="b">
         <v>1</v>
@@ -5577,7 +5573,7 @@
         <v>6</v>
       </c>
       <c r="D62" s="108">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E62" s="108">
         <v>2</v>
@@ -5586,17 +5582,17 @@
         <v>152</v>
       </c>
       <c r="G62" s="107" t="s">
-        <v>102</v>
-      </c>
-      <c r="H62" s="107" t="s">
-        <v>233</v>
-      </c>
-      <c r="I62" s="107"/>
+        <v>112</v>
+      </c>
+      <c r="H62" s="107"/>
+      <c r="I62" s="107" t="s">
+        <v>249</v>
+      </c>
       <c r="J62" s="109" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K62" s="107" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="L62" s="109" t="s">
         <v>144</v>
@@ -5608,28 +5604,32 @@
     </row>
     <row r="63" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="106" t="s">
-        <v>163</v>
-      </c>
-      <c r="B63" s="107"/>
+        <v>176</v>
+      </c>
+      <c r="B63" s="107" t="s">
+        <v>280</v>
+      </c>
       <c r="C63" s="108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D63" s="108">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E63" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="107" t="s">
         <v>155</v>
       </c>
       <c r="G63" s="107" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
+      <c r="I63" s="107" t="s">
+        <v>371</v>
+      </c>
       <c r="J63" s="109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K63" s="107"/>
       <c r="L63" s="109" t="s">
@@ -5642,36 +5642,34 @@
     </row>
     <row r="64" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="106" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B64" s="107"/>
       <c r="C64" s="108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D64" s="108">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E64" s="108">
         <v>2</v>
       </c>
       <c r="F64" s="107" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="G64" s="107" t="s">
-        <v>103</v>
-      </c>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107" t="s">
-        <v>246</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="H64" s="107" t="s">
+        <v>430</v>
+      </c>
+      <c r="I64" s="107"/>
       <c r="J64" s="109" t="s">
-        <v>158</v>
-      </c>
-      <c r="K64" s="107" t="s">
-        <v>166</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K64" s="107"/>
       <c r="L64" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M64" s="110" t="b">
         <v>1</v>
@@ -5680,36 +5678,34 @@
     </row>
     <row r="65" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="106" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B65" s="107"/>
       <c r="C65" s="108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D65" s="108">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E65" s="108">
         <v>2</v>
       </c>
       <c r="F65" s="107" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="G65" s="107" t="s">
-        <v>111</v>
-      </c>
-      <c r="H65" s="107"/>
-      <c r="I65" s="107" t="s">
-        <v>247</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="H65" s="107" t="s">
+        <v>429</v>
+      </c>
+      <c r="I65" s="107"/>
       <c r="J65" s="109" t="s">
-        <v>158</v>
-      </c>
-      <c r="K65" s="107" t="s">
-        <v>201</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K65" s="107"/>
       <c r="L65" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M65" s="110" t="b">
         <v>1</v>
@@ -5718,36 +5714,34 @@
     </row>
     <row r="66" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="106" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B66" s="107"/>
       <c r="C66" s="108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D66" s="108">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E66" s="108">
         <v>2</v>
       </c>
       <c r="F66" s="107" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="G66" s="107" t="s">
-        <v>167</v>
-      </c>
-      <c r="H66" s="107"/>
-      <c r="I66" s="107" t="s">
-        <v>248</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="H66" s="107" t="s">
+        <v>436</v>
+      </c>
+      <c r="I66" s="107"/>
       <c r="J66" s="109" t="s">
-        <v>158</v>
-      </c>
-      <c r="K66" s="107" t="s">
-        <v>156</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K66" s="107"/>
       <c r="L66" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M66" s="110" t="b">
         <v>1</v>
@@ -5756,14 +5750,14 @@
     </row>
     <row r="67" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="106" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B67" s="107"/>
       <c r="C67" s="108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D67" s="108">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E67" s="108">
         <v>2</v>
@@ -5772,7 +5766,7 @@
         <v>155</v>
       </c>
       <c r="G67" s="107" t="s">
-        <v>200</v>
+        <v>421</v>
       </c>
       <c r="H67" s="107"/>
       <c r="I67" s="107"/>
@@ -5790,33 +5784,33 @@
     </row>
     <row r="68" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="106" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B68" s="107"/>
       <c r="C68" s="108">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D68" s="108">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E68" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" s="107" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G68" s="107" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="H68" s="107"/>
       <c r="I68" s="107" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="J68" s="109" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K68" s="107" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L68" s="109" t="s">
         <v>144</v>
@@ -5830,30 +5824,28 @@
       <c r="A69" s="106" t="s">
         <v>176</v>
       </c>
-      <c r="B69" s="107" t="s">
-        <v>280</v>
-      </c>
+      <c r="B69" s="107"/>
       <c r="C69" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G69" s="107" t="s">
-        <v>183</v>
-      </c>
-      <c r="H69" s="107"/>
-      <c r="I69" s="107" t="s">
-        <v>371</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="H69" s="107" t="s">
+        <v>431</v>
+      </c>
+      <c r="I69" s="107"/>
       <c r="J69" s="109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K69" s="107"/>
       <c r="L69" s="109" t="s">
@@ -5870,10 +5862,10 @@
       </c>
       <c r="B70" s="107"/>
       <c r="C70" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" s="108">
         <v>2</v>
@@ -5882,10 +5874,10 @@
         <v>178</v>
       </c>
       <c r="G70" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H70" s="107" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I70" s="107"/>
       <c r="J70" s="109" t="s">
@@ -5906,23 +5898,21 @@
       </c>
       <c r="B71" s="107"/>
       <c r="C71" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" s="108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" s="108">
         <v>2</v>
       </c>
       <c r="F71" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G71" s="107" t="s">
-        <v>208</v>
-      </c>
-      <c r="H71" s="107" t="s">
-        <v>429</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="H71" s="107"/>
       <c r="I71" s="107"/>
       <c r="J71" s="109" t="s">
         <v>154</v>
@@ -5942,30 +5932,32 @@
       </c>
       <c r="B72" s="107"/>
       <c r="C72" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G72" s="107" t="s">
-        <v>410</v>
-      </c>
-      <c r="H72" s="107" t="s">
-        <v>436</v>
-      </c>
-      <c r="I72" s="107"/>
+        <v>31</v>
+      </c>
+      <c r="H72" s="107"/>
+      <c r="I72" s="107" t="s">
+        <v>373</v>
+      </c>
       <c r="J72" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K72" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K72" s="107" t="s">
+        <v>173</v>
+      </c>
       <c r="L72" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M72" s="110" t="b">
         <v>1</v>
@@ -5978,21 +5970,23 @@
       </c>
       <c r="B73" s="107"/>
       <c r="C73" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D73" s="108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E73" s="108">
         <v>2</v>
       </c>
       <c r="F73" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G73" s="107" t="s">
-        <v>421</v>
-      </c>
-      <c r="H73" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H73" s="107" t="s">
+        <v>434</v>
+      </c>
       <c r="I73" s="107"/>
       <c r="J73" s="109" t="s">
         <v>154</v>
@@ -6012,32 +6006,30 @@
       </c>
       <c r="B74" s="107"/>
       <c r="C74" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G74" s="107" t="s">
-        <v>30</v>
-      </c>
-      <c r="H74" s="107"/>
-      <c r="I74" s="107" t="s">
-        <v>306</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H74" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I74" s="107"/>
       <c r="J74" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K74" s="107" t="s">
-        <v>164</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K74" s="107"/>
       <c r="L74" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M74" s="110" t="b">
         <v>1</v>
@@ -6050,23 +6042,21 @@
       </c>
       <c r="B75" s="107"/>
       <c r="C75" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75" s="108">
         <v>2</v>
       </c>
       <c r="F75" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G75" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H75" s="107" t="s">
-        <v>431</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="H75" s="107"/>
       <c r="I75" s="107"/>
       <c r="J75" s="109" t="s">
         <v>154</v>
@@ -6086,30 +6076,32 @@
       </c>
       <c r="B76" s="107"/>
       <c r="C76" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D76" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G76" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H76" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I76" s="107"/>
+        <v>32</v>
+      </c>
+      <c r="H76" s="107"/>
+      <c r="I76" s="107" t="s">
+        <v>374</v>
+      </c>
       <c r="J76" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K76" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K76" s="107" t="s">
+        <v>172</v>
+      </c>
       <c r="L76" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M76" s="110" t="b">
         <v>1</v>
@@ -6122,21 +6114,23 @@
       </c>
       <c r="B77" s="107"/>
       <c r="C77" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D77" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77" s="108">
         <v>2</v>
       </c>
       <c r="F77" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G77" s="107" t="s">
-        <v>372</v>
-      </c>
-      <c r="H77" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H77" s="107" t="s">
+        <v>435</v>
+      </c>
       <c r="I77" s="107"/>
       <c r="J77" s="109" t="s">
         <v>154</v>
@@ -6156,32 +6150,30 @@
       </c>
       <c r="B78" s="107"/>
       <c r="C78" s="108">
+        <v>4</v>
+      </c>
+      <c r="D78" s="108">
         <v>3</v>
       </c>
-      <c r="D78" s="108">
-        <v>1</v>
-      </c>
       <c r="E78" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G78" s="107" t="s">
-        <v>31</v>
-      </c>
-      <c r="H78" s="107"/>
-      <c r="I78" s="107" t="s">
-        <v>373</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H78" s="107" t="s">
+        <v>437</v>
+      </c>
+      <c r="I78" s="107"/>
       <c r="J78" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K78" s="107" t="s">
-        <v>173</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K78" s="107"/>
       <c r="L78" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M78" s="110" t="b">
         <v>1</v>
@@ -6194,23 +6186,21 @@
       </c>
       <c r="B79" s="107"/>
       <c r="C79" s="108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" s="108">
         <v>2</v>
       </c>
       <c r="F79" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G79" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H79" s="107" t="s">
-        <v>434</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="H79" s="107"/>
       <c r="I79" s="107"/>
       <c r="J79" s="109" t="s">
         <v>154</v>
@@ -6226,30 +6216,32 @@
     </row>
     <row r="80" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="106" t="s">
-        <v>176</v>
-      </c>
-      <c r="B80" s="107"/>
+        <v>164</v>
+      </c>
+      <c r="B80" s="107" t="s">
+        <v>281</v>
+      </c>
       <c r="C80" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G80" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H80" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I80" s="107"/>
+        <v>183</v>
+      </c>
+      <c r="H80" s="107"/>
+      <c r="I80" s="107" t="s">
+        <v>306</v>
+      </c>
       <c r="J80" s="109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K80" s="107"/>
       <c r="L80" s="109" t="s">
@@ -6262,25 +6254,27 @@
     </row>
     <row r="81" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="106" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B81" s="107"/>
       <c r="C81" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E81" s="108">
         <v>2</v>
       </c>
       <c r="F81" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G81" s="107" t="s">
-        <v>422</v>
-      </c>
-      <c r="H81" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H81" s="107" t="s">
+        <v>438</v>
+      </c>
       <c r="I81" s="107"/>
       <c r="J81" s="109" t="s">
         <v>154</v>
@@ -6296,36 +6290,34 @@
     </row>
     <row r="82" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="106" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B82" s="107"/>
       <c r="C82" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D82" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G82" s="107" t="s">
-        <v>32</v>
-      </c>
-      <c r="H82" s="107"/>
-      <c r="I82" s="107" t="s">
-        <v>374</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="H82" s="107" t="s">
+        <v>439</v>
+      </c>
+      <c r="I82" s="107"/>
       <c r="J82" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K82" s="107" t="s">
-        <v>172</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K82" s="107"/>
       <c r="L82" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M82" s="110" t="b">
         <v>1</v>
@@ -6334,14 +6326,14 @@
     </row>
     <row r="83" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="106" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B83" s="107"/>
       <c r="C83" s="108">
+        <v>1</v>
+      </c>
+      <c r="D83" s="108">
         <v>4</v>
-      </c>
-      <c r="D83" s="108">
-        <v>2</v>
       </c>
       <c r="E83" s="108">
         <v>2</v>
@@ -6350,10 +6342,10 @@
         <v>178</v>
       </c>
       <c r="G83" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H83" s="107" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I83" s="107"/>
       <c r="J83" s="109" t="s">
@@ -6370,27 +6362,25 @@
     </row>
     <row r="84" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="106" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B84" s="107"/>
       <c r="C84" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D84" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E84" s="108">
         <v>2</v>
       </c>
       <c r="F84" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G84" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H84" s="107" t="s">
-        <v>437</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="H84" s="107"/>
       <c r="I84" s="107"/>
       <c r="J84" s="109" t="s">
         <v>154</v>
@@ -6406,32 +6396,36 @@
     </row>
     <row r="85" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="106" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B85" s="107"/>
       <c r="C85" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D85" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E85" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="107" t="s">
         <v>155</v>
       </c>
       <c r="G85" s="107" t="s">
-        <v>375</v>
+        <v>36</v>
       </c>
       <c r="H85" s="107"/>
-      <c r="I85" s="107"/>
+      <c r="I85" s="107" t="s">
+        <v>260</v>
+      </c>
       <c r="J85" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K85" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K85" s="107" t="s">
+        <v>156</v>
+      </c>
       <c r="L85" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M85" s="110" t="b">
         <v>1</v>
@@ -6442,30 +6436,28 @@
       <c r="A86" s="106" t="s">
         <v>164</v>
       </c>
-      <c r="B86" s="107" t="s">
-        <v>281</v>
-      </c>
+      <c r="B86" s="107"/>
       <c r="C86" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G86" s="107" t="s">
-        <v>183</v>
-      </c>
-      <c r="H86" s="107"/>
-      <c r="I86" s="107" t="s">
-        <v>306</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="H86" s="107" t="s">
+        <v>440</v>
+      </c>
+      <c r="I86" s="107"/>
       <c r="J86" s="109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K86" s="107"/>
       <c r="L86" s="109" t="s">
@@ -6482,10 +6474,10 @@
       </c>
       <c r="B87" s="107"/>
       <c r="C87" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E87" s="108">
         <v>2</v>
@@ -6494,10 +6486,10 @@
         <v>178</v>
       </c>
       <c r="G87" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H87" s="107" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="I87" s="107"/>
       <c r="J87" s="109" t="s">
@@ -6518,23 +6510,21 @@
       </c>
       <c r="B88" s="107"/>
       <c r="C88" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" s="108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" s="108">
         <v>2</v>
       </c>
       <c r="F88" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G88" s="107" t="s">
-        <v>208</v>
-      </c>
-      <c r="H88" s="107" t="s">
-        <v>439</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="H88" s="107"/>
       <c r="I88" s="107"/>
       <c r="J88" s="109" t="s">
         <v>154</v>
@@ -6554,30 +6544,32 @@
       </c>
       <c r="B89" s="107"/>
       <c r="C89" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D89" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G89" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H89" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I89" s="107"/>
+        <v>37</v>
+      </c>
+      <c r="H89" s="107"/>
+      <c r="I89" s="107" t="s">
+        <v>174</v>
+      </c>
       <c r="J89" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K89" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K89" s="107" t="s">
+        <v>157</v>
+      </c>
       <c r="L89" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M89" s="110" t="b">
         <v>1</v>
@@ -6590,21 +6582,23 @@
       </c>
       <c r="B90" s="107"/>
       <c r="C90" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" s="108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E90" s="108">
         <v>2</v>
       </c>
       <c r="F90" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G90" s="107" t="s">
-        <v>376</v>
-      </c>
-      <c r="H90" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H90" s="107" t="s">
+        <v>441</v>
+      </c>
       <c r="I90" s="107"/>
       <c r="J90" s="109" t="s">
         <v>154</v>
@@ -6624,32 +6618,30 @@
       </c>
       <c r="B91" s="107"/>
       <c r="C91" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G91" s="107" t="s">
-        <v>36</v>
-      </c>
-      <c r="H91" s="107"/>
-      <c r="I91" s="107" t="s">
-        <v>260</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H91" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I91" s="107"/>
       <c r="J91" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K91" s="107" t="s">
-        <v>156</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K91" s="107"/>
       <c r="L91" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M91" s="110" t="b">
         <v>1</v>
@@ -6662,23 +6654,21 @@
       </c>
       <c r="B92" s="107"/>
       <c r="C92" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92" s="108">
         <v>2</v>
       </c>
       <c r="F92" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G92" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H92" s="107" t="s">
-        <v>440</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="H92" s="107"/>
       <c r="I92" s="107"/>
       <c r="J92" s="109" t="s">
         <v>154</v>
@@ -6694,30 +6684,32 @@
     </row>
     <row r="93" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="B93" s="107"/>
+        <v>173</v>
+      </c>
+      <c r="B93" s="107" t="s">
+        <v>282</v>
+      </c>
       <c r="C93" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G93" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H93" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I93" s="107"/>
+        <v>183</v>
+      </c>
+      <c r="H93" s="107"/>
+      <c r="I93" s="107" t="s">
+        <v>373</v>
+      </c>
       <c r="J93" s="109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K93" s="107"/>
       <c r="L93" s="109" t="s">
@@ -6730,25 +6722,27 @@
     </row>
     <row r="94" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="106" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B94" s="107"/>
       <c r="C94" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E94" s="108">
         <v>2</v>
       </c>
       <c r="F94" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G94" s="107" t="s">
-        <v>377</v>
-      </c>
-      <c r="H94" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H94" s="107" t="s">
+        <v>442</v>
+      </c>
       <c r="I94" s="107"/>
       <c r="J94" s="109" t="s">
         <v>154</v>
@@ -6764,36 +6758,34 @@
     </row>
     <row r="95" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="106" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B95" s="107"/>
       <c r="C95" s="108">
+        <v>1</v>
+      </c>
+      <c r="D95" s="108">
         <v>3</v>
       </c>
-      <c r="D95" s="108">
-        <v>1</v>
-      </c>
       <c r="E95" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G95" s="107" t="s">
-        <v>37</v>
-      </c>
-      <c r="H95" s="107"/>
-      <c r="I95" s="107" t="s">
-        <v>174</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="H95" s="107" t="s">
+        <v>443</v>
+      </c>
+      <c r="I95" s="107"/>
       <c r="J95" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K95" s="107" t="s">
-        <v>157</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K95" s="107"/>
       <c r="L95" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M95" s="110" t="b">
         <v>1</v>
@@ -6802,14 +6794,14 @@
     </row>
     <row r="96" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="106" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B96" s="107"/>
       <c r="C96" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E96" s="108">
         <v>2</v>
@@ -6818,10 +6810,10 @@
         <v>178</v>
       </c>
       <c r="G96" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H96" s="107" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="I96" s="107"/>
       <c r="J96" s="109" t="s">
@@ -6838,27 +6830,25 @@
     </row>
     <row r="97" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="106" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B97" s="107"/>
       <c r="C97" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E97" s="108">
         <v>2</v>
       </c>
       <c r="F97" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G97" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H97" s="107" t="s">
-        <v>432</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="H97" s="107"/>
       <c r="I97" s="107"/>
       <c r="J97" s="109" t="s">
         <v>154</v>
@@ -6874,32 +6864,36 @@
     </row>
     <row r="98" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="106" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B98" s="107"/>
       <c r="C98" s="108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E98" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="107" t="s">
         <v>155</v>
       </c>
       <c r="G98" s="107" t="s">
-        <v>378</v>
+        <v>39</v>
       </c>
       <c r="H98" s="107"/>
-      <c r="I98" s="107"/>
+      <c r="I98" s="107" t="s">
+        <v>263</v>
+      </c>
       <c r="J98" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K98" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K98" s="107" t="s">
+        <v>175</v>
+      </c>
       <c r="L98" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M98" s="110" t="b">
         <v>1</v>
@@ -6910,30 +6904,28 @@
       <c r="A99" s="106" t="s">
         <v>173</v>
       </c>
-      <c r="B99" s="107" t="s">
-        <v>282</v>
-      </c>
+      <c r="B99" s="107"/>
       <c r="C99" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G99" s="107" t="s">
-        <v>183</v>
-      </c>
-      <c r="H99" s="107"/>
-      <c r="I99" s="107" t="s">
-        <v>373</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="H99" s="107" t="s">
+        <v>444</v>
+      </c>
+      <c r="I99" s="107"/>
       <c r="J99" s="109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K99" s="107"/>
       <c r="L99" s="109" t="s">
@@ -6950,10 +6942,10 @@
       </c>
       <c r="B100" s="107"/>
       <c r="C100" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" s="108">
         <v>2</v>
@@ -6962,10 +6954,10 @@
         <v>178</v>
       </c>
       <c r="G100" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H100" s="107" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="I100" s="107"/>
       <c r="J100" s="109" t="s">
@@ -6986,23 +6978,21 @@
       </c>
       <c r="B101" s="107"/>
       <c r="C101" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" s="108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101" s="108">
         <v>2</v>
       </c>
       <c r="F101" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G101" s="107" t="s">
-        <v>208</v>
-      </c>
-      <c r="H101" s="107" t="s">
-        <v>443</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="H101" s="107"/>
       <c r="I101" s="107"/>
       <c r="J101" s="109" t="s">
         <v>154</v>
@@ -7022,30 +7012,32 @@
       </c>
       <c r="B102" s="107"/>
       <c r="C102" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D102" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G102" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H102" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I102" s="107"/>
+        <v>44</v>
+      </c>
+      <c r="H102" s="107"/>
+      <c r="I102" s="107" t="s">
+        <v>262</v>
+      </c>
       <c r="J102" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K102" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K102" s="107" t="s">
+        <v>166</v>
+      </c>
       <c r="L102" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M102" s="110" t="b">
         <v>1</v>
@@ -7058,21 +7050,23 @@
       </c>
       <c r="B103" s="107"/>
       <c r="C103" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D103" s="108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E103" s="108">
         <v>2</v>
       </c>
       <c r="F103" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G103" s="107" t="s">
-        <v>423</v>
-      </c>
-      <c r="H103" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H103" s="107" t="s">
+        <v>445</v>
+      </c>
       <c r="I103" s="107"/>
       <c r="J103" s="109" t="s">
         <v>154</v>
@@ -7092,32 +7086,30 @@
       </c>
       <c r="B104" s="107"/>
       <c r="C104" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D104" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E104" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G104" s="107" t="s">
-        <v>39</v>
-      </c>
-      <c r="H104" s="107"/>
-      <c r="I104" s="107" t="s">
-        <v>263</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H104" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I104" s="107"/>
       <c r="J104" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K104" s="107" t="s">
-        <v>175</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K104" s="107"/>
       <c r="L104" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M104" s="110" t="b">
         <v>1</v>
@@ -7130,23 +7122,21 @@
       </c>
       <c r="B105" s="107"/>
       <c r="C105" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D105" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E105" s="108">
         <v>2</v>
       </c>
       <c r="F105" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G105" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H105" s="107" t="s">
-        <v>444</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="H105" s="107"/>
       <c r="I105" s="107"/>
       <c r="J105" s="109" t="s">
         <v>154</v>
@@ -7162,30 +7152,32 @@
     </row>
     <row r="106" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="106" t="s">
-        <v>173</v>
-      </c>
-      <c r="B106" s="107"/>
+        <v>172</v>
+      </c>
+      <c r="B106" s="107" t="s">
+        <v>283</v>
+      </c>
       <c r="C106" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E106" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G106" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H106" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I106" s="107"/>
+        <v>183</v>
+      </c>
+      <c r="H106" s="107"/>
+      <c r="I106" s="107" t="s">
+        <v>374</v>
+      </c>
       <c r="J106" s="109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K106" s="107"/>
       <c r="L106" s="109" t="s">
@@ -7198,25 +7190,27 @@
     </row>
     <row r="107" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B107" s="107"/>
       <c r="C107" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E107" s="108">
         <v>2</v>
       </c>
       <c r="F107" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G107" s="107" t="s">
-        <v>379</v>
-      </c>
-      <c r="H107" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H107" s="107" t="s">
+        <v>446</v>
+      </c>
       <c r="I107" s="107"/>
       <c r="J107" s="109" t="s">
         <v>154</v>
@@ -7232,36 +7226,34 @@
     </row>
     <row r="108" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B108" s="107"/>
       <c r="C108" s="108">
+        <v>1</v>
+      </c>
+      <c r="D108" s="108">
         <v>3</v>
       </c>
-      <c r="D108" s="108">
-        <v>1</v>
-      </c>
       <c r="E108" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G108" s="107" t="s">
-        <v>44</v>
-      </c>
-      <c r="H108" s="107"/>
-      <c r="I108" s="107" t="s">
-        <v>262</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="H108" s="107" t="s">
+        <v>447</v>
+      </c>
+      <c r="I108" s="107"/>
       <c r="J108" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K108" s="107" t="s">
-        <v>166</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K108" s="107"/>
       <c r="L108" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M108" s="110" t="b">
         <v>1</v>
@@ -7270,14 +7262,14 @@
     </row>
     <row r="109" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B109" s="107"/>
       <c r="C109" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E109" s="108">
         <v>2</v>
@@ -7286,10 +7278,10 @@
         <v>178</v>
       </c>
       <c r="G109" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H109" s="107" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="I109" s="107"/>
       <c r="J109" s="109" t="s">
@@ -7306,14 +7298,14 @@
     </row>
     <row r="110" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B110" s="107"/>
       <c r="C110" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E110" s="108">
         <v>2</v>
@@ -7322,10 +7314,10 @@
         <v>178</v>
       </c>
       <c r="G110" s="107" t="s">
-        <v>433</v>
+        <v>481</v>
       </c>
       <c r="H110" s="107" t="s">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="I110" s="107"/>
       <c r="J110" s="109" t="s">
@@ -7342,14 +7334,14 @@
     </row>
     <row r="111" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B111" s="107"/>
       <c r="C111" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111" s="108">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E111" s="108">
         <v>2</v>
@@ -7358,7 +7350,7 @@
         <v>155</v>
       </c>
       <c r="G111" s="107" t="s">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="H111" s="107"/>
       <c r="I111" s="107"/>
@@ -7378,11 +7370,9 @@
       <c r="A112" s="106" t="s">
         <v>172</v>
       </c>
-      <c r="B112" s="107" t="s">
-        <v>283</v>
-      </c>
+      <c r="B112" s="107"/>
       <c r="C112" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" s="108">
         <v>1</v>
@@ -7394,18 +7384,20 @@
         <v>155</v>
       </c>
       <c r="G112" s="107" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="H112" s="107"/>
       <c r="I112" s="107" t="s">
-        <v>374</v>
+        <v>268</v>
       </c>
       <c r="J112" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="K112" s="107"/>
+      <c r="K112" s="107" t="s">
+        <v>160</v>
+      </c>
       <c r="L112" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M112" s="110" t="b">
         <v>1</v>
@@ -7418,7 +7410,7 @@
       </c>
       <c r="B113" s="107"/>
       <c r="C113" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="108">
         <v>2</v>
@@ -7433,7 +7425,7 @@
         <v>351</v>
       </c>
       <c r="H113" s="107" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I113" s="107"/>
       <c r="J113" s="109" t="s">
@@ -7454,7 +7446,7 @@
       </c>
       <c r="B114" s="107"/>
       <c r="C114" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" s="108">
         <v>3</v>
@@ -7466,10 +7458,10 @@
         <v>178</v>
       </c>
       <c r="G114" s="107" t="s">
-        <v>208</v>
+        <v>433</v>
       </c>
       <c r="H114" s="107" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I114" s="107"/>
       <c r="J114" s="109" t="s">
@@ -7490,7 +7482,7 @@
       </c>
       <c r="B115" s="107"/>
       <c r="C115" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" s="108">
         <v>4</v>
@@ -7499,14 +7491,12 @@
         <v>2</v>
       </c>
       <c r="F115" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G115" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H115" s="107" t="s">
-        <v>437</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="H115" s="107"/>
       <c r="I115" s="107"/>
       <c r="J115" s="109" t="s">
         <v>154</v>
@@ -7526,30 +7516,32 @@
       </c>
       <c r="B116" s="107"/>
       <c r="C116" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D116" s="108">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E116" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G116" s="107" t="s">
-        <v>481</v>
-      </c>
-      <c r="H116" s="107" t="s">
-        <v>480</v>
-      </c>
-      <c r="I116" s="107"/>
+        <v>53</v>
+      </c>
+      <c r="H116" s="107"/>
+      <c r="I116" s="107" t="s">
+        <v>273</v>
+      </c>
       <c r="J116" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K116" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K116" s="107" t="s">
+        <v>161</v>
+      </c>
       <c r="L116" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M116" s="110" t="b">
         <v>1</v>
@@ -7562,21 +7554,23 @@
       </c>
       <c r="B117" s="107"/>
       <c r="C117" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D117" s="108">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E117" s="108">
         <v>2</v>
       </c>
       <c r="F117" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G117" s="107" t="s">
-        <v>482</v>
-      </c>
-      <c r="H117" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H117" s="107" t="s">
+        <v>450</v>
+      </c>
       <c r="I117" s="107"/>
       <c r="J117" s="109" t="s">
         <v>154</v>
@@ -7596,32 +7590,30 @@
       </c>
       <c r="B118" s="107"/>
       <c r="C118" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D118" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G118" s="107" t="s">
-        <v>52</v>
-      </c>
-      <c r="H118" s="107"/>
-      <c r="I118" s="107" t="s">
-        <v>268</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H118" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I118" s="107"/>
       <c r="J118" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K118" s="107" t="s">
-        <v>160</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K118" s="107"/>
       <c r="L118" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M118" s="110" t="b">
         <v>1</v>
@@ -7634,23 +7626,21 @@
       </c>
       <c r="B119" s="107"/>
       <c r="C119" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E119" s="108">
         <v>2</v>
       </c>
       <c r="F119" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G119" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H119" s="107" t="s">
-        <v>448</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="H119" s="107"/>
       <c r="I119" s="107"/>
       <c r="J119" s="109" t="s">
         <v>154</v>
@@ -7670,30 +7660,32 @@
       </c>
       <c r="B120" s="107"/>
       <c r="C120" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D120" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G120" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H120" s="107" t="s">
-        <v>449</v>
-      </c>
-      <c r="I120" s="107"/>
+        <v>58</v>
+      </c>
+      <c r="H120" s="107"/>
+      <c r="I120" s="107" t="s">
+        <v>207</v>
+      </c>
       <c r="J120" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K120" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K120" s="107" t="s">
+        <v>192</v>
+      </c>
       <c r="L120" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M120" s="110" t="b">
         <v>1</v>
@@ -7706,21 +7698,23 @@
       </c>
       <c r="B121" s="107"/>
       <c r="C121" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D121" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E121" s="108">
         <v>2</v>
       </c>
       <c r="F121" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G121" s="107" t="s">
-        <v>381</v>
-      </c>
-      <c r="H121" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H121" s="107" t="s">
+        <v>451</v>
+      </c>
       <c r="I121" s="107"/>
       <c r="J121" s="109" t="s">
         <v>154</v>
@@ -7740,32 +7734,30 @@
       </c>
       <c r="B122" s="107"/>
       <c r="C122" s="108">
+        <v>4</v>
+      </c>
+      <c r="D122" s="108">
         <v>3</v>
       </c>
-      <c r="D122" s="108">
-        <v>1</v>
-      </c>
       <c r="E122" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G122" s="107" t="s">
-        <v>53</v>
-      </c>
-      <c r="H122" s="107"/>
-      <c r="I122" s="107" t="s">
-        <v>273</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H122" s="107" t="s">
+        <v>452</v>
+      </c>
+      <c r="I122" s="107"/>
       <c r="J122" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K122" s="107" t="s">
-        <v>161</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K122" s="107"/>
       <c r="L122" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M122" s="110" t="b">
         <v>1</v>
@@ -7778,23 +7770,21 @@
       </c>
       <c r="B123" s="107"/>
       <c r="C123" s="108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D123" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E123" s="108">
         <v>2</v>
       </c>
       <c r="F123" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G123" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H123" s="107" t="s">
-        <v>450</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="H123" s="107"/>
       <c r="I123" s="107"/>
       <c r="J123" s="109" t="s">
         <v>154</v>
@@ -7814,30 +7804,32 @@
       </c>
       <c r="B124" s="107"/>
       <c r="C124" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D124" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E124" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F124" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G124" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H124" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I124" s="107"/>
+        <v>59</v>
+      </c>
+      <c r="H124" s="107"/>
+      <c r="I124" s="107" t="s">
+        <v>264</v>
+      </c>
       <c r="J124" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K124" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K124" s="107" t="s">
+        <v>204</v>
+      </c>
       <c r="L124" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M124" s="110" t="b">
         <v>1</v>
@@ -7850,21 +7842,23 @@
       </c>
       <c r="B125" s="107"/>
       <c r="C125" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D125" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E125" s="108">
         <v>2</v>
       </c>
       <c r="F125" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G125" s="107" t="s">
-        <v>382</v>
-      </c>
-      <c r="H125" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H125" s="107" t="s">
+        <v>453</v>
+      </c>
       <c r="I125" s="107"/>
       <c r="J125" s="109" t="s">
         <v>154</v>
@@ -7884,32 +7878,30 @@
       </c>
       <c r="B126" s="107"/>
       <c r="C126" s="108">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D126" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E126" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G126" s="107" t="s">
-        <v>58</v>
-      </c>
-      <c r="H126" s="107"/>
-      <c r="I126" s="107" t="s">
-        <v>207</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H126" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I126" s="107"/>
       <c r="J126" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K126" s="107" t="s">
-        <v>192</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K126" s="107"/>
       <c r="L126" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M126" s="110" t="b">
         <v>1</v>
@@ -7922,23 +7914,21 @@
       </c>
       <c r="B127" s="107"/>
       <c r="C127" s="108">
+        <v>5</v>
+      </c>
+      <c r="D127" s="108">
         <v>4</v>
       </c>
-      <c r="D127" s="108">
-        <v>2</v>
-      </c>
       <c r="E127" s="108">
         <v>2</v>
       </c>
       <c r="F127" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G127" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H127" s="107" t="s">
-        <v>451</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="H127" s="107"/>
       <c r="I127" s="107"/>
       <c r="J127" s="109" t="s">
         <v>154</v>
@@ -7958,30 +7948,32 @@
       </c>
       <c r="B128" s="107"/>
       <c r="C128" s="108">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D128" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G128" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H128" s="107" t="s">
-        <v>452</v>
-      </c>
-      <c r="I128" s="107"/>
+        <v>60</v>
+      </c>
+      <c r="H128" s="107"/>
+      <c r="I128" s="107" t="s">
+        <v>265</v>
+      </c>
       <c r="J128" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K128" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K128" s="107" t="s">
+        <v>197</v>
+      </c>
       <c r="L128" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M128" s="110" t="b">
         <v>1</v>
@@ -7994,21 +7986,23 @@
       </c>
       <c r="B129" s="107"/>
       <c r="C129" s="108">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D129" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E129" s="108">
         <v>2</v>
       </c>
       <c r="F129" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G129" s="107" t="s">
-        <v>383</v>
-      </c>
-      <c r="H129" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H129" s="107" t="s">
+        <v>454</v>
+      </c>
       <c r="I129" s="107"/>
       <c r="J129" s="109" t="s">
         <v>154</v>
@@ -8028,32 +8022,30 @@
       </c>
       <c r="B130" s="107"/>
       <c r="C130" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D130" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G130" s="107" t="s">
-        <v>59</v>
-      </c>
-      <c r="H130" s="107"/>
-      <c r="I130" s="107" t="s">
-        <v>264</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H130" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I130" s="107"/>
       <c r="J130" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K130" s="107" t="s">
-        <v>204</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K130" s="107"/>
       <c r="L130" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M130" s="110" t="b">
         <v>1</v>
@@ -8066,23 +8058,21 @@
       </c>
       <c r="B131" s="107"/>
       <c r="C131" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D131" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E131" s="108">
         <v>2</v>
       </c>
       <c r="F131" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G131" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H131" s="107" t="s">
-        <v>453</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="H131" s="107"/>
       <c r="I131" s="107"/>
       <c r="J131" s="109" t="s">
         <v>154</v>
@@ -8102,30 +8092,32 @@
       </c>
       <c r="B132" s="107"/>
       <c r="C132" s="108">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D132" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E132" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G132" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H132" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I132" s="107"/>
+        <v>61</v>
+      </c>
+      <c r="H132" s="107"/>
+      <c r="I132" s="107" t="s">
+        <v>266</v>
+      </c>
       <c r="J132" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K132" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K132" s="107" t="s">
+        <v>170</v>
+      </c>
       <c r="L132" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M132" s="110" t="b">
         <v>1</v>
@@ -8138,21 +8130,23 @@
       </c>
       <c r="B133" s="107"/>
       <c r="C133" s="108">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D133" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E133" s="108">
         <v>2</v>
       </c>
       <c r="F133" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G133" s="107" t="s">
-        <v>384</v>
-      </c>
-      <c r="H133" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H133" s="107" t="s">
+        <v>455</v>
+      </c>
       <c r="I133" s="107"/>
       <c r="J133" s="109" t="s">
         <v>154</v>
@@ -8172,32 +8166,30 @@
       </c>
       <c r="B134" s="107"/>
       <c r="C134" s="108">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D134" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E134" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G134" s="107" t="s">
-        <v>60</v>
-      </c>
-      <c r="H134" s="107"/>
-      <c r="I134" s="107" t="s">
-        <v>265</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H134" s="107" t="s">
+        <v>456</v>
+      </c>
+      <c r="I134" s="107"/>
       <c r="J134" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K134" s="107" t="s">
-        <v>197</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K134" s="107"/>
       <c r="L134" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M134" s="110" t="b">
         <v>1</v>
@@ -8210,23 +8202,21 @@
       </c>
       <c r="B135" s="107"/>
       <c r="C135" s="108">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D135" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E135" s="108">
         <v>2</v>
       </c>
       <c r="F135" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G135" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H135" s="107" t="s">
-        <v>454</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="H135" s="107"/>
       <c r="I135" s="107"/>
       <c r="J135" s="109" t="s">
         <v>154</v>
@@ -8240,63 +8230,67 @@
       </c>
       <c r="N135" s="111"/>
     </row>
-    <row r="136" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B136" s="107"/>
       <c r="C136" s="108">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D136" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F136" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G136" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H136" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I136" s="107"/>
+        <v>62</v>
+      </c>
+      <c r="H136" s="107"/>
+      <c r="I136" s="107" t="s">
+        <v>386</v>
+      </c>
       <c r="J136" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K136" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K136" s="107" t="s">
+        <v>168</v>
+      </c>
       <c r="L136" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M136" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N136" s="111"/>
     </row>
-    <row r="137" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B137" s="107"/>
       <c r="C137" s="108">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D137" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E137" s="108">
         <v>2</v>
       </c>
       <c r="F137" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G137" s="107" t="s">
-        <v>385</v>
-      </c>
-      <c r="H137" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H137" s="107" t="s">
+        <v>457</v>
+      </c>
       <c r="I137" s="107"/>
       <c r="J137" s="109" t="s">
         <v>154</v>
@@ -8310,67 +8304,63 @@
       </c>
       <c r="N137" s="111"/>
     </row>
-    <row r="138" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A138" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B138" s="107"/>
       <c r="C138" s="108">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D138" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E138" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G138" s="107" t="s">
-        <v>61</v>
-      </c>
-      <c r="H138" s="107"/>
-      <c r="I138" s="107" t="s">
-        <v>266</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H138" s="107" t="s">
+        <v>458</v>
+      </c>
+      <c r="I138" s="107"/>
       <c r="J138" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K138" s="107" t="s">
-        <v>170</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K138" s="107"/>
       <c r="L138" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M138" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N138" s="111"/>
     </row>
-    <row r="139" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A139" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B139" s="107"/>
       <c r="C139" s="108">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D139" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E139" s="108">
         <v>2</v>
       </c>
       <c r="F139" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G139" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H139" s="107" t="s">
-        <v>455</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="H139" s="107"/>
       <c r="I139" s="107"/>
       <c r="J139" s="109" t="s">
         <v>154</v>
@@ -8384,63 +8374,67 @@
       </c>
       <c r="N139" s="111"/>
     </row>
-    <row r="140" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B140" s="107"/>
       <c r="C140" s="108">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D140" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E140" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F140" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G140" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H140" s="107" t="s">
-        <v>456</v>
-      </c>
-      <c r="I140" s="107"/>
+        <v>63</v>
+      </c>
+      <c r="H140" s="107"/>
+      <c r="I140" s="107" t="s">
+        <v>267</v>
+      </c>
       <c r="J140" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K140" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K140" s="107" t="s">
+        <v>201</v>
+      </c>
       <c r="L140" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M140" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N140" s="111"/>
     </row>
-    <row r="141" spans="1:14" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B141" s="107"/>
       <c r="C141" s="108">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D141" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E141" s="108">
         <v>2</v>
       </c>
       <c r="F141" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G141" s="107" t="s">
-        <v>411</v>
-      </c>
-      <c r="H141" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H141" s="107" t="s">
+        <v>459</v>
+      </c>
       <c r="I141" s="107"/>
       <c r="J141" s="109" t="s">
         <v>154</v>
@@ -8454,67 +8448,63 @@
       </c>
       <c r="N141" s="111"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A142" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B142" s="107"/>
       <c r="C142" s="108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D142" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E142" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G142" s="107" t="s">
-        <v>62</v>
-      </c>
-      <c r="H142" s="107"/>
-      <c r="I142" s="107" t="s">
-        <v>386</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H142" s="107" t="s">
+        <v>460</v>
+      </c>
+      <c r="I142" s="107"/>
       <c r="J142" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K142" s="107" t="s">
-        <v>168</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K142" s="107"/>
       <c r="L142" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M142" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N142" s="111"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A143" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B143" s="107"/>
       <c r="C143" s="108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D143" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E143" s="108">
         <v>2</v>
       </c>
       <c r="F143" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G143" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H143" s="107" t="s">
-        <v>457</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="H143" s="107"/>
       <c r="I143" s="107"/>
       <c r="J143" s="109" t="s">
         <v>154</v>
@@ -8528,63 +8518,67 @@
       </c>
       <c r="N143" s="111"/>
     </row>
-    <row r="144" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B144" s="107"/>
       <c r="C144" s="108">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D144" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E144" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G144" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H144" s="107" t="s">
-        <v>458</v>
-      </c>
-      <c r="I144" s="107"/>
+        <v>70</v>
+      </c>
+      <c r="H144" s="107"/>
+      <c r="I144" s="107" t="s">
+        <v>268</v>
+      </c>
       <c r="J144" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K144" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K144" s="107" t="s">
+        <v>162</v>
+      </c>
       <c r="L144" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M144" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N144" s="111"/>
     </row>
-    <row r="145" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B145" s="107"/>
       <c r="C145" s="108">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D145" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E145" s="108">
         <v>2</v>
       </c>
       <c r="F145" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G145" s="107" t="s">
-        <v>387</v>
-      </c>
-      <c r="H145" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H145" s="107" t="s">
+        <v>461</v>
+      </c>
       <c r="I145" s="107"/>
       <c r="J145" s="109" t="s">
         <v>154</v>
@@ -8598,67 +8592,63 @@
       </c>
       <c r="N145" s="111"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A146" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B146" s="107"/>
       <c r="C146" s="108">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D146" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E146" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G146" s="107" t="s">
-        <v>63</v>
-      </c>
-      <c r="H146" s="107"/>
-      <c r="I146" s="107" t="s">
-        <v>267</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H146" s="107" t="s">
+        <v>462</v>
+      </c>
+      <c r="I146" s="107"/>
       <c r="J146" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K146" s="107" t="s">
-        <v>201</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K146" s="107"/>
       <c r="L146" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M146" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N146" s="111"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A147" s="106" t="s">
         <v>172</v>
       </c>
       <c r="B147" s="107"/>
       <c r="C147" s="108">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D147" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E147" s="108">
         <v>2</v>
       </c>
       <c r="F147" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G147" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H147" s="107" t="s">
-        <v>459</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="H147" s="107"/>
       <c r="I147" s="107"/>
       <c r="J147" s="109" t="s">
         <v>154</v>
@@ -8672,32 +8662,34 @@
       </c>
       <c r="N147" s="111"/>
     </row>
-    <row r="148" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="106" t="s">
-        <v>172</v>
-      </c>
-      <c r="B148" s="107"/>
+        <v>177</v>
+      </c>
+      <c r="B148" s="107" t="s">
+        <v>284</v>
+      </c>
       <c r="C148" s="108">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D148" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E148" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G148" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H148" s="107" t="s">
-        <v>460</v>
-      </c>
-      <c r="I148" s="107"/>
+        <v>183</v>
+      </c>
+      <c r="H148" s="107"/>
+      <c r="I148" s="107" t="s">
+        <v>390</v>
+      </c>
       <c r="J148" s="109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K148" s="107"/>
       <c r="L148" s="109" t="s">
@@ -8708,27 +8700,29 @@
       </c>
       <c r="N148" s="111"/>
     </row>
-    <row r="149" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="106" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B149" s="107"/>
       <c r="C149" s="108">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D149" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E149" s="108">
         <v>2</v>
       </c>
       <c r="F149" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G149" s="107" t="s">
-        <v>388</v>
-      </c>
-      <c r="H149" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H149" s="107" t="s">
+        <v>463</v>
+      </c>
       <c r="I149" s="107"/>
       <c r="J149" s="109" t="s">
         <v>154</v>
@@ -8742,38 +8736,36 @@
       </c>
       <c r="N149" s="111"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A150" s="106" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B150" s="107"/>
       <c r="C150" s="108">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D150" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E150" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G150" s="107" t="s">
-        <v>70</v>
-      </c>
-      <c r="H150" s="107"/>
-      <c r="I150" s="107" t="s">
-        <v>268</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="H150" s="107" t="s">
+        <v>464</v>
+      </c>
+      <c r="I150" s="107"/>
       <c r="J150" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K150" s="107" t="s">
-        <v>162</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K150" s="107"/>
       <c r="L150" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M150" s="110" t="b">
         <v>1</v>
@@ -8782,14 +8774,14 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="106" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B151" s="107"/>
       <c r="C151" s="108">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D151" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E151" s="108">
         <v>2</v>
@@ -8798,10 +8790,10 @@
         <v>178</v>
       </c>
       <c r="G151" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H151" s="107" t="s">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="I151" s="107"/>
       <c r="J151" s="109" t="s">
@@ -8816,29 +8808,27 @@
       </c>
       <c r="N151" s="111"/>
     </row>
-    <row r="152" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="106" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B152" s="107"/>
       <c r="C152" s="108">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D152" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E152" s="108">
         <v>2</v>
       </c>
       <c r="F152" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G152" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H152" s="107" t="s">
-        <v>462</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="H152" s="107"/>
       <c r="I152" s="107"/>
       <c r="J152" s="109" t="s">
         <v>154</v>
@@ -8852,16 +8842,16 @@
       </c>
       <c r="N152" s="111"/>
     </row>
-    <row r="153" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="106" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B153" s="107"/>
       <c r="C153" s="108">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D153" s="108">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E153" s="108">
         <v>2</v>
@@ -8870,7 +8860,7 @@
         <v>155</v>
       </c>
       <c r="G153" s="107" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
       <c r="H153" s="107"/>
       <c r="I153" s="107"/>
@@ -8890,11 +8880,9 @@
       <c r="A154" s="106" t="s">
         <v>177</v>
       </c>
-      <c r="B154" s="107" t="s">
-        <v>284</v>
-      </c>
+      <c r="B154" s="107"/>
       <c r="C154" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154" s="108">
         <v>1</v>
@@ -8906,18 +8894,20 @@
         <v>155</v>
       </c>
       <c r="G154" s="107" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="H154" s="107"/>
       <c r="I154" s="107" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J154" s="109" t="s">
         <v>153</v>
       </c>
-      <c r="K154" s="107"/>
+      <c r="K154" s="107" t="s">
+        <v>392</v>
+      </c>
       <c r="L154" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M154" s="110" t="b">
         <v>1</v>
@@ -8930,7 +8920,7 @@
       </c>
       <c r="B155" s="107"/>
       <c r="C155" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D155" s="108">
         <v>2</v>
@@ -8945,7 +8935,7 @@
         <v>351</v>
       </c>
       <c r="H155" s="107" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I155" s="107"/>
       <c r="J155" s="109" t="s">
@@ -8960,13 +8950,13 @@
       </c>
       <c r="N155" s="111"/>
     </row>
-    <row r="156" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B156" s="107"/>
       <c r="C156" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" s="108">
         <v>3</v>
@@ -8978,10 +8968,10 @@
         <v>178</v>
       </c>
       <c r="G156" s="107" t="s">
-        <v>208</v>
+        <v>433</v>
       </c>
       <c r="H156" s="107" t="s">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="I156" s="107"/>
       <c r="J156" s="109" t="s">
@@ -8996,13 +8986,13 @@
       </c>
       <c r="N156" s="111"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A157" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B157" s="107"/>
       <c r="C157" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" s="108">
         <v>4</v>
@@ -9011,14 +9001,12 @@
         <v>2</v>
       </c>
       <c r="F157" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G157" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H157" s="107" t="s">
-        <v>432</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="H157" s="107"/>
       <c r="I157" s="107"/>
       <c r="J157" s="109" t="s">
         <v>154</v>
@@ -9038,28 +9026,32 @@
       </c>
       <c r="B158" s="107"/>
       <c r="C158" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" s="108">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E158" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F158" s="107" t="s">
         <v>155</v>
       </c>
       <c r="G158" s="107" t="s">
-        <v>489</v>
+        <v>393</v>
       </c>
       <c r="H158" s="107"/>
-      <c r="I158" s="107"/>
+      <c r="I158" s="107" t="s">
+        <v>394</v>
+      </c>
       <c r="J158" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K158" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K158" s="107" t="s">
+        <v>165</v>
+      </c>
       <c r="L158" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M158" s="110" t="b">
         <v>1</v>
@@ -9072,21 +9064,23 @@
       </c>
       <c r="B159" s="107"/>
       <c r="C159" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D159" s="108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E159" s="108">
         <v>2</v>
       </c>
       <c r="F159" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G159" s="107" t="s">
-        <v>488</v>
-      </c>
-      <c r="H159" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H159" s="107" t="s">
+        <v>466</v>
+      </c>
       <c r="I159" s="107"/>
       <c r="J159" s="109" t="s">
         <v>154</v>
@@ -9106,61 +9100,57 @@
       </c>
       <c r="B160" s="107"/>
       <c r="C160" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D160" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E160" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G160" s="107" t="s">
-        <v>71</v>
-      </c>
-      <c r="H160" s="107"/>
-      <c r="I160" s="107" t="s">
-        <v>391</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H160" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I160" s="107"/>
       <c r="J160" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K160" s="107" t="s">
-        <v>392</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K160" s="107"/>
       <c r="L160" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M160" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N160" s="111"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A161" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B161" s="107"/>
       <c r="C161" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D161" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E161" s="108">
         <v>2</v>
       </c>
       <c r="F161" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G161" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H161" s="107" t="s">
-        <v>465</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="H161" s="107"/>
       <c r="I161" s="107"/>
       <c r="J161" s="109" t="s">
         <v>154</v>
@@ -9180,57 +9170,61 @@
       </c>
       <c r="B162" s="107"/>
       <c r="C162" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D162" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E162" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G162" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H162" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I162" s="107"/>
+        <v>396</v>
+      </c>
+      <c r="H162" s="107"/>
+      <c r="I162" s="107" t="s">
+        <v>397</v>
+      </c>
       <c r="J162" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K162" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K162" s="107" t="s">
+        <v>398</v>
+      </c>
       <c r="L162" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M162" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N162" s="111"/>
     </row>
-    <row r="163" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B163" s="107"/>
       <c r="C163" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D163" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E163" s="108">
         <v>2</v>
       </c>
       <c r="F163" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G163" s="107" t="s">
-        <v>485</v>
-      </c>
-      <c r="H163" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H163" s="107" t="s">
+        <v>467</v>
+      </c>
       <c r="I163" s="107"/>
       <c r="J163" s="109" t="s">
         <v>154</v>
@@ -9250,61 +9244,57 @@
       </c>
       <c r="B164" s="107"/>
       <c r="C164" s="108">
+        <v>4</v>
+      </c>
+      <c r="D164" s="108">
         <v>3</v>
       </c>
-      <c r="D164" s="108">
-        <v>1</v>
-      </c>
       <c r="E164" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G164" s="107" t="s">
-        <v>393</v>
-      </c>
-      <c r="H164" s="107"/>
-      <c r="I164" s="107" t="s">
-        <v>394</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H164" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I164" s="107"/>
       <c r="J164" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K164" s="107" t="s">
-        <v>165</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K164" s="107"/>
       <c r="L164" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M164" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N164" s="111"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A165" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B165" s="107"/>
       <c r="C165" s="108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E165" s="108">
         <v>2</v>
       </c>
       <c r="F165" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G165" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H165" s="107" t="s">
-        <v>466</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="H165" s="107"/>
       <c r="I165" s="107"/>
       <c r="J165" s="109" t="s">
         <v>154</v>
@@ -9324,57 +9314,61 @@
       </c>
       <c r="B166" s="107"/>
       <c r="C166" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D166" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G166" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H166" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I166" s="107"/>
+        <v>400</v>
+      </c>
+      <c r="H166" s="107"/>
+      <c r="I166" s="107" t="s">
+        <v>260</v>
+      </c>
       <c r="J166" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K166" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K166" s="107" t="s">
+        <v>199</v>
+      </c>
       <c r="L166" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M166" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N166" s="111"/>
     </row>
-    <row r="167" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B167" s="107"/>
       <c r="C167" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D167" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E167" s="108">
         <v>2</v>
       </c>
       <c r="F167" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G167" s="107" t="s">
-        <v>395</v>
-      </c>
-      <c r="H167" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H167" s="107" t="s">
+        <v>468</v>
+      </c>
       <c r="I167" s="107"/>
       <c r="J167" s="109" t="s">
         <v>154</v>
@@ -9394,61 +9388,57 @@
       </c>
       <c r="B168" s="107"/>
       <c r="C168" s="108">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D168" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E168" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G168" s="107" t="s">
-        <v>396</v>
-      </c>
-      <c r="H168" s="107"/>
-      <c r="I168" s="107" t="s">
-        <v>397</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H168" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I168" s="107"/>
       <c r="J168" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K168" s="107" t="s">
-        <v>398</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K168" s="107"/>
       <c r="L168" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M168" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N168" s="111"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A169" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B169" s="107"/>
       <c r="C169" s="108">
+        <v>5</v>
+      </c>
+      <c r="D169" s="108">
         <v>4</v>
       </c>
-      <c r="D169" s="108">
-        <v>2</v>
-      </c>
       <c r="E169" s="108">
         <v>2</v>
       </c>
       <c r="F169" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G169" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H169" s="107" t="s">
-        <v>467</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="H169" s="107"/>
       <c r="I169" s="107"/>
       <c r="J169" s="109" t="s">
         <v>154</v>
@@ -9468,57 +9458,61 @@
       </c>
       <c r="B170" s="107"/>
       <c r="C170" s="108">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D170" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F170" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G170" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H170" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I170" s="107"/>
+        <v>75</v>
+      </c>
+      <c r="H170" s="107"/>
+      <c r="I170" s="107" t="s">
+        <v>402</v>
+      </c>
       <c r="J170" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="K170" s="107"/>
+      <c r="K170" s="107" t="s">
+        <v>403</v>
+      </c>
       <c r="L170" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M170" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N170" s="111"/>
     </row>
-    <row r="171" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B171" s="107"/>
       <c r="C171" s="108">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D171" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E171" s="108">
         <v>2</v>
       </c>
       <c r="F171" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G171" s="107" t="s">
-        <v>399</v>
-      </c>
-      <c r="H171" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H171" s="107" t="s">
+        <v>469</v>
+      </c>
       <c r="I171" s="107"/>
       <c r="J171" s="109" t="s">
         <v>154</v>
@@ -9538,32 +9532,30 @@
       </c>
       <c r="B172" s="107"/>
       <c r="C172" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D172" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E172" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F172" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G172" s="107" t="s">
-        <v>400</v>
-      </c>
-      <c r="H172" s="107"/>
-      <c r="I172" s="107" t="s">
-        <v>260</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H172" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I172" s="107"/>
       <c r="J172" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K172" s="107" t="s">
-        <v>199</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K172" s="107"/>
       <c r="L172" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M172" s="110" t="b">
         <v>1</v>
@@ -9576,23 +9568,21 @@
       </c>
       <c r="B173" s="107"/>
       <c r="C173" s="108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D173" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E173" s="108">
         <v>2</v>
       </c>
       <c r="F173" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G173" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H173" s="107" t="s">
-        <v>468</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="H173" s="107"/>
       <c r="I173" s="107"/>
       <c r="J173" s="109" t="s">
         <v>154</v>
@@ -9608,30 +9598,32 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" s="106" t="s">
-        <v>177</v>
-      </c>
-      <c r="B174" s="107"/>
+        <v>171</v>
+      </c>
+      <c r="B174" s="107" t="s">
+        <v>285</v>
+      </c>
       <c r="C174" s="108">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D174" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E174" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F174" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G174" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H174" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I174" s="107"/>
+        <v>183</v>
+      </c>
+      <c r="H174" s="107"/>
+      <c r="I174" s="107" t="s">
+        <v>405</v>
+      </c>
       <c r="J174" s="109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K174" s="107"/>
       <c r="L174" s="109" t="s">
@@ -9644,25 +9636,27 @@
     </row>
     <row r="175" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A175" s="106" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B175" s="107"/>
       <c r="C175" s="108">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D175" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E175" s="108">
         <v>2</v>
       </c>
       <c r="F175" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G175" s="107" t="s">
-        <v>401</v>
-      </c>
-      <c r="H175" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H175" s="107" t="s">
+        <v>470</v>
+      </c>
       <c r="I175" s="107"/>
       <c r="J175" s="109" t="s">
         <v>154</v>
@@ -9678,36 +9672,34 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" s="106" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B176" s="107"/>
       <c r="C176" s="108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D176" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E176" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G176" s="107" t="s">
-        <v>75</v>
-      </c>
-      <c r="H176" s="107"/>
-      <c r="I176" s="107" t="s">
-        <v>402</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="H176" s="107" t="s">
+        <v>490</v>
+      </c>
+      <c r="I176" s="107"/>
       <c r="J176" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="K176" s="107" t="s">
-        <v>403</v>
-      </c>
+      <c r="K176" s="107"/>
       <c r="L176" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M176" s="110" t="b">
         <v>1</v>
@@ -9716,14 +9708,14 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" s="106" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B177" s="107"/>
       <c r="C177" s="108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D177" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E177" s="108">
         <v>2</v>
@@ -9732,10 +9724,10 @@
         <v>178</v>
       </c>
       <c r="G177" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H177" s="107" t="s">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="I177" s="107"/>
       <c r="J177" s="109" t="s">
@@ -9750,29 +9742,27 @@
       </c>
       <c r="N177" s="111"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:14" ht="30" x14ac:dyDescent="0.2">
       <c r="A178" s="106" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B178" s="107"/>
       <c r="C178" s="108">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D178" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E178" s="108">
         <v>2</v>
       </c>
       <c r="F178" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G178" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H178" s="107" t="s">
-        <v>432</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="H178" s="107"/>
       <c r="I178" s="107"/>
       <c r="J178" s="109" t="s">
         <v>154</v>
@@ -9788,32 +9778,36 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" s="106" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B179" s="107"/>
       <c r="C179" s="108">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D179" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E179" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F179" s="107" t="s">
         <v>155</v>
       </c>
       <c r="G179" s="107" t="s">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="H179" s="107"/>
-      <c r="I179" s="107"/>
+      <c r="I179" s="107" t="s">
+        <v>174</v>
+      </c>
       <c r="J179" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K179" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K179" s="107" t="s">
+        <v>235</v>
+      </c>
       <c r="L179" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M179" s="110" t="b">
         <v>1</v>
@@ -9824,30 +9818,28 @@
       <c r="A180" s="106" t="s">
         <v>171</v>
       </c>
-      <c r="B180" s="107" t="s">
-        <v>285</v>
-      </c>
+      <c r="B180" s="107"/>
       <c r="C180" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G180" s="107" t="s">
-        <v>183</v>
-      </c>
-      <c r="H180" s="107"/>
-      <c r="I180" s="107" t="s">
-        <v>405</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="H180" s="107" t="s">
+        <v>441</v>
+      </c>
+      <c r="I180" s="107"/>
       <c r="J180" s="109" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K180" s="107"/>
       <c r="L180" s="109" t="s">
@@ -9858,16 +9850,16 @@
       </c>
       <c r="N180" s="111"/>
     </row>
-    <row r="181" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="106" t="s">
         <v>171</v>
       </c>
       <c r="B181" s="107"/>
       <c r="C181" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D181" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E181" s="108">
         <v>2</v>
@@ -9876,10 +9868,10 @@
         <v>178</v>
       </c>
       <c r="G181" s="107" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="H181" s="107" t="s">
-        <v>470</v>
+        <v>432</v>
       </c>
       <c r="I181" s="107"/>
       <c r="J181" s="109" t="s">
@@ -9900,23 +9892,21 @@
       </c>
       <c r="B182" s="107"/>
       <c r="C182" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" s="108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E182" s="108">
         <v>2</v>
       </c>
       <c r="F182" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G182" s="107" t="s">
-        <v>208</v>
-      </c>
-      <c r="H182" s="107" t="s">
-        <v>490</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="H182" s="107"/>
       <c r="I182" s="107"/>
       <c r="J182" s="109" t="s">
         <v>154</v>
@@ -9936,57 +9926,61 @@
       </c>
       <c r="B183" s="107"/>
       <c r="C183" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D183" s="108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E183" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F183" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G183" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H183" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I183" s="107"/>
+        <v>79</v>
+      </c>
+      <c r="H183" s="107"/>
+      <c r="I183" s="107" t="s">
+        <v>174</v>
+      </c>
       <c r="J183" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K183" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K183" s="107" t="s">
+        <v>407</v>
+      </c>
       <c r="L183" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M183" s="110" t="b">
         <v>1</v>
       </c>
       <c r="N183" s="111"/>
     </row>
-    <row r="184" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" s="106" t="s">
         <v>171</v>
       </c>
       <c r="B184" s="107"/>
       <c r="C184" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D184" s="108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E184" s="108">
         <v>2</v>
       </c>
       <c r="F184" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G184" s="107" t="s">
-        <v>483</v>
-      </c>
-      <c r="H184" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H184" s="107" t="s">
+        <v>441</v>
+      </c>
       <c r="I184" s="107"/>
       <c r="J184" s="109" t="s">
         <v>154</v>
@@ -10006,32 +10000,30 @@
       </c>
       <c r="B185" s="107"/>
       <c r="C185" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D185" s="108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E185" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F185" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G185" s="107" t="s">
-        <v>78</v>
-      </c>
-      <c r="H185" s="107"/>
-      <c r="I185" s="107" t="s">
-        <v>174</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H185" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I185" s="107"/>
       <c r="J185" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K185" s="107" t="s">
-        <v>235</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K185" s="107"/>
       <c r="L185" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M185" s="110" t="b">
         <v>1</v>
@@ -10044,23 +10036,21 @@
       </c>
       <c r="B186" s="107"/>
       <c r="C186" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D186" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E186" s="108">
         <v>2</v>
       </c>
       <c r="F186" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G186" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H186" s="107" t="s">
-        <v>441</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="H186" s="107"/>
       <c r="I186" s="107"/>
       <c r="J186" s="109" t="s">
         <v>154</v>
@@ -10080,30 +10070,32 @@
       </c>
       <c r="B187" s="107"/>
       <c r="C187" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D187" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E187" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F187" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G187" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H187" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I187" s="107"/>
+        <v>84</v>
+      </c>
+      <c r="H187" s="107"/>
+      <c r="I187" s="107" t="s">
+        <v>174</v>
+      </c>
       <c r="J187" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K187" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K187" s="107" t="s">
+        <v>408</v>
+      </c>
       <c r="L187" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M187" s="110" t="b">
         <v>1</v>
@@ -10116,21 +10108,23 @@
       </c>
       <c r="B188" s="107"/>
       <c r="C188" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D188" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E188" s="108">
         <v>2</v>
       </c>
       <c r="F188" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G188" s="107" t="s">
-        <v>406</v>
-      </c>
-      <c r="H188" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H188" s="107" t="s">
+        <v>441</v>
+      </c>
       <c r="I188" s="107"/>
       <c r="J188" s="109" t="s">
         <v>154</v>
@@ -10150,32 +10144,30 @@
       </c>
       <c r="B189" s="107"/>
       <c r="C189" s="108">
+        <v>4</v>
+      </c>
+      <c r="D189" s="108">
         <v>3</v>
       </c>
-      <c r="D189" s="108">
-        <v>1</v>
-      </c>
       <c r="E189" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G189" s="107" t="s">
-        <v>79</v>
-      </c>
-      <c r="H189" s="107"/>
-      <c r="I189" s="107" t="s">
-        <v>174</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H189" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I189" s="107"/>
       <c r="J189" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K189" s="107" t="s">
-        <v>407</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K189" s="107"/>
       <c r="L189" s="109" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M189" s="110" t="b">
         <v>1</v>
@@ -10188,23 +10180,21 @@
       </c>
       <c r="B190" s="107"/>
       <c r="C190" s="108">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D190" s="108">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E190" s="108">
         <v>2</v>
       </c>
       <c r="F190" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G190" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H190" s="107" t="s">
-        <v>441</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="H190" s="107"/>
       <c r="I190" s="107"/>
       <c r="J190" s="109" t="s">
         <v>154</v>
@@ -10224,30 +10214,32 @@
       </c>
       <c r="B191" s="107"/>
       <c r="C191" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D191" s="108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E191" s="108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F191" s="107" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G191" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H191" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I191" s="107"/>
+        <v>89</v>
+      </c>
+      <c r="H191" s="107"/>
+      <c r="I191" s="107" t="s">
+        <v>174</v>
+      </c>
       <c r="J191" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K191" s="107"/>
+        <v>153</v>
+      </c>
+      <c r="K191" s="107" t="s">
+        <v>409</v>
+      </c>
       <c r="L191" s="109" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="M191" s="110" t="b">
         <v>1</v>
@@ -10260,21 +10252,23 @@
       </c>
       <c r="B192" s="107"/>
       <c r="C192" s="108">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D192" s="108">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E192" s="108">
         <v>2</v>
       </c>
       <c r="F192" s="107" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G192" s="107" t="s">
-        <v>406</v>
-      </c>
-      <c r="H192" s="107"/>
+        <v>351</v>
+      </c>
+      <c r="H192" s="107" t="s">
+        <v>441</v>
+      </c>
       <c r="I192" s="107"/>
       <c r="J192" s="109" t="s">
         <v>154</v>
@@ -10294,313 +10288,95 @@
       </c>
       <c r="B193" s="107"/>
       <c r="C193" s="108">
+        <v>5</v>
+      </c>
+      <c r="D193" s="108">
+        <v>3</v>
+      </c>
+      <c r="E193" s="108">
+        <v>2</v>
+      </c>
+      <c r="F193" s="107" t="s">
+        <v>178</v>
+      </c>
+      <c r="G193" s="107" t="s">
+        <v>433</v>
+      </c>
+      <c r="H193" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="I193" s="107"/>
+      <c r="J193" s="109" t="s">
+        <v>154</v>
+      </c>
+      <c r="K193" s="107"/>
+      <c r="L193" s="109" t="s">
+        <v>154</v>
+      </c>
+      <c r="M193" s="110" t="b">
+        <v>1</v>
+      </c>
+      <c r="N193" s="111"/>
+    </row>
+    <row r="194" spans="1:14" ht="30" x14ac:dyDescent="0.2">
+      <c r="A194" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="B194" s="113"/>
+      <c r="C194" s="114">
+        <v>5</v>
+      </c>
+      <c r="D194" s="114">
         <v>4</v>
       </c>
-      <c r="D193" s="108">
-        <v>1</v>
-      </c>
-      <c r="E193" s="108">
-        <v>1</v>
-      </c>
-      <c r="F193" s="107" t="s">
+      <c r="E194" s="114">
+        <v>2</v>
+      </c>
+      <c r="F194" s="113" t="s">
         <v>155</v>
       </c>
-      <c r="G193" s="107" t="s">
-        <v>84</v>
-      </c>
-      <c r="H193" s="107"/>
-      <c r="I193" s="107" t="s">
-        <v>174</v>
-      </c>
-      <c r="J193" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K193" s="107" t="s">
-        <v>408</v>
-      </c>
-      <c r="L193" s="109" t="s">
-        <v>144</v>
-      </c>
-      <c r="M193" s="110" t="b">
-        <v>1</v>
-      </c>
-      <c r="N193" s="111"/>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A194" s="106" t="s">
-        <v>171</v>
-      </c>
-      <c r="B194" s="107"/>
-      <c r="C194" s="108">
-        <v>4</v>
-      </c>
-      <c r="D194" s="108">
-        <v>2</v>
-      </c>
-      <c r="E194" s="108">
-        <v>2</v>
-      </c>
-      <c r="F194" s="107" t="s">
-        <v>178</v>
-      </c>
-      <c r="G194" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H194" s="107" t="s">
-        <v>441</v>
-      </c>
-      <c r="I194" s="107"/>
-      <c r="J194" s="109" t="s">
+      <c r="G194" s="113" t="s">
+        <v>484</v>
+      </c>
+      <c r="H194" s="113"/>
+      <c r="I194" s="113"/>
+      <c r="J194" s="115" t="s">
         <v>154</v>
       </c>
-      <c r="K194" s="107"/>
-      <c r="L194" s="109" t="s">
+      <c r="K194" s="113"/>
+      <c r="L194" s="115" t="s">
         <v>154</v>
       </c>
-      <c r="M194" s="110" t="b">
-        <v>1</v>
-      </c>
-      <c r="N194" s="111"/>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A195" s="106" t="s">
-        <v>171</v>
-      </c>
-      <c r="B195" s="107"/>
-      <c r="C195" s="108">
-        <v>4</v>
-      </c>
-      <c r="D195" s="108">
-        <v>3</v>
-      </c>
-      <c r="E195" s="108">
-        <v>2</v>
-      </c>
-      <c r="F195" s="107" t="s">
-        <v>178</v>
-      </c>
-      <c r="G195" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H195" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I195" s="107"/>
-      <c r="J195" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K195" s="107"/>
-      <c r="L195" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="M195" s="110" t="b">
-        <v>1</v>
-      </c>
-      <c r="N195" s="111"/>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A196" s="106" t="s">
-        <v>171</v>
-      </c>
-      <c r="B196" s="107"/>
-      <c r="C196" s="108">
-        <v>4</v>
-      </c>
-      <c r="D196" s="108">
-        <v>4</v>
-      </c>
-      <c r="E196" s="108">
-        <v>2</v>
-      </c>
-      <c r="F196" s="107" t="s">
-        <v>155</v>
-      </c>
-      <c r="G196" s="107" t="s">
-        <v>406</v>
-      </c>
-      <c r="H196" s="107"/>
-      <c r="I196" s="107"/>
-      <c r="J196" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K196" s="107"/>
-      <c r="L196" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="M196" s="110" t="b">
-        <v>1</v>
-      </c>
-      <c r="N196" s="111"/>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A197" s="106" t="s">
-        <v>171</v>
-      </c>
-      <c r="B197" s="107"/>
-      <c r="C197" s="108">
-        <v>5</v>
-      </c>
-      <c r="D197" s="108">
-        <v>1</v>
-      </c>
-      <c r="E197" s="108">
-        <v>1</v>
-      </c>
-      <c r="F197" s="107" t="s">
-        <v>155</v>
-      </c>
-      <c r="G197" s="107" t="s">
-        <v>89</v>
-      </c>
-      <c r="H197" s="107"/>
-      <c r="I197" s="107" t="s">
-        <v>174</v>
-      </c>
-      <c r="J197" s="109" t="s">
-        <v>153</v>
-      </c>
-      <c r="K197" s="107" t="s">
-        <v>409</v>
-      </c>
-      <c r="L197" s="109" t="s">
-        <v>144</v>
-      </c>
-      <c r="M197" s="110" t="b">
-        <v>1</v>
-      </c>
-      <c r="N197" s="111"/>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A198" s="106" t="s">
-        <v>171</v>
-      </c>
-      <c r="B198" s="107"/>
-      <c r="C198" s="108">
-        <v>5</v>
-      </c>
-      <c r="D198" s="108">
-        <v>2</v>
-      </c>
-      <c r="E198" s="108">
-        <v>2</v>
-      </c>
-      <c r="F198" s="107" t="s">
-        <v>178</v>
-      </c>
-      <c r="G198" s="107" t="s">
-        <v>351</v>
-      </c>
-      <c r="H198" s="107" t="s">
-        <v>441</v>
-      </c>
-      <c r="I198" s="107"/>
-      <c r="J198" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K198" s="107"/>
-      <c r="L198" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="M198" s="110" t="b">
-        <v>1</v>
-      </c>
-      <c r="N198" s="111"/>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A199" s="106" t="s">
-        <v>171</v>
-      </c>
-      <c r="B199" s="107"/>
-      <c r="C199" s="108">
-        <v>5</v>
-      </c>
-      <c r="D199" s="108">
-        <v>3</v>
-      </c>
-      <c r="E199" s="108">
-        <v>2</v>
-      </c>
-      <c r="F199" s="107" t="s">
-        <v>178</v>
-      </c>
-      <c r="G199" s="107" t="s">
-        <v>433</v>
-      </c>
-      <c r="H199" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="I199" s="107"/>
-      <c r="J199" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="K199" s="107"/>
-      <c r="L199" s="109" t="s">
-        <v>154</v>
-      </c>
-      <c r="M199" s="110" t="b">
-        <v>1</v>
-      </c>
-      <c r="N199" s="111"/>
-    </row>
-    <row r="200" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A200" s="112" t="s">
-        <v>171</v>
-      </c>
-      <c r="B200" s="113"/>
-      <c r="C200" s="114">
-        <v>5</v>
-      </c>
-      <c r="D200" s="114">
-        <v>4</v>
-      </c>
-      <c r="E200" s="114">
-        <v>2</v>
-      </c>
-      <c r="F200" s="113" t="s">
-        <v>155</v>
-      </c>
-      <c r="G200" s="113" t="s">
-        <v>484</v>
-      </c>
-      <c r="H200" s="113"/>
-      <c r="I200" s="113"/>
-      <c r="J200" s="115" t="s">
-        <v>154</v>
-      </c>
-      <c r="K200" s="113"/>
-      <c r="L200" s="115" t="s">
-        <v>154</v>
-      </c>
-      <c r="M200" s="116" t="b">
-        <v>1</v>
-      </c>
-      <c r="N200" s="117"/>
+      <c r="M194" s="116" t="b">
+        <v>1</v>
+      </c>
+      <c r="N194" s="117"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
-  <conditionalFormatting sqref="J2:J91">
+  <conditionalFormatting sqref="J2:J85">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="plan"/>
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="available"/>
     <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="shortage"/>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="6">
-    <dataValidation type="whole" sqref="E2:E200" xr:uid="{8B816CBE-1163-BF43-9CD2-B0BAD7AAFA9B}">
+  <dataValidations count="6">
+    <dataValidation type="whole" sqref="E2:E194" xr:uid="{8B816CBE-1163-BF43-9CD2-B0BAD7AAFA9B}">
       <formula1>1</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="M2:M200" xr:uid="{566A8967-E8B0-614C-A1DE-0E0E8222DB5B}">
+    <dataValidation type="list" sqref="M2:M194" xr:uid="{566A8967-E8B0-614C-A1DE-0E0E8222DB5B}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L200" xr:uid="{C14E220C-E4EF-6341-B5F4-F621FC444A92}">
+    <dataValidation type="list" sqref="L2:L194" xr:uid="{C14E220C-E4EF-6341-B5F4-F621FC444A92}">
       <formula1>"none,label,data,highlight,all"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J200" xr:uid="{2D79B2FD-4905-7144-98C6-7F64A69AD11D}">
+    <dataValidation type="list" sqref="J2:J194" xr:uid="{2D79B2FD-4905-7144-98C6-7F64A69AD11D}">
       <formula1>"none,plan,available,avai,shortage"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F200" xr:uid="{7809C96B-EC76-034B-BF27-B6E5DB975334}">
+    <dataValidation type="list" sqref="F2:F194" xr:uid="{7809C96B-EC76-034B-BF27-B6E5DB975334}">
       <formula1>"text,text-inline,label-data,grid-item"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A2:A200" xr:uid="{0DDB31BF-3C3C-004F-80CD-737EA3BCAE24}">
+    <dataValidation type="list" sqref="A2:A194" xr:uid="{0DDB31BF-3C3C-004F-80CD-737EA3BCAE24}">
       <formula1>"index,delivery,cps,pse,sd,aic,tde"</formula1>
     </dataValidation>
   </dataValidations>

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miiintra/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A2EA2D-7A6B-214D-8B9C-696BA90B0913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B92EF83-FF87-7B4B-A80E-65200AFE4DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="44800" windowHeight="22640" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" firstSheet="11" activeTab="20" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="17" r:id="rId1"/>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="B4">
         <f>IF(PSE!C4&gt;0,PSE!C4,"")</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <f>IF(PSE!D4&gt;0,PSE!D4,"")</f>
@@ -10611,51 +10611,51 @@
       </c>
       <c r="E4">
         <f>IF(PSE!F4&gt;0,PSE!F4,"")</f>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4">
         <f>IF(PSE!G4&gt;0,PSE!G4,"")</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G4">
         <f>IF(PSE!H4&gt;0,PSE!H4,"")</f>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H4">
         <f>IF(PSE!I4&gt;0,PSE!I4,"")</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I4">
         <f>IF(PSE!J4&gt;0,PSE!J4,"")</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J4">
         <f>IF(PSE!K4&gt;0,PSE!K4,"")</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K4">
         <f>IF(PSE!L4&gt;0,PSE!L4,"")</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4">
         <f>IF(PSE!M4&gt;0,PSE!M4,"")</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4">
         <f>IF(PSE!N4&gt;0,PSE!N4,"")</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N4">
         <f>IF(PSE!O4&gt;0,PSE!O4,"")</f>
-        <v>24.625</v>
+        <v>23.774999999999999</v>
       </c>
       <c r="O4">
         <f>IF(PSE!P4&gt;0,PSE!P4,"")</f>
-        <v>23.425000000000001</v>
+        <v>22.574999999999999</v>
       </c>
       <c r="P4">
         <f>IF(PSE!Q4&gt;0,PSE!Q4,"")</f>
-        <v>22.75</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -10665,63 +10665,63 @@
       </c>
       <c r="B5">
         <f>IF(PSE!C11&gt;0,PSE!C11,"")</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <f>IF(PSE!D11&gt;0,PSE!D11,"")</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <f>IF(PSE!E11&gt;0,PSE!E11,"")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <f>IF(PSE!F11&gt;0,PSE!F11,"")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <f>IF(PSE!G11&gt;0,PSE!G11,"")</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G5">
         <f>IF(PSE!H11&gt;0,PSE!H11,"")</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H5">
         <f>IF(PSE!I11&gt;0,PSE!I11,"")</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I5">
         <f>IF(PSE!J11&gt;0,PSE!J11,"")</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <f>IF(PSE!K11&gt;0,PSE!K11,"")</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K5">
         <f>IF(PSE!L11&gt;0,PSE!L11,"")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5">
         <f>IF(PSE!M11&gt;0,PSE!M11,"")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M5">
         <f>IF(PSE!N11&gt;0,PSE!N11,"")</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N5">
         <f>IF(PSE!O11&gt;0,PSE!O11,"")</f>
-        <v>16.25</v>
+        <v>15.4</v>
       </c>
       <c r="O5">
         <f>IF(PSE!P11&gt;0,PSE!P11,"")</f>
-        <v>15.05</v>
+        <v>14.2</v>
       </c>
       <c r="P5">
         <f>IF(PSE!Q11&gt;0,PSE!Q11,"")</f>
-        <v>14.375</v>
+        <v>13.525</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -11057,63 +11057,63 @@
       </c>
       <c r="B14">
         <f>IF(PSE!C11&gt;0,PSE!C11,"")</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <f>IF(PSE!D11&gt;0,PSE!D11,"")</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <f>IF(PSE!E11&gt;0,PSE!E11,"")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14">
         <f>IF(PSE!F11&gt;0,PSE!F11,"")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14">
         <f>IF(PSE!G11&gt;0,PSE!G11,"")</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G14">
         <f>IF(PSE!H11&gt;0,PSE!H11,"")</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H14">
         <f>IF(PSE!I11&gt;0,PSE!I11,"")</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I14">
         <f>IF(PSE!J11&gt;0,PSE!J11,"")</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J14">
         <f>IF(PSE!K11&gt;0,PSE!K11,"")</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K14">
         <f>IF(PSE!L11&gt;0,PSE!L11,"")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L14">
         <f>IF(PSE!M11&gt;0,PSE!M11,"")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M14">
         <f>IF(PSE!N11&gt;0,PSE!N11,"")</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N14">
         <f>IF(PSE!O11&gt;0,PSE!O11,"")</f>
-        <v>16.25</v>
+        <v>15.4</v>
       </c>
       <c r="O14">
         <f>IF(PSE!P11&gt;0,PSE!P11,"")</f>
-        <v>15.05</v>
+        <v>14.2</v>
       </c>
       <c r="P14">
         <f>IF(PSE!Q11&gt;0,PSE!Q11,"")</f>
-        <v>14.375</v>
+        <v>13.525</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -11717,23 +11717,23 @@
       </c>
       <c r="B44">
         <f>IF(PSE!C34&gt;0,PSE!C34,"")</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44">
         <f>IF(PSE!D34&gt;0,PSE!D34,"")</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D44">
         <f>IF(PSE!E34&gt;0,PSE!E34,"")</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E44">
         <f>IF(PSE!F34&gt;0,PSE!F34,"")</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F44">
         <f>IF(PSE!G34&gt;0,PSE!G34,"")</f>
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -11743,23 +11743,23 @@
       </c>
       <c r="B45">
         <f>IF(PSE!C41&gt;0,PSE!C41,"")</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45">
         <f>IF(PSE!D41&gt;0,PSE!D41,"")</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D45">
         <f>IF(PSE!E41&gt;0,PSE!E41,"")</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E45">
         <f>IF(PSE!F41&gt;0,PSE!F41,"")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F45">
         <f>IF(PSE!G41&gt;0,PSE!G41,"")</f>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -12264,63 +12264,63 @@
       </c>
       <c r="B63">
         <f>PSE!C73</f>
-        <v>38.93</v>
+        <v>38.43</v>
       </c>
       <c r="C63">
         <f>PSE!D73</f>
-        <v>40.28</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="D63">
         <f>PSE!E73</f>
-        <v>36.414999999999999</v>
+        <v>35.564999999999998</v>
       </c>
       <c r="E63">
         <f>PSE!F73</f>
-        <v>35.39</v>
+        <v>34.54</v>
       </c>
       <c r="F63">
         <f>PSE!G73</f>
-        <v>35.924999999999997</v>
+        <v>34.075000000000003</v>
       </c>
       <c r="G63">
         <f>PSE!H73</f>
-        <v>34.15</v>
+        <v>31.6</v>
       </c>
       <c r="H63">
         <f>PSE!I73</f>
-        <v>31.074999999999999</v>
+        <v>28.875</v>
       </c>
       <c r="I63">
         <f>PSE!J73</f>
-        <v>31.05</v>
+        <v>28.4</v>
       </c>
       <c r="J63">
         <f>PSE!K73</f>
-        <v>30.65</v>
+        <v>28</v>
       </c>
       <c r="K63">
         <f>PSE!L73</f>
-        <v>19.350000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="L63">
         <f>PSE!M73</f>
-        <v>19.350000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="M63">
         <f>PSE!N73</f>
-        <v>20.225000000000001</v>
+        <v>18.875</v>
       </c>
       <c r="N63">
         <f>PSE!O73</f>
-        <v>17.625</v>
+        <v>16.774999999999999</v>
       </c>
       <c r="O63">
         <f>PSE!P73</f>
-        <v>16.425000000000001</v>
+        <v>15.574999999999999</v>
       </c>
       <c r="P63">
         <f>PSE!Q73</f>
-        <v>15.75</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="64" spans="1:16" s="57" customFormat="1" x14ac:dyDescent="0.2">
@@ -12329,63 +12329,63 @@
       </c>
       <c r="B64" s="58">
         <f>B62-B63</f>
-        <v>2.0700000000000003</v>
+        <v>2.5700000000000003</v>
       </c>
       <c r="C64" s="58">
         <f t="shared" ref="C64:P64" si="2">C62-C63</f>
-        <v>0.71999999999999886</v>
+        <v>1.3699999999999974</v>
       </c>
       <c r="D64" s="58">
         <f t="shared" si="2"/>
-        <v>4.5850000000000009</v>
+        <v>5.4350000000000023</v>
       </c>
       <c r="E64" s="58">
         <f t="shared" si="2"/>
-        <v>5.6099999999999994</v>
+        <v>6.4600000000000009</v>
       </c>
       <c r="F64" s="58">
         <f t="shared" si="2"/>
-        <v>5.0750000000000028</v>
+        <v>6.9249999999999972</v>
       </c>
       <c r="G64" s="58">
         <f t="shared" si="2"/>
-        <v>6.8500000000000014</v>
+        <v>9.3999999999999986</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="2"/>
-        <v>9.9250000000000007</v>
+        <v>12.125</v>
       </c>
       <c r="I64" s="58">
         <f t="shared" si="2"/>
-        <v>9.9499999999999993</v>
+        <v>12.600000000000001</v>
       </c>
       <c r="J64" s="58">
         <f t="shared" si="2"/>
-        <v>10.350000000000001</v>
+        <v>13</v>
       </c>
       <c r="K64" s="58">
         <f t="shared" si="2"/>
-        <v>21.65</v>
+        <v>23.5</v>
       </c>
       <c r="L64" s="58">
         <f t="shared" si="2"/>
-        <v>21.65</v>
+        <v>23.5</v>
       </c>
       <c r="M64" s="58">
         <f t="shared" si="2"/>
-        <v>20.774999999999999</v>
+        <v>22.125</v>
       </c>
       <c r="N64" s="58">
         <f t="shared" si="2"/>
-        <v>23.375</v>
+        <v>24.225000000000001</v>
       </c>
       <c r="O64" s="58">
         <f t="shared" si="2"/>
-        <v>24.574999999999999</v>
+        <v>25.425000000000001</v>
       </c>
       <c r="P64" s="58">
         <f t="shared" si="2"/>
-        <v>25.25</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.2">
@@ -12417,23 +12417,23 @@
       </c>
       <c r="B66" s="50">
         <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
-        <v>94.004065040650403</v>
+        <v>92.378048780487802</v>
       </c>
       <c r="C66" s="50">
         <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
-        <v>85.743902439024396</v>
+        <v>81.475609756097569</v>
       </c>
       <c r="D66" s="50">
         <f>(AVERAGE(H63:J63)/AVERAGE(H62:J62))*100</f>
-        <v>75.426829268292678</v>
+        <v>69.32926829268294</v>
       </c>
       <c r="E66" s="50">
         <f>(AVERAGE(K63:M63)/AVERAGE(K62:M62))*100</f>
-        <v>47.906504065040657</v>
+        <v>43.800813008130078</v>
       </c>
       <c r="F66" s="50">
         <f>(AVERAGE(N63:P63)/AVERAGE(N62:P62))*100</f>
-        <v>40.487804878048777</v>
+        <v>38.414634146341456</v>
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
@@ -12505,63 +12505,63 @@
       </c>
       <c r="B152">
         <f>PSE!C6*100</f>
-        <v>95.69</v>
+        <v>94.65</v>
       </c>
       <c r="C152">
         <f>PSE!D6*100</f>
-        <v>98.5</v>
+        <v>97.15</v>
       </c>
       <c r="D152">
         <f>PSE!E6*100</f>
-        <v>90.45</v>
+        <v>88.68</v>
       </c>
       <c r="E152">
         <f>PSE!F6*100</f>
-        <v>88.160000000000011</v>
+        <v>86.39</v>
       </c>
       <c r="F152">
         <f>PSE!G6*100</f>
-        <v>88.649999999999991</v>
+        <v>84.789999999999992</v>
       </c>
       <c r="G152">
         <f>PSE!H6*100</f>
-        <v>85.05</v>
+        <v>79.739999999999995</v>
       </c>
       <c r="H152">
         <f>PSE!I6*100</f>
-        <v>79.010000000000005</v>
+        <v>74.429999999999993</v>
       </c>
       <c r="I152">
         <f>PSE!J6*100</f>
-        <v>78.959999999999994</v>
+        <v>73.440000000000012</v>
       </c>
       <c r="J152">
         <f>PSE!K6*100</f>
-        <v>78.44</v>
+        <v>72.92</v>
       </c>
       <c r="K152">
         <f>PSE!L6*100</f>
-        <v>54.900000000000006</v>
+        <v>51.04</v>
       </c>
       <c r="L152">
         <f>PSE!M6*100</f>
-        <v>54.900000000000006</v>
+        <v>51.04</v>
       </c>
       <c r="M152">
         <f>PSE!N6*100</f>
-        <v>56.720000000000006</v>
+        <v>53.910000000000004</v>
       </c>
       <c r="N152">
         <f>PSE!O6*100</f>
-        <v>51.300000000000004</v>
+        <v>49.53</v>
       </c>
       <c r="O152">
         <f>PSE!P6*100</f>
-        <v>48.8</v>
+        <v>47.03</v>
       </c>
       <c r="P152">
         <f>PSE!Q6*100</f>
-        <v>47.4</v>
+        <v>45.629999999999995</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="B153">
         <f>PSE!C7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C153">
         <f>PSE!D7</f>
@@ -12583,43 +12583,43 @@
       </c>
       <c r="E153">
         <f>PSE!F7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F153">
         <f>PSE!G7</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G153">
         <f>PSE!H7</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H153">
         <f>PSE!I7</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I153">
         <f>PSE!J7</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J153">
         <f>PSE!K7</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K153">
         <f>PSE!L7</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L153">
         <f>PSE!M7</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M153">
         <f>PSE!N7</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N153">
         <f>PSE!O7</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O153">
         <f>PSE!P7</f>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="P153">
         <f>PSE!Q7</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -12659,23 +12659,23 @@
       </c>
       <c r="B156">
         <f>PSE!C36*100</f>
-        <v>94.88</v>
+        <v>93.49</v>
       </c>
       <c r="C156">
         <f>PSE!D36*100</f>
-        <v>87.28</v>
+        <v>83.64</v>
       </c>
       <c r="D156">
         <f>PSE!E36*100</f>
-        <v>78.8</v>
+        <v>73.59</v>
       </c>
       <c r="E156">
         <f>PSE!F36*100</f>
-        <v>55.500000000000007</v>
+        <v>52</v>
       </c>
       <c r="F156">
         <f>PSE!G36*100</f>
-        <v>49.17</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -12685,23 +12685,23 @@
       </c>
       <c r="B157">
         <f>PSE!C37</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C157">
         <f>PSE!D37</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D157">
         <f>PSE!E37</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E157">
         <f>PSE!F37</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F157">
         <f>PSE!G37</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -12891,40 +12891,40 @@
         <v>46</v>
       </c>
       <c r="F4" s="7">
+        <v>45</v>
+      </c>
+      <c r="G4" s="7">
+        <v>49</v>
+      </c>
+      <c r="H4" s="7">
+        <v>48</v>
+      </c>
+      <c r="I4" s="7">
+        <v>50</v>
+      </c>
+      <c r="J4" s="7">
         <v>46</v>
       </c>
-      <c r="G4" s="13">
-        <v>55</v>
-      </c>
-      <c r="H4" s="13">
-        <v>54</v>
-      </c>
-      <c r="I4" s="13">
-        <v>54</v>
-      </c>
-      <c r="J4" s="7">
-        <v>50</v>
-      </c>
       <c r="K4" s="7">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L4" s="7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M4" s="7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N4" s="7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O4" s="7">
-        <v>22.143750000000001</v>
+        <v>20.07</v>
       </c>
       <c r="P4" s="7">
-        <v>21.184999999999999</v>
+        <v>19.68</v>
       </c>
       <c r="Q4" s="7">
-        <v>21.184999999999999</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -12952,49 +12952,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>0.90980000000000005</v>
+        <v>0.90329999999999999</v>
       </c>
       <c r="D6" s="18">
-        <v>0.92430000000000001</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="E6" s="18">
-        <v>0.9022</v>
+        <v>0.89239999999999997</v>
       </c>
       <c r="F6" s="18">
-        <v>0.87629999999999997</v>
+        <v>0.8579</v>
       </c>
       <c r="G6" s="18">
-        <v>1.0302</v>
+        <v>0.93210000000000004</v>
       </c>
       <c r="H6" s="18">
-        <v>1.0116000000000001</v>
+        <v>0.91490000000000005</v>
       </c>
       <c r="I6" s="18">
-        <v>1.0185999999999999</v>
+        <v>0.93469999999999998</v>
       </c>
       <c r="J6" s="18">
-        <v>0.95009999999999994</v>
+        <v>0.86719999999999997</v>
       </c>
       <c r="K6" s="18">
-        <v>0.92530000000000001</v>
+        <v>0.84330000000000005</v>
       </c>
       <c r="L6" s="18">
-        <v>0.70569999999999999</v>
+        <v>0.68269999999999997</v>
       </c>
       <c r="M6" s="18">
-        <v>0.68700000000000006</v>
+        <v>0.66490000000000005</v>
       </c>
       <c r="N6" s="18">
-        <v>0.67849999999999999</v>
+        <v>0.65649999999999997</v>
       </c>
       <c r="O6" s="18">
-        <v>0.4178</v>
+        <v>0.37869999999999998</v>
       </c>
       <c r="P6" s="18">
-        <v>0.3997</v>
+        <v>0.37130000000000002</v>
       </c>
       <c r="Q6" s="18">
-        <v>0.3997</v>
+        <v>0.37130000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -13012,40 +13012,40 @@
         <v>5</v>
       </c>
       <c r="F7" s="19">
+        <v>8</v>
+      </c>
+      <c r="G7" s="19">
+        <v>4</v>
+      </c>
+      <c r="H7" s="19">
+        <v>5</v>
+      </c>
+      <c r="I7" s="19">
+        <v>3</v>
+      </c>
+      <c r="J7" s="19">
         <v>7</v>
       </c>
-      <c r="G7" s="19">
-        <v>-2</v>
-      </c>
-      <c r="H7" s="19">
-        <v>-1</v>
-      </c>
-      <c r="I7" s="19">
-        <v>-1</v>
-      </c>
-      <c r="J7" s="19">
-        <v>3</v>
-      </c>
       <c r="K7" s="19">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L7" s="19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7" s="19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O7" s="19">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P7" s="19">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q7" s="19">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -13181,49 +13181,49 @@
         <v>19</v>
       </c>
       <c r="C11" s="7">
+        <v>31</v>
+      </c>
+      <c r="D11" s="7">
         <v>32</v>
-      </c>
-      <c r="D11" s="7">
-        <v>33</v>
       </c>
       <c r="E11" s="7">
         <v>32</v>
       </c>
       <c r="F11" s="7">
+        <v>31</v>
+      </c>
+      <c r="G11" s="7">
+        <v>33</v>
+      </c>
+      <c r="H11" s="7">
         <v>32</v>
       </c>
-      <c r="G11" s="7">
-        <v>35</v>
-      </c>
-      <c r="H11" s="7">
-        <v>34</v>
-      </c>
       <c r="I11" s="7">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J11" s="7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K11" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L11" s="7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M11" s="7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N11" s="7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O11" s="7">
-        <v>19.568750000000001</v>
+        <v>17.495000000000001</v>
       </c>
       <c r="P11" s="7">
-        <v>18.61</v>
+        <v>17.105</v>
       </c>
       <c r="Q11" s="7">
-        <v>18.61</v>
+        <v>17.105</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -13548,20 +13548,20 @@
       <c r="F19" s="7">
         <v>13</v>
       </c>
-      <c r="G19" s="13">
-        <v>17</v>
-      </c>
-      <c r="H19" s="13">
-        <v>17</v>
-      </c>
-      <c r="I19" s="13">
-        <v>17</v>
-      </c>
-      <c r="J19" s="13">
+      <c r="G19" s="7">
         <v>15</v>
       </c>
-      <c r="K19" s="13">
+      <c r="H19" s="7">
         <v>15</v>
+      </c>
+      <c r="I19" s="7">
+        <v>15</v>
+      </c>
+      <c r="J19" s="7">
+        <v>13</v>
+      </c>
+      <c r="K19" s="7">
+        <v>13</v>
       </c>
       <c r="L19" s="7">
         <v>10</v>
@@ -13660,35 +13660,35 @@
         <v>44</v>
       </c>
       <c r="D34" s="20">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E34" s="20">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F34" s="20">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G34" s="20">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="16"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24">
-        <v>8.7999999999999995E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="D35" s="24">
-        <v>2.7300000000000001E-2</v>
+        <v>9.8400000000000001E-2</v>
       </c>
       <c r="E35" s="24">
-        <v>3.5400000000000001E-2</v>
+        <v>0.1183</v>
       </c>
       <c r="F35" s="24">
-        <v>0.30959999999999999</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="G35" s="24">
-        <v>0.59430000000000005</v>
+        <v>0.62619999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -13697,19 +13697,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="18">
-        <v>0.91200000000000003</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="D36" s="18">
-        <v>0.97270000000000001</v>
+        <v>0.90159999999999996</v>
       </c>
       <c r="E36" s="18">
-        <v>0.96460000000000001</v>
+        <v>0.88170000000000004</v>
       </c>
       <c r="F36" s="18">
-        <v>0.69040000000000001</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="G36" s="18">
-        <v>0.40570000000000001</v>
+        <v>0.37380000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -13718,19 +13718,19 @@
         <v>24</v>
       </c>
       <c r="C37" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E37" s="19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F37" s="19">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G37" s="19">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -13799,16 +13799,16 @@
         <v>32</v>
       </c>
       <c r="D41" s="20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E41" s="20">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F41" s="20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G41" s="20">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -13954,11 +13954,11 @@
       <c r="C49" s="20">
         <v>10</v>
       </c>
-      <c r="D49" s="13">
-        <v>16</v>
-      </c>
-      <c r="E49" s="13">
-        <v>16</v>
+      <c r="D49" s="20">
+        <v>14</v>
+      </c>
+      <c r="E49" s="20">
+        <v>14</v>
       </c>
       <c r="F49" s="20">
         <v>10</v>
@@ -14075,49 +14075,49 @@
         <v>18</v>
       </c>
       <c r="C63" s="39">
-        <v>41.85125</v>
+        <v>41.551250000000003</v>
       </c>
       <c r="D63" s="39">
-        <v>45.28875</v>
+        <v>44.926250000000003</v>
       </c>
       <c r="E63" s="39">
-        <v>46.013750000000002</v>
+        <v>45.513750000000002</v>
       </c>
       <c r="F63" s="39">
-        <v>46.445</v>
+        <v>45.47</v>
       </c>
       <c r="G63" s="39">
-        <v>54.6</v>
+        <v>49.4</v>
       </c>
       <c r="H63" s="39">
-        <v>53.615000000000002</v>
+        <v>48.49</v>
       </c>
       <c r="I63" s="39">
-        <v>53.983750000000001</v>
+        <v>49.54</v>
       </c>
       <c r="J63" s="39">
-        <v>50.353749999999998</v>
+        <v>45.96</v>
       </c>
       <c r="K63" s="39">
-        <v>49.041249999999998</v>
+        <v>44.697499999999998</v>
       </c>
       <c r="L63" s="39">
-        <v>37.400624999999998</v>
+        <v>36.181874999999998</v>
       </c>
       <c r="M63" s="39">
-        <v>36.410625000000003</v>
+        <v>35.241875</v>
       </c>
       <c r="N63" s="39">
-        <v>35.960625</v>
+        <v>34.791874999999997</v>
       </c>
       <c r="O63" s="39">
-        <v>22.143750000000001</v>
+        <v>20.07</v>
       </c>
       <c r="P63" s="39">
-        <v>21.184999999999999</v>
+        <v>19.68</v>
       </c>
       <c r="Q63" s="39">
-        <v>21.184999999999999</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -14299,31 +14299,31 @@
         <v>3.2</v>
       </c>
       <c r="G67" s="7">
-        <v>4.8250000000000002</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H67" s="7">
-        <v>4.8875000000000002</v>
+        <v>4.1624999999999996</v>
       </c>
       <c r="I67" s="7">
-        <v>5.3312499999999998</v>
+        <v>5.2374999999999998</v>
       </c>
       <c r="J67" s="7">
-        <v>4.5812499999999998</v>
+        <v>4.4874999999999998</v>
       </c>
       <c r="K67" s="7">
-        <v>4.5187499999999998</v>
+        <v>4.4249999999999998</v>
       </c>
       <c r="L67" s="7">
-        <v>3.703125</v>
+        <v>3.609375</v>
       </c>
       <c r="M67" s="7">
-        <v>3.2281249999999999</v>
+        <v>3.1343749999999999</v>
       </c>
       <c r="N67" s="7">
-        <v>3.2281249999999999</v>
+        <v>3.1343749999999999</v>
       </c>
       <c r="O67" s="7">
-        <v>3.0562499999999999</v>
+        <v>2.9624999999999999</v>
       </c>
       <c r="P67" s="7">
         <v>2.9125000000000001</v>
@@ -14399,7 +14399,7 @@
         <v>5.7149999999999999</v>
       </c>
       <c r="E69" s="7">
-        <v>6.42</v>
+        <v>6.3825000000000003</v>
       </c>
       <c r="F69" s="7">
         <v>5.89</v>
@@ -14505,7 +14505,7 @@
         <v>4.7149999999999999</v>
       </c>
       <c r="E71" s="32">
-        <v>5.42</v>
+        <v>5.3825000000000003</v>
       </c>
       <c r="F71" s="32">
         <v>5.04</v>
@@ -14711,49 +14711,49 @@
         <v>18</v>
       </c>
       <c r="C75" s="7">
-        <v>3.9275000000000002</v>
+        <v>3.8650000000000002</v>
       </c>
       <c r="D75" s="7">
-        <v>3.5049999999999999</v>
+        <v>3.38</v>
       </c>
       <c r="E75" s="7">
-        <v>3.9049999999999998</v>
+        <v>3.68</v>
       </c>
       <c r="F75" s="7">
-        <v>4.085</v>
+        <v>3.81</v>
       </c>
       <c r="G75" s="7">
-        <v>4.2625000000000002</v>
+        <v>3.9874999999999998</v>
       </c>
       <c r="H75" s="7">
-        <v>3.7749999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="I75" s="7">
-        <v>3.7749999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="J75" s="7">
-        <v>3.7749999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="K75" s="7">
-        <v>3.65</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="L75" s="7">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="M75" s="7">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="N75" s="7">
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="O75" s="7">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="P75" s="7">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="Q75" s="7">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
@@ -14817,49 +14817,49 @@
         <v>18</v>
       </c>
       <c r="C77" s="7">
-        <v>2.605</v>
+        <v>2.5550000000000002</v>
       </c>
       <c r="D77" s="7">
-        <v>2.6349999999999998</v>
+        <v>2.585</v>
       </c>
       <c r="E77" s="7">
-        <v>2.2650000000000001</v>
+        <v>2.2149999999999999</v>
       </c>
       <c r="F77" s="7">
-        <v>2.4624999999999999</v>
+        <v>2.2625000000000002</v>
       </c>
       <c r="G77" s="7">
-        <v>2.4624999999999999</v>
+        <v>2.2625000000000002</v>
       </c>
       <c r="H77" s="7">
-        <v>2.4424999999999999</v>
+        <v>2.2925</v>
       </c>
       <c r="I77" s="7">
-        <v>2.5049999999999999</v>
+        <v>2.355</v>
       </c>
       <c r="J77" s="7">
-        <v>2.3050000000000002</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="K77" s="7">
-        <v>2.3050000000000002</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="L77" s="7">
-        <v>0.92500000000000004</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="M77" s="7">
-        <v>0.875</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="N77" s="7">
-        <v>0.875</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="O77" s="7">
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="P77" s="7">
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="Q77" s="7">
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
@@ -14932,40 +14932,40 @@
         <v>2.5125000000000002</v>
       </c>
       <c r="F79" s="7">
-        <v>2.2075</v>
+        <v>2.1575000000000002</v>
       </c>
       <c r="G79" s="7">
-        <v>2.1825000000000001</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="H79" s="7">
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="I79" s="7">
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="J79" s="7">
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="K79" s="7">
-        <v>1.8574999999999999</v>
+        <v>1.8325</v>
       </c>
       <c r="L79" s="7">
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="M79" s="7">
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="N79" s="7">
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="O79" s="7">
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="P79" s="7">
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="Q79" s="7">
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
@@ -15038,40 +15038,40 @@
         <v>3.48</v>
       </c>
       <c r="F81" s="7">
-        <v>3.5049999999999999</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="G81" s="7">
-        <v>4.3550000000000004</v>
+        <v>3.9049999999999998</v>
       </c>
       <c r="H81" s="7">
-        <v>4.4424999999999999</v>
+        <v>3.9925000000000002</v>
       </c>
       <c r="I81" s="7">
-        <v>4.8949999999999996</v>
+        <v>4.4450000000000003</v>
       </c>
       <c r="J81" s="7">
-        <v>4.5449999999999999</v>
+        <v>4.0949999999999998</v>
       </c>
       <c r="K81" s="7">
-        <v>4.0199999999999996</v>
+        <v>3.57</v>
       </c>
       <c r="L81" s="7">
-        <v>2.5625</v>
+        <v>2.1124999999999998</v>
       </c>
       <c r="M81" s="7">
-        <v>2.2374999999999998</v>
+        <v>1.7875000000000001</v>
       </c>
       <c r="N81" s="7">
-        <v>1.9375</v>
+        <v>1.4875</v>
       </c>
       <c r="O81" s="7">
-        <v>1.3875</v>
+        <v>0.9375</v>
       </c>
       <c r="P81" s="7">
-        <v>1.0125</v>
+        <v>0.78749999999999998</v>
       </c>
       <c r="Q81" s="7">
-        <v>1.0125</v>
+        <v>0.78749999999999998</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
@@ -15135,43 +15135,43 @@
         <v>18</v>
       </c>
       <c r="C83" s="7">
-        <v>5.0875000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D83" s="7">
-        <v>5.4625000000000004</v>
+        <v>5.2750000000000004</v>
       </c>
       <c r="E83" s="7">
-        <v>5.1375000000000002</v>
+        <v>4.95</v>
       </c>
       <c r="F83" s="7">
         <v>4.9050000000000002</v>
       </c>
       <c r="G83" s="7">
-        <v>5.9024999999999999</v>
+        <v>5.4024999999999999</v>
       </c>
       <c r="H83" s="7">
-        <v>5.54</v>
+        <v>5.04</v>
       </c>
       <c r="I83" s="7">
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="J83" s="7">
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="K83" s="7">
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="L83" s="7">
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="M83" s="7">
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="N83" s="7">
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="O83" s="7">
-        <v>3.4024999999999999</v>
+        <v>3.1524999999999999</v>
       </c>
       <c r="P83" s="7">
         <v>3.1524999999999999</v>
@@ -15253,19 +15253,19 @@
         <v>16.059999999999999</v>
       </c>
       <c r="G85" s="7">
-        <v>20.76</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="H85" s="7">
-        <v>20.434999999999999</v>
+        <v>17.434999999999999</v>
       </c>
       <c r="I85" s="7">
-        <v>20.350000000000001</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="J85" s="7">
-        <v>18.074999999999999</v>
+        <v>15.074999999999999</v>
       </c>
       <c r="K85" s="7">
-        <v>17.824999999999999</v>
+        <v>14.824999999999999</v>
       </c>
       <c r="L85" s="7">
         <v>12.824999999999999</v>
@@ -15359,19 +15359,19 @@
         <v>2.21</v>
       </c>
       <c r="G87" s="32">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="H87" s="32">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="I87" s="32">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="J87" s="32">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="K87" s="32">
-        <v>1.6</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L87" s="32">
         <v>1.6</v>
@@ -15571,19 +15571,19 @@
         <v>12.85</v>
       </c>
       <c r="G91" s="32">
-        <v>17.350000000000001</v>
+        <v>14.85</v>
       </c>
       <c r="H91" s="32">
-        <v>17.274999999999999</v>
+        <v>14.775</v>
       </c>
       <c r="I91" s="32">
-        <v>17.399999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="J91" s="32">
-        <v>15.375</v>
+        <v>12.875</v>
       </c>
       <c r="K91" s="32">
-        <v>15.225</v>
+        <v>12.725</v>
       </c>
       <c r="L91" s="32">
         <v>10.225</v>
@@ -15701,13 +15701,13 @@
         <v>3.73</v>
       </c>
       <c r="O93" s="7">
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
       <c r="P93" s="7">
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
       <c r="Q93" s="7">
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
     </row>
   </sheetData>
@@ -15939,51 +15939,51 @@
       </c>
       <c r="E4">
         <f>IF(SD!F4&gt;0,SD!F4,"")</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4">
         <f>IF(SD!G4&gt;0,SD!G4,"")</f>
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <f>IF(SD!H4&gt;0,SD!H4,"")</f>
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H4">
         <f>IF(SD!I4&gt;0,SD!I4,"")</f>
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I4">
         <f>IF(SD!J4&gt;0,SD!J4,"")</f>
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J4">
         <f>IF(SD!K4&gt;0,SD!K4,"")</f>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K4">
         <f>IF(SD!L4&gt;0,SD!L4,"")</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L4">
         <f>IF(SD!M4&gt;0,SD!M4,"")</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M4">
         <f>IF(SD!N4&gt;0,SD!N4,"")</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N4">
         <f>IF(SD!O4&gt;0,SD!O4,"")</f>
-        <v>22.143750000000001</v>
+        <v>20.07</v>
       </c>
       <c r="O4">
         <f>IF(SD!P4&gt;0,SD!P4,"")</f>
-        <v>21.184999999999999</v>
+        <v>19.68</v>
       </c>
       <c r="P4">
         <f>IF(SD!Q4&gt;0,SD!Q4,"")</f>
-        <v>21.184999999999999</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -15993,11 +15993,11 @@
       </c>
       <c r="B5">
         <f>IF(SD!C11&gt;0,SD!C11,"")</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <f>IF(SD!D11&gt;0,SD!D11,"")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5">
         <f>IF(SD!E11&gt;0,SD!E11,"")</f>
@@ -16005,51 +16005,51 @@
       </c>
       <c r="E5">
         <f>IF(SD!F11&gt;0,SD!F11,"")</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <f>IF(SD!G11&gt;0,SD!G11,"")</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <f>IF(SD!H11&gt;0,SD!H11,"")</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H5">
         <f>IF(SD!I11&gt;0,SD!I11,"")</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I5">
         <f>IF(SD!J11&gt;0,SD!J11,"")</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J5">
         <f>IF(SD!K11&gt;0,SD!K11,"")</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K5">
         <f>IF(SD!L11&gt;0,SD!L11,"")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L5">
         <f>IF(SD!M11&gt;0,SD!M11,"")</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5">
         <f>IF(SD!N11&gt;0,SD!N11,"")</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N5">
         <f>IF(SD!O11&gt;0,SD!O11,"")</f>
-        <v>19.568750000000001</v>
+        <v>17.495000000000001</v>
       </c>
       <c r="O5">
         <f>IF(SD!P11&gt;0,SD!P11,"")</f>
-        <v>18.61</v>
+        <v>17.105</v>
       </c>
       <c r="P5">
         <f>IF(SD!Q11&gt;0,SD!Q11,"")</f>
-        <v>18.61</v>
+        <v>17.105</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -16141,23 +16141,23 @@
       </c>
       <c r="F7">
         <f>IF(SD!G19&gt;0,SD!G19,"")</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <f>IF(SD!H19&gt;0,SD!H19,"")</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <f>IF(SD!I19&gt;0,SD!I19,"")</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I7">
         <f>IF(SD!J19&gt;0,SD!J19,"")</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J7">
         <f>IF(SD!K19&gt;0,SD!K19,"")</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <f>IF(SD!L19&gt;0,SD!L19,"")</f>
@@ -16385,11 +16385,11 @@
       </c>
       <c r="B14">
         <f>IF(SD!C11&gt;0,SD!C11,"")</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14">
         <f>IF(SD!D11&gt;0,SD!D11,"")</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <f>IF(SD!E11&gt;0,SD!E11,"")</f>
@@ -16397,51 +16397,51 @@
       </c>
       <c r="E14">
         <f>IF(SD!F11&gt;0,SD!F11,"")</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14">
         <f>IF(SD!G11&gt;0,SD!G11,"")</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G14">
         <f>IF(SD!H11&gt;0,SD!H11,"")</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H14">
         <f>IF(SD!I11&gt;0,SD!I11,"")</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I14">
         <f>IF(SD!J11&gt;0,SD!J11,"")</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J14">
         <f>IF(SD!K11&gt;0,SD!K11,"")</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K14">
         <f>IF(SD!L11&gt;0,SD!L11,"")</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L14">
         <f>IF(SD!M11&gt;0,SD!M11,"")</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M14">
         <f>IF(SD!N11&gt;0,SD!N11,"")</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N14">
         <f>IF(SD!O11&gt;0,SD!O11,"")</f>
-        <v>19.568750000000001</v>
+        <v>17.495000000000001</v>
       </c>
       <c r="O14">
         <f>IF(SD!P11&gt;0,SD!P11,"")</f>
-        <v>18.61</v>
+        <v>17.105</v>
       </c>
       <c r="P14">
         <f>IF(SD!Q11&gt;0,SD!Q11,"")</f>
-        <v>18.61</v>
+        <v>17.105</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -16921,23 +16921,23 @@
       </c>
       <c r="F34">
         <f>IF(SD!G19&gt;0,SD!G19,"")</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G34">
         <f>IF(SD!H19&gt;0,SD!H19,"")</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H34">
         <f>IF(SD!I19&gt;0,SD!I19,"")</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I34">
         <f>IF(SD!J19&gt;0,SD!J19,"")</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J34">
         <f>IF(SD!K19&gt;0,SD!K19,"")</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K34">
         <f>IF(SD!L19&gt;0,SD!L19,"")</f>
@@ -17049,19 +17049,19 @@
       </c>
       <c r="C44">
         <f>IF(SD!D34&gt;0,SD!D34,"")</f>
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D44">
         <f>IF(SD!E34&gt;0,SD!E34,"")</f>
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E44">
         <f>IF(SD!F34&gt;0,SD!F34,"")</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F44">
         <f>IF(SD!G34&gt;0,SD!G34,"")</f>
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -17075,19 +17075,19 @@
       </c>
       <c r="C45">
         <f>IF(SD!D41&gt;0,SD!D41,"")</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D45">
         <f>IF(SD!E41&gt;0,SD!E41,"")</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E45">
         <f>IF(SD!F41&gt;0,SD!F41,"")</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F45">
         <f>IF(SD!G41&gt;0,SD!G41,"")</f>
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -17127,11 +17127,11 @@
       </c>
       <c r="C47">
         <f>IF(SD!D49&gt;0,SD!D49,"")</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D47">
         <f>IF(SD!E49&gt;0,SD!E49,"")</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E47">
         <f>IF(SD!F49&gt;0,SD!F49,"")</f>
@@ -17297,39 +17297,39 @@
       </c>
       <c r="F53">
         <f>SD!G67</f>
-        <v>4.8250000000000002</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G53">
         <f>SD!H67</f>
-        <v>4.8875000000000002</v>
+        <v>4.1624999999999996</v>
       </c>
       <c r="H53">
         <f>SD!I67</f>
-        <v>5.3312499999999998</v>
+        <v>5.2374999999999998</v>
       </c>
       <c r="I53">
         <f>SD!J67</f>
-        <v>4.5812499999999998</v>
+        <v>4.4874999999999998</v>
       </c>
       <c r="J53">
         <f>SD!K67</f>
-        <v>4.5187499999999998</v>
+        <v>4.4249999999999998</v>
       </c>
       <c r="K53">
         <f>SD!L67</f>
-        <v>3.703125</v>
+        <v>3.609375</v>
       </c>
       <c r="L53">
         <f>SD!M67</f>
-        <v>3.2281249999999999</v>
+        <v>3.1343749999999999</v>
       </c>
       <c r="M53">
         <f>SD!N67</f>
-        <v>3.2281249999999999</v>
+        <v>3.1343749999999999</v>
       </c>
       <c r="N53">
         <f>SD!O67</f>
-        <v>3.0562499999999999</v>
+        <v>2.9624999999999999</v>
       </c>
       <c r="O53">
         <f>SD!P67</f>
@@ -17362,39 +17362,39 @@
       </c>
       <c r="F54" s="58">
         <f t="shared" si="0"/>
-        <v>-0.82500000000000018</v>
+        <v>-9.9999999999999645E-2</v>
       </c>
       <c r="G54" s="58">
         <f t="shared" si="0"/>
-        <v>-0.88750000000000018</v>
+        <v>-0.16249999999999964</v>
       </c>
       <c r="H54" s="58">
         <f t="shared" si="0"/>
-        <v>-1.3312499999999998</v>
+        <v>-1.2374999999999998</v>
       </c>
       <c r="I54" s="58">
         <f t="shared" si="0"/>
-        <v>-0.58124999999999982</v>
+        <v>-0.48749999999999982</v>
       </c>
       <c r="J54" s="58">
         <f t="shared" si="0"/>
-        <v>-0.51874999999999982</v>
+        <v>-0.42499999999999982</v>
       </c>
       <c r="K54" s="58">
         <f t="shared" si="0"/>
-        <v>0.296875</v>
+        <v>0.390625</v>
       </c>
       <c r="L54" s="58">
         <f t="shared" si="0"/>
-        <v>0.77187500000000009</v>
+        <v>0.86562500000000009</v>
       </c>
       <c r="M54" s="58">
         <f t="shared" si="0"/>
-        <v>0.77187500000000009</v>
+        <v>0.86562500000000009</v>
       </c>
       <c r="N54" s="58">
         <f t="shared" si="0"/>
-        <v>0.94375000000000009</v>
+        <v>1.0375000000000001</v>
       </c>
       <c r="O54" s="58">
         <f t="shared" si="0"/>
@@ -17438,19 +17438,19 @@
       </c>
       <c r="C56" s="50">
         <f>(AVERAGE(E53:G53)/AVERAGE(E52:G52))*100</f>
-        <v>107.60416666666669</v>
+        <v>95.520833333333314</v>
       </c>
       <c r="D56" s="50">
         <f>(AVERAGE(H53:J53)/AVERAGE(H52:J52))*100</f>
-        <v>120.26041666666664</v>
+        <v>117.91666666666664</v>
       </c>
       <c r="E56" s="50">
         <f>(AVERAGE(K53:M53)/AVERAGE(K52:M52))*100</f>
-        <v>84.661458333333343</v>
+        <v>82.317708333333343</v>
       </c>
       <c r="F56" s="50">
         <f>(AVERAGE(N53:P53)/AVERAGE(N52:P52))*100</f>
-        <v>74.010416666666671</v>
+        <v>73.229166666666671</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="D63">
         <f>SD!E69</f>
-        <v>6.42</v>
+        <v>6.3825000000000003</v>
       </c>
       <c r="E63">
         <f>SD!F69</f>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="D64" s="58">
         <f t="shared" si="2"/>
-        <v>0.58000000000000007</v>
+        <v>0.61749999999999972</v>
       </c>
       <c r="E64" s="58">
         <f t="shared" si="2"/>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="B66" s="50">
         <f>(AVERAGE(B63:D63)/AVERAGE(B62:D62))*100</f>
-        <v>86.928571428571445</v>
+        <v>86.75</v>
       </c>
       <c r="C66" s="50">
         <f>(AVERAGE(E63:G63)/AVERAGE(E62:G62))*100</f>
@@ -17903,63 +17903,63 @@
       </c>
       <c r="B73">
         <f>SD!C75</f>
-        <v>3.9275000000000002</v>
+        <v>3.8650000000000002</v>
       </c>
       <c r="C73">
         <f>SD!D75</f>
-        <v>3.5049999999999999</v>
+        <v>3.38</v>
       </c>
       <c r="D73">
         <f>SD!E75</f>
-        <v>3.9049999999999998</v>
+        <v>3.68</v>
       </c>
       <c r="E73">
         <f>SD!F75</f>
-        <v>4.085</v>
+        <v>3.81</v>
       </c>
       <c r="F73">
         <f>SD!G75</f>
-        <v>4.2625000000000002</v>
+        <v>3.9874999999999998</v>
       </c>
       <c r="G73">
         <f>SD!H75</f>
-        <v>3.7749999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="H73">
         <f>SD!I75</f>
-        <v>3.7749999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="I73">
         <f>SD!J75</f>
-        <v>3.7749999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="J73">
         <f>SD!K75</f>
-        <v>3.65</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="K73">
         <f>SD!L75</f>
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="L73">
         <f>SD!M75</f>
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="M73">
         <f>SD!N75</f>
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="N73">
         <f>SD!O75</f>
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="O73">
         <f>SD!P75</f>
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="P73">
         <f>SD!Q75</f>
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="74" spans="1:16" s="57" customFormat="1" x14ac:dyDescent="0.2">
@@ -17968,63 +17968,63 @@
       </c>
       <c r="B74" s="58">
         <f>B72-B73</f>
-        <v>7.2499999999999787E-2</v>
+        <v>0.13499999999999979</v>
       </c>
       <c r="C74" s="58">
         <f t="shared" ref="C74:P74" si="4">C72-C73</f>
-        <v>0.49500000000000011</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="D74" s="58">
         <f t="shared" si="4"/>
-        <v>9.5000000000000195E-2</v>
+        <v>0.31999999999999984</v>
       </c>
       <c r="E74" s="58">
         <f t="shared" si="4"/>
-        <v>-8.4999999999999964E-2</v>
+        <v>0.18999999999999995</v>
       </c>
       <c r="F74" s="58">
         <f t="shared" si="4"/>
-        <v>-0.26250000000000018</v>
+        <v>1.2500000000000178E-2</v>
       </c>
       <c r="G74" s="58">
         <f t="shared" si="4"/>
-        <v>0.22500000000000009</v>
+        <v>0.5</v>
       </c>
       <c r="H74" s="58">
         <f t="shared" si="4"/>
-        <v>0.22500000000000009</v>
+        <v>0.45000000000000018</v>
       </c>
       <c r="I74" s="58">
         <f t="shared" si="4"/>
-        <v>0.22500000000000009</v>
+        <v>0.45000000000000018</v>
       </c>
       <c r="J74" s="58">
         <f t="shared" si="4"/>
-        <v>0.35000000000000009</v>
+        <v>0.52499999999999991</v>
       </c>
       <c r="K74" s="58">
         <f t="shared" si="4"/>
-        <v>1.04</v>
+        <v>1.2400000000000002</v>
       </c>
       <c r="L74" s="58">
         <f t="shared" si="4"/>
-        <v>1.04</v>
+        <v>1.2400000000000002</v>
       </c>
       <c r="M74" s="58">
         <f t="shared" si="4"/>
-        <v>1.0899999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="N74" s="58">
         <f t="shared" si="4"/>
-        <v>3.68</v>
+        <v>3.73</v>
       </c>
       <c r="O74" s="58">
         <f t="shared" si="4"/>
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="P74" s="58">
         <f t="shared" si="4"/>
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="75" spans="1:16" s="50" customFormat="1" x14ac:dyDescent="0.2">
@@ -18056,23 +18056,23 @@
       </c>
       <c r="B76" s="50">
         <f>(AVERAGE(B73:D73)/AVERAGE(B72:D72))*100</f>
-        <v>94.479166666666671</v>
+        <v>91.041666666666671</v>
       </c>
       <c r="C76" s="50">
         <f>(AVERAGE(E73:G73)/AVERAGE(E72:G72))*100</f>
-        <v>101.02083333333334</v>
+        <v>94.145833333333329</v>
       </c>
       <c r="D76" s="50">
         <f>(AVERAGE(H73:J73)/AVERAGE(H72:J72))*100</f>
-        <v>93.333333333333329</v>
+        <v>88.125</v>
       </c>
       <c r="E76" s="50">
         <f>(AVERAGE(K73:M73)/AVERAGE(K72:M72))*100</f>
-        <v>73.583333333333329</v>
+        <v>68.583333333333343</v>
       </c>
       <c r="F76" s="50">
         <f>(AVERAGE(N73:P73)/AVERAGE(N72:P72))*100</f>
-        <v>7.166666666666667</v>
+        <v>5.916666666666667</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
@@ -18214,63 +18214,63 @@
       </c>
       <c r="B83">
         <f>SD!C77</f>
-        <v>2.605</v>
+        <v>2.5550000000000002</v>
       </c>
       <c r="C83">
         <f>SD!D77</f>
-        <v>2.6349999999999998</v>
+        <v>2.585</v>
       </c>
       <c r="D83">
         <f>SD!E77</f>
-        <v>2.2650000000000001</v>
+        <v>2.2149999999999999</v>
       </c>
       <c r="E83">
         <f>SD!F77</f>
-        <v>2.4624999999999999</v>
+        <v>2.2625000000000002</v>
       </c>
       <c r="F83">
         <f>SD!G77</f>
-        <v>2.4624999999999999</v>
+        <v>2.2625000000000002</v>
       </c>
       <c r="G83">
         <f>SD!H77</f>
-        <v>2.4424999999999999</v>
+        <v>2.2925</v>
       </c>
       <c r="H83">
         <f>SD!I77</f>
-        <v>2.5049999999999999</v>
+        <v>2.355</v>
       </c>
       <c r="I83">
         <f>SD!J77</f>
-        <v>2.3050000000000002</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="J83">
         <f>SD!K77</f>
-        <v>2.3050000000000002</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="K83">
         <f>SD!L77</f>
-        <v>0.92500000000000004</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="L83">
         <f>SD!M77</f>
-        <v>0.875</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="M83">
         <f>SD!N77</f>
-        <v>0.875</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="N83">
         <f>SD!O77</f>
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="O83">
         <f>SD!P77</f>
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="P83">
         <f>SD!Q77</f>
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
     </row>
     <row r="84" spans="1:16" s="57" customFormat="1" x14ac:dyDescent="0.2">
@@ -18279,63 +18279,63 @@
       </c>
       <c r="B84" s="58">
         <f>B82-B83</f>
-        <v>-0.60499999999999998</v>
+        <v>-0.55500000000000016</v>
       </c>
       <c r="C84" s="58">
         <f t="shared" ref="C84:P84" si="6">C82-C83</f>
-        <v>-0.63499999999999979</v>
+        <v>-0.58499999999999996</v>
       </c>
       <c r="D84" s="58">
         <f t="shared" si="6"/>
-        <v>-0.26500000000000012</v>
+        <v>-0.21499999999999986</v>
       </c>
       <c r="E84" s="58">
         <f t="shared" si="6"/>
-        <v>0.53750000000000009</v>
+        <v>0.73749999999999982</v>
       </c>
       <c r="F84" s="58">
         <f t="shared" si="6"/>
-        <v>0.53750000000000009</v>
+        <v>0.73749999999999982</v>
       </c>
       <c r="G84" s="58">
         <f t="shared" si="6"/>
-        <v>0.55750000000000011</v>
+        <v>0.70750000000000002</v>
       </c>
       <c r="H84" s="58">
         <f t="shared" si="6"/>
-        <v>0.49500000000000011</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="I84" s="58">
         <f t="shared" si="6"/>
-        <v>0.69499999999999984</v>
+        <v>0.79499999999999993</v>
       </c>
       <c r="J84" s="58">
         <f t="shared" si="6"/>
-        <v>0.69499999999999984</v>
+        <v>0.79499999999999993</v>
       </c>
       <c r="K84" s="58">
         <f t="shared" si="6"/>
-        <v>2.0750000000000002</v>
+        <v>2.1749999999999998</v>
       </c>
       <c r="L84" s="58">
         <f t="shared" si="6"/>
-        <v>2.125</v>
+        <v>2.1749999999999998</v>
       </c>
       <c r="M84" s="58">
         <f t="shared" si="6"/>
-        <v>2.125</v>
+        <v>2.1749999999999998</v>
       </c>
       <c r="N84" s="58">
         <f t="shared" si="6"/>
-        <v>2.375</v>
+        <v>2.4249999999999998</v>
       </c>
       <c r="O84" s="58">
         <f t="shared" si="6"/>
-        <v>2.375</v>
+        <v>2.4249999999999998</v>
       </c>
       <c r="P84" s="58">
         <f t="shared" si="6"/>
-        <v>2.375</v>
+        <v>2.4249999999999998</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="50" customFormat="1" x14ac:dyDescent="0.2">
@@ -18367,23 +18367,23 @@
       </c>
       <c r="B86" s="50">
         <f>(AVERAGE(B83:D83)/AVERAGE(B82:D82))*100</f>
-        <v>125.08333333333334</v>
+        <v>122.58333333333333</v>
       </c>
       <c r="C86" s="50">
         <f>(AVERAGE(E83:G83)/AVERAGE(E82:G82))*100</f>
-        <v>81.8611111111111</v>
+        <v>75.750000000000014</v>
       </c>
       <c r="D86" s="50">
         <f>(AVERAGE(H83:J83)/AVERAGE(H82:J82))*100</f>
-        <v>79.055555555555557</v>
+        <v>75.166666666666686</v>
       </c>
       <c r="E86" s="50">
         <f>(AVERAGE(K83:M83)/AVERAGE(K82:M82))*100</f>
-        <v>29.722222222222221</v>
+        <v>27.499999999999996</v>
       </c>
       <c r="F86" s="50">
         <f>(AVERAGE(N83:P83)/AVERAGE(N82:P82))*100</f>
-        <v>20.833333333333336</v>
+        <v>19.166666666666664</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
@@ -18537,51 +18537,51 @@
       </c>
       <c r="E93">
         <f>SD!F79</f>
-        <v>2.2075</v>
+        <v>2.1575000000000002</v>
       </c>
       <c r="F93">
         <f>SD!G79</f>
-        <v>2.1825000000000001</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="G93">
         <f>SD!H79</f>
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="H93">
         <f>SD!I79</f>
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="I93">
         <f>SD!J79</f>
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="J93">
         <f>SD!K79</f>
-        <v>1.8574999999999999</v>
+        <v>1.8325</v>
       </c>
       <c r="K93">
         <f>SD!L79</f>
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="L93">
         <f>SD!M79</f>
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="M93">
         <f>SD!N79</f>
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="N93">
         <f>SD!O79</f>
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="O93">
         <f>SD!P79</f>
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="P93">
         <f>SD!Q79</f>
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
     </row>
     <row r="94" spans="1:16" s="57" customFormat="1" x14ac:dyDescent="0.2">
@@ -18602,51 +18602,51 @@
       </c>
       <c r="E94" s="58">
         <f t="shared" si="8"/>
-        <v>0.79249999999999998</v>
+        <v>0.8424999999999998</v>
       </c>
       <c r="F94" s="58">
         <f t="shared" si="8"/>
-        <v>0.81749999999999989</v>
+        <v>0.86750000000000016</v>
       </c>
       <c r="G94" s="58">
         <f t="shared" si="8"/>
-        <v>0.8424999999999998</v>
+        <v>0.86750000000000016</v>
       </c>
       <c r="H94" s="58">
         <f t="shared" si="8"/>
-        <v>0.8424999999999998</v>
+        <v>0.86750000000000016</v>
       </c>
       <c r="I94" s="58">
         <f t="shared" si="8"/>
-        <v>0.8424999999999998</v>
+        <v>0.86750000000000016</v>
       </c>
       <c r="J94" s="58">
         <f t="shared" si="8"/>
-        <v>1.1425000000000001</v>
+        <v>1.1675</v>
       </c>
       <c r="K94" s="58">
         <f t="shared" si="8"/>
-        <v>1.6625000000000001</v>
+        <v>1.6875</v>
       </c>
       <c r="L94" s="58">
         <f t="shared" si="8"/>
-        <v>1.6625000000000001</v>
+        <v>1.6875</v>
       </c>
       <c r="M94" s="58">
         <f t="shared" si="8"/>
-        <v>1.6625000000000001</v>
+        <v>1.6875</v>
       </c>
       <c r="N94" s="58">
         <f t="shared" si="8"/>
-        <v>2.4624999999999999</v>
+        <v>2.4874999999999998</v>
       </c>
       <c r="O94" s="58">
         <f t="shared" si="8"/>
-        <v>2.4624999999999999</v>
+        <v>2.4874999999999998</v>
       </c>
       <c r="P94" s="58">
         <f t="shared" si="8"/>
-        <v>2.4624999999999999</v>
+        <v>2.4874999999999998</v>
       </c>
     </row>
     <row r="95" spans="1:16" s="50" customFormat="1" x14ac:dyDescent="0.2">
@@ -18682,19 +18682,19 @@
       </c>
       <c r="C96" s="50">
         <f>(AVERAGE(E93:G93)/AVERAGE(E92:G92))*100</f>
-        <v>72.750000000000014</v>
+        <v>71.361111111111114</v>
       </c>
       <c r="D96" s="50">
         <f>(AVERAGE(H93:J93)/AVERAGE(H92:J92))*100</f>
-        <v>68.583333333333343</v>
+        <v>67.750000000000014</v>
       </c>
       <c r="E96" s="50">
         <f>(AVERAGE(K93:M93)/AVERAGE(K92:M92))*100</f>
-        <v>44.583333333333321</v>
+        <v>43.75</v>
       </c>
       <c r="F96" s="50">
         <f>(AVERAGE(N93:P93)/AVERAGE(N92:P92))*100</f>
-        <v>17.916666666666668</v>
+        <v>17.083333333333332</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
@@ -18848,51 +18848,51 @@
       </c>
       <c r="E103">
         <f>SD!F81</f>
-        <v>3.5049999999999999</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="F103">
         <f>SD!G81</f>
-        <v>4.3550000000000004</v>
+        <v>3.9049999999999998</v>
       </c>
       <c r="G103">
         <f>SD!H81</f>
-        <v>4.4424999999999999</v>
+        <v>3.9925000000000002</v>
       </c>
       <c r="H103">
         <f>SD!I81</f>
-        <v>4.8949999999999996</v>
+        <v>4.4450000000000003</v>
       </c>
       <c r="I103">
         <f>SD!J81</f>
-        <v>4.5449999999999999</v>
+        <v>4.0949999999999998</v>
       </c>
       <c r="J103">
         <f>SD!K81</f>
-        <v>4.0199999999999996</v>
+        <v>3.57</v>
       </c>
       <c r="K103">
         <f>SD!L81</f>
-        <v>2.5625</v>
+        <v>2.1124999999999998</v>
       </c>
       <c r="L103">
         <f>SD!M81</f>
-        <v>2.2374999999999998</v>
+        <v>1.7875000000000001</v>
       </c>
       <c r="M103">
         <f>SD!N81</f>
-        <v>1.9375</v>
+        <v>1.4875</v>
       </c>
       <c r="N103">
         <f>SD!O81</f>
-        <v>1.3875</v>
+        <v>0.9375</v>
       </c>
       <c r="O103">
         <f>SD!P81</f>
-        <v>1.0125</v>
+        <v>0.78749999999999998</v>
       </c>
       <c r="P103">
         <f>SD!Q81</f>
-        <v>1.0125</v>
+        <v>0.78749999999999998</v>
       </c>
     </row>
     <row r="104" spans="1:16" s="57" customFormat="1" x14ac:dyDescent="0.2">
@@ -18913,51 +18913,51 @@
       </c>
       <c r="E104" s="58">
         <f t="shared" si="10"/>
-        <v>0.49500000000000011</v>
+        <v>0.94499999999999984</v>
       </c>
       <c r="F104" s="58">
         <f t="shared" si="10"/>
-        <v>-0.35500000000000043</v>
+        <v>9.5000000000000195E-2</v>
       </c>
       <c r="G104" s="58">
         <f t="shared" si="10"/>
-        <v>-0.44249999999999989</v>
+        <v>7.4999999999998401E-3</v>
       </c>
       <c r="H104" s="58">
         <f t="shared" si="10"/>
-        <v>-0.89499999999999957</v>
+        <v>-0.44500000000000028</v>
       </c>
       <c r="I104" s="58">
         <f t="shared" si="10"/>
-        <v>-0.54499999999999993</v>
+        <v>-9.4999999999999751E-2</v>
       </c>
       <c r="J104" s="58">
         <f t="shared" si="10"/>
-        <v>-1.9999999999999574E-2</v>
+        <v>0.43000000000000016</v>
       </c>
       <c r="K104" s="58">
         <f t="shared" si="10"/>
-        <v>1.4375</v>
+        <v>1.8875000000000002</v>
       </c>
       <c r="L104" s="58">
         <f t="shared" si="10"/>
-        <v>1.7625000000000002</v>
+        <v>2.2124999999999999</v>
       </c>
       <c r="M104" s="58">
         <f t="shared" si="10"/>
-        <v>2.0625</v>
+        <v>2.5125000000000002</v>
       </c>
       <c r="N104" s="58">
         <f t="shared" si="10"/>
-        <v>2.6124999999999998</v>
+        <v>3.0625</v>
       </c>
       <c r="O104" s="58">
         <f t="shared" si="10"/>
-        <v>2.9874999999999998</v>
+        <v>3.2124999999999999</v>
       </c>
       <c r="P104" s="58">
         <f t="shared" si="10"/>
-        <v>2.9874999999999998</v>
+        <v>3.2124999999999999</v>
       </c>
     </row>
     <row r="105" spans="1:16" s="50" customFormat="1" x14ac:dyDescent="0.2">
@@ -18993,19 +18993,19 @@
       </c>
       <c r="C106" s="50">
         <f>(AVERAGE(E103:G103)/AVERAGE(E102:G102))*100</f>
-        <v>102.52083333333333</v>
+        <v>91.270833333333329</v>
       </c>
       <c r="D106" s="50">
         <f>(AVERAGE(H103:J103)/AVERAGE(H102:J102))*100</f>
-        <v>112.16666666666666</v>
+        <v>100.91666666666666</v>
       </c>
       <c r="E106" s="50">
         <f>(AVERAGE(K103:M103)/AVERAGE(K102:M102))*100</f>
-        <v>56.145833333333329</v>
+        <v>44.895833333333336</v>
       </c>
       <c r="F106" s="50">
         <f>(AVERAGE(N103:P103)/AVERAGE(N102:P102))*100</f>
-        <v>28.4375</v>
+        <v>20.9375</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.2">
@@ -19147,15 +19147,15 @@
       </c>
       <c r="B113">
         <f>SD!C83</f>
-        <v>5.0875000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C113">
         <f>SD!D83</f>
-        <v>5.4625000000000004</v>
+        <v>5.2750000000000004</v>
       </c>
       <c r="D113">
         <f>SD!E83</f>
-        <v>5.1375000000000002</v>
+        <v>4.95</v>
       </c>
       <c r="E113">
         <f>SD!F83</f>
@@ -19163,39 +19163,39 @@
       </c>
       <c r="F113">
         <f>SD!G83</f>
-        <v>5.9024999999999999</v>
+        <v>5.4024999999999999</v>
       </c>
       <c r="G113">
         <f>SD!H83</f>
-        <v>5.54</v>
+        <v>5.04</v>
       </c>
       <c r="H113">
         <f>SD!I83</f>
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="I113">
         <f>SD!J83</f>
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="J113">
         <f>SD!K83</f>
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="K113">
         <f>SD!L83</f>
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="L113">
         <f>SD!M83</f>
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="M113">
         <f>SD!N83</f>
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="N113">
         <f>SD!O83</f>
-        <v>3.4024999999999999</v>
+        <v>3.1524999999999999</v>
       </c>
       <c r="O113">
         <f>SD!P83</f>
@@ -19212,15 +19212,15 @@
       </c>
       <c r="B114" s="58">
         <f>B112-B113</f>
-        <v>-8.7500000000000355E-2</v>
+        <v>9.9999999999999645E-2</v>
       </c>
       <c r="C114" s="58">
         <f t="shared" ref="C114:P114" si="12">C112-C113</f>
-        <v>0.53749999999999964</v>
+        <v>0.72499999999999964</v>
       </c>
       <c r="D114" s="58">
         <f t="shared" si="12"/>
-        <v>-0.13750000000000018</v>
+        <v>4.9999999999999822E-2</v>
       </c>
       <c r="E114" s="58">
         <f t="shared" si="12"/>
@@ -19228,39 +19228,39 @@
       </c>
       <c r="F114" s="58">
         <f t="shared" si="12"/>
-        <v>-0.90249999999999986</v>
+        <v>-0.40249999999999986</v>
       </c>
       <c r="G114" s="58">
         <f t="shared" si="12"/>
-        <v>-0.54</v>
+        <v>-4.0000000000000036E-2</v>
       </c>
       <c r="H114" s="58">
         <f t="shared" si="12"/>
-        <v>-0.11500000000000021</v>
+        <v>0.38499999999999979</v>
       </c>
       <c r="I114" s="58">
         <f t="shared" si="12"/>
-        <v>-0.11500000000000021</v>
+        <v>0.38499999999999979</v>
       </c>
       <c r="J114" s="58">
         <f t="shared" si="12"/>
-        <v>-0.11500000000000021</v>
+        <v>0.38499999999999979</v>
       </c>
       <c r="K114" s="58">
         <f t="shared" si="12"/>
-        <v>1.3475000000000001</v>
+        <v>1.6974999999999998</v>
       </c>
       <c r="L114" s="58">
         <f t="shared" si="12"/>
-        <v>1.3475000000000001</v>
+        <v>1.6974999999999998</v>
       </c>
       <c r="M114" s="58">
         <f t="shared" si="12"/>
-        <v>1.3475000000000001</v>
+        <v>1.6974999999999998</v>
       </c>
       <c r="N114" s="58">
         <f t="shared" si="12"/>
-        <v>1.5975000000000001</v>
+        <v>1.8475000000000001</v>
       </c>
       <c r="O114" s="58">
         <f t="shared" si="12"/>
@@ -19300,23 +19300,23 @@
       </c>
       <c r="B116" s="50">
         <f>(AVERAGE(B113:D113)/AVERAGE(B112:D112))*100</f>
-        <v>98.046875000000014</v>
+        <v>94.531250000000014</v>
       </c>
       <c r="C116" s="50">
         <f>(AVERAGE(E113:G113)/AVERAGE(E112:G112))*100</f>
-        <v>108.98333333333335</v>
+        <v>102.31666666666668</v>
       </c>
       <c r="D116" s="50">
         <f>(AVERAGE(H113:J113)/AVERAGE(H112:J112))*100</f>
-        <v>102.30000000000001</v>
+        <v>92.300000000000011</v>
       </c>
       <c r="E116" s="50">
         <f>(AVERAGE(K113:M113)/AVERAGE(K112:M112))*100</f>
-        <v>73.05</v>
+        <v>66.050000000000011</v>
       </c>
       <c r="F116" s="50">
         <f>(AVERAGE(N113:P113)/AVERAGE(N112:P112))*100</f>
-        <v>64.716666666666669</v>
+        <v>63.05</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.2">
@@ -19474,23 +19474,23 @@
       </c>
       <c r="F123">
         <f>SD!G85</f>
-        <v>20.76</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="G123">
         <f>SD!H85</f>
-        <v>20.434999999999999</v>
+        <v>17.434999999999999</v>
       </c>
       <c r="H123">
         <f>SD!I85</f>
-        <v>20.350000000000001</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="I123">
         <f>SD!J85</f>
-        <v>18.074999999999999</v>
+        <v>15.074999999999999</v>
       </c>
       <c r="J123">
         <f>SD!K85</f>
-        <v>17.824999999999999</v>
+        <v>14.824999999999999</v>
       </c>
       <c r="K123">
         <f>SD!L85</f>
@@ -19539,23 +19539,23 @@
       </c>
       <c r="F124" s="58">
         <f t="shared" si="14"/>
-        <v>-2.7600000000000016</v>
+        <v>0.23999999999999844</v>
       </c>
       <c r="G124" s="58">
         <f t="shared" si="14"/>
-        <v>-2.4349999999999987</v>
+        <v>0.56500000000000128</v>
       </c>
       <c r="H124" s="58">
         <f t="shared" si="14"/>
-        <v>-2.3500000000000014</v>
+        <v>0.64999999999999858</v>
       </c>
       <c r="I124" s="58">
         <f t="shared" si="14"/>
-        <v>-7.4999999999999289E-2</v>
+        <v>2.9250000000000007</v>
       </c>
       <c r="J124" s="58">
         <f t="shared" si="14"/>
-        <v>0.17500000000000071</v>
+        <v>3.1750000000000007</v>
       </c>
       <c r="K124" s="58">
         <f t="shared" si="14"/>
@@ -19615,11 +19615,11 @@
       </c>
       <c r="C126" s="50">
         <f>(AVERAGE(E123:G123)/AVERAGE(E122:G122))*100</f>
-        <v>106.02777777777777</v>
+        <v>94.916666666666643</v>
       </c>
       <c r="D126" s="50">
         <f>(AVERAGE(H123:J123)/AVERAGE(H122:J122))*100</f>
-        <v>104.16666666666667</v>
+        <v>87.5</v>
       </c>
       <c r="E126" s="50">
         <f>(AVERAGE(K123:M123)/AVERAGE(K122:M122))*100</f>
@@ -19817,15 +19817,15 @@
       </c>
       <c r="N133">
         <f>SD!O93</f>
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
       <c r="O133">
         <f>SD!P93</f>
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
       <c r="P133">
         <f>SD!Q93</f>
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="134" spans="1:16" s="57" customFormat="1" x14ac:dyDescent="0.2">
@@ -19882,15 +19882,15 @@
       </c>
       <c r="N134" s="58">
         <f t="shared" si="16"/>
-        <v>-0.88499999999999979</v>
+        <v>0.27</v>
       </c>
       <c r="O134" s="58">
         <f t="shared" si="16"/>
-        <v>-0.88499999999999979</v>
+        <v>0.27</v>
       </c>
       <c r="P134" s="58">
         <f t="shared" si="16"/>
-        <v>-0.88499999999999979</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="135" spans="1:16" s="50" customFormat="1" x14ac:dyDescent="0.2">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="F136" s="50">
         <f>(AVERAGE(N133:P133)/AVERAGE(N132:P132))*100</f>
-        <v>122.125</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.2">
@@ -20010,63 +20010,63 @@
       </c>
       <c r="B152">
         <f>SD!C6*100</f>
-        <v>90.98</v>
+        <v>90.33</v>
       </c>
       <c r="C152">
         <f>SD!D6*100</f>
-        <v>92.43</v>
+        <v>91.69</v>
       </c>
       <c r="D152">
         <f>SD!E6*100</f>
-        <v>90.22</v>
+        <v>89.24</v>
       </c>
       <c r="E152">
         <f>SD!F6*100</f>
-        <v>87.63</v>
+        <v>85.79</v>
       </c>
       <c r="F152">
         <f>SD!G6*100</f>
-        <v>103.02</v>
+        <v>93.210000000000008</v>
       </c>
       <c r="G152">
         <f>SD!H6*100</f>
-        <v>101.16000000000001</v>
+        <v>91.490000000000009</v>
       </c>
       <c r="H152">
         <f>SD!I6*100</f>
-        <v>101.86</v>
+        <v>93.47</v>
       </c>
       <c r="I152">
         <f>SD!J6*100</f>
-        <v>95.009999999999991</v>
+        <v>86.72</v>
       </c>
       <c r="J152">
         <f>SD!K6*100</f>
-        <v>92.53</v>
+        <v>84.33</v>
       </c>
       <c r="K152">
         <f>SD!L6*100</f>
-        <v>70.569999999999993</v>
+        <v>68.27</v>
       </c>
       <c r="L152">
         <f>SD!M6*100</f>
-        <v>68.7</v>
+        <v>66.490000000000009</v>
       </c>
       <c r="M152">
         <f>SD!N6*100</f>
-        <v>67.849999999999994</v>
+        <v>65.649999999999991</v>
       </c>
       <c r="N152">
         <f>SD!O6*100</f>
-        <v>41.78</v>
+        <v>37.869999999999997</v>
       </c>
       <c r="O152">
         <f>SD!P6*100</f>
-        <v>39.97</v>
+        <v>37.130000000000003</v>
       </c>
       <c r="P152">
         <f>SD!Q6*100</f>
-        <v>39.97</v>
+        <v>37.130000000000003</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -20088,51 +20088,51 @@
       </c>
       <c r="E153">
         <f>SD!F7</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F153">
         <f>SD!G7</f>
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G153">
         <f>SD!H7</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H153">
         <f>SD!I7</f>
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I153">
         <f>SD!J7</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J153">
         <f>SD!K7</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K153">
         <f>SD!L7</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L153">
         <f>SD!M7</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M153">
         <f>SD!N7</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N153">
         <f>SD!O7</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O153">
         <f>SD!P7</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P153">
         <f>SD!Q7</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -20164,23 +20164,23 @@
       </c>
       <c r="B156">
         <f>SD!C36*100</f>
-        <v>91.2</v>
+        <v>90.4</v>
       </c>
       <c r="C156">
         <f>SD!D36*100</f>
-        <v>97.27</v>
+        <v>90.16</v>
       </c>
       <c r="D156">
         <f>SD!E36*100</f>
-        <v>96.460000000000008</v>
+        <v>88.17</v>
       </c>
       <c r="E156">
         <f>SD!F36*100</f>
-        <v>69.040000000000006</v>
+        <v>66.8</v>
       </c>
       <c r="F156">
         <f>SD!G36*100</f>
-        <v>40.57</v>
+        <v>37.380000000000003</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -20190,23 +20190,23 @@
       </c>
       <c r="B157">
         <f>SD!C37</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C157">
         <f>SD!D37</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D157">
         <f>SD!E37</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E157">
         <f>SD!F37</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F157">
         <f>SD!G37</f>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -55294,63 +55294,63 @@
       </c>
       <c r="B3">
         <f>ALL!C4</f>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <f>ALL!D4</f>
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3">
         <f>ALL!E4</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E3">
         <f>ALL!F4</f>
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F3">
         <f>ALL!G4</f>
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G3">
         <f>ALL!H4</f>
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H3">
         <f>ALL!I4</f>
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I3">
         <f>ALL!J4</f>
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J3">
         <f>ALL!K4</f>
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K3">
         <f>ALL!L4</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L3">
         <f>ALL!M4</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="M3">
         <f>ALL!N4</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N3">
         <f>ALL!O4</f>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O3">
         <f>ALL!P4</f>
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P3">
         <f>ALL!Q4</f>
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AA3" t="str">
         <f t="shared" ref="AA3:AA4" si="0">_xlfn.CONCAT("% ",A3)</f>
@@ -55358,23 +55358,23 @@
       </c>
       <c r="AB3">
         <f>SUM(B3:D3)/SUM(B2:D2)*100</f>
-        <v>93.449781659388648</v>
+        <v>92.576419213973807</v>
       </c>
       <c r="AC3">
         <f>SUM(E3:G3)/SUM(E2:G2)*100</f>
-        <v>91.612903225806448</v>
+        <v>87.956989247311824</v>
       </c>
       <c r="AD3">
         <f>SUM(H3:J3)/SUM(H2:J2)*100</f>
-        <v>87.878787878787875</v>
+        <v>83.549783549783555</v>
       </c>
       <c r="AE3">
         <f>SUM(K3:M3)/SUM(K2:M2)*100</f>
-        <v>68.297872340425542</v>
+        <v>66.38297872340425</v>
       </c>
       <c r="AF3">
         <f>SUM(N3:P3)/SUM(N2:P2)*100</f>
-        <v>54.989384288747345</v>
+        <v>53.290870488322717</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
@@ -55653,63 +55653,63 @@
       </c>
       <c r="B13">
         <f>DV!C4</f>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13">
         <f>DV!D4</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13">
         <f>DV!E4</f>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E13">
         <f>DV!F4</f>
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F13">
         <f>DV!G4</f>
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G13">
         <f>DV!H4</f>
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H13">
         <f>DV!I4</f>
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I13">
         <f>DV!J4</f>
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J13">
         <f>DV!K4</f>
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K13">
         <f>DV!L4</f>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L13">
         <f>DV!M4</f>
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M13">
         <f>DV!N4</f>
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N13">
         <f>DV!O4</f>
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O13">
         <f>DV!P4</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P13">
         <f>DV!Q4</f>
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AA13" t="str">
         <f t="shared" ref="AA13:AA14" si="2">_xlfn.CONCAT("% ",A13)</f>
@@ -55717,23 +55717,23 @@
       </c>
       <c r="AB13">
         <f>SUM(B13:D13)/SUM(B12:D12)*100</f>
-        <v>94.42815249266863</v>
+        <v>93.548387096774192</v>
       </c>
       <c r="AC13">
         <f>SUM(E13:G13)/SUM(E12:G12)*100</f>
-        <v>92.090395480225979</v>
+        <v>87.288135593220346</v>
       </c>
       <c r="AD13">
         <f>SUM(H13:J13)/SUM(H12:J12)*100</f>
-        <v>87.288135593220346</v>
+        <v>81.355932203389841</v>
       </c>
       <c r="AE13">
         <f>SUM(K13:M13)/SUM(K12:M12)*100</f>
-        <v>64.689265536723155</v>
+        <v>62.146892655367239</v>
       </c>
       <c r="AF13">
         <f>SUM(N13:P13)/SUM(N12:P12)*100</f>
-        <v>48.305084745762713</v>
+        <v>46.045197740112989</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.2">
@@ -57098,7 +57098,7 @@
       </c>
       <c r="B53">
         <f>PSE!C4</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C53">
         <f>PSE!D4</f>
@@ -57110,51 +57110,51 @@
       </c>
       <c r="E53">
         <f>PSE!F4</f>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F53">
         <f>PSE!G4</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G53">
         <f>PSE!H4</f>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H53">
         <f>PSE!I4</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I53">
         <f>PSE!J4</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J53">
         <f>PSE!K4</f>
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K53">
         <f>PSE!L4</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L53">
         <f>PSE!M4</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M53">
         <f>PSE!N4</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N53">
         <f>PSE!O4</f>
-        <v>24.625</v>
+        <v>23.774999999999999</v>
       </c>
       <c r="O53">
         <f>PSE!P4</f>
-        <v>23.425000000000001</v>
+        <v>22.574999999999999</v>
       </c>
       <c r="P53">
         <f>PSE!Q4</f>
-        <v>22.75</v>
+        <v>21.9</v>
       </c>
       <c r="AA53" t="str">
         <f t="shared" ref="AA53:AA54" si="10">_xlfn.CONCAT("% ",A53)</f>
@@ -57162,23 +57162,23 @@
       </c>
       <c r="AB53">
         <f>SUM(B53:D53)/SUM(B52:D52)*100</f>
-        <v>94.444444444444443</v>
+        <v>93.75</v>
       </c>
       <c r="AC53">
         <f>SUM(E53:G53)/SUM(E52:G52)*100</f>
-        <v>87.5</v>
+        <v>83.333333333333343</v>
       </c>
       <c r="AD53">
         <f>SUM(H53:J53)/SUM(H52:J52)*100</f>
-        <v>79.166666666666657</v>
+        <v>73.611111111111114</v>
       </c>
       <c r="AE53">
         <f>SUM(K53:M53)/SUM(K52:M52)*100</f>
-        <v>54.861111111111114</v>
+        <v>52.777777777777779</v>
       </c>
       <c r="AF53">
         <f>SUM(N53:P53)/SUM(N52:P52)*100</f>
-        <v>49.166666666666664</v>
+        <v>47.395833333333329</v>
       </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.2">
@@ -57818,63 +57818,63 @@
       </c>
       <c r="B73">
         <f>PSE!C73</f>
-        <v>38.93</v>
+        <v>38.43</v>
       </c>
       <c r="C73">
         <f>PSE!D73</f>
-        <v>40.28</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="D73">
         <f>PSE!E73</f>
-        <v>36.414999999999999</v>
+        <v>35.564999999999998</v>
       </c>
       <c r="E73">
         <f>PSE!F73</f>
-        <v>35.39</v>
+        <v>34.54</v>
       </c>
       <c r="F73">
         <f>PSE!G73</f>
-        <v>35.924999999999997</v>
+        <v>34.075000000000003</v>
       </c>
       <c r="G73">
         <f>PSE!H73</f>
-        <v>34.15</v>
+        <v>31.6</v>
       </c>
       <c r="H73">
         <f>PSE!I73</f>
-        <v>31.074999999999999</v>
+        <v>28.875</v>
       </c>
       <c r="I73">
         <f>PSE!J73</f>
-        <v>31.05</v>
+        <v>28.4</v>
       </c>
       <c r="J73">
         <f>PSE!K73</f>
-        <v>30.65</v>
+        <v>28</v>
       </c>
       <c r="K73">
         <f>PSE!L73</f>
-        <v>19.350000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="L73">
         <f>PSE!M73</f>
-        <v>19.350000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="M73">
         <f>PSE!N73</f>
-        <v>20.225000000000001</v>
+        <v>18.875</v>
       </c>
       <c r="N73">
         <f>PSE!O73</f>
-        <v>17.625</v>
+        <v>16.774999999999999</v>
       </c>
       <c r="O73">
         <f>PSE!P73</f>
-        <v>16.425000000000001</v>
+        <v>15.574999999999999</v>
       </c>
       <c r="P73">
         <f>PSE!Q73</f>
-        <v>15.75</v>
+        <v>14.9</v>
       </c>
       <c r="AA73" t="str">
         <f t="shared" ref="AA73:AA74" si="14">_xlfn.CONCAT("% ",A73)</f>
@@ -57882,23 +57882,23 @@
       </c>
       <c r="AB73">
         <f>SUM(B73:D73)/SUM(B72:D72)*100</f>
-        <v>94.004065040650403</v>
+        <v>92.378048780487802</v>
       </c>
       <c r="AC73">
         <f>SUM(E73:G73)/SUM(E72:G72)*100</f>
-        <v>85.743902439024396</v>
+        <v>81.475609756097569</v>
       </c>
       <c r="AD73">
         <f>SUM(H73:J73)/SUM(H72:J72)*100</f>
-        <v>75.426829268292678</v>
+        <v>69.32926829268294</v>
       </c>
       <c r="AE73">
         <f>SUM(K73:M73)/SUM(K72:M72)*100</f>
-        <v>47.906504065040657</v>
+        <v>43.800813008130078</v>
       </c>
       <c r="AF73">
         <f>SUM(N73:P73)/SUM(N72:P72)*100</f>
-        <v>40.487804878048777</v>
+        <v>38.414634146341456</v>
       </c>
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.2">
@@ -58190,51 +58190,51 @@
       </c>
       <c r="E83">
         <f>SD!F4</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F83">
         <f>SD!G4</f>
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G83">
         <f>SD!H4</f>
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H83">
         <f>SD!I4</f>
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I83">
         <f>SD!J4</f>
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J83">
         <f>SD!K4</f>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K83">
         <f>SD!L4</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L83">
         <f>SD!M4</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M83">
         <f>SD!N4</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N83">
         <f>SD!O4</f>
-        <v>22.143750000000001</v>
+        <v>20.07</v>
       </c>
       <c r="O83">
         <f>SD!P4</f>
-        <v>21.184999999999999</v>
+        <v>19.68</v>
       </c>
       <c r="P83">
         <f>SD!Q4</f>
-        <v>21.184999999999999</v>
+        <v>19.68</v>
       </c>
       <c r="AA83" t="str">
         <f t="shared" ref="AA83:AA84" si="16">_xlfn.CONCAT("% ",A83)</f>
@@ -58246,19 +58246,19 @@
       </c>
       <c r="AC83">
         <f>SUM(E83:G83)/SUM(E82:G82)*100</f>
-        <v>97.484276729559753</v>
+        <v>89.308176100628927</v>
       </c>
       <c r="AD83">
         <f>SUM(H83:J83)/SUM(H82:J82)*100</f>
-        <v>96.226415094339629</v>
+        <v>88.679245283018872</v>
       </c>
       <c r="AE83">
         <f>SUM(K83:M83)/SUM(K82:M82)*100</f>
-        <v>68.55345911949685</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="AF83">
         <f>SUM(N83:P83)/SUM(N82:P82)*100</f>
-        <v>40.574685534591197</v>
+        <v>37.377358490566039</v>
       </c>
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.2">
@@ -58554,39 +58554,39 @@
       </c>
       <c r="F93">
         <f>SD!G67</f>
-        <v>4.8250000000000002</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G93">
         <f>SD!H67</f>
-        <v>4.8875000000000002</v>
+        <v>4.1624999999999996</v>
       </c>
       <c r="H93">
         <f>SD!I67</f>
-        <v>5.3312499999999998</v>
+        <v>5.2374999999999998</v>
       </c>
       <c r="I93">
         <f>SD!J67</f>
-        <v>4.5812499999999998</v>
+        <v>4.4874999999999998</v>
       </c>
       <c r="J93">
         <f>SD!K67</f>
-        <v>4.5187499999999998</v>
+        <v>4.4249999999999998</v>
       </c>
       <c r="K93">
         <f>SD!L67</f>
-        <v>3.703125</v>
+        <v>3.609375</v>
       </c>
       <c r="L93">
         <f>SD!M67</f>
-        <v>3.2281249999999999</v>
+        <v>3.1343749999999999</v>
       </c>
       <c r="M93">
         <f>SD!N67</f>
-        <v>3.2281249999999999</v>
+        <v>3.1343749999999999</v>
       </c>
       <c r="N93">
         <f>SD!O67</f>
-        <v>3.0562499999999999</v>
+        <v>2.9624999999999999</v>
       </c>
       <c r="O93">
         <f>SD!P67</f>
@@ -58606,19 +58606,19 @@
       </c>
       <c r="AC93">
         <f>SUM(E93:G93)/SUM(E92:G92)*100</f>
-        <v>107.60416666666669</v>
+        <v>95.520833333333314</v>
       </c>
       <c r="AD93">
         <f>SUM(H93:J93)/SUM(H92:J92)*100</f>
-        <v>120.26041666666664</v>
+        <v>117.91666666666664</v>
       </c>
       <c r="AE93">
         <f>SUM(K93:M93)/SUM(K92:M92)*100</f>
-        <v>84.661458333333343</v>
+        <v>82.317708333333343</v>
       </c>
       <c r="AF93">
         <f>SUM(N93:P93)/SUM(N92:P92)*100</f>
-        <v>74.010416666666671</v>
+        <v>73.229166666666671</v>
       </c>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.2">
@@ -58906,7 +58906,7 @@
       </c>
       <c r="D103">
         <f>SD!E69</f>
-        <v>6.42</v>
+        <v>6.3825000000000003</v>
       </c>
       <c r="E103">
         <f>SD!F69</f>
@@ -58962,7 +58962,7 @@
       </c>
       <c r="AB103">
         <f>SUM(B103:D103)/SUM(B102:D102)*100</f>
-        <v>86.928571428571445</v>
+        <v>86.75</v>
       </c>
       <c r="AC103">
         <f>SUM(E103:G103)/SUM(E102:G102)*100</f>
@@ -59258,63 +59258,63 @@
       </c>
       <c r="B113">
         <f>SD!C75</f>
-        <v>3.9275000000000002</v>
+        <v>3.8650000000000002</v>
       </c>
       <c r="C113">
         <f>SD!D75</f>
-        <v>3.5049999999999999</v>
+        <v>3.38</v>
       </c>
       <c r="D113">
         <f>SD!E75</f>
-        <v>3.9049999999999998</v>
+        <v>3.68</v>
       </c>
       <c r="E113">
         <f>SD!F75</f>
-        <v>4.085</v>
+        <v>3.81</v>
       </c>
       <c r="F113">
         <f>SD!G75</f>
-        <v>4.2625000000000002</v>
+        <v>3.9874999999999998</v>
       </c>
       <c r="G113">
         <f>SD!H75</f>
-        <v>3.7749999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="H113">
         <f>SD!I75</f>
-        <v>3.7749999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="I113">
         <f>SD!J75</f>
-        <v>3.7749999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="J113">
         <f>SD!K75</f>
-        <v>3.65</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="K113">
         <f>SD!L75</f>
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="L113">
         <f>SD!M75</f>
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="M113">
         <f>SD!N75</f>
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="N113">
         <f>SD!O75</f>
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="O113">
         <f>SD!P75</f>
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="P113">
         <f>SD!Q75</f>
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="AA113" t="str">
         <f t="shared" ref="AA113:AA114" si="22">_xlfn.CONCAT("% ",A113)</f>
@@ -59322,23 +59322,23 @@
       </c>
       <c r="AB113">
         <f>SUM(B113:D113)/SUM(B112:D112)*100</f>
-        <v>94.479166666666671</v>
+        <v>91.041666666666671</v>
       </c>
       <c r="AC113">
         <f>SUM(E113:G113)/SUM(E112:G112)*100</f>
-        <v>101.02083333333334</v>
+        <v>94.145833333333329</v>
       </c>
       <c r="AD113">
         <f>SUM(H113:J113)/SUM(H112:J112)*100</f>
-        <v>93.333333333333329</v>
+        <v>88.125</v>
       </c>
       <c r="AE113">
         <f>SUM(K113:M113)/SUM(K112:M112)*100</f>
-        <v>73.583333333333329</v>
+        <v>68.583333333333343</v>
       </c>
       <c r="AF113">
         <f>SUM(N113:P113)/SUM(N112:P112)*100</f>
-        <v>7.166666666666667</v>
+        <v>5.916666666666667</v>
       </c>
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.2">
@@ -59618,63 +59618,63 @@
       </c>
       <c r="B123">
         <f>SD!C77</f>
-        <v>2.605</v>
+        <v>2.5550000000000002</v>
       </c>
       <c r="C123">
         <f>SD!D77</f>
-        <v>2.6349999999999998</v>
+        <v>2.585</v>
       </c>
       <c r="D123">
         <f>SD!E77</f>
-        <v>2.2650000000000001</v>
+        <v>2.2149999999999999</v>
       </c>
       <c r="E123">
         <f>SD!F77</f>
-        <v>2.4624999999999999</v>
+        <v>2.2625000000000002</v>
       </c>
       <c r="F123">
         <f>SD!G77</f>
-        <v>2.4624999999999999</v>
+        <v>2.2625000000000002</v>
       </c>
       <c r="G123">
         <f>SD!H77</f>
-        <v>2.4424999999999999</v>
+        <v>2.2925</v>
       </c>
       <c r="H123">
         <f>SD!I77</f>
-        <v>2.5049999999999999</v>
+        <v>2.355</v>
       </c>
       <c r="I123">
         <f>SD!J77</f>
-        <v>2.3050000000000002</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="J123">
         <f>SD!K77</f>
-        <v>2.3050000000000002</v>
+        <v>2.2050000000000001</v>
       </c>
       <c r="K123">
         <f>SD!L77</f>
-        <v>0.92500000000000004</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="L123">
         <f>SD!M77</f>
-        <v>0.875</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="M123">
         <f>SD!N77</f>
-        <v>0.875</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="N123">
         <f>SD!O77</f>
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="O123">
         <f>SD!P77</f>
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="P123">
         <f>SD!Q77</f>
-        <v>0.625</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="AA123" t="str">
         <f t="shared" ref="AA123:AA124" si="24">_xlfn.CONCAT("% ",A123)</f>
@@ -59682,23 +59682,23 @@
       </c>
       <c r="AB123">
         <f>SUM(B123:D123)/SUM(B122:D122)*100</f>
-        <v>125.08333333333334</v>
+        <v>122.58333333333333</v>
       </c>
       <c r="AC123">
         <f>SUM(E123:G123)/SUM(E122:G122)*100</f>
-        <v>81.8611111111111</v>
+        <v>75.75</v>
       </c>
       <c r="AD123">
         <f>SUM(H123:J123)/SUM(H122:J122)*100</f>
-        <v>79.055555555555557</v>
+        <v>75.166666666666671</v>
       </c>
       <c r="AE123">
         <f>SUM(K123:M123)/SUM(K122:M122)*100</f>
-        <v>29.722222222222221</v>
+        <v>27.499999999999996</v>
       </c>
       <c r="AF123">
         <f>SUM(N123:P123)/SUM(N122:P122)*100</f>
-        <v>20.833333333333336</v>
+        <v>19.166666666666664</v>
       </c>
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.2">
@@ -59990,51 +59990,51 @@
       </c>
       <c r="E133">
         <f>SD!F79</f>
-        <v>2.2075</v>
+        <v>2.1575000000000002</v>
       </c>
       <c r="F133">
         <f>SD!G79</f>
-        <v>2.1825000000000001</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="G133">
         <f>SD!H79</f>
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="H133">
         <f>SD!I79</f>
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="I133">
         <f>SD!J79</f>
-        <v>2.1575000000000002</v>
+        <v>2.1324999999999998</v>
       </c>
       <c r="J133">
         <f>SD!K79</f>
-        <v>1.8574999999999999</v>
+        <v>1.8325</v>
       </c>
       <c r="K133">
         <f>SD!L79</f>
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="L133">
         <f>SD!M79</f>
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="M133">
         <f>SD!N79</f>
-        <v>1.3374999999999999</v>
+        <v>1.3125</v>
       </c>
       <c r="N133">
         <f>SD!O79</f>
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="O133">
         <f>SD!P79</f>
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="P133">
         <f>SD!Q79</f>
-        <v>0.53749999999999998</v>
+        <v>0.51249999999999996</v>
       </c>
       <c r="AA133" t="str">
         <f t="shared" ref="AA133:AA134" si="26">_xlfn.CONCAT("% ",A133)</f>
@@ -60046,19 +60046,19 @@
       </c>
       <c r="AC133">
         <f>SUM(E133:G133)/SUM(E132:G132)*100</f>
-        <v>72.750000000000014</v>
+        <v>71.361111111111114</v>
       </c>
       <c r="AD133">
         <f>SUM(H133:J133)/SUM(H132:J132)*100</f>
-        <v>68.583333333333343</v>
+        <v>67.75</v>
       </c>
       <c r="AE133">
         <f>SUM(K133:M133)/SUM(K132:M132)*100</f>
-        <v>44.583333333333321</v>
+        <v>43.75</v>
       </c>
       <c r="AF133">
         <f>SUM(N133:P133)/SUM(N132:P132)*100</f>
-        <v>17.916666666666664</v>
+        <v>17.083333333333332</v>
       </c>
     </row>
     <row r="134" spans="1:32" x14ac:dyDescent="0.2">
@@ -60350,51 +60350,51 @@
       </c>
       <c r="E143">
         <f>SD!F81</f>
-        <v>3.5049999999999999</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="F143">
         <f>SD!G81</f>
-        <v>4.3550000000000004</v>
+        <v>3.9049999999999998</v>
       </c>
       <c r="G143">
         <f>SD!H81</f>
-        <v>4.4424999999999999</v>
+        <v>3.9925000000000002</v>
       </c>
       <c r="H143">
         <f>SD!I81</f>
-        <v>4.8949999999999996</v>
+        <v>4.4450000000000003</v>
       </c>
       <c r="I143">
         <f>SD!J81</f>
-        <v>4.5449999999999999</v>
+        <v>4.0949999999999998</v>
       </c>
       <c r="J143">
         <f>SD!K81</f>
-        <v>4.0199999999999996</v>
+        <v>3.57</v>
       </c>
       <c r="K143">
         <f>SD!L81</f>
-        <v>2.5625</v>
+        <v>2.1124999999999998</v>
       </c>
       <c r="L143">
         <f>SD!M81</f>
-        <v>2.2374999999999998</v>
+        <v>1.7875000000000001</v>
       </c>
       <c r="M143">
         <f>SD!N81</f>
-        <v>1.9375</v>
+        <v>1.4875</v>
       </c>
       <c r="N143">
         <f>SD!O81</f>
-        <v>1.3875</v>
+        <v>0.9375</v>
       </c>
       <c r="O143">
         <f>SD!P81</f>
-        <v>1.0125</v>
+        <v>0.78749999999999998</v>
       </c>
       <c r="P143">
         <f>SD!Q81</f>
-        <v>1.0125</v>
+        <v>0.78749999999999998</v>
       </c>
       <c r="AA143" t="str">
         <f t="shared" ref="AA143:AA144" si="28">_xlfn.CONCAT("% ",A143)</f>
@@ -60406,19 +60406,19 @@
       </c>
       <c r="AC143">
         <f>SUM(E143:G143)/SUM(E142:G142)*100</f>
-        <v>102.52083333333333</v>
+        <v>91.270833333333329</v>
       </c>
       <c r="AD143">
         <f>SUM(H143:J143)/SUM(H142:J142)*100</f>
-        <v>112.16666666666666</v>
+        <v>100.91666666666666</v>
       </c>
       <c r="AE143">
         <f>SUM(K143:M143)/SUM(K142:M142)*100</f>
-        <v>56.145833333333329</v>
+        <v>44.895833333333336</v>
       </c>
       <c r="AF143">
         <f>SUM(N143:P143)/SUM(N142:P142)*100</f>
-        <v>28.4375</v>
+        <v>20.9375</v>
       </c>
     </row>
     <row r="144" spans="1:32" x14ac:dyDescent="0.2">
@@ -60698,15 +60698,15 @@
       </c>
       <c r="B153">
         <f>SD!C83</f>
-        <v>5.0875000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C153">
         <f>SD!D83</f>
-        <v>5.4625000000000004</v>
+        <v>5.2750000000000004</v>
       </c>
       <c r="D153">
         <f>SD!E83</f>
-        <v>5.1375000000000002</v>
+        <v>4.95</v>
       </c>
       <c r="E153">
         <f>SD!F83</f>
@@ -60714,39 +60714,39 @@
       </c>
       <c r="F153">
         <f>SD!G83</f>
-        <v>5.9024999999999999</v>
+        <v>5.4024999999999999</v>
       </c>
       <c r="G153">
         <f>SD!H83</f>
-        <v>5.54</v>
+        <v>5.04</v>
       </c>
       <c r="H153">
         <f>SD!I83</f>
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="I153">
         <f>SD!J83</f>
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="J153">
         <f>SD!K83</f>
-        <v>5.1150000000000002</v>
+        <v>4.6150000000000002</v>
       </c>
       <c r="K153">
         <f>SD!L83</f>
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="L153">
         <f>SD!M83</f>
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="M153">
         <f>SD!N83</f>
-        <v>3.6524999999999999</v>
+        <v>3.3025000000000002</v>
       </c>
       <c r="N153">
         <f>SD!O83</f>
-        <v>3.4024999999999999</v>
+        <v>3.1524999999999999</v>
       </c>
       <c r="O153">
         <f>SD!P83</f>
@@ -60762,23 +60762,23 @@
       </c>
       <c r="AB153">
         <f>SUM(B153:D153)/SUM(B152:D152)*100</f>
-        <v>98.046875</v>
+        <v>94.53125</v>
       </c>
       <c r="AC153">
         <f>SUM(E153:G153)/SUM(E152:G152)*100</f>
-        <v>108.98333333333335</v>
+        <v>102.31666666666668</v>
       </c>
       <c r="AD153">
         <f>SUM(H153:J153)/SUM(H152:J152)*100</f>
-        <v>102.30000000000001</v>
+        <v>92.300000000000011</v>
       </c>
       <c r="AE153">
         <f>SUM(K153:M153)/SUM(K152:M152)*100</f>
-        <v>73.05</v>
+        <v>66.050000000000011</v>
       </c>
       <c r="AF153">
         <f>SUM(N153:P153)/SUM(N152:P152)*100</f>
-        <v>64.716666666666669</v>
+        <v>63.05</v>
       </c>
     </row>
     <row r="154" spans="1:32" x14ac:dyDescent="0.2">
@@ -61074,23 +61074,23 @@
       </c>
       <c r="F163">
         <f>SD!G85</f>
-        <v>20.76</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="G163">
         <f>SD!H85</f>
-        <v>20.434999999999999</v>
+        <v>17.434999999999999</v>
       </c>
       <c r="H163">
         <f>SD!I85</f>
-        <v>20.350000000000001</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="I163">
         <f>SD!J85</f>
-        <v>18.074999999999999</v>
+        <v>15.074999999999999</v>
       </c>
       <c r="J163">
         <f>SD!K85</f>
-        <v>17.824999999999999</v>
+        <v>14.824999999999999</v>
       </c>
       <c r="K163">
         <f>SD!L85</f>
@@ -61126,11 +61126,11 @@
       </c>
       <c r="AC163">
         <f>SUM(E163:G163)/SUM(E162:G162)*100</f>
-        <v>106.02777777777777</v>
+        <v>94.916666666666657</v>
       </c>
       <c r="AD163">
         <f>SUM(H163:J163)/SUM(H162:J162)*100</f>
-        <v>104.16666666666667</v>
+        <v>87.5</v>
       </c>
       <c r="AE163">
         <f>SUM(K163:M163)/SUM(K162:M162)*100</f>
@@ -61466,15 +61466,15 @@
       </c>
       <c r="N173">
         <f>SD!O93</f>
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
       <c r="O173">
         <f>SD!P93</f>
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
       <c r="P173">
         <f>SD!Q93</f>
-        <v>4.8849999999999998</v>
+        <v>3.73</v>
       </c>
       <c r="AA173" t="str">
         <f t="shared" ref="AA173:AA174" si="34">_xlfn.CONCAT("% ",A173)</f>
@@ -61498,7 +61498,7 @@
       </c>
       <c r="AF173">
         <f>SUM(N173:P173)/SUM(N172:P172)*100</f>
-        <v>122.125</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="174" spans="1:32" x14ac:dyDescent="0.2">
@@ -65714,49 +65714,49 @@
         <v>18</v>
       </c>
       <c r="C4" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D4" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" s="7">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F4" s="7">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G4" s="7">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H4" s="7">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I4" s="7">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J4" s="7">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K4" s="7">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L4" s="7">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="M4" s="7">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N4" s="7">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O4" s="7">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P4" s="7">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Q4" s="7">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -65784,49 +65784,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>0.93810000000000004</v>
+        <v>0.93279999999999996</v>
       </c>
       <c r="D6" s="18">
-        <v>0.94910000000000005</v>
+        <v>0.9425</v>
       </c>
       <c r="E6" s="18">
-        <v>0.91320000000000001</v>
+        <v>0.90449999999999997</v>
       </c>
       <c r="F6" s="18">
-        <v>0.88749999999999996</v>
+        <v>0.87570000000000003</v>
       </c>
       <c r="G6" s="18">
-        <v>0.94450000000000001</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="H6" s="18">
-        <v>0.91469999999999996</v>
+        <v>0.86519999999999997</v>
       </c>
       <c r="I6" s="18">
-        <v>0.89880000000000004</v>
+        <v>0.85560000000000003</v>
       </c>
       <c r="J6" s="18">
-        <v>0.87380000000000002</v>
+        <v>0.82809999999999995</v>
       </c>
       <c r="K6" s="18">
-        <v>0.86299999999999999</v>
+        <v>0.81759999999999999</v>
       </c>
       <c r="L6" s="18">
-        <v>0.68879999999999997</v>
+        <v>0.66910000000000003</v>
       </c>
       <c r="M6" s="18">
-        <v>0.68320000000000003</v>
+        <v>0.66400000000000003</v>
       </c>
       <c r="N6" s="18">
-        <v>0.68100000000000005</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="O6" s="18">
-        <v>0.56059999999999999</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="P6" s="18">
-        <v>0.54600000000000004</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="Q6" s="18">
-        <v>0.54169999999999996</v>
+        <v>0.52669999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -65835,49 +65835,49 @@
         <v>24</v>
       </c>
       <c r="C7" s="19">
+        <v>10</v>
+      </c>
+      <c r="D7" s="19">
         <v>9</v>
       </c>
-      <c r="D7" s="19">
-        <v>8</v>
-      </c>
       <c r="E7" s="19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" s="19">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="19">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H7" s="19">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I7" s="19">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J7" s="19">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K7" s="19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L7" s="19">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M7" s="19">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N7" s="19">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O7" s="19">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P7" s="19">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q7" s="19">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -66016,46 +66016,46 @@
         <v>110</v>
       </c>
       <c r="D11" s="7">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E11" s="7">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F11" s="7">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G11" s="7">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H11" s="7">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I11" s="7">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J11" s="7">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K11" s="7">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L11" s="7">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M11" s="7">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N11" s="7">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O11" s="7">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P11" s="7">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q11" s="7">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -66380,20 +66380,20 @@
       <c r="F19" s="7">
         <v>16</v>
       </c>
-      <c r="G19" s="13">
-        <v>20</v>
-      </c>
-      <c r="H19" s="13">
-        <v>20</v>
-      </c>
-      <c r="I19" s="13">
+      <c r="G19" s="7">
         <v>18</v>
       </c>
+      <c r="H19" s="7">
+        <v>18</v>
+      </c>
+      <c r="I19" s="7">
+        <v>16</v>
+      </c>
       <c r="J19" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K19" s="7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L19" s="7">
         <v>11</v>
@@ -66544,19 +66544,19 @@
         <v>18</v>
       </c>
       <c r="C34" s="20">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D34" s="20">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E34" s="20">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F34" s="20">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G34" s="20">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H34" s="20"/>
     </row>
@@ -66564,19 +66564,19 @@
       <c r="A35" s="16"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24">
-        <v>6.6699999999999995E-2</v>
+        <v>7.3599999999999999E-2</v>
       </c>
       <c r="D35" s="24">
-        <v>8.4400000000000003E-2</v>
+        <v>0.12</v>
       </c>
       <c r="E35" s="24">
-        <v>0.12139999999999999</v>
+        <v>0.16619999999999999</v>
       </c>
       <c r="F35" s="24">
-        <v>0.31569999999999998</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="G35" s="24">
-        <v>0.4506</v>
+        <v>0.46679999999999999</v>
       </c>
       <c r="H35" s="7"/>
     </row>
@@ -66586,19 +66586,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="18">
-        <v>0.93330000000000002</v>
+        <v>0.9264</v>
       </c>
       <c r="D36" s="18">
-        <v>0.91559999999999997</v>
+        <v>0.88</v>
       </c>
       <c r="E36" s="18">
-        <v>0.87860000000000005</v>
+        <v>0.83379999999999999</v>
       </c>
       <c r="F36" s="18">
-        <v>0.68430000000000002</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="G36" s="18">
-        <v>0.5494</v>
+        <v>0.53320000000000001</v>
       </c>
       <c r="H36" s="19"/>
     </row>
@@ -66608,19 +66608,19 @@
         <v>24</v>
       </c>
       <c r="C37" s="19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D37" s="19">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E37" s="19">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F37" s="19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G37" s="19">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H37" s="19"/>
     </row>
@@ -66690,19 +66690,19 @@
         <v>19</v>
       </c>
       <c r="C41" s="20">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D41" s="20">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E41" s="20">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F41" s="20">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G41" s="20">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H41" s="20"/>
     </row>
@@ -66856,11 +66856,11 @@
       <c r="C49" s="20">
         <v>12</v>
       </c>
-      <c r="D49" s="13">
-        <v>19</v>
+      <c r="D49" s="20">
+        <v>17</v>
       </c>
       <c r="E49" s="20">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F49" s="20">
         <v>11</v>
@@ -67087,63 +67087,63 @@
       </c>
       <c r="B4">
         <f>IF(ALL!C4&gt;0,ALL!C4,"")</f>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4">
         <f>IF(ALL!D4&gt;0,ALL!D4,"")</f>
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4">
         <f>IF(ALL!E4&gt;0,ALL!E4,"")</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E4">
         <f>IF(ALL!F4&gt;0,ALL!F4,"")</f>
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F4">
         <f>IF(ALL!G4&gt;0,ALL!G4,"")</f>
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G4">
         <f>IF(ALL!H4&gt;0,ALL!H4,"")</f>
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H4">
         <f>IF(ALL!I4&gt;0,ALL!I4,"")</f>
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I4">
         <f>IF(ALL!J4&gt;0,ALL!J4,"")</f>
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J4">
         <f>IF(ALL!K4&gt;0,ALL!K4,"")</f>
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K4">
         <f>IF(ALL!L4&gt;0,ALL!L4,"")</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L4">
         <f>IF(ALL!M4&gt;0,ALL!M4,"")</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="M4">
         <f>IF(ALL!N4&gt;0,ALL!N4,"")</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N4">
         <f>IF(ALL!O4&gt;0,ALL!O4,"")</f>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O4">
         <f>IF(ALL!P4&gt;0,ALL!P4,"")</f>
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P4">
         <f>IF(ALL!Q4&gt;0,ALL!Q4,"")</f>
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -67157,59 +67157,59 @@
       </c>
       <c r="C5">
         <f>IF(ALL!D11&gt;0,ALL!D11,"")</f>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <f>IF(ALL!E11&gt;0,ALL!E11,"")</f>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5">
         <f>IF(ALL!F11&gt;0,ALL!F11,"")</f>
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F5">
         <f>IF(ALL!G11&gt;0,ALL!G11,"")</f>
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G5">
         <f>IF(ALL!H11&gt;0,ALL!H11,"")</f>
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H5">
         <f>IF(ALL!I11&gt;0,ALL!I11,"")</f>
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I5">
         <f>IF(ALL!J11&gt;0,ALL!J11,"")</f>
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J5">
         <f>IF(ALL!K11&gt;0,ALL!K11,"")</f>
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K5">
         <f>IF(ALL!L11&gt;0,ALL!L11,"")</f>
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L5">
         <f>IF(ALL!M11&gt;0,ALL!M11,"")</f>
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M5">
         <f>IF(ALL!N11&gt;0,ALL!N11,"")</f>
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N5">
         <f>IF(ALL!O11&gt;0,ALL!O11,"")</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O5">
         <f>IF(ALL!P11&gt;0,ALL!P11,"")</f>
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="P5">
         <f>IF(ALL!Q11&gt;0,ALL!Q11,"")</f>
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -67301,23 +67301,23 @@
       </c>
       <c r="F7">
         <f>IF(ALL!G19&gt;0,ALL!G19,"")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <f>IF(ALL!H19&gt;0,ALL!H19,"")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H7">
         <f>IF(ALL!I19&gt;0,ALL!I19,"")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I7">
         <f>IF(ALL!J19&gt;0,ALL!J19,"")</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <f>IF(ALL!K19&gt;0,ALL!K19,"")</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <f>IF(ALL!L19&gt;0,ALL!L19,"")</f>
@@ -67549,59 +67549,59 @@
       </c>
       <c r="C14">
         <f>IF(ALL!D11&gt;0,ALL!D11,"")</f>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D14">
         <f>IF(ALL!E11&gt;0,ALL!E11,"")</f>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14">
         <f>IF(ALL!F11&gt;0,ALL!F11,"")</f>
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F14">
         <f>IF(ALL!G11&gt;0,ALL!G11,"")</f>
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G14">
         <f>IF(ALL!H11&gt;0,ALL!H11,"")</f>
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H14">
         <f>IF(ALL!I11&gt;0,ALL!I11,"")</f>
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I14">
         <f>IF(ALL!J11&gt;0,ALL!J11,"")</f>
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J14">
         <f>IF(ALL!K11&gt;0,ALL!K11,"")</f>
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K14">
         <f>IF(ALL!L11&gt;0,ALL!L11,"")</f>
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L14">
         <f>IF(ALL!M11&gt;0,ALL!M11,"")</f>
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M14">
         <f>IF(ALL!N11&gt;0,ALL!N11,"")</f>
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N14">
         <f>IF(ALL!O11&gt;0,ALL!O11,"")</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O14">
         <f>IF(ALL!P11&gt;0,ALL!P11,"")</f>
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="P14">
         <f>IF(ALL!Q11&gt;0,ALL!Q11,"")</f>
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -68081,23 +68081,23 @@
       </c>
       <c r="F34">
         <f>IF(ALL!G19&gt;0,ALL!G19,"")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G34">
         <f>IF(ALL!H19&gt;0,ALL!H19,"")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H34">
         <f>IF(ALL!I19&gt;0,ALL!I19,"")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I34">
         <f>IF(ALL!J19&gt;0,ALL!J19,"")</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J34">
         <f>IF(ALL!K19&gt;0,ALL!K19,"")</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K34">
         <f>IF(ALL!L19&gt;0,ALL!L19,"")</f>
@@ -68205,23 +68205,23 @@
       </c>
       <c r="B44">
         <f>IF(ALL!C34&gt;0,ALL!C34,"")</f>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C44">
         <f>IF(ALL!D34&gt;0,ALL!D34,"")</f>
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D44">
         <f>IF(ALL!E34&gt;0,ALL!E34,"")</f>
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E44">
         <f>IF(ALL!F34&gt;0,ALL!F34,"")</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F44">
         <f>IF(ALL!G34&gt;0,ALL!G34,"")</f>
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -68231,23 +68231,23 @@
       </c>
       <c r="B45">
         <f>IF(ALL!C41&gt;0,ALL!C41,"")</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C45">
         <f>IF(ALL!D41&gt;0,ALL!D41,"")</f>
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D45">
         <f>IF(ALL!E41&gt;0,ALL!E41,"")</f>
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E45">
         <f>IF(ALL!F41&gt;0,ALL!F41,"")</f>
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F45">
         <f>IF(ALL!G41&gt;0,ALL!G41,"")</f>
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -68287,11 +68287,11 @@
       </c>
       <c r="C47">
         <f>IF(ALL!D49&gt;0,ALL!D49,"")</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D47">
         <f>IF(ALL!E49&gt;0,ALL!E49,"")</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E47">
         <f>IF(ALL!F49&gt;0,ALL!F49,"")</f>
@@ -68371,63 +68371,63 @@
       </c>
       <c r="B152">
         <f>ALL!C6*100</f>
-        <v>93.81</v>
+        <v>93.28</v>
       </c>
       <c r="C152">
         <f>ALL!D6*100</f>
-        <v>94.910000000000011</v>
+        <v>94.25</v>
       </c>
       <c r="D152">
         <f>ALL!E6*100</f>
-        <v>91.320000000000007</v>
+        <v>90.45</v>
       </c>
       <c r="E152">
         <f>ALL!F6*100</f>
-        <v>88.75</v>
+        <v>87.570000000000007</v>
       </c>
       <c r="F152">
         <f>ALL!G6*100</f>
-        <v>94.45</v>
+        <v>89.9</v>
       </c>
       <c r="G152">
         <f>ALL!H6*100</f>
-        <v>91.47</v>
+        <v>86.52</v>
       </c>
       <c r="H152">
         <f>ALL!I6*100</f>
-        <v>89.88000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="I152">
         <f>ALL!J6*100</f>
-        <v>87.38</v>
+        <v>82.809999999999988</v>
       </c>
       <c r="J152">
         <f>ALL!K6*100</f>
-        <v>86.3</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="K152">
         <f>ALL!L6*100</f>
-        <v>68.88</v>
+        <v>66.91</v>
       </c>
       <c r="L152">
         <f>ALL!M6*100</f>
-        <v>68.320000000000007</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="M152">
         <f>ALL!N6*100</f>
-        <v>68.100000000000009</v>
+        <v>66.5</v>
       </c>
       <c r="N152">
         <f>ALL!O6*100</f>
-        <v>56.06</v>
+        <v>54.2</v>
       </c>
       <c r="O152">
         <f>ALL!P6*100</f>
-        <v>54.6</v>
+        <v>53.1</v>
       </c>
       <c r="P152">
         <f>ALL!Q6*100</f>
-        <v>54.169999999999995</v>
+        <v>52.669999999999995</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -68437,63 +68437,63 @@
       </c>
       <c r="B153">
         <f>ALL!C7</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C153">
         <f>ALL!D7</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D153">
         <f>ALL!E7</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E153">
         <f>ALL!F7</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F153">
         <f>ALL!G7</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G153">
         <f>ALL!H7</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H153">
         <f>ALL!I7</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I153">
         <f>ALL!J7</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J153">
         <f>ALL!K7</f>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K153">
         <f>ALL!L7</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L153">
         <f>ALL!M7</f>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M153">
         <f>ALL!N7</f>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N153">
         <f>ALL!O7</f>
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O153">
         <f>ALL!P7</f>
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P153">
         <f>ALL!Q7</f>
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -68525,23 +68525,23 @@
       </c>
       <c r="B156">
         <f>ALL!C36*100</f>
-        <v>93.33</v>
+        <v>92.64</v>
       </c>
       <c r="C156">
         <f>ALL!D36*100</f>
-        <v>91.56</v>
+        <v>88</v>
       </c>
       <c r="D156">
         <f>ALL!E36*100</f>
-        <v>87.86</v>
+        <v>83.38</v>
       </c>
       <c r="E156">
         <f>ALL!F36*100</f>
-        <v>68.430000000000007</v>
+        <v>66.600000000000009</v>
       </c>
       <c r="F156">
         <f>ALL!G36*100</f>
-        <v>54.94</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -68551,23 +68551,23 @@
       </c>
       <c r="B157">
         <f>ALL!C37</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C157">
         <f>ALL!D37</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D157">
         <f>ALL!E37</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E157">
         <f>ALL!F37</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F157">
         <f>ALL!G37</f>
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.2">
@@ -68705,51 +68705,51 @@
       </c>
       <c r="E163">
         <f t="shared" ref="E163:P163" si="1">E4</f>
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F163">
         <f t="shared" si="1"/>
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G163">
         <f t="shared" si="1"/>
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H163">
         <f t="shared" si="1"/>
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I163">
         <f t="shared" si="1"/>
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J163">
         <f t="shared" si="1"/>
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K163">
         <f t="shared" si="1"/>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L163">
         <f t="shared" si="1"/>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="M163">
         <f t="shared" si="1"/>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N163">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O163">
         <f t="shared" si="1"/>
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P163">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.2">
@@ -68995,49 +68995,49 @@
         <v>18</v>
       </c>
       <c r="C4" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D4" s="7">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E4" s="7">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F4" s="7">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G4" s="7">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H4" s="7">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I4" s="7">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="J4" s="7">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K4" s="7">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="L4" s="7">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M4" s="7">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N4" s="7">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O4" s="7">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P4" s="7">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="7">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -69065,49 +69065,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>0.94799999999999995</v>
+        <v>0.94079999999999997</v>
       </c>
       <c r="D6" s="18">
-        <v>0.9677</v>
+        <v>0.95879999999999999</v>
       </c>
       <c r="E6" s="18">
-        <v>0.92479999999999996</v>
+        <v>0.91320000000000001</v>
       </c>
       <c r="F6" s="18">
-        <v>0.87990000000000002</v>
+        <v>0.86439999999999995</v>
       </c>
       <c r="G6" s="18">
-        <v>0.95399999999999996</v>
+        <v>0.89419999999999999</v>
       </c>
       <c r="H6" s="18">
-        <v>0.92249999999999999</v>
+        <v>0.85740000000000005</v>
       </c>
       <c r="I6" s="18">
-        <v>0.8972</v>
+        <v>0.84089999999999998</v>
       </c>
       <c r="J6" s="18">
-        <v>0.8649</v>
+        <v>0.80530000000000002</v>
       </c>
       <c r="K6" s="18">
-        <v>0.85170000000000001</v>
+        <v>0.79239999999999999</v>
       </c>
       <c r="L6" s="18">
-        <v>0.6492</v>
+        <v>0.62319999999999998</v>
       </c>
       <c r="M6" s="18">
-        <v>0.64029999999999998</v>
+        <v>0.61480000000000001</v>
       </c>
       <c r="N6" s="18">
-        <v>0.64390000000000003</v>
+        <v>0.62260000000000004</v>
       </c>
       <c r="O6" s="18">
-        <v>0.49630000000000002</v>
+        <v>0.47160000000000002</v>
       </c>
       <c r="P6" s="18">
-        <v>0.47810000000000002</v>
+        <v>0.45810000000000001</v>
       </c>
       <c r="Q6" s="18">
-        <v>0.4723</v>
+        <v>0.45240000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -69116,49 +69116,49 @@
         <v>24</v>
       </c>
       <c r="C7" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G7" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H7" s="19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I7" s="19">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J7" s="19">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K7" s="19">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L7" s="19">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M7" s="19">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N7" s="19">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O7" s="19">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P7" s="19">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q7" s="19">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -69294,49 +69294,49 @@
         <v>19</v>
       </c>
       <c r="C11" s="7">
+        <v>76</v>
+      </c>
+      <c r="D11" s="7">
         <v>77</v>
       </c>
-      <c r="D11" s="7">
-        <v>78</v>
-      </c>
       <c r="E11" s="7">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" s="7">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G11" s="7">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H11" s="7">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I11" s="7">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="J11" s="7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K11" s="7">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L11" s="7">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M11" s="7">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N11" s="7">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O11" s="7">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P11" s="7">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q11" s="7">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -69661,20 +69661,20 @@
       <c r="F19" s="7">
         <v>16</v>
       </c>
-      <c r="G19" s="13">
-        <v>20</v>
-      </c>
-      <c r="H19" s="13">
-        <v>20</v>
-      </c>
-      <c r="I19" s="13">
+      <c r="G19" s="7">
         <v>18</v>
       </c>
+      <c r="H19" s="7">
+        <v>18</v>
+      </c>
+      <c r="I19" s="7">
+        <v>16</v>
+      </c>
       <c r="J19" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K19" s="7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L19" s="7">
         <v>11</v>
@@ -69825,19 +69825,19 @@
         <v>18</v>
       </c>
       <c r="C34" s="20">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" s="20">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E34" s="20">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F34" s="20">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G34" s="20">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H34" s="20"/>
     </row>
@@ -69845,19 +69845,19 @@
       <c r="A35" s="16"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24">
-        <v>5.33E-2</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="D35" s="24">
-        <v>8.1199999999999994E-2</v>
+        <v>0.128</v>
       </c>
       <c r="E35" s="24">
-        <v>0.12870000000000001</v>
+        <v>0.18709999999999999</v>
       </c>
       <c r="F35" s="24">
-        <v>0.35549999999999998</v>
+        <v>0.37980000000000003</v>
       </c>
       <c r="G35" s="24">
-        <v>0.51780000000000004</v>
+        <v>0.5393</v>
       </c>
       <c r="H35" s="7"/>
     </row>
@@ -69867,19 +69867,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="18">
-        <v>0.94669999999999999</v>
+        <v>0.93740000000000001</v>
       </c>
       <c r="D36" s="18">
-        <v>0.91879999999999995</v>
+        <v>0.872</v>
       </c>
       <c r="E36" s="18">
-        <v>0.87129999999999996</v>
+        <v>0.81289999999999996</v>
       </c>
       <c r="F36" s="18">
-        <v>0.64449999999999996</v>
+        <v>0.62019999999999997</v>
       </c>
       <c r="G36" s="18">
-        <v>0.48220000000000002</v>
+        <v>0.4607</v>
       </c>
       <c r="H36" s="19"/>
     </row>
@@ -69889,19 +69889,19 @@
         <v>24</v>
       </c>
       <c r="C37" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" s="19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E37" s="19">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F37" s="19">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G37" s="19">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H37" s="19"/>
     </row>
@@ -69971,19 +69971,19 @@
         <v>19</v>
       </c>
       <c r="C41" s="20">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D41" s="20">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E41" s="20">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F41" s="20">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G41" s="20">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H41" s="20"/>
     </row>
@@ -70137,11 +70137,11 @@
       <c r="C49" s="20">
         <v>12</v>
       </c>
-      <c r="D49" s="13">
-        <v>19</v>
+      <c r="D49" s="20">
+        <v>17</v>
       </c>
       <c r="E49" s="20">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F49" s="20">
         <v>11</v>
@@ -70368,63 +70368,63 @@
       </c>
       <c r="B4">
         <f>IF(DV!C4&gt;0,DV!C4,"")</f>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4">
         <f>IF(DV!D4&gt;0,DV!D4,"")</f>
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4">
         <f>IF(DV!E4&gt;0,DV!E4,"")</f>
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E4">
         <f>IF(DV!F4&gt;0,DV!F4,"")</f>
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F4">
         <f>IF(DV!G4&gt;0,DV!G4,"")</f>
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G4">
         <f>IF(DV!H4&gt;0,DV!H4,"")</f>
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H4">
         <f>IF(DV!I4&gt;0,DV!I4,"")</f>
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I4">
         <f>IF(DV!J4&gt;0,DV!J4,"")</f>
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J4">
         <f>IF(DV!K4&gt;0,DV!K4,"")</f>
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K4">
         <f>IF(DV!L4&gt;0,DV!L4,"")</f>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L4">
         <f>IF(DV!M4&gt;0,DV!M4,"")</f>
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M4">
         <f>IF(DV!N4&gt;0,DV!N4,"")</f>
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N4">
         <f>IF(DV!O4&gt;0,DV!O4,"")</f>
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O4">
         <f>IF(DV!P4&gt;0,DV!P4,"")</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P4">
         <f>IF(DV!Q4&gt;0,DV!Q4,"")</f>
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -70434,63 +70434,63 @@
       </c>
       <c r="B5">
         <f>IF(DV!C11&gt;0,DV!C11,"")</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5">
         <f>IF(DV!D11&gt;0,DV!D11,"")</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5">
         <f>IF(DV!E11&gt;0,DV!E11,"")</f>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <f>IF(DV!F11&gt;0,DV!F11,"")</f>
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <f>IF(DV!G11&gt;0,DV!G11,"")</f>
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <f>IF(DV!H11&gt;0,DV!H11,"")</f>
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H5">
         <f>IF(DV!I11&gt;0,DV!I11,"")</f>
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I5">
         <f>IF(DV!J11&gt;0,DV!J11,"")</f>
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J5">
         <f>IF(DV!K11&gt;0,DV!K11,"")</f>
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="K5">
         <f>IF(DV!L11&gt;0,DV!L11,"")</f>
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L5">
         <f>IF(DV!M11&gt;0,DV!M11,"")</f>
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M5">
         <f>IF(DV!N11&gt;0,DV!N11,"")</f>
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N5">
         <f>IF(DV!O11&gt;0,DV!O11,"")</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O5">
         <f>IF(DV!P11&gt;0,DV!P11,"")</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P5">
         <f>IF(DV!Q11&gt;0,DV!Q11,"")</f>
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -70582,23 +70582,23 @@
       </c>
       <c r="F7">
         <f>IF(DV!G19&gt;0,DV!G19,"")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <f>IF(DV!H19&gt;0,DV!H19,"")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H7">
         <f>IF(DV!I19&gt;0,DV!I19,"")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I7">
         <f>IF(DV!J19&gt;0,DV!J19,"")</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7">
         <f>IF(DV!K19&gt;0,DV!K19,"")</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K7">
         <f>IF(DV!L19&gt;0,DV!L19,"")</f>
@@ -70826,63 +70826,63 @@
       </c>
       <c r="B14">
         <f>IF(DV!C11&gt;0,DV!C11,"")</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14">
         <f>IF(DV!D11&gt;0,DV!D11,"")</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14">
         <f>IF(DV!E11&gt;0,DV!E11,"")</f>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E14">
         <f>IF(DV!F11&gt;0,DV!F11,"")</f>
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F14">
         <f>IF(DV!G11&gt;0,DV!G11,"")</f>
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G14">
         <f>IF(DV!H11&gt;0,DV!H11,"")</f>
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H14">
         <f>IF(DV!I11&gt;0,DV!I11,"")</f>
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I14">
         <f>IF(DV!J11&gt;0,DV!J11,"")</f>
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J14">
         <f>IF(DV!K11&gt;0,DV!K11,"")</f>
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="K14">
         <f>IF(DV!L11&gt;0,DV!L11,"")</f>
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L14">
         <f>IF(DV!M11&gt;0,DV!M11,"")</f>
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M14">
         <f>IF(DV!N11&gt;0,DV!N11,"")</f>
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N14">
         <f>IF(DV!O11&gt;0,DV!O11,"")</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O14">
         <f>IF(DV!P11&gt;0,DV!P11,"")</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P14">
         <f>IF(DV!Q11&gt;0,DV!Q11,"")</f>
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -71362,23 +71362,23 @@
       </c>
       <c r="F34">
         <f>IF(DV!G19&gt;0,DV!G19,"")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G34">
         <f>IF(DV!H19&gt;0,DV!H19,"")</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H34">
         <f>IF(DV!I19&gt;0,DV!I19,"")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I34">
         <f>IF(DV!J19&gt;0,DV!J19,"")</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J34">
         <f>IF(DV!K19&gt;0,DV!K19,"")</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K34">
         <f>IF(DV!L19&gt;0,DV!L19,"")</f>
@@ -71486,23 +71486,23 @@
       </c>
       <c r="B44">
         <f>IF(DV!C34&gt;0,DV!C34,"")</f>
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C44">
         <f>IF(DV!D34&gt;0,DV!D34,"")</f>
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D44">
         <f>IF(DV!E34&gt;0,DV!E34,"")</f>
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E44">
         <f>IF(DV!F34&gt;0,DV!F34,"")</f>
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F44">
         <f>IF(DV!G34&gt;0,DV!G34,"")</f>
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
@@ -71512,23 +71512,23 @@
       </c>
       <c r="B45">
         <f>IF(DV!C41&gt;0,DV!C41,"")</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C45">
         <f>IF(DV!D41&gt;0,DV!D41,"")</f>
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D45">
         <f>IF(DV!E41&gt;0,DV!E41,"")</f>
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E45">
         <f>IF(DV!F41&gt;0,DV!F41,"")</f>
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F45">
         <f>IF(DV!G41&gt;0,DV!G41,"")</f>
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
@@ -71568,11 +71568,11 @@
       </c>
       <c r="C47">
         <f>IF(DV!D49&gt;0,DV!D49,"")</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D47">
         <f>IF(DV!E49&gt;0,DV!E49,"")</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E47">
         <f>IF(DV!F49&gt;0,DV!F49,"")</f>
@@ -71652,63 +71652,63 @@
       </c>
       <c r="B152">
         <f>DV!C6*100</f>
-        <v>94.8</v>
+        <v>94.08</v>
       </c>
       <c r="C152">
         <f>DV!D6*100</f>
-        <v>96.77</v>
+        <v>95.88</v>
       </c>
       <c r="D152">
         <f>DV!E6*100</f>
-        <v>92.47999999999999</v>
+        <v>91.320000000000007</v>
       </c>
       <c r="E152">
         <f>DV!F6*100</f>
-        <v>87.99</v>
+        <v>86.44</v>
       </c>
       <c r="F152">
         <f>DV!G6*100</f>
-        <v>95.399999999999991</v>
+        <v>89.42</v>
       </c>
       <c r="G152">
         <f>DV!H6*100</f>
-        <v>92.25</v>
+        <v>85.740000000000009</v>
       </c>
       <c r="H152">
         <f>DV!I6*100</f>
-        <v>89.72</v>
+        <v>84.09</v>
       </c>
       <c r="I152">
         <f>DV!J6*100</f>
-        <v>86.49</v>
+        <v>80.53</v>
       </c>
       <c r="J152">
         <f>DV!K6*100</f>
-        <v>85.17</v>
+        <v>79.239999999999995</v>
       </c>
       <c r="K152">
         <f>DV!L6*100</f>
-        <v>64.92</v>
+        <v>62.32</v>
       </c>
       <c r="L152">
         <f>DV!M6*100</f>
-        <v>64.03</v>
+        <v>61.480000000000004</v>
       </c>
       <c r="M152">
         <f>DV!N6*100</f>
-        <v>64.39</v>
+        <v>62.260000000000005</v>
       </c>
       <c r="N152">
         <f>DV!O6*100</f>
-        <v>49.63</v>
+        <v>47.160000000000004</v>
       </c>
       <c r="O152">
         <f>DV!P6*100</f>
-        <v>47.81</v>
+        <v>45.81</v>
       </c>
       <c r="P152">
         <f>DV!Q6*100</f>
-        <v>47.23</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.2">
@@ -71718,63 +71718,63 @@
       </c>
       <c r="B153">
         <f>DV!C7</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C153">
         <f>DV!D7</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D153">
         <f>DV!E7</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E153">
         <f>DV!F7</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F153">
         <f>DV!G7</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G153">
         <f>DV!H7</f>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H153">
         <f>DV!I7</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I153">
         <f>DV!J7</f>
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J153">
         <f>DV!K7</f>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K153">
         <f>DV!L7</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L153">
         <f>DV!M7</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M153">
         <f>DV!N7</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N153">
         <f>DV!O7</f>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="O153">
         <f>DV!P7</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P153">
         <f>DV!Q7</f>
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.2">
@@ -71806,23 +71806,23 @@
       </c>
       <c r="B156">
         <f>DV!C36*100</f>
-        <v>94.67</v>
+        <v>93.74</v>
       </c>
       <c r="C156">
         <f>DV!D36*100</f>
-        <v>91.88</v>
+        <v>87.2</v>
       </c>
       <c r="D156">
         <f>DV!E36*100</f>
-        <v>87.13</v>
+        <v>81.289999999999992</v>
       </c>
       <c r="E156">
         <f>DV!F36*100</f>
-        <v>64.45</v>
+        <v>62.019999999999996</v>
       </c>
       <c r="F156">
         <f>DV!G36*100</f>
-        <v>48.22</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.2">
@@ -71832,23 +71832,23 @@
       </c>
       <c r="B157">
         <f>DV!C37</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C157">
         <f>DV!D37</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D157">
         <f>DV!E37</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E157">
         <f>DV!F37</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F157">
         <f>DV!G37</f>
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.2">
@@ -71986,51 +71986,51 @@
       </c>
       <c r="E163">
         <f t="shared" ref="E163:P163" si="1">E4</f>
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F163">
         <f t="shared" si="1"/>
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G163">
         <f t="shared" si="1"/>
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H163">
         <f t="shared" si="1"/>
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I163">
         <f t="shared" si="1"/>
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J163">
         <f t="shared" si="1"/>
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K163">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L163">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M163">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N163">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O163">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P163">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.2">
@@ -76332,7 +76332,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="7">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="7">
         <v>47</v>
@@ -76341,40 +76341,40 @@
         <v>43</v>
       </c>
       <c r="F4" s="7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="7">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H4" s="7">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I4" s="7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J4" s="7">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K4" s="7">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L4" s="7">
+        <v>25</v>
+      </c>
+      <c r="M4" s="7">
+        <v>25</v>
+      </c>
+      <c r="N4" s="7">
         <v>26</v>
       </c>
-      <c r="M4" s="7">
-        <v>26</v>
-      </c>
-      <c r="N4" s="7">
-        <v>27</v>
-      </c>
       <c r="O4" s="7">
-        <v>24.625</v>
+        <v>23.774999999999999</v>
       </c>
       <c r="P4" s="7">
-        <v>23.425000000000001</v>
+        <v>22.574999999999999</v>
       </c>
       <c r="Q4" s="7">
-        <v>22.75</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -76402,49 +76402,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>0.95689999999999997</v>
+        <v>0.94650000000000001</v>
       </c>
       <c r="D6" s="18">
-        <v>0.98499999999999999</v>
+        <v>0.97150000000000003</v>
       </c>
       <c r="E6" s="18">
-        <v>0.90449999999999997</v>
+        <v>0.88680000000000003</v>
       </c>
       <c r="F6" s="18">
-        <v>0.88160000000000005</v>
+        <v>0.8639</v>
       </c>
       <c r="G6" s="18">
-        <v>0.88649999999999995</v>
+        <v>0.84789999999999999</v>
       </c>
       <c r="H6" s="18">
-        <v>0.85050000000000003</v>
+        <v>0.7974</v>
       </c>
       <c r="I6" s="18">
-        <v>0.79010000000000002</v>
+        <v>0.74429999999999996</v>
       </c>
       <c r="J6" s="18">
-        <v>0.78959999999999997</v>
+        <v>0.73440000000000005</v>
       </c>
       <c r="K6" s="18">
-        <v>0.78439999999999999</v>
+        <v>0.72919999999999996</v>
       </c>
       <c r="L6" s="18">
-        <v>0.54900000000000004</v>
+        <v>0.51039999999999996</v>
       </c>
       <c r="M6" s="18">
-        <v>0.54900000000000004</v>
+        <v>0.51039999999999996</v>
       </c>
       <c r="N6" s="18">
-        <v>0.56720000000000004</v>
+        <v>0.53910000000000002</v>
       </c>
       <c r="O6" s="18">
-        <v>0.51300000000000001</v>
+        <v>0.49530000000000002</v>
       </c>
       <c r="P6" s="18">
-        <v>0.48799999999999999</v>
+        <v>0.4703</v>
       </c>
       <c r="Q6" s="18">
-        <v>0.47399999999999998</v>
+        <v>0.45629999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -76453,7 +76453,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="19">
         <v>1</v>
@@ -76462,40 +76462,40 @@
         <v>5</v>
       </c>
       <c r="F7" s="19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" s="19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K7" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L7" s="19">
+        <v>24</v>
+      </c>
+      <c r="M7" s="19">
+        <v>24</v>
+      </c>
+      <c r="N7" s="19">
         <v>22</v>
       </c>
-      <c r="M7" s="19">
-        <v>22</v>
-      </c>
-      <c r="N7" s="19">
-        <v>21</v>
-      </c>
       <c r="O7" s="19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P7" s="19">
         <v>25</v>
       </c>
       <c r="Q7" s="19">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -76631,49 +76631,49 @@
         <v>19</v>
       </c>
       <c r="C11" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="7">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H11" s="7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I11" s="7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J11" s="7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K11" s="7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L11" s="7">
+        <v>16</v>
+      </c>
+      <c r="M11" s="7">
+        <v>16</v>
+      </c>
+      <c r="N11" s="7">
         <v>18</v>
       </c>
-      <c r="M11" s="7">
-        <v>18</v>
-      </c>
-      <c r="N11" s="7">
-        <v>19</v>
-      </c>
       <c r="O11" s="7">
-        <v>16.25</v>
+        <v>15.4</v>
       </c>
       <c r="P11" s="7">
-        <v>15.05</v>
+        <v>14.2</v>
       </c>
       <c r="Q11" s="7">
-        <v>14.375</v>
+        <v>13.525</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -77107,38 +77107,38 @@
         <v>18</v>
       </c>
       <c r="C34" s="20">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D34" s="20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E34" s="20">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F34" s="20">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G34" s="20">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="16"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24">
-        <v>5.1200000000000002E-2</v>
+        <v>6.5100000000000005E-2</v>
       </c>
       <c r="D35" s="24">
-        <v>0.12720000000000001</v>
+        <v>0.1636</v>
       </c>
       <c r="E35" s="24">
-        <v>0.21199999999999999</v>
+        <v>0.2641</v>
       </c>
       <c r="F35" s="24">
-        <v>0.44500000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="G35" s="24">
-        <v>0.50829999999999997</v>
+        <v>0.52600000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -77147,19 +77147,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="18">
-        <v>0.94879999999999998</v>
+        <v>0.93489999999999995</v>
       </c>
       <c r="D36" s="18">
-        <v>0.87280000000000002</v>
+        <v>0.83640000000000003</v>
       </c>
       <c r="E36" s="18">
-        <v>0.78800000000000003</v>
+        <v>0.7359</v>
       </c>
       <c r="F36" s="18">
-        <v>0.55500000000000005</v>
+        <v>0.52</v>
       </c>
       <c r="G36" s="18">
-        <v>0.49170000000000003</v>
+        <v>0.47399999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -77168,19 +77168,19 @@
         <v>24</v>
       </c>
       <c r="C37" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E37" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F37" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G37" s="19">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -77246,19 +77246,19 @@
         <v>19</v>
       </c>
       <c r="C41" s="20">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D41" s="20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E41" s="20">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F41" s="20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G41" s="20">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -77525,49 +77525,49 @@
         <v>18</v>
       </c>
       <c r="C63" s="30">
-        <v>45.93</v>
+        <v>45.43</v>
       </c>
       <c r="D63" s="30">
-        <v>47.28</v>
+        <v>46.63</v>
       </c>
       <c r="E63" s="30">
-        <v>43.414999999999999</v>
+        <v>42.564999999999998</v>
       </c>
       <c r="F63" s="30">
-        <v>42.314999999999998</v>
+        <v>41.465000000000003</v>
       </c>
       <c r="G63" s="30">
-        <v>42.55</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="H63" s="30">
-        <v>40.825000000000003</v>
+        <v>38.274999999999999</v>
       </c>
       <c r="I63" s="30">
-        <v>37.924999999999997</v>
+        <v>35.725000000000001</v>
       </c>
       <c r="J63" s="30">
-        <v>37.9</v>
+        <v>35.25</v>
       </c>
       <c r="K63" s="30">
-        <v>37.65</v>
+        <v>35</v>
       </c>
       <c r="L63" s="30">
-        <v>26.35</v>
+        <v>24.5</v>
       </c>
       <c r="M63" s="30">
-        <v>26.35</v>
+        <v>24.5</v>
       </c>
       <c r="N63" s="30">
-        <v>27.225000000000001</v>
+        <v>25.875</v>
       </c>
       <c r="O63" s="30">
-        <v>24.625</v>
+        <v>23.774999999999999</v>
       </c>
       <c r="P63" s="30">
-        <v>23.425000000000001</v>
+        <v>22.574999999999999</v>
       </c>
       <c r="Q63" s="30">
-        <v>22.75</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -78055,49 +78055,49 @@
         <v>18</v>
       </c>
       <c r="C73" s="7">
-        <v>38.93</v>
+        <v>38.43</v>
       </c>
       <c r="D73" s="7">
-        <v>40.28</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="E73" s="7">
-        <v>36.414999999999999</v>
+        <v>35.564999999999998</v>
       </c>
       <c r="F73" s="7">
-        <v>35.39</v>
+        <v>34.54</v>
       </c>
       <c r="G73" s="7">
-        <v>35.924999999999997</v>
+        <v>34.075000000000003</v>
       </c>
       <c r="H73" s="7">
-        <v>34.15</v>
+        <v>31.6</v>
       </c>
       <c r="I73" s="7">
-        <v>31.074999999999999</v>
+        <v>28.875</v>
       </c>
       <c r="J73" s="7">
-        <v>31.05</v>
+        <v>28.4</v>
       </c>
       <c r="K73" s="7">
-        <v>30.65</v>
+        <v>28</v>
       </c>
       <c r="L73" s="7">
-        <v>19.350000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="M73" s="7">
-        <v>19.350000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="N73" s="7">
-        <v>20.225000000000001</v>
+        <v>18.875</v>
       </c>
       <c r="O73" s="7">
-        <v>17.625</v>
+        <v>16.774999999999999</v>
       </c>
       <c r="P73" s="7">
-        <v>16.425000000000001</v>
+        <v>15.574999999999999</v>
       </c>
       <c r="Q73" s="7">
-        <v>15.75</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
@@ -78161,49 +78161,49 @@
         <v>18</v>
       </c>
       <c r="C75" s="32">
-        <v>21.93</v>
+        <v>21.43</v>
       </c>
       <c r="D75" s="32">
-        <v>21.78</v>
+        <v>21.13</v>
       </c>
       <c r="E75" s="32">
-        <v>19.114999999999998</v>
+        <v>18.265000000000001</v>
       </c>
       <c r="F75" s="32">
-        <v>19.14</v>
+        <v>18.29</v>
       </c>
       <c r="G75" s="32">
-        <v>18.925000000000001</v>
+        <v>17.074999999999999</v>
       </c>
       <c r="H75" s="32">
-        <v>17.774999999999999</v>
+        <v>15.225</v>
       </c>
       <c r="I75" s="32">
-        <v>17.024999999999999</v>
+        <v>14.824999999999999</v>
       </c>
       <c r="J75" s="32">
-        <v>17</v>
+        <v>14.35</v>
       </c>
       <c r="K75" s="32">
-        <v>17.100000000000001</v>
+        <v>14.45</v>
       </c>
       <c r="L75" s="32">
-        <v>11.975</v>
+        <v>10.125</v>
       </c>
       <c r="M75" s="32">
-        <v>11.975</v>
+        <v>10.125</v>
       </c>
       <c r="N75" s="32">
-        <v>12.85</v>
+        <v>11.5</v>
       </c>
       <c r="O75" s="32">
-        <v>10.25</v>
+        <v>9.4</v>
       </c>
       <c r="P75" s="32">
-        <v>9.0500000000000007</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="Q75" s="32">
-        <v>8.375</v>
+        <v>7.5250000000000004</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">

--- a/workforceresult.xlsx
+++ b/workforceresult.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miintra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B92EF83-FF87-7B4B-A80E-65200AFE4DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B542A99C-C286-2848-B8F1-C8AEFD3241F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" firstSheet="11" activeTab="20" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" firstSheet="11" activeTab="22" xr2:uid="{9B62DE01-5AE9-7A46-A5D4-95A9ED94E5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="17" r:id="rId1"/>
@@ -35614,49 +35614,49 @@
         <v>18</v>
       </c>
       <c r="C4" s="7">
+        <v>142</v>
+      </c>
+      <c r="D4" s="7">
+        <v>147</v>
+      </c>
+      <c r="E4" s="7">
+        <v>145</v>
+      </c>
+      <c r="F4" s="7">
+        <v>142</v>
+      </c>
+      <c r="G4" s="7">
+        <v>149</v>
+      </c>
+      <c r="H4" s="7">
         <v>144</v>
       </c>
-      <c r="D4" s="7">
-        <v>150</v>
-      </c>
-      <c r="E4" s="7">
-        <v>148</v>
-      </c>
-      <c r="F4" s="7">
-        <v>145</v>
-      </c>
-      <c r="G4" s="13">
-        <v>163</v>
-      </c>
-      <c r="H4" s="13">
-        <v>159</v>
-      </c>
-      <c r="I4" s="13">
-        <v>156</v>
+      <c r="I4" s="7">
+        <v>143</v>
       </c>
       <c r="J4" s="7">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="K4" s="7">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="L4" s="7">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="M4" s="7">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="N4" s="7">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="O4" s="7">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="P4" s="7">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="Q4" s="7">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -35684,49 +35684,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>0.95889999999999997</v>
+        <v>0.94520000000000004</v>
       </c>
       <c r="D6" s="18">
-        <v>0.97760000000000002</v>
+        <v>0.96209999999999996</v>
       </c>
       <c r="E6" s="18">
-        <v>0.95399999999999996</v>
+        <v>0.93379999999999996</v>
       </c>
       <c r="F6" s="18">
-        <v>0.93789999999999996</v>
+        <v>0.9153</v>
       </c>
       <c r="G6" s="18">
-        <v>1.0499000000000001</v>
+        <v>0.96250000000000002</v>
       </c>
       <c r="H6" s="18">
-        <v>1.0273000000000001</v>
+        <v>0.93220000000000003</v>
       </c>
       <c r="I6" s="18">
-        <v>1.0111000000000001</v>
+        <v>0.92720000000000002</v>
       </c>
       <c r="J6" s="18">
-        <v>0.9869</v>
+        <v>0.89780000000000004</v>
       </c>
       <c r="K6" s="18">
-        <v>0.96970000000000001</v>
+        <v>0.88119999999999998</v>
       </c>
       <c r="L6" s="18">
-        <v>0.82</v>
+        <v>0.7833</v>
       </c>
       <c r="M6" s="18">
-        <v>0.81040000000000001</v>
+        <v>0.77459999999999996</v>
       </c>
       <c r="N6" s="18">
-        <v>0.80279999999999996</v>
+        <v>0.77329999999999999</v>
       </c>
       <c r="O6" s="18">
-        <v>0.67749999999999999</v>
+        <v>0.64259999999999995</v>
       </c>
       <c r="P6" s="18">
-        <v>0.64880000000000004</v>
+        <v>0.61970000000000003</v>
       </c>
       <c r="Q6" s="18">
-        <v>0.64300000000000002</v>
+        <v>0.61399999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -35735,49 +35735,49 @@
         <v>24</v>
       </c>
       <c r="C7" s="19">
+        <v>8</v>
+      </c>
+      <c r="D7" s="19">
         <v>6</v>
       </c>
-      <c r="D7" s="19">
-        <v>3</v>
-      </c>
       <c r="E7" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7" s="19">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="19">
-        <v>-4</v>
+        <v>11</v>
       </c>
       <c r="I7" s="19">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="J7" s="19">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K7" s="19">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L7" s="19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M7" s="19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N7" s="19">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="O7" s="19">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P7" s="19">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="19">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -35913,49 +35913,49 @@
         <v>19</v>
       </c>
       <c r="C11" s="7">
+        <v>111</v>
+      </c>
+      <c r="D11" s="7">
         <v>113</v>
       </c>
-      <c r="D11" s="7">
-        <v>115</v>
-      </c>
       <c r="E11" s="7">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F11" s="7">
-        <v>110</v>
-      </c>
-      <c r="G11" s="13">
-        <v>117</v>
+        <v>107</v>
+      </c>
+      <c r="G11" s="7">
+        <v>108</v>
       </c>
       <c r="H11" s="7">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="I11" s="7">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="J11" s="7">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="K11" s="7">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="L11" s="7">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="M11" s="7">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N11" s="7">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O11" s="7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="P11" s="7">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="Q11" s="7">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -36281,19 +36281,19 @@
         <v>16</v>
       </c>
       <c r="G19" s="13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H19" s="13">
-        <v>25</v>
-      </c>
-      <c r="I19" s="13">
-        <v>23</v>
-      </c>
-      <c r="J19" s="13">
-        <v>21</v>
-      </c>
-      <c r="K19" s="13">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="I19" s="7">
+        <v>18</v>
+      </c>
+      <c r="J19" s="7">
+        <v>16</v>
+      </c>
+      <c r="K19" s="7">
+        <v>16</v>
       </c>
       <c r="L19" s="7">
         <v>12</v>
@@ -36444,19 +36444,19 @@
         <v>18</v>
       </c>
       <c r="C34" s="20">
-        <v>147</v>
-      </c>
-      <c r="D34" s="13">
-        <v>156</v>
+        <v>145</v>
+      </c>
+      <c r="D34" s="20">
+        <v>145</v>
       </c>
       <c r="E34" s="20">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="F34" s="20">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G34" s="20">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H34" s="20"/>
     </row>
@@ -36464,19 +36464,19 @@
       <c r="A35" s="16"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24">
-        <v>3.6499999999999998E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="D35" s="24">
-        <v>-5.0000000000000001E-3</v>
+        <v>6.3399999999999998E-2</v>
       </c>
       <c r="E35" s="24">
-        <v>1.0800000000000001E-2</v>
+        <v>9.7900000000000001E-2</v>
       </c>
       <c r="F35" s="24">
-        <v>0.189</v>
+        <v>0.223</v>
       </c>
       <c r="G35" s="24">
-        <v>0.34360000000000002</v>
+        <v>0.37459999999999999</v>
       </c>
       <c r="H35" s="7"/>
     </row>
@@ -36486,19 +36486,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="18">
-        <v>0.96350000000000002</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="D36" s="18">
-        <v>1.0049999999999999</v>
+        <v>0.93659999999999999</v>
       </c>
       <c r="E36" s="18">
-        <v>0.98919999999999997</v>
+        <v>0.90210000000000001</v>
       </c>
       <c r="F36" s="18">
-        <v>0.81100000000000005</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="G36" s="18">
-        <v>0.65639999999999998</v>
+        <v>0.62539999999999996</v>
       </c>
       <c r="H36" s="19"/>
     </row>
@@ -36508,19 +36508,19 @@
         <v>24</v>
       </c>
       <c r="C37" s="19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37" s="19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E37" s="19">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F37" s="19">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G37" s="19">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H37" s="19"/>
     </row>
@@ -36590,19 +36590,19 @@
         <v>19</v>
       </c>
       <c r="C41" s="20">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D41" s="20">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E41" s="20">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F41" s="20">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G41" s="20">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H41" s="20"/>
     </row>
@@ -36757,10 +36757,10 @@
         <v>13</v>
       </c>
       <c r="D49" s="13">
-        <v>22</v>
-      </c>
-      <c r="E49" s="13">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="E49" s="20">
+        <v>16</v>
       </c>
       <c r="F49" s="20">
         <v>12</v>
@@ -42629,49 +42629,49 @@
         <v>18</v>
       </c>
       <c r="C4" s="7">
-        <v>108</v>
-      </c>
-      <c r="D4" s="13">
-        <v>114</v>
+        <v>106</v>
+      </c>
+      <c r="D4" s="7">
+        <v>112</v>
       </c>
       <c r="E4" s="7">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F4" s="7">
+        <v>107</v>
+      </c>
+      <c r="G4" s="7">
+        <v>115</v>
+      </c>
+      <c r="H4" s="7">
         <v>111</v>
       </c>
-      <c r="G4" s="13">
-        <v>128</v>
-      </c>
-      <c r="H4" s="13">
-        <v>126</v>
-      </c>
-      <c r="I4" s="13">
-        <v>122</v>
-      </c>
-      <c r="J4" s="13">
-        <v>119</v>
+      <c r="I4" s="7">
+        <v>109</v>
+      </c>
+      <c r="J4" s="7">
+        <v>105</v>
       </c>
       <c r="K4" s="7">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="L4" s="7">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="M4" s="7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N4" s="7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O4" s="7">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="P4" s="7">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Q4" s="7">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -42699,49 +42699,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>0.97499999999999998</v>
+        <v>0.95650000000000002</v>
       </c>
       <c r="D6" s="18">
-        <v>1.0038</v>
+        <v>0.9829</v>
       </c>
       <c r="E6" s="18">
-        <v>0.97719999999999996</v>
+        <v>0.95030000000000003</v>
       </c>
       <c r="F6" s="18">
-        <v>0.93889999999999996</v>
+        <v>0.90920000000000001</v>
       </c>
       <c r="G6" s="18">
-        <v>1.0855999999999999</v>
+        <v>0.9708</v>
       </c>
       <c r="H6" s="18">
-        <v>1.0636000000000001</v>
+        <v>0.93859999999999999</v>
       </c>
       <c r="I6" s="18">
-        <v>1.0369999999999999</v>
+        <v>0.9274</v>
       </c>
       <c r="J6" s="18">
-        <v>1.0058</v>
+        <v>0.88949999999999996</v>
       </c>
       <c r="K6" s="18">
-        <v>0.98409999999999997</v>
+        <v>0.86860000000000004</v>
       </c>
       <c r="L6" s="18">
-        <v>0.81930000000000003</v>
+        <v>0.77080000000000004</v>
       </c>
       <c r="M6" s="18">
-        <v>0.80610000000000004</v>
+        <v>0.75849999999999995</v>
       </c>
       <c r="N6" s="18">
-        <v>0.80530000000000002</v>
+        <v>0.7661</v>
       </c>
       <c r="O6" s="18">
-        <v>0.65129999999999999</v>
+        <v>0.6048</v>
       </c>
       <c r="P6" s="18">
-        <v>0.61419999999999997</v>
+        <v>0.57550000000000001</v>
       </c>
       <c r="Q6" s="18">
-        <v>0.60650000000000004</v>
+        <v>0.56789999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -42750,49 +42750,49 @@
         <v>24</v>
       </c>
       <c r="C7" s="19">
+        <v>5</v>
+      </c>
+      <c r="D7" s="19">
+        <v>2</v>
+      </c>
+      <c r="E7" s="19">
+        <v>6</v>
+      </c>
+      <c r="F7" s="19">
+        <v>11</v>
+      </c>
+      <c r="G7" s="19">
         <v>3</v>
       </c>
-      <c r="D7" s="19">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19">
-        <v>3</v>
-      </c>
-      <c r="F7" s="19">
+      <c r="H7" s="19">
         <v>7</v>
       </c>
-      <c r="G7" s="19">
-        <v>-10</v>
-      </c>
-      <c r="H7" s="19">
-        <v>-8</v>
-      </c>
       <c r="I7" s="19">
-        <v>-4</v>
+        <v>9</v>
       </c>
       <c r="J7" s="19">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="K7" s="19">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L7" s="19">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M7" s="19">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N7" s="19">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="O7" s="19">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="P7" s="19">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="19">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -42928,49 +42928,49 @@
         <v>19</v>
       </c>
       <c r="C11" s="7">
+        <v>78</v>
+      </c>
+      <c r="D11" s="7">
         <v>80</v>
       </c>
-      <c r="D11" s="13">
-        <v>82</v>
-      </c>
-      <c r="E11" s="13">
-        <v>80</v>
+      <c r="E11" s="7">
+        <v>77</v>
       </c>
       <c r="F11" s="7">
-        <v>78</v>
-      </c>
-      <c r="G11" s="13">
-        <v>84</v>
-      </c>
-      <c r="H11" s="13">
-        <v>82</v>
+        <v>74</v>
+      </c>
+      <c r="G11" s="7">
+        <v>76</v>
+      </c>
+      <c r="H11" s="7">
+        <v>72</v>
       </c>
       <c r="I11" s="7">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="J11" s="7">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K11" s="7">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="L11" s="7">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="M11" s="7">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="N11" s="7">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O11" s="7">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="P11" s="7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="7">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -43296,19 +43296,19 @@
         <v>16</v>
       </c>
       <c r="G19" s="13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H19" s="13">
-        <v>25</v>
-      </c>
-      <c r="I19" s="13">
-        <v>23</v>
-      </c>
-      <c r="J19" s="13">
-        <v>21</v>
-      </c>
-      <c r="K19" s="13">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="I19" s="7">
+        <v>18</v>
+      </c>
+      <c r="J19" s="7">
+        <v>16</v>
+      </c>
+      <c r="K19" s="7">
+        <v>16</v>
       </c>
       <c r="L19" s="7">
         <v>12</v>
@@ -43459,19 +43459,19 @@
         <v>18</v>
       </c>
       <c r="C34" s="20">
-        <v>112</v>
-      </c>
-      <c r="D34" s="13">
-        <v>121</v>
-      </c>
-      <c r="E34" s="13">
-        <v>119</v>
+        <v>109</v>
+      </c>
+      <c r="D34" s="20">
+        <v>111</v>
+      </c>
+      <c r="E34" s="20">
+        <v>106</v>
       </c>
       <c r="F34" s="20">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G34" s="20">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H34" s="20"/>
     </row>
@@ -43479,19 +43479,19 @@
       <c r="A35" s="16"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24">
-        <v>1.46E-2</v>
+        <v>3.6799999999999999E-2</v>
       </c>
       <c r="D35" s="24">
-        <v>-2.9399999999999999E-2</v>
+        <v>6.0499999999999998E-2</v>
       </c>
       <c r="E35" s="24">
-        <v>-8.8999999999999999E-3</v>
+        <v>0.1048</v>
       </c>
       <c r="F35" s="24">
-        <v>0.1898</v>
+        <v>0.2349</v>
       </c>
       <c r="G35" s="24">
-        <v>0.376</v>
+        <v>0.4173</v>
       </c>
       <c r="H35" s="7"/>
     </row>
@@ -43501,19 +43501,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="18">
-        <v>0.98540000000000005</v>
+        <v>0.96319999999999995</v>
       </c>
       <c r="D36" s="18">
-        <v>1.0294000000000001</v>
+        <v>0.9395</v>
       </c>
       <c r="E36" s="18">
-        <v>1.0088999999999999</v>
+        <v>0.8952</v>
       </c>
       <c r="F36" s="18">
-        <v>0.81020000000000003</v>
+        <v>0.7651</v>
       </c>
       <c r="G36" s="18">
-        <v>0.624</v>
+        <v>0.5827</v>
       </c>
       <c r="H36" s="19"/>
     </row>
@@ -43523,19 +43523,19 @@
         <v>24</v>
       </c>
       <c r="C37" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D37" s="19">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="E37" s="19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="F37" s="19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G37" s="19">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H37" s="19"/>
     </row>
@@ -43604,20 +43604,20 @@
       <c r="B41" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="13">
-        <v>81</v>
-      </c>
-      <c r="D41" s="13">
-        <v>81</v>
+      <c r="C41" s="20">
+        <v>78</v>
+      </c>
+      <c r="D41" s="20">
+        <v>74</v>
       </c>
       <c r="E41" s="20">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F41" s="20">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G41" s="20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H41" s="20"/>
     </row>
@@ -43772,10 +43772,10 @@
         <v>13</v>
       </c>
       <c r="D49" s="13">
-        <v>22</v>
-      </c>
-      <c r="E49" s="13">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="E49" s="20">
+        <v>16</v>
       </c>
       <c r="F49" s="20">
         <v>12</v>
@@ -45691,49 +45691,49 @@
         <v>18</v>
       </c>
       <c r="C4" s="7">
-        <v>47</v>
-      </c>
-      <c r="D4" s="13">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="D4" s="7">
+        <v>48</v>
       </c>
       <c r="E4" s="7">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" s="7">
-        <v>45</v>
-      </c>
-      <c r="G4" s="13">
-        <v>48</v>
+        <v>43</v>
+      </c>
+      <c r="G4" s="7">
+        <v>44</v>
       </c>
       <c r="H4" s="7">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I4" s="7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J4" s="7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K4" s="7">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L4" s="7">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M4" s="7">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N4" s="7">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O4" s="7">
-        <v>39.700000000000003</v>
+        <v>38</v>
       </c>
       <c r="P4" s="7">
-        <v>36.799999999999997</v>
+        <v>35.1</v>
       </c>
       <c r="Q4" s="7">
-        <v>35.9</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -45761,49 +45761,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>0.97289999999999999</v>
+        <v>0.95209999999999995</v>
       </c>
       <c r="D6" s="18">
-        <v>1.0187999999999999</v>
+        <v>0.99170000000000003</v>
       </c>
       <c r="E6" s="18">
-        <v>0.96460000000000001</v>
+        <v>0.92710000000000004</v>
       </c>
       <c r="F6" s="18">
-        <v>0.93959999999999999</v>
+        <v>0.90210000000000001</v>
       </c>
       <c r="G6" s="18">
-        <v>1.0021</v>
+        <v>0.92290000000000005</v>
       </c>
       <c r="H6" s="18">
-        <v>0.99380000000000002</v>
+        <v>0.88539999999999996</v>
       </c>
       <c r="I6" s="18">
-        <v>0.92920000000000003</v>
+        <v>0.83750000000000002</v>
       </c>
       <c r="J6" s="18">
-        <v>0.9375</v>
+        <v>0.82709999999999995</v>
       </c>
       <c r="K6" s="18">
-        <v>0.91459999999999997</v>
+        <v>0.80420000000000003</v>
       </c>
       <c r="L6" s="18">
-        <v>0.88539999999999996</v>
+        <v>0.80830000000000002</v>
       </c>
       <c r="M6" s="18">
-        <v>0.88539999999999996</v>
+        <v>0.80830000000000002</v>
       </c>
       <c r="N6" s="18">
-        <v>0.9042</v>
+        <v>0.84789999999999999</v>
       </c>
       <c r="O6" s="18">
-        <v>0.82709999999999995</v>
+        <v>0.79169999999999996</v>
       </c>
       <c r="P6" s="18">
-        <v>0.76670000000000005</v>
+        <v>0.73129999999999995</v>
       </c>
       <c r="Q6" s="18">
-        <v>0.74790000000000001</v>
+        <v>0.71250000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -45812,49 +45812,49 @@
         <v>24</v>
       </c>
       <c r="C7" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I7" s="19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J7" s="19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K7" s="19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L7" s="19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M7" s="19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N7" s="19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O7" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P7" s="19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q7" s="19">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -45989,50 +45989,50 @@
       <c r="B11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="13">
-        <v>29</v>
-      </c>
-      <c r="D11" s="13">
-        <v>29</v>
+      <c r="C11" s="7">
+        <v>28</v>
+      </c>
+      <c r="D11" s="7">
+        <v>28</v>
       </c>
       <c r="E11" s="7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="7">
-        <v>27</v>
-      </c>
-      <c r="G11" s="13">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="G11" s="7">
+        <v>24</v>
       </c>
       <c r="H11" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I11" s="7">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J11" s="7">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K11" s="7">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L11" s="7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M11" s="7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N11" s="7">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O11" s="7">
-        <v>23.2</v>
+        <v>21.5</v>
       </c>
       <c r="P11" s="7">
-        <v>21.3</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="Q11" s="7">
-        <v>20.399999999999999</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -46466,38 +46466,38 @@
         <v>18</v>
       </c>
       <c r="C34" s="20">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D34" s="20">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E34" s="20">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F34" s="20">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G34" s="20">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="16"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24">
-        <v>1.46E-2</v>
+        <v>4.3099999999999999E-2</v>
       </c>
       <c r="D35" s="24">
-        <v>2.1499999999999998E-2</v>
+        <v>9.6500000000000002E-2</v>
       </c>
       <c r="E35" s="24">
-        <v>7.2900000000000006E-2</v>
+        <v>0.17710000000000001</v>
       </c>
       <c r="F35" s="24">
-        <v>0.10829999999999999</v>
+        <v>0.17849999999999999</v>
       </c>
       <c r="G35" s="24">
-        <v>0.21940000000000001</v>
+        <v>0.25490000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -46506,19 +46506,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="18">
-        <v>0.98540000000000005</v>
+        <v>0.95689999999999997</v>
       </c>
       <c r="D36" s="18">
-        <v>0.97850000000000004</v>
+        <v>0.90349999999999997</v>
       </c>
       <c r="E36" s="18">
-        <v>0.92710000000000004</v>
+        <v>0.82289999999999996</v>
       </c>
       <c r="F36" s="18">
-        <v>0.89170000000000005</v>
+        <v>0.82150000000000001</v>
       </c>
       <c r="G36" s="18">
-        <v>0.78059999999999996</v>
+        <v>0.74509999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -46527,19 +46527,19 @@
         <v>24</v>
       </c>
       <c r="C37" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E37" s="19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F37" s="19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G37" s="19">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -46604,20 +46604,20 @@
       <c r="B41" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="13">
-        <v>28</v>
+      <c r="C41" s="20">
+        <v>27</v>
       </c>
       <c r="D41" s="20">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E41" s="20">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F41" s="20">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G41" s="20">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -46884,49 +46884,49 @@
         <v>18</v>
       </c>
       <c r="C63" s="30">
-        <v>46.7</v>
+        <v>45.7</v>
       </c>
       <c r="D63" s="30">
-        <v>48.9</v>
+        <v>47.6</v>
       </c>
       <c r="E63" s="30">
-        <v>46.3</v>
+        <v>44.5</v>
       </c>
       <c r="F63" s="30">
-        <v>45.1</v>
+        <v>43.3</v>
       </c>
       <c r="G63" s="30">
-        <v>48.1</v>
+        <v>44.3</v>
       </c>
       <c r="H63" s="30">
-        <v>47.7</v>
+        <v>42.5</v>
       </c>
       <c r="I63" s="30">
-        <v>44.6</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="J63" s="30">
-        <v>45</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="K63" s="30">
-        <v>43.9</v>
+        <v>38.6</v>
       </c>
       <c r="L63" s="30">
-        <v>42.5</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="M63" s="30">
-        <v>42.5</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="N63" s="30">
-        <v>43.4</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="O63" s="30">
-        <v>39.700000000000003</v>
+        <v>38</v>
       </c>
       <c r="P63" s="30">
-        <v>36.799999999999997</v>
+        <v>35.1</v>
       </c>
       <c r="Q63" s="30">
-        <v>35.9</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -47414,49 +47414,49 @@
         <v>18</v>
       </c>
       <c r="C73" s="7">
-        <v>39.700000000000003</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="D73" s="7">
-        <v>41.9</v>
+        <v>40.6</v>
       </c>
       <c r="E73" s="7">
-        <v>39.299999999999997</v>
+        <v>37.5</v>
       </c>
       <c r="F73" s="7">
-        <v>38.1</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="G73" s="7">
-        <v>41.1</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="H73" s="7">
-        <v>40.700000000000003</v>
+        <v>35.5</v>
       </c>
       <c r="I73" s="7">
-        <v>37.6</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="J73" s="7">
-        <v>38</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="K73" s="7">
-        <v>36.9</v>
+        <v>31.6</v>
       </c>
       <c r="L73" s="7">
-        <v>35.5</v>
+        <v>31.8</v>
       </c>
       <c r="M73" s="7">
-        <v>35.5</v>
+        <v>31.8</v>
       </c>
       <c r="N73" s="7">
-        <v>36.4</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="O73" s="7">
-        <v>32.700000000000003</v>
+        <v>31</v>
       </c>
       <c r="P73" s="7">
-        <v>29.8</v>
+        <v>28.1</v>
       </c>
       <c r="Q73" s="7">
-        <v>28.9</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
@@ -47520,49 +47520,49 @@
         <v>18</v>
       </c>
       <c r="C75" s="32">
-        <v>22.7</v>
+        <v>21.7</v>
       </c>
       <c r="D75" s="32">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="E75" s="32">
-        <v>21.3</v>
+        <v>19.5</v>
       </c>
       <c r="F75" s="32">
-        <v>21.1</v>
+        <v>19.3</v>
       </c>
       <c r="G75" s="32">
-        <v>22.1</v>
+        <v>18.3</v>
       </c>
       <c r="H75" s="32">
-        <v>21.7</v>
+        <v>16.5</v>
       </c>
       <c r="I75" s="32">
-        <v>20.9</v>
+        <v>16.5</v>
       </c>
       <c r="J75" s="32">
-        <v>21.3</v>
+        <v>16</v>
       </c>
       <c r="K75" s="32">
-        <v>21.2</v>
+        <v>15.9</v>
       </c>
       <c r="L75" s="32">
-        <v>20</v>
+        <v>16.3</v>
       </c>
       <c r="M75" s="32">
-        <v>20</v>
+        <v>16.3</v>
       </c>
       <c r="N75" s="32">
-        <v>20.9</v>
+        <v>18.2</v>
       </c>
       <c r="O75" s="32">
-        <v>17.2</v>
+        <v>15.5</v>
       </c>
       <c r="P75" s="32">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="Q75" s="32">
-        <v>14.4</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
@@ -47952,49 +47952,49 @@
         <v>18</v>
       </c>
       <c r="C4" s="7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="7">
+        <v>47</v>
+      </c>
+      <c r="E4" s="7">
         <v>48</v>
       </c>
-      <c r="E4" s="7">
+      <c r="F4" s="7">
         <v>49</v>
       </c>
-      <c r="F4" s="7">
+      <c r="G4" s="13">
+        <v>55</v>
+      </c>
+      <c r="H4" s="13">
+        <v>54</v>
+      </c>
+      <c r="I4" s="13">
+        <v>55</v>
+      </c>
+      <c r="J4" s="7">
         <v>51</v>
       </c>
-      <c r="G4" s="13">
-        <v>65</v>
-      </c>
-      <c r="H4" s="13">
-        <v>63</v>
-      </c>
-      <c r="I4" s="13">
-        <v>64</v>
-      </c>
-      <c r="J4" s="13">
-        <v>60</v>
-      </c>
-      <c r="K4" s="13">
-        <v>58</v>
+      <c r="K4" s="7">
+        <v>50</v>
       </c>
       <c r="L4" s="7">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M4" s="7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N4" s="7">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O4" s="7">
-        <v>25.3475</v>
+        <v>21.5625</v>
       </c>
       <c r="P4" s="7">
-        <v>23.872499999999999</v>
+        <v>21.012499999999999</v>
       </c>
       <c r="Q4" s="7">
-        <v>23.872499999999999</v>
+        <v>21.012499999999999</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -48022,49 +48022,49 @@
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>0.95809999999999995</v>
+        <v>0.93530000000000002</v>
       </c>
       <c r="D6" s="18">
-        <v>0.97509999999999997</v>
+        <v>0.95309999999999995</v>
       </c>
       <c r="E6" s="18">
-        <v>0.96489999999999998</v>
+        <v>0.93889999999999996</v>
       </c>
       <c r="F6" s="18">
-        <v>0.95499999999999996</v>
+        <v>0.92290000000000005</v>
       </c>
       <c r="G6" s="18">
-        <v>1.2184999999999999</v>
+        <v>1.0345</v>
       </c>
       <c r="H6" s="18">
-        <v>1.1960999999999999</v>
+        <v>1.0159</v>
       </c>
       <c r="I6" s="18">
-        <v>1.2038</v>
+        <v>1.0429999999999999</v>
       </c>
       <c r="J6" s="18">
-        <v>1.1296999999999999</v>
+        <v>0.97070000000000001</v>
       </c>
       <c r="K6" s="18">
-        <v>1.1021000000000001</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="L6" s="18">
-        <v>0.77969999999999995</v>
+        <v>0.74150000000000005</v>
       </c>
       <c r="M6" s="18">
-        <v>0.75139999999999996</v>
+        <v>0.71509999999999996</v>
       </c>
       <c r="N6" s="18">
-        <v>0.73250000000000004</v>
+        <v>0.69620000000000004</v>
       </c>
       <c r="O6" s="18">
-        <v>0.4783</v>
+        <v>0.40679999999999999</v>
       </c>
       <c r="P6" s="18">
-        <v>0.45040000000000002</v>
+        <v>0.39650000000000002</v>
       </c>
       <c r="Q6" s="18">
-        <v>0.45040000000000002</v>
+        <v>0.39650000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -48073,49 +48073,49 @@
         <v>24</v>
       </c>
       <c r="C7" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="19">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="H7" s="19">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="I7" s="19">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="J7" s="19">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="K7" s="19">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="L7" s="19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M7" s="19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N7" s="19">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O7" s="19">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P7" s="19">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="19">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -48251,49 +48251,49 @@
         <v>19</v>
       </c>
       <c r="C11" s="7">
+        <v>33</v>
+      </c>
+      <c r="D11" s="7">
         <v>34</v>
       </c>
-      <c r="D11" s="7">
+      <c r="E11" s="7">
+        <v>34</v>
+      </c>
+      <c r="F11" s="7">
+        <v>34</v>
+      </c>
+      <c r="G11" s="13">
+        <v>36</v>
+      </c>
+      <c r="H11" s="7">
         <v>35</v>
       </c>
-      <c r="E11" s="13">
+      <c r="I11" s="13">
+        <v>37</v>
+      </c>
+      <c r="J11" s="7">
         <v>35</v>
       </c>
-      <c r="F11" s="7">
-        <v>35</v>
-      </c>
-      <c r="G11" s="13">
-        <v>41</v>
-      </c>
-      <c r="H11" s="13">
-        <v>40</v>
-      </c>
-      <c r="I11" s="13">
-        <v>40</v>
-      </c>
-      <c r="J11" s="13">
-        <v>38</v>
-      </c>
-      <c r="K11" s="13">
-        <v>37</v>
+      <c r="K11" s="7">
+        <v>34</v>
       </c>
       <c r="L11" s="7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M11" s="7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N11" s="7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O11" s="7">
-        <v>22.497499999999999</v>
+        <v>18.712499999999999</v>
       </c>
       <c r="P11" s="7">
-        <v>21.022500000000001</v>
+        <v>18.162500000000001</v>
       </c>
       <c r="Q11" s="7">
-        <v>21.022500000000001</v>
+        <v>18.162500000000001</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -48619,19 +48619,19 @@
         <v>13</v>
       </c>
       <c r="G19" s="13">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H19" s="13">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I19" s="13">
-        <v>22</v>
-      </c>
-      <c r="J19" s="13">
-        <v>20</v>
-      </c>
-      <c r="K19" s="13">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="J19" s="7">
+        <v>15</v>
+      </c>
+      <c r="K19" s="7">
+        <v>15</v>
       </c>
       <c r="L19" s="7">
         <v>11</v>
@@ -48727,38 +48727,38 @@
         <v>18</v>
       </c>
       <c r="C34" s="20">
-        <v>47</v>
-      </c>
-      <c r="D34" s="13">
-        <v>60</v>
-      </c>
-      <c r="E34" s="13">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="D34" s="20">
+        <v>53</v>
+      </c>
+      <c r="E34" s="20">
+        <v>52</v>
       </c>
       <c r="F34" s="20">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G34" s="20">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="16"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24">
-        <v>3.39E-2</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="D35" s="24">
-        <v>-0.1232</v>
+        <v>8.8999999999999999E-3</v>
       </c>
       <c r="E35" s="24">
-        <v>-0.1452</v>
+        <v>1.38E-2</v>
       </c>
       <c r="F35" s="24">
-        <v>0.24540000000000001</v>
+        <v>0.28239999999999998</v>
       </c>
       <c r="G35" s="24">
-        <v>0.5403</v>
+        <v>0.60009999999999997</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -48767,19 +48767,19 @@
         <v>23</v>
       </c>
       <c r="C36" s="18">
-        <v>0.96609999999999996</v>
+        <v>0.9425</v>
       </c>
       <c r="D36" s="18">
-        <v>1.1232</v>
+        <v>0.99109999999999998</v>
       </c>
       <c r="E36" s="18">
-        <v>1.1452</v>
+        <v>0.98619999999999997</v>
       </c>
       <c r="F36" s="18">
-        <v>0.75460000000000005</v>
+        <v>0.71760000000000002</v>
       </c>
       <c r="G36" s="18">
-        <v>0.4597</v>
+        <v>0.39989999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -48788,19 +48788,19 @@
         <v>24</v>
       </c>
       <c r="C37" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" s="19">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="E37" s="19">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="F37" s="19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G37" s="19">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -48866,19 +48866,19 @@
         <v>19</v>
       </c>
       <c r="C41" s="20">
+        <v>33</v>
+      </c>
+      <c r="D41" s="20">
         <v>35</v>
       </c>
-      <c r="D41" s="13">
-        <v>39</v>
-      </c>
-      <c r="E41" s="13">
-        <v>38</v>
+      <c r="E41" s="20">
+        <v>35</v>
       </c>
       <c r="F41" s="20">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G41" s="20">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -49025,10 +49025,10 @@
         <v>10</v>
       </c>
       <c r="D49" s="13">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E49" s="13">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F49" s="20">
         <v>11</v>
@@ -49145,49 +49145,49 @@
         <v>18</v>
       </c>
       <c r="C63" s="39">
-        <v>44.072499999999998</v>
+        <v>43.022500000000001</v>
       </c>
       <c r="D63" s="39">
-        <v>47.777500000000003</v>
+        <v>46.702500000000001</v>
       </c>
       <c r="E63" s="39">
-        <v>49.207500000000003</v>
+        <v>47.8825</v>
       </c>
       <c r="F63" s="39">
-        <v>50.615000000000002</v>
+        <v>48.914999999999999</v>
       </c>
       <c r="G63" s="39">
-        <v>64.58</v>
+        <v>54.83</v>
       </c>
       <c r="H63" s="39">
-        <v>63.395000000000003</v>
+        <v>53.844999999999999</v>
       </c>
       <c r="I63" s="39">
-        <v>63.802500000000002</v>
+        <v>55.277500000000003</v>
       </c>
       <c r="J63" s="39">
-        <v>59.872500000000002</v>
+        <v>51.447499999999998</v>
       </c>
       <c r="K63" s="39">
-        <v>58.41</v>
+        <v>50.085000000000001</v>
       </c>
       <c r="L63" s="39">
-        <v>41.325000000000003</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="M63" s="39">
-        <v>39.825000000000003</v>
+        <v>37.9</v>
       </c>
       <c r="N63" s="39">
-        <v>38.825000000000003</v>
+        <v>36.9</v>
       </c>
       <c r="O63" s="39">
-        <v>25.3475</v>
+        <v>21.5625</v>
       </c>
       <c r="P63" s="39">
-        <v>23.872499999999999</v>
+        <v>21.012499999999999</v>
       </c>
       <c r="Q63" s="39">
-        <v>23.872499999999999</v>
+        <v>21.012499999999999</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -49369,31 +49369,31 @@
         <v>3.4750000000000001</v>
       </c>
       <c r="G67" s="7">
-        <v>5.6749999999999998</v>
+        <v>4.625</v>
       </c>
       <c r="H67" s="7">
-        <v>5.85</v>
+        <v>4.8</v>
       </c>
       <c r="I67" s="7">
-        <v>6.3875000000000002</v>
+        <v>6.2625000000000002</v>
       </c>
       <c r="J67" s="7">
-        <v>5.1375000000000002</v>
+        <v>5.0125000000000002</v>
       </c>
       <c r="K67" s="7">
-        <v>5.0750000000000002</v>
+        <v>4.95</v>
       </c>
       <c r="L67" s="7">
-        <v>4.1500000000000004</v>
+        <v>4.0250000000000004</v>
       </c>
       <c r="M67" s="7">
-        <v>3.45</v>
+        <v>3.3250000000000002</v>
       </c>
       <c r="N67" s="7">
-        <v>3.45</v>
+        <v>3.3250000000000002</v>
       </c>
       <c r="O67" s="7">
-        <v>3.2625000000000002</v>
+        <v>3.1375000000000002</v>
       </c>
       <c r="P67" s="7">
         <v>3.0375000000000001</v>
@@ -49469,7 +49469,7 @@
         <v>5.9874999999999998</v>
       </c>
       <c r="E69" s="7">
-        <v>6.6624999999999996</v>
+        <v>6.6124999999999998</v>
       </c>
       <c r="F69" s="7">
         <v>6.25</v>
@@ -49575,7 +49575,7 @@
         <v>4.9874999999999998</v>
       </c>
       <c r="E71" s="32">
-        <v>5.6624999999999996</v>
+        <v>5.6124999999999998</v>
       </c>
       <c r="F71" s="32">
         <v>5.4</v>
@@ -49781,49 +49781,49 @@
         <v>18</v>
       </c>
       <c r="C75" s="7">
-        <v>4.57</v>
+        <v>4.42</v>
       </c>
       <c r="D75" s="7">
-        <v>4.01</v>
+        <v>3.71</v>
       </c>
       <c r="E75" s="7">
-        <v>4.66</v>
+        <v>4.16</v>
       </c>
       <c r="F75" s="7">
-        <v>4.8899999999999997</v>
+        <v>4.29</v>
       </c>
       <c r="G75" s="7">
-        <v>4.92</v>
+        <v>4.32</v>
       </c>
       <c r="H75" s="7">
-        <v>4.37</v>
+        <v>3.82</v>
       </c>
       <c r="I75" s="7">
-        <v>4.42</v>
+        <v>3.97</v>
       </c>
       <c r="J75" s="7">
-        <v>4.42</v>
+        <v>3.97</v>
       </c>
       <c r="K75" s="7">
-        <v>4.2699999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="L75" s="7">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="M75" s="7">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="N75" s="7">
-        <v>3.42</v>
+        <v>3.07</v>
       </c>
       <c r="O75" s="7">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="P75" s="7">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="Q75" s="7">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
@@ -49887,49 +49887,49 @@
         <v>18</v>
       </c>
       <c r="C77" s="7">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="D77" s="7">
-        <v>3.01</v>
+        <v>2.71</v>
       </c>
       <c r="E77" s="7">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="F77" s="7">
-        <v>2.82</v>
+        <v>2.42</v>
       </c>
       <c r="G77" s="7">
-        <v>2.82</v>
+        <v>2.42</v>
       </c>
       <c r="H77" s="7">
-        <v>2.75</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="I77" s="7">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J77" s="7">
-        <v>2.5499999999999998</v>
+        <v>2.35</v>
       </c>
       <c r="K77" s="7">
-        <v>2.5499999999999998</v>
+        <v>2.35</v>
       </c>
       <c r="L77" s="7">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="M77" s="7">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="N77" s="7">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="O77" s="7">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="P77" s="7">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="Q77" s="7">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
@@ -49993,49 +49993,49 @@
         <v>18</v>
       </c>
       <c r="C79" s="7">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="D79" s="7">
-        <v>3.375</v>
+        <v>3.35</v>
       </c>
       <c r="E79" s="7">
-        <v>2.6749999999999998</v>
+        <v>2.65</v>
       </c>
       <c r="F79" s="7">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="G79" s="7">
-        <v>2.4700000000000002</v>
+        <v>2.37</v>
       </c>
       <c r="H79" s="7">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="I79" s="7">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="J79" s="7">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="K79" s="7">
-        <v>2.12</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="L79" s="7">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M79" s="7">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="N79" s="7">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O79" s="7">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="P79" s="7">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q79" s="7">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
@@ -50108,40 +50108,40 @@
         <v>3.62</v>
       </c>
       <c r="F81" s="7">
-        <v>3.87</v>
+        <v>3.27</v>
       </c>
       <c r="G81" s="7">
-        <v>5.0199999999999996</v>
+        <v>4.42</v>
       </c>
       <c r="H81" s="7">
-        <v>5.22</v>
+        <v>4.62</v>
       </c>
       <c r="I81" s="7">
-        <v>6.07</v>
+        <v>5.47</v>
       </c>
       <c r="J81" s="7">
-        <v>5.97</v>
+        <v>5.37</v>
       </c>
       <c r="K81" s="7">
-        <v>5.47</v>
+        <v>4.87</v>
       </c>
       <c r="L81" s="7">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="M81" s="7">
-        <v>3.15</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="N81" s="7">
-        <v>2.4500000000000002</v>
+        <v>1.85</v>
       </c>
       <c r="O81" s="7">
-        <v>1.65</v>
+        <v>1.05</v>
       </c>
       <c r="P81" s="7">
-        <v>1.1499999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="Q81" s="7">
-        <v>1.1499999999999999</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
@@ -50205,43 +50205,43 @@
         <v>18</v>
       </c>
       <c r="C83" s="7">
-        <v>5.6</v>
+        <v>5.05</v>
       </c>
       <c r="D83" s="7">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="E83" s="7">
-        <v>5.85</v>
+        <v>5.4</v>
       </c>
       <c r="F83" s="7">
         <v>5.91</v>
       </c>
       <c r="G83" s="7">
-        <v>7.57</v>
+        <v>6.57</v>
       </c>
       <c r="H83" s="7">
-        <v>7.07</v>
+        <v>6.07</v>
       </c>
       <c r="I83" s="7">
-        <v>6.27</v>
+        <v>5.27</v>
       </c>
       <c r="J83" s="7">
-        <v>6.27</v>
+        <v>5.27</v>
       </c>
       <c r="K83" s="7">
-        <v>6.27</v>
+        <v>5.27</v>
       </c>
       <c r="L83" s="7">
-        <v>4.62</v>
+        <v>3.92</v>
       </c>
       <c r="M83" s="7">
-        <v>4.62</v>
+        <v>3.92</v>
       </c>
       <c r="N83" s="7">
-        <v>4.62</v>
+        <v>3.92</v>
       </c>
       <c r="O83" s="7">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="P83" s="7">
         <v>3.62</v>
@@ -50323,19 +50323,19 @@
         <v>16.75</v>
       </c>
       <c r="G85" s="7">
-        <v>25.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H85" s="7">
-        <v>25.55</v>
+        <v>19.55</v>
       </c>
       <c r="I85" s="7">
-        <v>25.35</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="J85" s="7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K85" s="7">
-        <v>22.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="L85" s="7">
         <v>13.1</v>
@@ -50429,19 +50429,19 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="G87" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H87" s="32">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="I87" s="32">
-        <v>2.4500000000000002</v>
+        <v>1.45</v>
       </c>
       <c r="J87" s="32">
-        <v>2.2000000000000002</v>
+        <v>1.2</v>
       </c>
       <c r="K87" s="32">
-        <v>2.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L87" s="32">
         <v>1.6</v>
@@ -50641,19 +50641,19 @@
         <v>13.3</v>
       </c>
       <c r="G91" s="32">
-        <v>21.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="H91" s="32">
-        <v>21.8</v>
+        <v>16.8</v>
       </c>
       <c r="I91" s="32">
-        <v>21.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="J91" s="32">
-        <v>19.8</v>
+        <v>14.8</v>
       </c>
       <c r="K91" s="32">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="L91" s="32">
         <v>10.5</v>
@@ -50771,13 +50771,13 @@
         <v>3.73</v>
       </c>
       <c r="O93" s="7">
-        <v>6.04</v>
+        <v>3.73</v>
       </c>
       <c r="P93" s="7">
-        <v>6.04</v>
+        <v>3.73</v>
       </c>
       <c r="Q93" s="7">
-        <v>6.04</v>
+        <v>3.73</v>
       </c>
     </row>
   </sheetData>
@@ -55383,63 +55383,63 @@
       </c>
       <c r="B4">
         <f>'Full-ALL'!C4</f>
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C4">
         <f>'Full-ALL'!D4</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D4">
         <f>'Full-ALL'!E4</f>
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E4">
         <f>'Full-ALL'!F4</f>
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F4">
         <f>'Full-ALL'!G4</f>
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="G4">
         <f>'Full-ALL'!H4</f>
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="H4">
         <f>'Full-ALL'!I4</f>
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="I4">
         <f>'Full-ALL'!J4</f>
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="J4">
         <f>'Full-ALL'!K4</f>
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="K4">
         <f>'Full-ALL'!L4</f>
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="L4">
         <f>'Full-ALL'!M4</f>
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="M4">
         <f>'Full-ALL'!N4</f>
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="N4">
         <f>'Full-ALL'!O4</f>
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O4">
         <f>'Full-ALL'!P4</f>
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="P4">
         <f>'Full-ALL'!Q4</f>
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AA4" t="str">
         <f t="shared" si="0"/>
@@ -55447,23 +55447,23 @@
       </c>
       <c r="AB4">
         <f>SUM(B4:D4)/SUM(B2:D2)*100</f>
-        <v>96.506550218340621</v>
+        <v>94.75982532751091</v>
       </c>
       <c r="AC4">
         <f>SUM(E4:G4)/SUM(E2:G2)*100</f>
-        <v>100.43010752688173</v>
+        <v>93.548387096774192</v>
       </c>
       <c r="AD4">
         <f>SUM(H4:J4)/SUM(H2:J2)*100</f>
-        <v>98.917748917748909</v>
+        <v>90.259740259740255</v>
       </c>
       <c r="AE4">
         <f>SUM(K4:M4)/SUM(K2:M2)*100</f>
-        <v>81.063829787234042</v>
+        <v>77.659574468085097</v>
       </c>
       <c r="AF4">
         <f>SUM(N4:P4)/SUM(N2:P2)*100</f>
-        <v>65.605095541401269</v>
+        <v>62.420382165605091</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
@@ -55743,63 +55743,63 @@
       </c>
       <c r="B14">
         <f>'Full-DV'!C4</f>
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14">
         <f>'Full-DV'!D4</f>
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D14">
         <f>'Full-DV'!E4</f>
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E14">
         <f>'Full-DV'!F4</f>
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F14">
         <f>'Full-DV'!G4</f>
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="G14">
         <f>'Full-DV'!H4</f>
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="H14">
         <f>'Full-DV'!I4</f>
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="I14">
         <f>'Full-DV'!J4</f>
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="J14">
         <f>'Full-DV'!K4</f>
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="K14">
         <f>'Full-DV'!L4</f>
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="L14">
         <f>'Full-DV'!M4</f>
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M14">
         <f>'Full-DV'!N4</f>
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N14">
         <f>'Full-DV'!O4</f>
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="O14">
         <f>'Full-DV'!P4</f>
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P14">
         <f>'Full-DV'!Q4</f>
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="AA14" t="str">
         <f t="shared" si="2"/>
@@ -55807,23 +55807,23 @@
       </c>
       <c r="AB14">
         <f>SUM(B14:D14)/SUM(B12:D12)*100</f>
-        <v>98.240469208211152</v>
+        <v>96.187683284457478</v>
       </c>
       <c r="AC14">
         <f>SUM(E14:G14)/SUM(E12:G12)*100</f>
-        <v>103.10734463276836</v>
+        <v>94.067796610169495</v>
       </c>
       <c r="AD14">
         <f>SUM(H14:J14)/SUM(H12:J12)*100</f>
-        <v>100.84745762711864</v>
+        <v>89.265536723163848</v>
       </c>
       <c r="AE14">
         <f>SUM(K14:M14)/SUM(K12:M12)*100</f>
-        <v>81.073446327683612</v>
+        <v>76.55367231638418</v>
       </c>
       <c r="AF14">
         <f>SUM(N14:P14)/SUM(N12:P12)*100</f>
-        <v>62.429378531073439</v>
+        <v>58.192090395480221</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.2">
@@ -57188,63 +57188,63 @@
       </c>
       <c r="B54">
         <f>'Full-PSE'!C4</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C54">
         <f>'Full-PSE'!D4</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D54">
         <f>'Full-PSE'!E4</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E54">
         <f>'Full-PSE'!F4</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F54">
         <f>'Full-PSE'!G4</f>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G54">
         <f>'Full-PSE'!H4</f>
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H54">
         <f>'Full-PSE'!I4</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I54">
         <f>'Full-PSE'!J4</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J54">
         <f>'Full-PSE'!K4</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K54">
         <f>'Full-PSE'!L4</f>
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L54">
         <f>'Full-PSE'!M4</f>
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M54">
         <f>'Full-PSE'!N4</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N54">
         <f>'Full-PSE'!O4</f>
-        <v>39.700000000000003</v>
+        <v>38</v>
       </c>
       <c r="O54">
         <f>'Full-PSE'!P4</f>
-        <v>36.799999999999997</v>
+        <v>35.1</v>
       </c>
       <c r="P54">
         <f>'Full-PSE'!Q4</f>
-        <v>35.9</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="AA54" t="str">
         <f t="shared" si="10"/>
@@ -57252,23 +57252,23 @@
       </c>
       <c r="AB54">
         <f>SUM(B54:D54)/SUM(B52:D52)*100</f>
-        <v>98.611111111111114</v>
+        <v>96.527777777777786</v>
       </c>
       <c r="AC54">
         <f>SUM(E54:G54)/SUM(E52:G52)*100</f>
-        <v>97.916666666666657</v>
+        <v>90.277777777777786</v>
       </c>
       <c r="AD54">
         <f>SUM(H54:J54)/SUM(H52:J52)*100</f>
-        <v>93.055555555555557</v>
+        <v>82.638888888888886</v>
       </c>
       <c r="AE54">
         <f>SUM(K54:M54)/SUM(K52:M52)*100</f>
-        <v>89.583333333333343</v>
+        <v>82.638888888888886</v>
       </c>
       <c r="AF54">
         <f>SUM(N54:P54)/SUM(N52:P52)*100</f>
-        <v>78.055555555555557</v>
+        <v>74.513888888888886</v>
       </c>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.2">
@@ -57908,63 +57908,63 @@
       </c>
       <c r="B74">
         <f>'Full-PSE'!C73</f>
-        <v>39.700000000000003</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="C74">
         <f>'Full-PSE'!D73</f>
-        <v>41.9</v>
+        <v>40.6</v>
       </c>
       <c r="D74">
         <f>'Full-PSE'!E73</f>
-        <v>39.299999999999997</v>
+        <v>37.5</v>
       </c>
       <c r="E74">
         <f>'Full-PSE'!F73</f>
-        <v>38.1</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="F74">
         <f>'Full-PSE'!G73</f>
-        <v>41.1</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="G74">
         <f>'Full-PSE'!H73</f>
-        <v>40.700000000000003</v>
+        <v>35.5</v>
       </c>
       <c r="H74">
         <f>'Full-PSE'!I73</f>
-        <v>37.6</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="I74">
         <f>'Full-PSE'!J73</f>
-        <v>38</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="J74">
         <f>'Full-PSE'!K73</f>
-        <v>36.9</v>
+        <v>31.6</v>
       </c>
       <c r="K74">
         <f>'Full-PSE'!L73</f>
-        <v>35.5</v>
+        <v>31.8</v>
       </c>
       <c r="L74">
         <f>'Full-PSE'!M73</f>
-        <v>35.5</v>
+        <v>31.8</v>
       </c>
       <c r="M74">
         <f>'Full-PSE'!N73</f>
-        <v>36.4</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="N74">
         <f>'Full-PSE'!O73</f>
-        <v>32.700000000000003</v>
+        <v>31</v>
       </c>
       <c r="O74">
         <f>'Full-PSE'!P73</f>
-        <v>29.8</v>
+        <v>28.1</v>
       </c>
       <c r="P74">
         <f>'Full-PSE'!Q73</f>
-        <v>28.9</v>
+        <v>27.2</v>
       </c>
       <c r="AA74" t="str">
         <f t="shared" si="14"/>
@@ -57972,23 +57972,23 @@
       </c>
       <c r="AB74">
         <f>SUM(B74:D74)/SUM(B72:D72)*100</f>
-        <v>98.292682926829272</v>
+        <v>94.959349593495944</v>
       </c>
       <c r="AC74">
         <f>SUM(E74:G74)/SUM(E72:G72)*100</f>
-        <v>97.479674796747972</v>
+        <v>88.699186991869922</v>
       </c>
       <c r="AD74">
         <f>SUM(H74:J74)/SUM(H72:J72)*100</f>
-        <v>91.463414634146346</v>
+        <v>79.268292682926827</v>
       </c>
       <c r="AE74">
         <f>SUM(K74:M74)/SUM(K72:M72)*100</f>
-        <v>87.317073170731703</v>
+        <v>79.105691056910572</v>
       </c>
       <c r="AF74">
         <f>SUM(N74:P74)/SUM(N72:P72)*100</f>
-        <v>74.308943089430898</v>
+        <v>70.162601626016269</v>
       </c>
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.2">
@@ -58268,63 +58268,63 @@
       </c>
       <c r="B84">
         <f>'Full-SD'!C4</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C84">
         <f>'Full-SD'!D4</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D84">
         <f>'Full-SD'!E4</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E84">
         <f>'Full-SD'!F4</f>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F84">
         <f>'Full-SD'!G4</f>
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G84">
         <f>'Full-SD'!H4</f>
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H84">
         <f>'Full-SD'!I4</f>
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="I84">
         <f>'Full-SD'!J4</f>
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J84">
         <f>'Full-SD'!K4</f>
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="K84">
         <f>'Full-SD'!L4</f>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L84">
         <f>'Full-SD'!M4</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M84">
         <f>'Full-SD'!N4</f>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N84">
         <f>'Full-SD'!O4</f>
-        <v>25.3475</v>
+        <v>21.5625</v>
       </c>
       <c r="O84">
         <f>'Full-SD'!P4</f>
-        <v>23.872499999999999</v>
+        <v>21.012499999999999</v>
       </c>
       <c r="P84">
         <f>'Full-SD'!Q4</f>
-        <v>23.872499999999999</v>
+        <v>21.012499999999999</v>
       </c>
       <c r="AA84" t="str">
         <f t="shared" si="16"/>
@@ -58332,23 +58332,23 @@
       </c>
       <c r="AB84">
         <f>SUM(B84:D84)/SUM(B82:D82)*100</f>
-        <v>96.575342465753423</v>
+        <v>94.520547945205479</v>
       </c>
       <c r="AC84">
         <f>SUM(E84:G84)/SUM(E82:G82)*100</f>
-        <v>112.57861635220125</v>
+        <v>99.371069182389931</v>
       </c>
       <c r="AD84">
         <f>SUM(H84:J84)/SUM(H82:J82)*100</f>
-        <v>114.46540880503144</v>
+        <v>98.113207547169807</v>
       </c>
       <c r="AE84">
         <f>SUM(K84:M84)/SUM(K82:M82)*100</f>
-        <v>75.471698113207552</v>
+        <v>71.698113207547166</v>
       </c>
       <c r="AF84">
         <f>SUM(N84:P84)/SUM(N82:P82)*100</f>
-        <v>45.970125786163521</v>
+        <v>39.992138364779876</v>
       </c>
     </row>
     <row r="91" spans="1:32" x14ac:dyDescent="0.2">
@@ -58644,39 +58644,39 @@
       </c>
       <c r="F94">
         <f>'Full-SD'!G67</f>
-        <v>5.6749999999999998</v>
+        <v>4.625</v>
       </c>
       <c r="G94">
         <f>'Full-SD'!H67</f>
-        <v>5.85</v>
+        <v>4.8</v>
       </c>
       <c r="H94">
         <f>'Full-SD'!I67</f>
-        <v>6.3875000000000002</v>
+        <v>6.2625000000000002</v>
       </c>
       <c r="I94">
         <f>'Full-SD'!J67</f>
-        <v>5.1375000000000002</v>
+        <v>5.0125000000000002</v>
       </c>
       <c r="J94">
         <f>'Full-SD'!K67</f>
-        <v>5.0750000000000002</v>
+        <v>4.95</v>
       </c>
       <c r="K94">
         <f>'Full-SD'!L67</f>
-        <v>4.1500000000000004</v>
+        <v>4.0250000000000004</v>
       </c>
       <c r="L94">
         <f>'Full-SD'!M67</f>
-        <v>3.45</v>
+        <v>3.3250000000000002</v>
       </c>
       <c r="M94">
         <f>'Full-SD'!N67</f>
-        <v>3.45</v>
+        <v>3.3250000000000002</v>
       </c>
       <c r="N94">
         <f>'Full-SD'!O67</f>
-        <v>3.2625000000000002</v>
+        <v>3.1375000000000002</v>
       </c>
       <c r="O94">
         <f>'Full-SD'!P67</f>
@@ -58696,19 +58696,19 @@
       </c>
       <c r="AC94">
         <f>SUM(E94:G94)/SUM(E92:G92)*100</f>
-        <v>125</v>
+        <v>107.5</v>
       </c>
       <c r="AD94">
         <f>SUM(H94:J94)/SUM(H92:J92)*100</f>
-        <v>138.33333333333334</v>
+        <v>135.20833333333334</v>
       </c>
       <c r="AE94">
         <f>SUM(K94:M94)/SUM(K92:M92)*100</f>
-        <v>92.083333333333343</v>
+        <v>88.958333333333343</v>
       </c>
       <c r="AF94">
         <f>SUM(N94:P94)/SUM(N92:P92)*100</f>
-        <v>77.8125</v>
+        <v>76.770833333333329</v>
       </c>
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.2">
@@ -58996,7 +58996,7 @@
       </c>
       <c r="D104">
         <f>'Full-SD'!E69</f>
-        <v>6.6624999999999996</v>
+        <v>6.6124999999999998</v>
       </c>
       <c r="E104">
         <f>'Full-SD'!F69</f>
@@ -59052,7 +59052,7 @@
       </c>
       <c r="AB104">
         <f>SUM(B104:D104)/SUM(B102:D102)*100</f>
-        <v>90.178571428571431</v>
+        <v>89.940476190476176</v>
       </c>
       <c r="AC104">
         <f>SUM(E104:G104)/SUM(E102:G102)*100</f>
@@ -59348,63 +59348,63 @@
       </c>
       <c r="B114">
         <f>'Full-SD'!C75</f>
-        <v>4.57</v>
+        <v>4.42</v>
       </c>
       <c r="C114">
         <f>'Full-SD'!D75</f>
-        <v>4.01</v>
+        <v>3.71</v>
       </c>
       <c r="D114">
         <f>'Full-SD'!E75</f>
-        <v>4.66</v>
+        <v>4.16</v>
       </c>
       <c r="E114">
         <f>'Full-SD'!F75</f>
-        <v>4.8899999999999997</v>
+        <v>4.29</v>
       </c>
       <c r="F114">
         <f>'Full-SD'!G75</f>
-        <v>4.92</v>
+        <v>4.32</v>
       </c>
       <c r="G114">
         <f>'Full-SD'!H75</f>
-        <v>4.37</v>
+        <v>3.82</v>
       </c>
       <c r="H114">
         <f>'Full-SD'!I75</f>
-        <v>4.42</v>
+        <v>3.97</v>
       </c>
       <c r="I114">
         <f>'Full-SD'!J75</f>
-        <v>4.42</v>
+        <v>3.97</v>
       </c>
       <c r="J114">
         <f>'Full-SD'!K75</f>
-        <v>4.2699999999999996</v>
+        <v>3.92</v>
       </c>
       <c r="K114">
         <f>'Full-SD'!L75</f>
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="L114">
         <f>'Full-SD'!M75</f>
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="M114">
         <f>'Full-SD'!N75</f>
-        <v>3.42</v>
+        <v>3.07</v>
       </c>
       <c r="N114">
         <f>'Full-SD'!O75</f>
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="O114">
         <f>'Full-SD'!P75</f>
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="P114">
         <f>'Full-SD'!Q75</f>
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="AA114" t="str">
         <f t="shared" si="22"/>
@@ -59412,23 +59412,23 @@
       </c>
       <c r="AB114">
         <f>SUM(B114:D114)/SUM(B112:D112)*100</f>
-        <v>110.33333333333333</v>
+        <v>102.41666666666667</v>
       </c>
       <c r="AC114">
         <f>SUM(E114:G114)/SUM(E112:G112)*100</f>
-        <v>118.16666666666666</v>
+        <v>103.58333333333334</v>
       </c>
       <c r="AD114">
         <f>SUM(H114:J114)/SUM(H112:J112)*100</f>
-        <v>109.25</v>
+        <v>98.833333333333329</v>
       </c>
       <c r="AE114">
         <f>SUM(K114:M114)/SUM(K112:M112)*100</f>
-        <v>87.166666666666671</v>
+        <v>78.416666666666671</v>
       </c>
       <c r="AF114">
         <f>SUM(N114:P114)/SUM(N112:P112)*100</f>
-        <v>11.333333333333332</v>
+        <v>8.8333333333333339</v>
       </c>
     </row>
     <row r="121" spans="1:32" x14ac:dyDescent="0.2">
@@ -59708,63 +59708,63 @@
       </c>
       <c r="B124">
         <f>'Full-SD'!C77</f>
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="C124">
         <f>'Full-SD'!D77</f>
-        <v>3.01</v>
+        <v>2.71</v>
       </c>
       <c r="D124">
         <f>'Full-SD'!E77</f>
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="E124">
         <f>'Full-SD'!F77</f>
-        <v>2.82</v>
+        <v>2.42</v>
       </c>
       <c r="F124">
         <f>'Full-SD'!G77</f>
-        <v>2.82</v>
+        <v>2.42</v>
       </c>
       <c r="G124">
         <f>'Full-SD'!H77</f>
-        <v>2.75</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H124">
         <f>'Full-SD'!I77</f>
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I124">
         <f>'Full-SD'!J77</f>
-        <v>2.5499999999999998</v>
+        <v>2.35</v>
       </c>
       <c r="J124">
         <f>'Full-SD'!K77</f>
-        <v>2.5499999999999998</v>
+        <v>2.35</v>
       </c>
       <c r="K124">
         <f>'Full-SD'!L77</f>
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="L124">
         <f>'Full-SD'!M77</f>
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="M124">
         <f>'Full-SD'!N77</f>
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="N124">
         <f>'Full-SD'!O77</f>
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="O124">
         <f>'Full-SD'!P77</f>
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="P124">
         <f>'Full-SD'!Q77</f>
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="AA124" t="str">
         <f t="shared" si="24"/>
@@ -59772,23 +59772,23 @@
       </c>
       <c r="AB124">
         <f>SUM(B124:D124)/SUM(B122:D122)*100</f>
-        <v>143.33333333333334</v>
+        <v>128.33333333333331</v>
       </c>
       <c r="AC124">
         <f>SUM(E124:G124)/SUM(E122:G122)*100</f>
-        <v>93.222222222222229</v>
+        <v>81</v>
       </c>
       <c r="AD124">
         <f>SUM(H124:J124)/SUM(H122:J122)*100</f>
-        <v>87.777777777777771</v>
+        <v>80</v>
       </c>
       <c r="AE124">
         <f>SUM(K124:M124)/SUM(K122:M122)*100</f>
-        <v>33.777777777777779</v>
+        <v>29.333333333333332</v>
       </c>
       <c r="AF124">
         <f>SUM(N124:P124)/SUM(N122:P122)*100</f>
-        <v>24.333333333333332</v>
+        <v>21.000000000000004</v>
       </c>
     </row>
     <row r="131" spans="1:32" x14ac:dyDescent="0.2">
@@ -60068,63 +60068,63 @@
       </c>
       <c r="B134">
         <f>'Full-SD'!C79</f>
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="C134">
         <f>'Full-SD'!D79</f>
-        <v>3.375</v>
+        <v>3.35</v>
       </c>
       <c r="D134">
         <f>'Full-SD'!E79</f>
-        <v>2.6749999999999998</v>
+        <v>2.65</v>
       </c>
       <c r="E134">
         <f>'Full-SD'!F79</f>
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="F134">
         <f>'Full-SD'!G79</f>
-        <v>2.4700000000000002</v>
+        <v>2.37</v>
       </c>
       <c r="G134">
         <f>'Full-SD'!H79</f>
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="H134">
         <f>'Full-SD'!I79</f>
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="I134">
         <f>'Full-SD'!J79</f>
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="J134">
         <f>'Full-SD'!K79</f>
-        <v>2.12</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="K134">
         <f>'Full-SD'!L79</f>
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="L134">
         <f>'Full-SD'!M79</f>
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M134">
         <f>'Full-SD'!N79</f>
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="N134">
         <f>'Full-SD'!O79</f>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="O134">
         <f>'Full-SD'!P79</f>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="P134">
         <f>'Full-SD'!Q79</f>
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AA134" t="str">
         <f t="shared" si="26"/>
@@ -60132,23 +60132,23 @@
       </c>
       <c r="AB134">
         <f>SUM(B134:D134)/SUM(B132:D132)*100</f>
-        <v>99.444444444444429</v>
+        <v>98.333333333333329</v>
       </c>
       <c r="AC134">
         <f>SUM(E134:G134)/SUM(E132:G132)*100</f>
-        <v>82.333333333333343</v>
+        <v>79.555555555555557</v>
       </c>
       <c r="AD134">
         <f>SUM(H134:J134)/SUM(H132:J132)*100</f>
-        <v>77.333333333333329</v>
+        <v>75.666666666666671</v>
       </c>
       <c r="AE134">
         <f>SUM(K134:M134)/SUM(K132:M132)*100</f>
-        <v>53.333333333333343</v>
+        <v>51.666666666666671</v>
       </c>
       <c r="AF134">
         <f>SUM(N134:P134)/SUM(N132:P132)*100</f>
-        <v>26.666666666666671</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:32" x14ac:dyDescent="0.2">
@@ -60440,51 +60440,51 @@
       </c>
       <c r="E144">
         <f>'Full-SD'!F81</f>
-        <v>3.87</v>
+        <v>3.27</v>
       </c>
       <c r="F144">
         <f>'Full-SD'!G81</f>
-        <v>5.0199999999999996</v>
+        <v>4.42</v>
       </c>
       <c r="G144">
         <f>'Full-SD'!H81</f>
-        <v>5.22</v>
+        <v>4.62</v>
       </c>
       <c r="H144">
         <f>'Full-SD'!I81</f>
-        <v>6.07</v>
+        <v>5.47</v>
       </c>
       <c r="I144">
         <f>'Full-SD'!J81</f>
-        <v>5.97</v>
+        <v>5.37</v>
       </c>
       <c r="J144">
         <f>'Full-SD'!K81</f>
-        <v>5.47</v>
+        <v>4.87</v>
       </c>
       <c r="K144">
         <f>'Full-SD'!L81</f>
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="L144">
         <f>'Full-SD'!M81</f>
-        <v>3.15</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="M144">
         <f>'Full-SD'!N81</f>
-        <v>2.4500000000000002</v>
+        <v>1.85</v>
       </c>
       <c r="N144">
         <f>'Full-SD'!O81</f>
-        <v>1.65</v>
+        <v>1.05</v>
       </c>
       <c r="O144">
         <f>'Full-SD'!P81</f>
-        <v>1.1499999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="P144">
         <f>'Full-SD'!Q81</f>
-        <v>1.1499999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="AA144" t="str">
         <f t="shared" si="28"/>
@@ -60496,19 +60496,19 @@
       </c>
       <c r="AC144">
         <f>SUM(E144:G144)/SUM(E142:G142)*100</f>
-        <v>117.58333333333333</v>
+        <v>102.58333333333331</v>
       </c>
       <c r="AD144">
         <f>SUM(H144:J144)/SUM(H142:J142)*100</f>
-        <v>145.91666666666666</v>
+        <v>130.91666666666669</v>
       </c>
       <c r="AE144">
         <f>SUM(K144:M144)/SUM(K142:M142)*100</f>
-        <v>77.5</v>
+        <v>62.5</v>
       </c>
       <c r="AF144">
         <f>SUM(N144:P144)/SUM(N142:P142)*100</f>
-        <v>32.916666666666664</v>
+        <v>22.916666666666664</v>
       </c>
     </row>
     <row r="151" spans="1:32" x14ac:dyDescent="0.2">
@@ -60788,15 +60788,15 @@
       </c>
       <c r="B154">
         <f>'Full-SD'!C83</f>
-        <v>5.6</v>
+        <v>5.05</v>
       </c>
       <c r="C154">
         <f>'Full-SD'!D83</f>
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="D154">
         <f>'Full-SD'!E83</f>
-        <v>5.85</v>
+        <v>5.4</v>
       </c>
       <c r="E154">
         <f>'Full-SD'!F83</f>
@@ -60804,39 +60804,39 @@
       </c>
       <c r="F154">
         <f>'Full-SD'!G83</f>
-        <v>7.57</v>
+        <v>6.57</v>
       </c>
       <c r="G154">
         <f>'Full-SD'!H83</f>
-        <v>7.07</v>
+        <v>6.07</v>
       </c>
       <c r="H154">
         <f>'Full-SD'!I83</f>
-        <v>6.27</v>
+        <v>5.27</v>
       </c>
       <c r="I154">
         <f>'Full-SD'!J83</f>
-        <v>6.27</v>
+        <v>5.27</v>
       </c>
       <c r="J154">
         <f>'Full-SD'!K83</f>
-        <v>6.27</v>
+        <v>5.27</v>
       </c>
       <c r="K154">
         <f>'Full-SD'!L83</f>
-        <v>4.62</v>
+        <v>3.92</v>
       </c>
       <c r="L154">
         <f>'Full-SD'!M83</f>
-        <v>4.62</v>
+        <v>3.92</v>
       </c>
       <c r="M154">
         <f>'Full-SD'!N83</f>
-        <v>4.62</v>
+        <v>3.92</v>
       </c>
       <c r="N154">
         <f>'Full-SD'!O83</f>
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="O154">
         <f>'Full-SD'!P83</f>
@@ -60852,23 +60852,23 @@
       </c>
       <c r="AB154">
         <f>SUM(B154:D154)/SUM(B152:D152)*100</f>
-        <v>110.31249999999999</v>
+        <v>101.25000000000001</v>
       </c>
       <c r="AC154">
         <f>SUM(E154:G154)/SUM(E152:G152)*100</f>
-        <v>137</v>
+        <v>123.66666666666669</v>
       </c>
       <c r="AD154">
         <f>SUM(H154:J154)/SUM(H152:J152)*100</f>
-        <v>125.4</v>
+        <v>105.39999999999998</v>
       </c>
       <c r="AE154">
         <f>SUM(K154:M154)/SUM(K152:M152)*100</f>
-        <v>92.399999999999991</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="AF154">
         <f>SUM(N154:P154)/SUM(N152:P152)*100</f>
-        <v>75.733333333333334</v>
+        <v>72.399999999999991</v>
       </c>
     </row>
     <row r="161" spans="1:32" x14ac:dyDescent="0.2">
@@ -61164,23 +61164,23 @@
       </c>
       <c r="F164">
         <f>'Full-SD'!G85</f>
-        <v>25.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G164">
         <f>'Full-SD'!H85</f>
-        <v>25.55</v>
+        <v>19.55</v>
       </c>
       <c r="H164">
         <f>'Full-SD'!I85</f>
-        <v>25.35</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="I164">
         <f>'Full-SD'!J85</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J164">
         <f>'Full-SD'!K85</f>
-        <v>22.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="K164">
         <f>'Full-SD'!L85</f>
@@ -61216,11 +61216,11 @@
       </c>
       <c r="AC164">
         <f>SUM(E164:G164)/SUM(E162:G162)*100</f>
-        <v>126.2962962962963</v>
+        <v>104.07407407407408</v>
       </c>
       <c r="AD164">
         <f>SUM(H164:J164)/SUM(H162:J162)*100</f>
-        <v>131.38888888888889</v>
+        <v>98.055555555555557</v>
       </c>
       <c r="AE164">
         <f>SUM(K164:M164)/SUM(K162:M162)*100</f>
@@ -61556,15 +61556,15 @@
       </c>
       <c r="N174">
         <f>'Full-SD'!O93</f>
-        <v>6.04</v>
+        <v>3.73</v>
       </c>
       <c r="O174">
         <f>'Full-SD'!P93</f>
-        <v>6.04</v>
+        <v>3.73</v>
       </c>
       <c r="P174">
         <f>'Full-SD'!Q93</f>
-        <v>6.04</v>
+        <v>3.73</v>
       </c>
       <c r="AA174" t="str">
         <f t="shared" si="34"/>
@@ -61588,7 +61588,7 @@
       </c>
       <c r="AF174">
         <f>SUM(N174:P174)/SUM(N172:P172)*100</f>
-        <v>151</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="181" spans="1:32" x14ac:dyDescent="0.2">
